--- a/projections/kicker_2026_combined.xlsx
+++ b/projections/kicker_2026_combined.xlsx
@@ -612,31 +612,31 @@
         <v>16</v>
       </c>
       <c r="D3" t="n">
-        <v>45.79</v>
+        <v>46.09</v>
       </c>
       <c r="E3" t="n">
-        <v>45.79</v>
+        <v>46.09</v>
       </c>
       <c r="F3" t="n">
-        <v>45.79</v>
+        <v>46.09</v>
       </c>
       <c r="G3" t="n">
-        <v>30.24</v>
+        <v>30.28</v>
       </c>
       <c r="H3" t="n">
-        <v>16.47</v>
+        <v>16.49</v>
       </c>
       <c r="I3" t="n">
-        <v>8.99</v>
+        <v>9</v>
       </c>
       <c r="J3" t="n">
-        <v>4.78</v>
+        <v>4.79</v>
       </c>
       <c r="K3" t="n">
-        <v>88.16</v>
+        <v>88.29000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>133.95</v>
+        <v>134.38</v>
       </c>
       <c r="M3" t="n">
         <v>1</v>
@@ -651,16 +651,16 @@
         <v>0.6859</v>
       </c>
       <c r="Q3" t="n">
-        <v>93.52</v>
+        <v>93.95999999999999</v>
       </c>
       <c r="R3" t="n">
-        <v>174.3</v>
+        <v>174.84</v>
       </c>
       <c r="S3" t="n">
         <v>140.24</v>
       </c>
       <c r="T3" t="n">
-        <v>-6.29</v>
+        <v>-5.86</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
@@ -804,67 +804,67 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Eddy Pineiro</t>
+          <t>Cameron Dicker</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>16</v>
       </c>
       <c r="D6" t="n">
-        <v>45.81</v>
+        <v>32.04</v>
       </c>
       <c r="E6" t="n">
-        <v>41.9</v>
+        <v>31.06</v>
       </c>
       <c r="F6" t="n">
-        <v>41.9</v>
+        <v>31.06</v>
       </c>
       <c r="G6" t="n">
-        <v>30.55</v>
+        <v>31.76</v>
       </c>
       <c r="H6" t="n">
-        <v>16.64</v>
+        <v>17.3</v>
       </c>
       <c r="I6" t="n">
-        <v>9.08</v>
+        <v>9.44</v>
       </c>
       <c r="J6" t="n">
-        <v>4.83</v>
+        <v>5.02</v>
       </c>
       <c r="K6" t="n">
-        <v>90.88</v>
+        <v>102</v>
       </c>
       <c r="L6" t="n">
-        <v>132.78</v>
+        <v>133.06</v>
       </c>
       <c r="M6" t="n">
-        <v>0.915</v>
+        <v>0.969</v>
       </c>
       <c r="N6" t="n">
-        <v>0.9639</v>
+        <v>0.9857</v>
       </c>
       <c r="O6" t="n">
-        <v>0.8235</v>
+        <v>0.9512</v>
       </c>
       <c r="P6" t="n">
         <v>0.6859</v>
       </c>
       <c r="Q6" t="n">
-        <v>92.7</v>
+        <v>91.44</v>
       </c>
       <c r="R6" t="n">
-        <v>172.88</v>
+        <v>174.67</v>
       </c>
       <c r="S6" t="n">
-        <v>141.18</v>
+        <v>160</v>
       </c>
       <c r="T6" t="n">
-        <v>-8.4</v>
+        <v>-26.94</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
@@ -872,67 +872,67 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cameron Dicker</t>
+          <t>Eddy Pineiro</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>16</v>
       </c>
       <c r="D7" t="n">
-        <v>32</v>
+        <v>45.81</v>
       </c>
       <c r="E7" t="n">
-        <v>31.01</v>
+        <v>41.9</v>
       </c>
       <c r="F7" t="n">
-        <v>31.01</v>
+        <v>41.9</v>
       </c>
       <c r="G7" t="n">
-        <v>31.67</v>
+        <v>30.55</v>
       </c>
       <c r="H7" t="n">
-        <v>17.25</v>
+        <v>16.64</v>
       </c>
       <c r="I7" t="n">
-        <v>9.41</v>
+        <v>9.08</v>
       </c>
       <c r="J7" t="n">
-        <v>5.01</v>
+        <v>4.83</v>
       </c>
       <c r="K7" t="n">
-        <v>101.73</v>
+        <v>90.88</v>
       </c>
       <c r="L7" t="n">
-        <v>132.74</v>
+        <v>132.78</v>
       </c>
       <c r="M7" t="n">
-        <v>0.969</v>
+        <v>0.915</v>
       </c>
       <c r="N7" t="n">
-        <v>0.9857</v>
+        <v>0.9639</v>
       </c>
       <c r="O7" t="n">
-        <v>0.9512</v>
+        <v>0.8235</v>
       </c>
       <c r="P7" t="n">
         <v>0.6859</v>
       </c>
       <c r="Q7" t="n">
-        <v>91.2</v>
+        <v>92.7</v>
       </c>
       <c r="R7" t="n">
-        <v>174.26</v>
+        <v>172.88</v>
       </c>
       <c r="S7" t="n">
-        <v>160</v>
+        <v>141.18</v>
       </c>
       <c r="T7" t="n">
-        <v>-27.26</v>
+        <v>-8.4</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
@@ -952,31 +952,31 @@
         <v>16</v>
       </c>
       <c r="D8" t="n">
-        <v>45.89</v>
+        <v>46.19</v>
       </c>
       <c r="E8" t="n">
-        <v>43.89</v>
+        <v>44.18</v>
       </c>
       <c r="F8" t="n">
-        <v>43.89</v>
+        <v>44.18</v>
       </c>
       <c r="G8" t="n">
-        <v>30.24</v>
+        <v>30.29</v>
       </c>
       <c r="H8" t="n">
-        <v>16.47</v>
+        <v>16.5</v>
       </c>
       <c r="I8" t="n">
-        <v>8.99</v>
+        <v>9</v>
       </c>
       <c r="J8" t="n">
-        <v>4.78</v>
+        <v>4.79</v>
       </c>
       <c r="K8" t="n">
-        <v>88.17</v>
+        <v>88.31999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>132.06</v>
+        <v>132.51</v>
       </c>
       <c r="M8" t="n">
         <v>0.956</v>
@@ -991,16 +991,16 @@
         <v>0.6859</v>
       </c>
       <c r="Q8" t="n">
-        <v>92.15000000000001</v>
+        <v>92.56</v>
       </c>
       <c r="R8" t="n">
-        <v>171.9</v>
+        <v>172.46</v>
       </c>
       <c r="S8" t="n">
         <v>137.41</v>
       </c>
       <c r="T8" t="n">
-        <v>-5.35</v>
+        <v>-4.9</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
@@ -1020,31 +1020,31 @@
         <v>16</v>
       </c>
       <c r="D9" t="n">
-        <v>46.29</v>
+        <v>46.53</v>
       </c>
       <c r="E9" t="n">
-        <v>44.6</v>
+        <v>44.84</v>
       </c>
       <c r="F9" t="n">
-        <v>44.6</v>
+        <v>44.84</v>
       </c>
       <c r="G9" t="n">
-        <v>29.78</v>
+        <v>29.8</v>
       </c>
       <c r="H9" t="n">
-        <v>16.22</v>
+        <v>16.23</v>
       </c>
       <c r="I9" t="n">
-        <v>8.85</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="J9" t="n">
         <v>4.71</v>
       </c>
       <c r="K9" t="n">
-        <v>86.81999999999999</v>
+        <v>86.89</v>
       </c>
       <c r="L9" t="n">
-        <v>131.43</v>
+        <v>131.73</v>
       </c>
       <c r="M9" t="n">
         <v>0.964</v>
@@ -1059,16 +1059,16 @@
         <v>0.6859</v>
       </c>
       <c r="Q9" t="n">
-        <v>91.52</v>
+        <v>91.79000000000001</v>
       </c>
       <c r="R9" t="n">
-        <v>171.3</v>
+        <v>171.67</v>
       </c>
       <c r="S9" t="n">
         <v>137.41</v>
       </c>
       <c r="T9" t="n">
-        <v>-5.98</v>
+        <v>-5.68</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
@@ -1088,31 +1088,31 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>46.12</v>
+        <v>46.11</v>
       </c>
       <c r="E10" t="n">
-        <v>44.09</v>
+        <v>44.08</v>
       </c>
       <c r="F10" t="n">
-        <v>44.09</v>
+        <v>44.08</v>
       </c>
       <c r="G10" t="n">
-        <v>30.2</v>
+        <v>30.23</v>
       </c>
       <c r="H10" t="n">
-        <v>16.45</v>
+        <v>16.47</v>
       </c>
       <c r="I10" t="n">
-        <v>8.970000000000001</v>
+        <v>8.98</v>
       </c>
       <c r="J10" t="n">
-        <v>4.77</v>
+        <v>4.78</v>
       </c>
       <c r="K10" t="n">
-        <v>86.45999999999999</v>
+        <v>86.56</v>
       </c>
       <c r="L10" t="n">
-        <v>130.55</v>
+        <v>130.64</v>
       </c>
       <c r="M10" t="n">
         <v>0.956</v>
@@ -1127,16 +1127,16 @@
         <v>0.66</v>
       </c>
       <c r="Q10" t="n">
-        <v>91.12</v>
+        <v>91.22</v>
       </c>
       <c r="R10" t="n">
-        <v>169.98</v>
+        <v>170.01</v>
       </c>
       <c r="S10" t="n">
         <v>141.18</v>
       </c>
       <c r="T10" t="n">
-        <v>-10.63</v>
+        <v>-10.54</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
@@ -1156,31 +1156,31 @@
         <v>16</v>
       </c>
       <c r="D11" t="n">
-        <v>39.39</v>
+        <v>39.63</v>
       </c>
       <c r="E11" t="n">
-        <v>38.46</v>
+        <v>38.69</v>
       </c>
       <c r="F11" t="n">
-        <v>38.46</v>
+        <v>38.69</v>
       </c>
       <c r="G11" t="n">
-        <v>31.9</v>
+        <v>31.96</v>
       </c>
       <c r="H11" t="n">
-        <v>17.38</v>
+        <v>17.41</v>
       </c>
       <c r="I11" t="n">
-        <v>9.48</v>
+        <v>9.5</v>
       </c>
       <c r="J11" t="n">
-        <v>5.04</v>
+        <v>5.05</v>
       </c>
       <c r="K11" t="n">
-        <v>91.33</v>
+        <v>91.48999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>129.79</v>
+        <v>130.18</v>
       </c>
       <c r="M11" t="n">
         <v>0.976</v>
@@ -1195,16 +1195,16 @@
         <v>0.8431</v>
       </c>
       <c r="Q11" t="n">
-        <v>90.29000000000001</v>
+        <v>90.62</v>
       </c>
       <c r="R11" t="n">
-        <v>169.25</v>
+        <v>169.73</v>
       </c>
       <c r="S11" t="n">
         <v>132.71</v>
       </c>
       <c r="T11" t="n">
-        <v>-2.92</v>
+        <v>-2.53</v>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
@@ -1263,10 +1263,10 @@
         <v>0.7391</v>
       </c>
       <c r="Q12" t="n">
-        <v>89.68000000000001</v>
+        <v>89.77</v>
       </c>
       <c r="R12" t="n">
-        <v>169.89</v>
+        <v>169.81</v>
       </c>
       <c r="S12" t="n">
         <v>147.76</v>
@@ -1416,67 +1416,67 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Dominic Zvada</t>
+          <t>Harrison Butker</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>16</v>
       </c>
       <c r="D15" t="n">
-        <v>41.58</v>
+        <v>34.67</v>
       </c>
       <c r="E15" t="n">
-        <v>39.55</v>
+        <v>32.55</v>
       </c>
       <c r="F15" t="n">
-        <v>39.55</v>
+        <v>32.55</v>
       </c>
       <c r="G15" t="n">
-        <v>30.65</v>
+        <v>32.11</v>
       </c>
       <c r="H15" t="n">
-        <v>16.7</v>
+        <v>17.49</v>
       </c>
       <c r="I15" t="n">
-        <v>9.109999999999999</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>4.85</v>
+        <v>5.08</v>
       </c>
       <c r="K15" t="n">
-        <v>89.38</v>
+        <v>96.87</v>
       </c>
       <c r="L15" t="n">
-        <v>128.92</v>
+        <v>129.42</v>
       </c>
       <c r="M15" t="n">
-        <v>0.951</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9543</v>
+        <v>0.963</v>
       </c>
       <c r="O15" t="n">
-        <v>0.798</v>
+        <v>0.8696</v>
       </c>
       <c r="P15" t="n">
-        <v>0.6859</v>
+        <v>0.6604</v>
       </c>
       <c r="Q15" t="n">
-        <v>89.48</v>
+        <v>89.29000000000001</v>
       </c>
       <c r="R15" t="n">
-        <v>168.35</v>
+        <v>169.52</v>
       </c>
       <c r="S15" t="n">
-        <v>128</v>
+        <v>136.47</v>
       </c>
       <c r="T15" t="n">
-        <v>0.92</v>
+        <v>-7.05</v>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
@@ -1484,67 +1484,67 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Harrison Butker</t>
+          <t>Dominic Zvada</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>16</v>
       </c>
       <c r="D16" t="n">
-        <v>34.44</v>
+        <v>41.7</v>
       </c>
       <c r="E16" t="n">
-        <v>32.34</v>
+        <v>39.66</v>
       </c>
       <c r="F16" t="n">
-        <v>32.34</v>
+        <v>39.66</v>
       </c>
       <c r="G16" t="n">
-        <v>31.99</v>
+        <v>30.73</v>
       </c>
       <c r="H16" t="n">
-        <v>17.43</v>
+        <v>16.74</v>
       </c>
       <c r="I16" t="n">
-        <v>9.51</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>5.06</v>
+        <v>4.86</v>
       </c>
       <c r="K16" t="n">
-        <v>96.51000000000001</v>
+        <v>89.59</v>
       </c>
       <c r="L16" t="n">
-        <v>128.86</v>
+        <v>129.25</v>
       </c>
       <c r="M16" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.951</v>
       </c>
       <c r="N16" t="n">
-        <v>0.963</v>
+        <v>0.9543</v>
       </c>
       <c r="O16" t="n">
-        <v>0.8696</v>
+        <v>0.798</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6604</v>
+        <v>0.6859</v>
       </c>
       <c r="Q16" t="n">
-        <v>88.86</v>
+        <v>89.75</v>
       </c>
       <c r="R16" t="n">
-        <v>168.84</v>
+        <v>168.68</v>
       </c>
       <c r="S16" t="n">
-        <v>136.47</v>
+        <v>128</v>
       </c>
       <c r="T16" t="n">
-        <v>-7.61</v>
+        <v>1.25</v>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
@@ -1620,67 +1620,67 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Daniel Carlson</t>
+          <t>Trey Smack</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>16</v>
       </c>
       <c r="D18" t="n">
-        <v>35.84</v>
+        <v>38.25</v>
       </c>
       <c r="E18" t="n">
-        <v>34.09</v>
+        <v>37.25</v>
       </c>
       <c r="F18" t="n">
-        <v>34.09</v>
+        <v>37.25</v>
       </c>
       <c r="G18" t="n">
-        <v>32.24</v>
+        <v>32.28</v>
       </c>
       <c r="H18" t="n">
-        <v>17.56</v>
+        <v>17.58</v>
       </c>
       <c r="I18" t="n">
-        <v>9.58</v>
+        <v>9.59</v>
       </c>
       <c r="J18" t="n">
         <v>5.1</v>
       </c>
       <c r="K18" t="n">
-        <v>94.01000000000001</v>
+        <v>91.23</v>
       </c>
       <c r="L18" t="n">
-        <v>128.1</v>
+        <v>128.48</v>
       </c>
       <c r="M18" t="n">
-        <v>0.951</v>
+        <v>0.974</v>
       </c>
       <c r="N18" t="n">
-        <v>0.9543</v>
+        <v>0.9492</v>
       </c>
       <c r="O18" t="n">
-        <v>0.798</v>
+        <v>0.8211000000000001</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6859</v>
+        <v>0.5667</v>
       </c>
       <c r="Q18" t="n">
-        <v>88.73999999999999</v>
+        <v>89.3</v>
       </c>
       <c r="R18" t="n">
-        <v>167.46</v>
+        <v>167.71</v>
       </c>
       <c r="S18" t="n">
-        <v>131.76</v>
+        <v>137.41</v>
       </c>
       <c r="T18" t="n">
-        <v>-3.66</v>
+        <v>-8.93</v>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
@@ -1688,67 +1688,67 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Trey Smack</t>
+          <t>Daniel Carlson</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>16</v>
       </c>
       <c r="D19" t="n">
-        <v>37.6</v>
+        <v>35.84</v>
       </c>
       <c r="E19" t="n">
-        <v>36.62</v>
+        <v>34.09</v>
       </c>
       <c r="F19" t="n">
-        <v>36.62</v>
+        <v>34.09</v>
       </c>
       <c r="G19" t="n">
-        <v>32.07</v>
+        <v>32.24</v>
       </c>
       <c r="H19" t="n">
-        <v>17.47</v>
+        <v>17.56</v>
       </c>
       <c r="I19" t="n">
-        <v>9.529999999999999</v>
+        <v>9.58</v>
       </c>
       <c r="J19" t="n">
-        <v>5.07</v>
+        <v>5.1</v>
       </c>
       <c r="K19" t="n">
-        <v>90.62</v>
+        <v>94.01000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>127.24</v>
+        <v>128.1</v>
       </c>
       <c r="M19" t="n">
-        <v>0.974</v>
+        <v>0.951</v>
       </c>
       <c r="N19" t="n">
-        <v>0.9492</v>
+        <v>0.9543</v>
       </c>
       <c r="O19" t="n">
-        <v>0.8211000000000001</v>
+        <v>0.798</v>
       </c>
       <c r="P19" t="n">
-        <v>0.5667</v>
+        <v>0.6859</v>
       </c>
       <c r="Q19" t="n">
-        <v>88.20999999999999</v>
+        <v>88.73</v>
       </c>
       <c r="R19" t="n">
-        <v>166.24</v>
+        <v>167.41</v>
       </c>
       <c r="S19" t="n">
-        <v>137.41</v>
+        <v>131.76</v>
       </c>
       <c r="T19" t="n">
-        <v>-10.17</v>
+        <v>-3.66</v>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr"/>
@@ -1836,31 +1836,31 @@
         <v>16</v>
       </c>
       <c r="D21" t="n">
-        <v>36.76</v>
+        <v>37.06</v>
       </c>
       <c r="E21" t="n">
-        <v>35.95</v>
+        <v>36.24</v>
       </c>
       <c r="F21" t="n">
-        <v>35.95</v>
+        <v>36.24</v>
       </c>
       <c r="G21" t="n">
-        <v>31.19</v>
+        <v>31.28</v>
       </c>
       <c r="H21" t="n">
-        <v>16.99</v>
+        <v>17.04</v>
       </c>
       <c r="I21" t="n">
-        <v>9.27</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>4.93</v>
+        <v>4.95</v>
       </c>
       <c r="K21" t="n">
-        <v>90.13</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>126.08</v>
+        <v>126.64</v>
       </c>
       <c r="M21" t="n">
         <v>0.978</v>
@@ -1875,16 +1875,16 @@
         <v>0.617</v>
       </c>
       <c r="Q21" t="n">
-        <v>86.87</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="R21" t="n">
-        <v>165.27</v>
+        <v>165.88</v>
       </c>
       <c r="S21" t="n">
         <v>139.29</v>
       </c>
       <c r="T21" t="n">
-        <v>-13.21</v>
+        <v>-12.65</v>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr"/>
@@ -1892,46 +1892,46 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Jake Bates</t>
+          <t>Will Reichard</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D22" t="n">
-        <v>41.96</v>
+        <v>34.81</v>
       </c>
       <c r="E22" t="n">
-        <v>40.25</v>
+        <v>34.81</v>
       </c>
       <c r="F22" t="n">
-        <v>40.25</v>
+        <v>34.81</v>
       </c>
       <c r="G22" t="n">
-        <v>29.32</v>
+        <v>31.37</v>
       </c>
       <c r="H22" t="n">
-        <v>15.97</v>
+        <v>17.09</v>
       </c>
       <c r="I22" t="n">
-        <v>8.720000000000001</v>
+        <v>9.32</v>
       </c>
       <c r="J22" t="n">
-        <v>4.64</v>
+        <v>4.96</v>
       </c>
       <c r="K22" t="n">
-        <v>85.5</v>
+        <v>91.47</v>
       </c>
       <c r="L22" t="n">
-        <v>125.75</v>
+        <v>126.28</v>
       </c>
       <c r="M22" t="n">
-        <v>0.959</v>
+        <v>1</v>
       </c>
       <c r="N22" t="n">
         <v>0.9543</v>
@@ -1943,16 +1943,16 @@
         <v>0.6859</v>
       </c>
       <c r="Q22" t="n">
-        <v>87.93000000000001</v>
+        <v>86.98999999999999</v>
       </c>
       <c r="R22" t="n">
-        <v>163.62</v>
+        <v>165.62</v>
       </c>
       <c r="S22" t="n">
-        <v>127.94</v>
+        <v>136.47</v>
       </c>
       <c r="T22" t="n">
-        <v>-2.19</v>
+        <v>-10.19</v>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr"/>
@@ -1960,46 +1960,46 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Will Reichard</t>
+          <t>Jake Bates</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D23" t="n">
-        <v>34.32</v>
+        <v>43.04</v>
       </c>
       <c r="E23" t="n">
-        <v>34.32</v>
+        <v>41.28</v>
       </c>
       <c r="F23" t="n">
-        <v>34.32</v>
+        <v>41.28</v>
       </c>
       <c r="G23" t="n">
-        <v>31.28</v>
+        <v>29.13</v>
       </c>
       <c r="H23" t="n">
-        <v>17.04</v>
+        <v>15.87</v>
       </c>
       <c r="I23" t="n">
-        <v>9.300000000000001</v>
+        <v>8.66</v>
       </c>
       <c r="J23" t="n">
-        <v>4.94</v>
+        <v>4.61</v>
       </c>
       <c r="K23" t="n">
-        <v>91.2</v>
+        <v>84.93000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>125.52</v>
+        <v>126.21</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>0.959</v>
       </c>
       <c r="N23" t="n">
         <v>0.9543</v>
@@ -2011,16 +2011,16 @@
         <v>0.6859</v>
       </c>
       <c r="Q23" t="n">
-        <v>86.26000000000001</v>
+        <v>88.36</v>
       </c>
       <c r="R23" t="n">
-        <v>164.7</v>
+        <v>164.06</v>
       </c>
       <c r="S23" t="n">
-        <v>136.47</v>
+        <v>127.94</v>
       </c>
       <c r="T23" t="n">
-        <v>-10.95</v>
+        <v>-1.73</v>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr"/>
@@ -2108,31 +2108,31 @@
         <v>15</v>
       </c>
       <c r="D25" t="n">
-        <v>45.66</v>
+        <v>46.33</v>
       </c>
       <c r="E25" t="n">
-        <v>44.33</v>
+        <v>44.98</v>
       </c>
       <c r="F25" t="n">
-        <v>44.33</v>
+        <v>44.98</v>
       </c>
       <c r="G25" t="n">
-        <v>27.68</v>
+        <v>27.86</v>
       </c>
       <c r="H25" t="n">
-        <v>15.08</v>
+        <v>15.17</v>
       </c>
       <c r="I25" t="n">
-        <v>8.23</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>4.38</v>
+        <v>4.4</v>
       </c>
       <c r="K25" t="n">
-        <v>78.43000000000001</v>
+        <v>78.93000000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>122.76</v>
+        <v>123.91</v>
       </c>
       <c r="M25" t="n">
         <v>0.971</v>
@@ -2147,16 +2147,16 @@
         <v>0.7455000000000001</v>
       </c>
       <c r="Q25" t="n">
-        <v>85.92</v>
+        <v>86.88</v>
       </c>
       <c r="R25" t="n">
-        <v>159.66</v>
+        <v>160.94</v>
       </c>
       <c r="S25" t="n">
         <v>124.41</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.65</v>
+        <v>-0.5</v>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr"/>
@@ -2176,31 +2176,31 @@
         <v>16</v>
       </c>
       <c r="D26" t="n">
-        <v>33.36</v>
+        <v>33.34</v>
       </c>
       <c r="E26" t="n">
-        <v>32.24</v>
+        <v>32.21</v>
       </c>
       <c r="F26" t="n">
-        <v>32.24</v>
+        <v>32.21</v>
       </c>
       <c r="G26" t="n">
-        <v>29.66</v>
+        <v>30.02</v>
       </c>
       <c r="H26" t="n">
-        <v>16.16</v>
+        <v>16.35</v>
       </c>
       <c r="I26" t="n">
-        <v>8.82</v>
+        <v>8.92</v>
       </c>
       <c r="J26" t="n">
-        <v>4.69</v>
+        <v>4.75</v>
       </c>
       <c r="K26" t="n">
-        <v>89.37</v>
+        <v>90.45999999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>121.6</v>
+        <v>122.67</v>
       </c>
       <c r="M26" t="n">
         <v>0.966</v>
@@ -2215,16 +2215,16 @@
         <v>0.6859</v>
       </c>
       <c r="Q26" t="n">
-        <v>82.67</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="R26" t="n">
-        <v>160.53</v>
+        <v>161.81</v>
       </c>
       <c r="S26" t="n">
         <v>110.12</v>
       </c>
       <c r="T26" t="n">
-        <v>11.48</v>
+        <v>12.55</v>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr"/>
@@ -2244,31 +2244,31 @@
         <v>16</v>
       </c>
       <c r="D27" t="n">
-        <v>35.15</v>
+        <v>35.2</v>
       </c>
       <c r="E27" t="n">
-        <v>33.51</v>
+        <v>33.56</v>
       </c>
       <c r="F27" t="n">
-        <v>33.51</v>
+        <v>33.56</v>
       </c>
       <c r="G27" t="n">
-        <v>30.64</v>
+        <v>30.7</v>
       </c>
       <c r="H27" t="n">
-        <v>16.69</v>
+        <v>16.72</v>
       </c>
       <c r="I27" t="n">
-        <v>9.1</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="J27" t="n">
-        <v>4.84</v>
+        <v>4.85</v>
       </c>
       <c r="K27" t="n">
-        <v>86.16</v>
+        <v>86.34999999999999</v>
       </c>
       <c r="L27" t="n">
-        <v>119.67</v>
+        <v>119.91</v>
       </c>
       <c r="M27" t="n">
         <v>0.953</v>
@@ -2283,16 +2283,16 @@
         <v>0.6859</v>
       </c>
       <c r="Q27" t="n">
-        <v>82.03</v>
+        <v>82.2</v>
       </c>
       <c r="R27" t="n">
-        <v>157.34</v>
+        <v>157.57</v>
       </c>
       <c r="S27" t="n">
         <v>127.06</v>
       </c>
       <c r="T27" t="n">
-        <v>-7.39</v>
+        <v>-7.15</v>
       </c>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr"/>
@@ -2380,31 +2380,31 @@
         <v>16</v>
       </c>
       <c r="D29" t="n">
-        <v>35.93</v>
+        <v>36.09</v>
       </c>
       <c r="E29" t="n">
-        <v>35.11</v>
+        <v>35.27</v>
       </c>
       <c r="F29" t="n">
-        <v>35.11</v>
+        <v>35.27</v>
       </c>
       <c r="G29" t="n">
-        <v>31.97</v>
+        <v>32.02</v>
       </c>
       <c r="H29" t="n">
-        <v>17.41</v>
+        <v>17.44</v>
       </c>
       <c r="I29" t="n">
-        <v>9.5</v>
+        <v>9.52</v>
       </c>
       <c r="J29" t="n">
-        <v>5.05</v>
+        <v>5.06</v>
       </c>
       <c r="K29" t="n">
-        <v>82.5</v>
+        <v>82.63</v>
       </c>
       <c r="L29" t="n">
-        <v>117.61</v>
+        <v>117.9</v>
       </c>
       <c r="M29" t="n">
         <v>0.977</v>
@@ -2419,16 +2419,16 @@
         <v>0.6859</v>
       </c>
       <c r="Q29" t="n">
-        <v>81.3</v>
+        <v>81.5</v>
       </c>
       <c r="R29" t="n">
-        <v>153.9</v>
+        <v>154.26</v>
       </c>
       <c r="S29" t="n">
         <v>126.12</v>
       </c>
       <c r="T29" t="n">
-        <v>-8.51</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr"/>
@@ -2436,67 +2436,67 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ryan Fitzgerald</t>
+          <t>Jason Sanders</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>16</v>
       </c>
       <c r="D30" t="n">
-        <v>32.24</v>
+        <v>31.45</v>
       </c>
       <c r="E30" t="n">
-        <v>29.01</v>
+        <v>30.48</v>
       </c>
       <c r="F30" t="n">
-        <v>29.01</v>
+        <v>30.48</v>
       </c>
       <c r="G30" t="n">
-        <v>29.58</v>
+        <v>29.88</v>
       </c>
       <c r="H30" t="n">
-        <v>16.11</v>
+        <v>16.28</v>
       </c>
       <c r="I30" t="n">
-        <v>8.789999999999999</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="J30" t="n">
-        <v>4.68</v>
+        <v>4.72</v>
       </c>
       <c r="K30" t="n">
-        <v>86.26000000000001</v>
+        <v>85.25</v>
       </c>
       <c r="L30" t="n">
-        <v>115.27</v>
+        <v>115.73</v>
       </c>
       <c r="M30" t="n">
-        <v>0.9</v>
+        <v>0.969</v>
       </c>
       <c r="N30" t="n">
-        <v>0.9543</v>
+        <v>0.9412</v>
       </c>
       <c r="O30" t="n">
-        <v>0.798</v>
+        <v>0.7707000000000001</v>
       </c>
       <c r="P30" t="n">
-        <v>0.6859</v>
+        <v>0.6923</v>
       </c>
       <c r="Q30" t="n">
-        <v>78.2</v>
+        <v>78.55</v>
       </c>
       <c r="R30" t="n">
-        <v>152.31</v>
+        <v>152.95</v>
       </c>
       <c r="S30" t="n">
-        <v>129.88</v>
+        <v>1.88</v>
       </c>
       <c r="T30" t="n">
-        <v>-14.61</v>
+        <v>113.85</v>
       </c>
       <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr"/>
@@ -2504,67 +2504,67 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Matt Gay</t>
+          <t>Ryan Fitzgerald</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>16</v>
       </c>
       <c r="D31" t="n">
-        <v>28.76</v>
+        <v>32.53</v>
       </c>
       <c r="E31" t="n">
-        <v>27.52</v>
+        <v>29.28</v>
       </c>
       <c r="F31" t="n">
-        <v>27.52</v>
+        <v>29.28</v>
       </c>
       <c r="G31" t="n">
-        <v>29.73</v>
+        <v>29.65</v>
       </c>
       <c r="H31" t="n">
-        <v>16.19</v>
+        <v>16.15</v>
       </c>
       <c r="I31" t="n">
-        <v>8.83</v>
+        <v>8.81</v>
       </c>
       <c r="J31" t="n">
-        <v>4.7</v>
+        <v>4.69</v>
       </c>
       <c r="K31" t="n">
-        <v>87.69</v>
+        <v>86.45</v>
       </c>
       <c r="L31" t="n">
-        <v>115.21</v>
+        <v>115.72</v>
       </c>
       <c r="M31" t="n">
-        <v>0.957</v>
+        <v>0.9</v>
       </c>
       <c r="N31" t="n">
-        <v>0.971</v>
+        <v>0.9543</v>
       </c>
       <c r="O31" t="n">
-        <v>0.7714</v>
+        <v>0.798</v>
       </c>
       <c r="P31" t="n">
-        <v>0.7255</v>
+        <v>0.6859</v>
       </c>
       <c r="Q31" t="n">
-        <v>77.77</v>
+        <v>78.62</v>
       </c>
       <c r="R31" t="n">
-        <v>152.62</v>
+        <v>152.91</v>
       </c>
       <c r="S31" t="n">
-        <v>125.18</v>
+        <v>129.88</v>
       </c>
       <c r="T31" t="n">
-        <v>-9.970000000000001</v>
+        <v>-14.16</v>
       </c>
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr"/>
@@ -2572,67 +2572,67 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Jason Sanders</t>
+          <t>Matt Gay</t>
         </is>
       </c>
       <c r="C32" t="n">
         <v>16</v>
       </c>
       <c r="D32" t="n">
-        <v>31.46</v>
+        <v>28.73</v>
       </c>
       <c r="E32" t="n">
-        <v>30.49</v>
+        <v>27.49</v>
       </c>
       <c r="F32" t="n">
-        <v>30.49</v>
+        <v>27.49</v>
       </c>
       <c r="G32" t="n">
-        <v>29.67</v>
+        <v>29.78</v>
       </c>
       <c r="H32" t="n">
-        <v>16.16</v>
+        <v>16.22</v>
       </c>
       <c r="I32" t="n">
-        <v>8.82</v>
+        <v>8.85</v>
       </c>
       <c r="J32" t="n">
-        <v>4.69</v>
+        <v>4.71</v>
       </c>
       <c r="K32" t="n">
-        <v>84.64</v>
+        <v>87.84</v>
       </c>
       <c r="L32" t="n">
-        <v>115.12</v>
+        <v>115.33</v>
       </c>
       <c r="M32" t="n">
-        <v>0.969</v>
+        <v>0.957</v>
       </c>
       <c r="N32" t="n">
-        <v>0.9412</v>
+        <v>0.971</v>
       </c>
       <c r="O32" t="n">
-        <v>0.7707000000000001</v>
+        <v>0.7714</v>
       </c>
       <c r="P32" t="n">
-        <v>0.6923</v>
+        <v>0.7255</v>
       </c>
       <c r="Q32" t="n">
-        <v>78.04000000000001</v>
+        <v>77.89</v>
       </c>
       <c r="R32" t="n">
-        <v>152.24</v>
+        <v>152.8</v>
       </c>
       <c r="S32" t="n">
-        <v>1.88</v>
+        <v>125.18</v>
       </c>
       <c r="T32" t="n">
-        <v>113.24</v>
+        <v>-9.85</v>
       </c>
       <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr"/>
@@ -2652,31 +2652,31 @@
         <v>16</v>
       </c>
       <c r="D33" t="n">
-        <v>30.85</v>
+        <v>30.9</v>
       </c>
       <c r="E33" t="n">
-        <v>27.9</v>
+        <v>27.95</v>
       </c>
       <c r="F33" t="n">
-        <v>27.9</v>
+        <v>27.95</v>
       </c>
       <c r="G33" t="n">
-        <v>30.05</v>
+        <v>30.1</v>
       </c>
       <c r="H33" t="n">
-        <v>16.37</v>
+        <v>16.4</v>
       </c>
       <c r="I33" t="n">
-        <v>8.93</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="J33" t="n">
-        <v>4.75</v>
+        <v>4.76</v>
       </c>
       <c r="K33" t="n">
-        <v>84</v>
+        <v>84.15000000000001</v>
       </c>
       <c r="L33" t="n">
-        <v>111.89</v>
+        <v>112.1</v>
       </c>
       <c r="M33" t="n">
         <v>0.904</v>
@@ -2691,16 +2691,16 @@
         <v>0.6364</v>
       </c>
       <c r="Q33" t="n">
-        <v>75.92</v>
+        <v>76.14</v>
       </c>
       <c r="R33" t="n">
-        <v>147.81</v>
+        <v>148.08</v>
       </c>
       <c r="S33" t="n">
         <v>126.12</v>
       </c>
       <c r="T33" t="n">
-        <v>-14.23</v>
+        <v>-14.02</v>
       </c>
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr"/>
@@ -4245,28 +4245,28 @@
         <v>-1</v>
       </c>
       <c r="F20" t="n">
-        <v>2.801</v>
+        <v>2.846</v>
       </c>
       <c r="G20" t="n">
         <v>0.964</v>
       </c>
       <c r="H20" t="n">
-        <v>2.699</v>
+        <v>2.743</v>
       </c>
       <c r="I20" t="n">
-        <v>2.699</v>
+        <v>2.743</v>
       </c>
       <c r="J20" t="n">
-        <v>1.8344</v>
+        <v>1.8532</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9992</v>
+        <v>1.0094</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5452</v>
+        <v>0.5508</v>
       </c>
       <c r="M20" t="n">
-        <v>0.29</v>
+        <v>0.293</v>
       </c>
       <c r="N20" t="n">
         <v>0.9543</v>
@@ -4278,25 +4278,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.8149</v>
+        <v>2.8437</v>
       </c>
       <c r="R20" t="n">
-        <v>1.6301</v>
+        <v>1.6469</v>
       </c>
       <c r="S20" t="n">
-        <v>0.9035</v>
+        <v>0.9127999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>5.3486</v>
+        <v>5.4034</v>
       </c>
       <c r="U20" t="n">
-        <v>8.048</v>
+        <v>8.146000000000001</v>
       </c>
       <c r="V20" t="n">
-        <v>2.786</v>
+        <v>2.82</v>
       </c>
       <c r="W20" t="n">
-        <v>14.696</v>
+        <v>14.835</v>
       </c>
     </row>
     <row r="21">
@@ -4707,28 +4707,28 @@
         <v>-1</v>
       </c>
       <c r="F26" t="n">
-        <v>2.827</v>
+        <v>2.846</v>
       </c>
       <c r="G26" t="n">
         <v>0.964</v>
       </c>
       <c r="H26" t="n">
-        <v>2.725</v>
+        <v>2.743</v>
       </c>
       <c r="I26" t="n">
-        <v>2.725</v>
+        <v>2.743</v>
       </c>
       <c r="J26" t="n">
-        <v>1.87</v>
+        <v>1.8532</v>
       </c>
       <c r="K26" t="n">
-        <v>1.0186</v>
+        <v>1.0094</v>
       </c>
       <c r="L26" t="n">
-        <v>0.5558</v>
+        <v>0.5508</v>
       </c>
       <c r="M26" t="n">
-        <v>0.2957</v>
+        <v>0.293</v>
       </c>
       <c r="N26" t="n">
         <v>0.9543</v>
@@ -4740,25 +4740,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.8696</v>
+        <v>2.8437</v>
       </c>
       <c r="R26" t="n">
-        <v>1.6618</v>
+        <v>1.6469</v>
       </c>
       <c r="S26" t="n">
-        <v>0.9212</v>
+        <v>0.9127999999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>5.4527</v>
+        <v>5.4034</v>
       </c>
       <c r="U26" t="n">
-        <v>8.178000000000001</v>
+        <v>8.146000000000001</v>
       </c>
       <c r="V26" t="n">
-        <v>2.831</v>
+        <v>2.82</v>
       </c>
       <c r="W26" t="n">
-        <v>14.881</v>
+        <v>14.835</v>
       </c>
     </row>
     <row r="27">
@@ -4861,28 +4861,28 @@
         <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>2.879</v>
+        <v>3.06</v>
       </c>
       <c r="G28" t="n">
         <v>0.964</v>
       </c>
       <c r="H28" t="n">
-        <v>2.774</v>
+        <v>2.948</v>
       </c>
       <c r="I28" t="n">
-        <v>2.774</v>
+        <v>2.948</v>
       </c>
       <c r="J28" t="n">
-        <v>1.8459</v>
+        <v>1.8688</v>
       </c>
       <c r="K28" t="n">
-        <v>1.0054</v>
+        <v>1.0179</v>
       </c>
       <c r="L28" t="n">
-        <v>0.5486</v>
+        <v>0.5554</v>
       </c>
       <c r="M28" t="n">
-        <v>0.2918</v>
+        <v>0.2955</v>
       </c>
       <c r="N28" t="n">
         <v>0.9543</v>
@@ -4894,25 +4894,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.8324</v>
+        <v>2.8676</v>
       </c>
       <c r="R28" t="n">
-        <v>1.6403</v>
+        <v>1.6606</v>
       </c>
       <c r="S28" t="n">
-        <v>0.9091</v>
+        <v>0.9206</v>
       </c>
       <c r="T28" t="n">
-        <v>5.3818</v>
+        <v>5.4489</v>
       </c>
       <c r="U28" t="n">
-        <v>8.156000000000001</v>
+        <v>8.397</v>
       </c>
       <c r="V28" t="n">
-        <v>2.823</v>
+        <v>2.906</v>
       </c>
       <c r="W28" t="n">
-        <v>14.846</v>
+        <v>15.178</v>
       </c>
     </row>
     <row r="29">
@@ -7248,28 +7248,28 @@
         <v>-1</v>
       </c>
       <c r="F59" t="n">
-        <v>3.01</v>
+        <v>3.013</v>
       </c>
       <c r="G59" t="n">
         <v>0.956</v>
       </c>
       <c r="H59" t="n">
-        <v>2.877</v>
+        <v>2.88</v>
       </c>
       <c r="I59" t="n">
-        <v>2.877</v>
+        <v>2.88</v>
       </c>
       <c r="J59" t="n">
-        <v>1.891</v>
+        <v>1.8931</v>
       </c>
       <c r="K59" t="n">
-        <v>1.03</v>
+        <v>1.0311</v>
       </c>
       <c r="L59" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.5626</v>
       </c>
       <c r="M59" t="n">
-        <v>0.299</v>
+        <v>0.2993</v>
       </c>
       <c r="N59" t="n">
         <v>0.9515</v>
@@ -7281,25 +7281,25 @@
         <v>0.66</v>
       </c>
       <c r="Q59" t="n">
-        <v>2.8902</v>
+        <v>2.8933</v>
       </c>
       <c r="R59" t="n">
-        <v>1.6396</v>
+        <v>1.6414</v>
       </c>
       <c r="S59" t="n">
-        <v>0.885</v>
+        <v>0.8859</v>
       </c>
       <c r="T59" t="n">
-        <v>5.4149</v>
+        <v>5.4206</v>
       </c>
       <c r="U59" t="n">
-        <v>8.292</v>
+        <v>8.301</v>
       </c>
       <c r="V59" t="n">
-        <v>2.87</v>
+        <v>2.873</v>
       </c>
       <c r="W59" t="n">
-        <v>14.983</v>
+        <v>14.995</v>
       </c>
     </row>
     <row r="60">
@@ -7479,28 +7479,28 @@
         <v>-1</v>
       </c>
       <c r="F62" t="n">
-        <v>2.848</v>
+        <v>3.013</v>
       </c>
       <c r="G62" t="n">
         <v>0.956</v>
       </c>
       <c r="H62" t="n">
-        <v>2.723</v>
+        <v>2.88</v>
       </c>
       <c r="I62" t="n">
-        <v>2.723</v>
+        <v>2.88</v>
       </c>
       <c r="J62" t="n">
-        <v>1.8724</v>
+        <v>1.8931</v>
       </c>
       <c r="K62" t="n">
-        <v>1.0199</v>
+        <v>1.0311</v>
       </c>
       <c r="L62" t="n">
-        <v>0.5565</v>
+        <v>0.5626</v>
       </c>
       <c r="M62" t="n">
-        <v>0.296</v>
+        <v>0.2993</v>
       </c>
       <c r="N62" t="n">
         <v>0.9515</v>
@@ -7512,25 +7512,25 @@
         <v>0.66</v>
       </c>
       <c r="Q62" t="n">
-        <v>2.8618</v>
+        <v>2.8933</v>
       </c>
       <c r="R62" t="n">
-        <v>1.6236</v>
+        <v>1.6414</v>
       </c>
       <c r="S62" t="n">
-        <v>0.8762</v>
+        <v>0.8859</v>
       </c>
       <c r="T62" t="n">
-        <v>5.3616</v>
+        <v>5.4206</v>
       </c>
       <c r="U62" t="n">
-        <v>8.085000000000001</v>
+        <v>8.301</v>
       </c>
       <c r="V62" t="n">
-        <v>2.799</v>
+        <v>2.873</v>
       </c>
       <c r="W62" t="n">
-        <v>14.698</v>
+        <v>14.995</v>
       </c>
     </row>
     <row r="63">
@@ -7633,28 +7633,28 @@
         <v>1</v>
       </c>
       <c r="F64" t="n">
-        <v>3.358</v>
+        <v>3.175</v>
       </c>
       <c r="G64" t="n">
         <v>0.956</v>
       </c>
       <c r="H64" t="n">
-        <v>3.209</v>
+        <v>3.035</v>
       </c>
       <c r="I64" t="n">
-        <v>3.209</v>
+        <v>3.035</v>
       </c>
       <c r="J64" t="n">
-        <v>1.9045</v>
+        <v>1.9164</v>
       </c>
       <c r="K64" t="n">
-        <v>1.0374</v>
+        <v>1.0439</v>
       </c>
       <c r="L64" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.5696</v>
       </c>
       <c r="M64" t="n">
-        <v>0.3011</v>
+        <v>0.303</v>
       </c>
       <c r="N64" t="n">
         <v>0.9515</v>
@@ -7666,25 +7666,25 @@
         <v>0.66</v>
       </c>
       <c r="Q64" t="n">
-        <v>2.9109</v>
+        <v>2.9292</v>
       </c>
       <c r="R64" t="n">
-        <v>1.6513</v>
+        <v>1.6618</v>
       </c>
       <c r="S64" t="n">
-        <v>0.8913</v>
+        <v>0.8969</v>
       </c>
       <c r="T64" t="n">
-        <v>5.4535</v>
+        <v>5.4879</v>
       </c>
       <c r="U64" t="n">
-        <v>8.662000000000001</v>
+        <v>8.523</v>
       </c>
       <c r="V64" t="n">
-        <v>2.998</v>
+        <v>2.95</v>
       </c>
       <c r="W64" t="n">
-        <v>15.484</v>
+        <v>15.302</v>
       </c>
     </row>
     <row r="65">
@@ -9096,28 +9096,28 @@
         <v>-1</v>
       </c>
       <c r="F83" t="n">
-        <v>1.992</v>
+        <v>2.04</v>
       </c>
       <c r="G83" t="n">
         <v>0.969</v>
       </c>
       <c r="H83" t="n">
-        <v>1.931</v>
+        <v>1.977</v>
       </c>
       <c r="I83" t="n">
-        <v>1.931</v>
+        <v>1.977</v>
       </c>
       <c r="J83" t="n">
-        <v>1.9696</v>
+        <v>2.0547</v>
       </c>
       <c r="K83" t="n">
-        <v>1.0728</v>
+        <v>1.1192</v>
       </c>
       <c r="L83" t="n">
-        <v>0.5854</v>
+        <v>0.6106</v>
       </c>
       <c r="M83" t="n">
-        <v>0.3114</v>
+        <v>0.3248</v>
       </c>
       <c r="N83" t="n">
         <v>0.9857</v>
@@ -9129,25 +9129,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.157</v>
+        <v>3.2936</v>
       </c>
       <c r="R83" t="n">
-        <v>2.1988</v>
+        <v>2.2934</v>
       </c>
       <c r="S83" t="n">
-        <v>0.9701</v>
+        <v>1.0119</v>
       </c>
       <c r="T83" t="n">
-        <v>6.3259</v>
+        <v>6.5989</v>
       </c>
       <c r="U83" t="n">
-        <v>8.257</v>
+        <v>8.576000000000001</v>
       </c>
       <c r="V83" t="n">
-        <v>2.858</v>
+        <v>2.968</v>
       </c>
       <c r="W83" t="n">
-        <v>15.259</v>
+        <v>15.711</v>
       </c>
     </row>
     <row r="84">
@@ -10482,28 +10482,28 @@
         <v>1</v>
       </c>
       <c r="F101" t="n">
-        <v>2.352</v>
+        <v>2.518</v>
       </c>
       <c r="G101" t="n">
         <v>0.977</v>
       </c>
       <c r="H101" t="n">
-        <v>2.299</v>
+        <v>2.46</v>
       </c>
       <c r="I101" t="n">
-        <v>2.299</v>
+        <v>2.46</v>
       </c>
       <c r="J101" t="n">
-        <v>2.0251</v>
+        <v>2.0755</v>
       </c>
       <c r="K101" t="n">
-        <v>1.1031</v>
+        <v>1.1305</v>
       </c>
       <c r="L101" t="n">
-        <v>0.6019</v>
+        <v>0.6168</v>
       </c>
       <c r="M101" t="n">
-        <v>0.3202</v>
+        <v>0.3281</v>
       </c>
       <c r="N101" t="n">
         <v>0.9268</v>
@@ -10515,25 +10515,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q101" t="n">
-        <v>2.9863</v>
+        <v>3.0605</v>
       </c>
       <c r="R101" t="n">
-        <v>1.2426</v>
+        <v>1.2734</v>
       </c>
       <c r="S101" t="n">
-        <v>0.9976</v>
+        <v>1.0222</v>
       </c>
       <c r="T101" t="n">
-        <v>5.2265</v>
+        <v>5.356</v>
       </c>
       <c r="U101" t="n">
-        <v>7.525</v>
+        <v>7.816</v>
       </c>
       <c r="V101" t="n">
-        <v>2.605</v>
+        <v>2.705</v>
       </c>
       <c r="W101" t="n">
-        <v>13.707</v>
+        <v>14.113</v>
       </c>
     </row>
     <row r="102">
@@ -12099,28 +12099,28 @@
         <v>-1</v>
       </c>
       <c r="F122" t="n">
-        <v>2.497</v>
+        <v>2.737</v>
       </c>
       <c r="G122" t="n">
         <v>0.976</v>
       </c>
       <c r="H122" t="n">
-        <v>2.438</v>
+        <v>2.673</v>
       </c>
       <c r="I122" t="n">
-        <v>2.438</v>
+        <v>2.673</v>
       </c>
       <c r="J122" t="n">
-        <v>2.01</v>
+        <v>2.0664</v>
       </c>
       <c r="K122" t="n">
-        <v>1.0948</v>
+        <v>1.1256</v>
       </c>
       <c r="L122" t="n">
-        <v>0.5974</v>
+        <v>0.6141</v>
       </c>
       <c r="M122" t="n">
-        <v>0.3178</v>
+        <v>0.3267</v>
       </c>
       <c r="N122" t="n">
         <v>0.9655</v>
@@ -12132,25 +12132,25 @@
         <v>0.8431</v>
       </c>
       <c r="Q122" t="n">
-        <v>3.1333</v>
+        <v>3.2215</v>
       </c>
       <c r="R122" t="n">
-        <v>1.3316</v>
+        <v>1.3688</v>
       </c>
       <c r="S122" t="n">
-        <v>1.2898</v>
+        <v>1.3259</v>
       </c>
       <c r="T122" t="n">
-        <v>5.7547</v>
+        <v>5.9162</v>
       </c>
       <c r="U122" t="n">
-        <v>8.193</v>
+        <v>8.589</v>
       </c>
       <c r="V122" t="n">
-        <v>2.836</v>
+        <v>2.973</v>
       </c>
       <c r="W122" t="n">
-        <v>14.883</v>
+        <v>15.437</v>
       </c>
     </row>
     <row r="123">
@@ -16180,28 +16180,28 @@
         <v>-1</v>
       </c>
       <c r="F175" t="n">
-        <v>2.577</v>
+        <v>2.693</v>
       </c>
       <c r="G175" t="n">
         <v>0.951</v>
       </c>
       <c r="H175" t="n">
-        <v>2.451</v>
+        <v>2.561</v>
       </c>
       <c r="I175" t="n">
-        <v>2.451</v>
+        <v>2.561</v>
       </c>
       <c r="J175" t="n">
-        <v>1.8842</v>
+        <v>1.9576</v>
       </c>
       <c r="K175" t="n">
-        <v>1.0263</v>
+        <v>1.0663</v>
       </c>
       <c r="L175" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5818</v>
       </c>
       <c r="M175" t="n">
-        <v>0.2979</v>
+        <v>0.3095</v>
       </c>
       <c r="N175" t="n">
         <v>0.9543</v>
@@ -16213,25 +16213,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q175" t="n">
-        <v>2.8913</v>
+        <v>3.004</v>
       </c>
       <c r="R175" t="n">
-        <v>1.6744</v>
+        <v>1.7396</v>
       </c>
       <c r="S175" t="n">
-        <v>0.9281</v>
+        <v>0.9641999999999999</v>
       </c>
       <c r="T175" t="n">
-        <v>5.4938</v>
+        <v>5.7078</v>
       </c>
       <c r="U175" t="n">
-        <v>7.945</v>
+        <v>8.269</v>
       </c>
       <c r="V175" t="n">
-        <v>2.75</v>
+        <v>2.862</v>
       </c>
       <c r="W175" t="n">
-        <v>14.549</v>
+        <v>15.006</v>
       </c>
     </row>
     <row r="176">
@@ -20800,28 +20800,28 @@
         <v>-1</v>
       </c>
       <c r="F235" t="n">
-        <v>2.238</v>
+        <v>2.462</v>
       </c>
       <c r="G235" t="n">
         <v>0.9389999999999999</v>
       </c>
       <c r="H235" t="n">
-        <v>2.102</v>
+        <v>2.311</v>
       </c>
       <c r="I235" t="n">
-        <v>2.102</v>
+        <v>2.311</v>
       </c>
       <c r="J235" t="n">
-        <v>1.9812</v>
+        <v>2.0998</v>
       </c>
       <c r="K235" t="n">
-        <v>1.0792</v>
+        <v>1.1438</v>
       </c>
       <c r="L235" t="n">
-        <v>0.5888</v>
+        <v>0.6241</v>
       </c>
       <c r="M235" t="n">
-        <v>0.3132</v>
+        <v>0.332</v>
       </c>
       <c r="N235" t="n">
         <v>0.963</v>
@@ -20833,25 +20833,25 @@
         <v>0.6604</v>
       </c>
       <c r="Q235" t="n">
-        <v>3.0779</v>
+        <v>3.2621</v>
       </c>
       <c r="R235" t="n">
-        <v>1.9713</v>
+        <v>2.0895</v>
       </c>
       <c r="S235" t="n">
-        <v>0.9278</v>
+        <v>0.9835</v>
       </c>
       <c r="T235" t="n">
-        <v>5.977</v>
+        <v>6.3351</v>
       </c>
       <c r="U235" t="n">
-        <v>8.079000000000001</v>
+        <v>8.646000000000001</v>
       </c>
       <c r="V235" t="n">
-        <v>2.796</v>
+        <v>2.993</v>
       </c>
       <c r="W235" t="n">
-        <v>14.82</v>
+        <v>15.618</v>
       </c>
     </row>
     <row r="236">
@@ -21570,28 +21570,28 @@
         <v>1</v>
       </c>
       <c r="F245" t="n">
-        <v>2.895</v>
+        <v>3.189</v>
       </c>
       <c r="G245" t="n">
         <v>1</v>
       </c>
       <c r="H245" t="n">
-        <v>2.895</v>
+        <v>3.189</v>
       </c>
       <c r="I245" t="n">
-        <v>2.895</v>
+        <v>3.189</v>
       </c>
       <c r="J245" t="n">
-        <v>1.8944</v>
+        <v>1.9381</v>
       </c>
       <c r="K245" t="n">
-        <v>1.0319</v>
+        <v>1.0557</v>
       </c>
       <c r="L245" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.576</v>
       </c>
       <c r="M245" t="n">
-        <v>0.2995</v>
+        <v>0.3064</v>
       </c>
       <c r="N245" t="n">
         <v>0.9543</v>
@@ -21603,25 +21603,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q245" t="n">
-        <v>2.9071</v>
+        <v>2.9741</v>
       </c>
       <c r="R245" t="n">
-        <v>1.6834</v>
+        <v>1.7222</v>
       </c>
       <c r="S245" t="n">
-        <v>0.9331</v>
+        <v>0.9546</v>
       </c>
       <c r="T245" t="n">
-        <v>5.5235</v>
+        <v>5.6509</v>
       </c>
       <c r="U245" t="n">
-        <v>8.417999999999999</v>
+        <v>8.84</v>
       </c>
       <c r="V245" t="n">
-        <v>2.914</v>
+        <v>3.06</v>
       </c>
       <c r="W245" t="n">
-        <v>15.252</v>
+        <v>15.832</v>
       </c>
     </row>
     <row r="246">
@@ -22571,28 +22571,28 @@
         <v>1</v>
       </c>
       <c r="F258" t="n">
-        <v>3.14</v>
+        <v>3.223</v>
       </c>
       <c r="G258" t="n">
         <v>0.959</v>
       </c>
       <c r="H258" t="n">
-        <v>3.012</v>
+        <v>3.092</v>
       </c>
       <c r="I258" t="n">
-        <v>3.012</v>
+        <v>3.092</v>
       </c>
       <c r="J258" t="n">
-        <v>1.977</v>
+        <v>1.9685</v>
       </c>
       <c r="K258" t="n">
-        <v>1.0768</v>
+        <v>1.0723</v>
       </c>
       <c r="L258" t="n">
-        <v>0.5876</v>
+        <v>0.5851</v>
       </c>
       <c r="M258" t="n">
-        <v>0.3126</v>
+        <v>0.3112</v>
       </c>
       <c r="N258" t="n">
         <v>0.9543</v>
@@ -22604,25 +22604,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q258" t="n">
-        <v>3.0336</v>
+        <v>3.0209</v>
       </c>
       <c r="R258" t="n">
-        <v>1.7569</v>
+        <v>1.7494</v>
       </c>
       <c r="S258" t="n">
-        <v>0.9739</v>
+        <v>0.9695</v>
       </c>
       <c r="T258" t="n">
-        <v>5.7644</v>
+        <v>5.7398</v>
       </c>
       <c r="U258" t="n">
-        <v>8.776</v>
+        <v>8.832000000000001</v>
       </c>
       <c r="V258" t="n">
-        <v>3.038</v>
+        <v>3.057</v>
       </c>
       <c r="W258" t="n">
-        <v>15.709</v>
+        <v>15.783</v>
       </c>
     </row>
     <row r="259">
@@ -22648,28 +22648,28 @@
         <v>-1</v>
       </c>
       <c r="F259" t="n">
-        <v>2.964</v>
+        <v>3.073</v>
       </c>
       <c r="G259" t="n">
         <v>0.959</v>
       </c>
       <c r="H259" t="n">
-        <v>2.843</v>
+        <v>2.948</v>
       </c>
       <c r="I259" t="n">
-        <v>2.843</v>
+        <v>2.948</v>
       </c>
       <c r="J259" t="n">
-        <v>1.9804</v>
+        <v>1.9624</v>
       </c>
       <c r="K259" t="n">
-        <v>1.0787</v>
+        <v>1.0689</v>
       </c>
       <c r="L259" t="n">
-        <v>0.5886</v>
+        <v>0.5832000000000001</v>
       </c>
       <c r="M259" t="n">
-        <v>0.3131</v>
+        <v>0.3103</v>
       </c>
       <c r="N259" t="n">
         <v>0.9543</v>
@@ -22681,25 +22681,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q259" t="n">
-        <v>3.0389</v>
+        <v>3.0113</v>
       </c>
       <c r="R259" t="n">
-        <v>1.7599</v>
+        <v>1.7438</v>
       </c>
       <c r="S259" t="n">
-        <v>0.9754</v>
+        <v>0.9667</v>
       </c>
       <c r="T259" t="n">
-        <v>5.7743</v>
+        <v>5.7218</v>
       </c>
       <c r="U259" t="n">
-        <v>8.617000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="V259" t="n">
-        <v>2.983</v>
+        <v>3.001</v>
       </c>
       <c r="W259" t="n">
-        <v>15.494</v>
+        <v>15.563</v>
       </c>
     </row>
     <row r="260">
@@ -22725,28 +22725,28 @@
         <v>-1</v>
       </c>
       <c r="F260" t="n">
-        <v>2.914</v>
+        <v>3.022</v>
       </c>
       <c r="G260" t="n">
         <v>0.959</v>
       </c>
       <c r="H260" t="n">
-        <v>2.795</v>
+        <v>2.899</v>
       </c>
       <c r="I260" t="n">
-        <v>2.795</v>
+        <v>2.899</v>
       </c>
       <c r="J260" t="n">
-        <v>1.9711</v>
+        <v>1.9598</v>
       </c>
       <c r="K260" t="n">
-        <v>1.0737</v>
+        <v>1.0675</v>
       </c>
       <c r="L260" t="n">
-        <v>0.5858</v>
+        <v>0.5825</v>
       </c>
       <c r="M260" t="n">
-        <v>0.3116</v>
+        <v>0.3099</v>
       </c>
       <c r="N260" t="n">
         <v>0.9543</v>
@@ -22758,25 +22758,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q260" t="n">
-        <v>3.0248</v>
+        <v>3.0074</v>
       </c>
       <c r="R260" t="n">
-        <v>1.7515</v>
+        <v>1.7417</v>
       </c>
       <c r="S260" t="n">
-        <v>0.9708</v>
+        <v>0.9655</v>
       </c>
       <c r="T260" t="n">
-        <v>5.7471</v>
+        <v>5.7145</v>
       </c>
       <c r="U260" t="n">
-        <v>8.542</v>
+        <v>8.614000000000001</v>
       </c>
       <c r="V260" t="n">
-        <v>2.957</v>
+        <v>2.982</v>
       </c>
       <c r="W260" t="n">
-        <v>15.391</v>
+        <v>15.486</v>
       </c>
     </row>
     <row r="261">
@@ -22802,28 +22802,28 @@
         <v>1</v>
       </c>
       <c r="F261" t="n">
-        <v>3.056</v>
+        <v>3.154</v>
       </c>
       <c r="G261" t="n">
         <v>0.959</v>
       </c>
       <c r="H261" t="n">
-        <v>2.932</v>
+        <v>3.025</v>
       </c>
       <c r="I261" t="n">
-        <v>2.932</v>
+        <v>3.025</v>
       </c>
       <c r="J261" t="n">
-        <v>1.9655</v>
+        <v>1.9525</v>
       </c>
       <c r="K261" t="n">
-        <v>1.0706</v>
+        <v>1.0635</v>
       </c>
       <c r="L261" t="n">
-        <v>0.5841</v>
+        <v>0.5803</v>
       </c>
       <c r="M261" t="n">
-        <v>0.3107</v>
+        <v>0.3087</v>
       </c>
       <c r="N261" t="n">
         <v>0.9543</v>
@@ -22835,25 +22835,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q261" t="n">
-        <v>3.0161</v>
+        <v>2.9961</v>
       </c>
       <c r="R261" t="n">
-        <v>1.7465</v>
+        <v>1.7351</v>
       </c>
       <c r="S261" t="n">
-        <v>0.968</v>
+        <v>0.9617</v>
       </c>
       <c r="T261" t="n">
-        <v>5.7305</v>
+        <v>5.6929</v>
       </c>
       <c r="U261" t="n">
-        <v>8.662000000000001</v>
+        <v>8.718</v>
       </c>
       <c r="V261" t="n">
-        <v>2.998</v>
+        <v>3.018</v>
       </c>
       <c r="W261" t="n">
-        <v>15.553</v>
+        <v>15.625</v>
       </c>
     </row>
     <row r="262">
@@ -22879,28 +22879,28 @@
         <v>1</v>
       </c>
       <c r="F262" t="n">
-        <v>2.546</v>
+        <v>2.556</v>
       </c>
       <c r="G262" t="n">
         <v>0.959</v>
       </c>
       <c r="H262" t="n">
-        <v>2.443</v>
+        <v>2.452</v>
       </c>
       <c r="I262" t="n">
-        <v>2.443</v>
+        <v>2.452</v>
       </c>
       <c r="J262" t="n">
-        <v>1.9208</v>
+        <v>1.9094</v>
       </c>
       <c r="K262" t="n">
-        <v>1.0463</v>
+        <v>1.04</v>
       </c>
       <c r="L262" t="n">
-        <v>0.5709</v>
+        <v>0.5675</v>
       </c>
       <c r="M262" t="n">
-        <v>0.3037</v>
+        <v>0.3019</v>
       </c>
       <c r="N262" t="n">
         <v>0.9543</v>
@@ -22912,25 +22912,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q262" t="n">
-        <v>2.9476</v>
+        <v>2.9299</v>
       </c>
       <c r="R262" t="n">
-        <v>1.707</v>
+        <v>1.6968</v>
       </c>
       <c r="S262" t="n">
-        <v>0.9461000000000001</v>
+        <v>0.9405</v>
       </c>
       <c r="T262" t="n">
-        <v>5.6008</v>
+        <v>5.5673</v>
       </c>
       <c r="U262" t="n">
-        <v>8.044</v>
+        <v>8.019</v>
       </c>
       <c r="V262" t="n">
-        <v>2.784</v>
+        <v>2.776</v>
       </c>
       <c r="W262" t="n">
-        <v>14.699</v>
+        <v>14.663</v>
       </c>
     </row>
     <row r="263">
@@ -22956,28 +22956,28 @@
         <v>-1</v>
       </c>
       <c r="F263" t="n">
-        <v>2.889</v>
+        <v>2.988</v>
       </c>
       <c r="G263" t="n">
         <v>0.959</v>
       </c>
       <c r="H263" t="n">
-        <v>2.772</v>
+        <v>2.866</v>
       </c>
       <c r="I263" t="n">
-        <v>2.772</v>
+        <v>2.866</v>
       </c>
       <c r="J263" t="n">
-        <v>1.9662</v>
+        <v>1.9546</v>
       </c>
       <c r="K263" t="n">
-        <v>1.071</v>
+        <v>1.0647</v>
       </c>
       <c r="L263" t="n">
-        <v>0.5844</v>
+        <v>0.5809</v>
       </c>
       <c r="M263" t="n">
-        <v>0.3109</v>
+        <v>0.309</v>
       </c>
       <c r="N263" t="n">
         <v>0.9543</v>
@@ -22989,25 +22989,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q263" t="n">
-        <v>3.0172</v>
+        <v>2.9995</v>
       </c>
       <c r="R263" t="n">
-        <v>1.7474</v>
+        <v>1.7369</v>
       </c>
       <c r="S263" t="n">
-        <v>0.9686</v>
+        <v>0.9627</v>
       </c>
       <c r="T263" t="n">
-        <v>5.7332</v>
+        <v>5.699</v>
       </c>
       <c r="U263" t="n">
-        <v>8.505000000000001</v>
+        <v>8.565</v>
       </c>
       <c r="V263" t="n">
-        <v>2.944</v>
+        <v>2.965</v>
       </c>
       <c r="W263" t="n">
-        <v>15.341</v>
+        <v>15.419</v>
       </c>
     </row>
     <row r="264">
@@ -23045,16 +23045,16 @@
         <v>2.516</v>
       </c>
       <c r="J264" t="n">
-        <v>1.9352</v>
+        <v>1.9202</v>
       </c>
       <c r="K264" t="n">
-        <v>1.0541</v>
+        <v>1.0459</v>
       </c>
       <c r="L264" t="n">
-        <v>0.5750999999999999</v>
+        <v>0.5707</v>
       </c>
       <c r="M264" t="n">
-        <v>0.3059</v>
+        <v>0.3036</v>
       </c>
       <c r="N264" t="n">
         <v>0.9543</v>
@@ -23066,25 +23066,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q264" t="n">
-        <v>2.9696</v>
+        <v>2.9465</v>
       </c>
       <c r="R264" t="n">
-        <v>1.7195</v>
+        <v>1.7064</v>
       </c>
       <c r="S264" t="n">
-        <v>0.953</v>
+        <v>0.9458</v>
       </c>
       <c r="T264" t="n">
-        <v>5.6422</v>
+        <v>5.5987</v>
       </c>
       <c r="U264" t="n">
-        <v>8.157999999999999</v>
+        <v>8.115</v>
       </c>
       <c r="V264" t="n">
-        <v>2.824</v>
+        <v>2.809</v>
       </c>
       <c r="W264" t="n">
-        <v>14.858</v>
+        <v>14.797</v>
       </c>
     </row>
     <row r="265">
@@ -23110,28 +23110,28 @@
         <v>1</v>
       </c>
       <c r="F265" t="n">
-        <v>3.003</v>
+        <v>3.177</v>
       </c>
       <c r="G265" t="n">
         <v>0.959</v>
       </c>
       <c r="H265" t="n">
-        <v>2.881</v>
+        <v>3.047</v>
       </c>
       <c r="I265" t="n">
-        <v>2.881</v>
+        <v>3.047</v>
       </c>
       <c r="J265" t="n">
-        <v>1.9602</v>
+        <v>1.9525</v>
       </c>
       <c r="K265" t="n">
-        <v>1.0677</v>
+        <v>1.0636</v>
       </c>
       <c r="L265" t="n">
-        <v>0.5826</v>
+        <v>0.5803</v>
       </c>
       <c r="M265" t="n">
-        <v>0.3099</v>
+        <v>0.3087</v>
       </c>
       <c r="N265" t="n">
         <v>0.9543</v>
@@ -23143,25 +23143,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q265" t="n">
-        <v>3.0079</v>
+        <v>2.9964</v>
       </c>
       <c r="R265" t="n">
-        <v>1.742</v>
+        <v>1.7351</v>
       </c>
       <c r="S265" t="n">
-        <v>0.9655</v>
+        <v>0.9617</v>
       </c>
       <c r="T265" t="n">
-        <v>5.7154</v>
+        <v>5.6932</v>
       </c>
       <c r="U265" t="n">
-        <v>8.596</v>
+        <v>8.74</v>
       </c>
       <c r="V265" t="n">
-        <v>2.975</v>
+        <v>3.025</v>
       </c>
       <c r="W265" t="n">
-        <v>15.462</v>
+        <v>15.656</v>
       </c>
     </row>
     <row r="266">
@@ -23187,28 +23187,28 @@
         <v>1</v>
       </c>
       <c r="F266" t="n">
-        <v>2.829</v>
+        <v>2.939</v>
       </c>
       <c r="G266" t="n">
         <v>0.959</v>
       </c>
       <c r="H266" t="n">
-        <v>2.714</v>
+        <v>2.819</v>
       </c>
       <c r="I266" t="n">
-        <v>2.714</v>
+        <v>2.819</v>
       </c>
       <c r="J266" t="n">
-        <v>1.9861</v>
+        <v>1.9627</v>
       </c>
       <c r="K266" t="n">
-        <v>1.0818</v>
+        <v>1.0691</v>
       </c>
       <c r="L266" t="n">
-        <v>0.5903</v>
+        <v>0.5833</v>
       </c>
       <c r="M266" t="n">
-        <v>0.314</v>
+        <v>0.3103</v>
       </c>
       <c r="N266" t="n">
         <v>0.9543</v>
@@ -23220,25 +23220,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q266" t="n">
-        <v>3.0476</v>
+        <v>3.0119</v>
       </c>
       <c r="R266" t="n">
-        <v>1.765</v>
+        <v>1.7441</v>
       </c>
       <c r="S266" t="n">
-        <v>0.9782</v>
+        <v>0.9667</v>
       </c>
       <c r="T266" t="n">
-        <v>5.7909</v>
+        <v>5.7226</v>
       </c>
       <c r="U266" t="n">
-        <v>8.505000000000001</v>
+        <v>8.542</v>
       </c>
       <c r="V266" t="n">
-        <v>2.944</v>
+        <v>2.957</v>
       </c>
       <c r="W266" t="n">
-        <v>15.342</v>
+        <v>15.389</v>
       </c>
     </row>
     <row r="267">
@@ -23264,28 +23264,28 @@
         <v>-1</v>
       </c>
       <c r="F267" t="n">
-        <v>2.558</v>
+        <v>2.605</v>
       </c>
       <c r="G267" t="n">
         <v>0.959</v>
       </c>
       <c r="H267" t="n">
-        <v>2.454</v>
+        <v>2.499</v>
       </c>
       <c r="I267" t="n">
-        <v>2.454</v>
+        <v>2.499</v>
       </c>
       <c r="J267" t="n">
-        <v>1.9223</v>
+        <v>1.9087</v>
       </c>
       <c r="K267" t="n">
-        <v>1.0471</v>
+        <v>1.0397</v>
       </c>
       <c r="L267" t="n">
-        <v>0.5713</v>
+        <v>0.5673</v>
       </c>
       <c r="M267" t="n">
-        <v>0.3039</v>
+        <v>0.3018</v>
       </c>
       <c r="N267" t="n">
         <v>0.9543</v>
@@ -23297,25 +23297,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q267" t="n">
-        <v>2.9499</v>
+        <v>2.929</v>
       </c>
       <c r="R267" t="n">
-        <v>1.7082</v>
+        <v>1.6962</v>
       </c>
       <c r="S267" t="n">
-        <v>0.9468</v>
+        <v>0.9402</v>
       </c>
       <c r="T267" t="n">
-        <v>5.6048</v>
+        <v>5.5655</v>
       </c>
       <c r="U267" t="n">
-        <v>8.058999999999999</v>
+        <v>8.065</v>
       </c>
       <c r="V267" t="n">
-        <v>2.79</v>
+        <v>2.792</v>
       </c>
       <c r="W267" t="n">
-        <v>14.72</v>
+        <v>14.726</v>
       </c>
     </row>
     <row r="268">
@@ -23341,28 +23341,28 @@
         <v>1</v>
       </c>
       <c r="F268" t="n">
-        <v>2.958</v>
+        <v>2.983</v>
       </c>
       <c r="G268" t="n">
         <v>0.959</v>
       </c>
       <c r="H268" t="n">
-        <v>2.837</v>
+        <v>2.862</v>
       </c>
       <c r="I268" t="n">
-        <v>2.837</v>
+        <v>2.862</v>
       </c>
       <c r="J268" t="n">
-        <v>1.982</v>
+        <v>1.965</v>
       </c>
       <c r="K268" t="n">
-        <v>1.0796</v>
+        <v>1.0703</v>
       </c>
       <c r="L268" t="n">
-        <v>0.589</v>
+        <v>0.584</v>
       </c>
       <c r="M268" t="n">
-        <v>0.3133</v>
+        <v>0.3107</v>
       </c>
       <c r="N268" t="n">
         <v>0.9543</v>
@@ -23374,25 +23374,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q268" t="n">
-        <v>3.0414</v>
+        <v>3.0152</v>
       </c>
       <c r="R268" t="n">
-        <v>1.7611</v>
+        <v>1.7462</v>
       </c>
       <c r="S268" t="n">
-        <v>0.9761</v>
+        <v>0.968</v>
       </c>
       <c r="T268" t="n">
-        <v>5.7786</v>
+        <v>5.7294</v>
       </c>
       <c r="U268" t="n">
-        <v>8.616</v>
+        <v>8.590999999999999</v>
       </c>
       <c r="V268" t="n">
-        <v>2.982</v>
+        <v>2.974</v>
       </c>
       <c r="W268" t="n">
-        <v>15.492</v>
+        <v>15.457</v>
       </c>
     </row>
     <row r="269">
@@ -23418,28 +23418,28 @@
         <v>-1</v>
       </c>
       <c r="F269" t="n">
-        <v>2.305</v>
+        <v>2.32</v>
       </c>
       <c r="G269" t="n">
         <v>0.959</v>
       </c>
       <c r="H269" t="n">
-        <v>2.211</v>
+        <v>2.225</v>
       </c>
       <c r="I269" t="n">
-        <v>2.211</v>
+        <v>2.225</v>
       </c>
       <c r="J269" t="n">
-        <v>1.8555</v>
+        <v>1.8544</v>
       </c>
       <c r="K269" t="n">
-        <v>1.0107</v>
+        <v>1.0101</v>
       </c>
       <c r="L269" t="n">
-        <v>0.5515</v>
+        <v>0.5511</v>
       </c>
       <c r="M269" t="n">
-        <v>0.2934</v>
+        <v>0.2932</v>
       </c>
       <c r="N269" t="n">
         <v>0.9543</v>
@@ -23451,25 +23451,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q269" t="n">
-        <v>2.8473</v>
+        <v>2.8457</v>
       </c>
       <c r="R269" t="n">
-        <v>1.649</v>
+        <v>1.6478</v>
       </c>
       <c r="S269" t="n">
-        <v>0.9141</v>
+        <v>0.9134</v>
       </c>
       <c r="T269" t="n">
-        <v>5.4104</v>
+        <v>5.4069</v>
       </c>
       <c r="U269" t="n">
-        <v>7.621</v>
+        <v>7.632</v>
       </c>
       <c r="V269" t="n">
-        <v>2.638</v>
+        <v>2.642</v>
       </c>
       <c r="W269" t="n">
-        <v>14.102</v>
+        <v>14.116</v>
       </c>
     </row>
     <row r="270">
@@ -23495,28 +23495,28 @@
         <v>1</v>
       </c>
       <c r="F270" t="n">
-        <v>2.714</v>
+        <v>2.697</v>
       </c>
       <c r="G270" t="n">
         <v>0.959</v>
       </c>
       <c r="H270" t="n">
-        <v>2.604</v>
+        <v>2.587</v>
       </c>
       <c r="I270" t="n">
-        <v>2.604</v>
+        <v>2.587</v>
       </c>
       <c r="J270" t="n">
-        <v>1.9695</v>
+        <v>1.9587</v>
       </c>
       <c r="K270" t="n">
-        <v>1.0728</v>
+        <v>1.0669</v>
       </c>
       <c r="L270" t="n">
-        <v>0.5853</v>
+        <v>0.5821</v>
       </c>
       <c r="M270" t="n">
-        <v>0.3114</v>
+        <v>0.3097</v>
       </c>
       <c r="N270" t="n">
         <v>0.9543</v>
@@ -23528,25 +23528,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q270" t="n">
-        <v>3.0223</v>
+        <v>3.0057</v>
       </c>
       <c r="R270" t="n">
-        <v>1.75</v>
+        <v>1.7405</v>
       </c>
       <c r="S270" t="n">
-        <v>0.9701</v>
+        <v>0.9648</v>
       </c>
       <c r="T270" t="n">
-        <v>5.7425</v>
+        <v>5.711</v>
       </c>
       <c r="U270" t="n">
-        <v>8.346</v>
+        <v>8.298</v>
       </c>
       <c r="V270" t="n">
-        <v>2.889</v>
+        <v>2.872</v>
       </c>
       <c r="W270" t="n">
-        <v>15.123</v>
+        <v>15.054</v>
       </c>
     </row>
     <row r="271">
@@ -23572,28 +23572,28 @@
         <v>-1</v>
       </c>
       <c r="F271" t="n">
-        <v>2.665</v>
+        <v>2.781</v>
       </c>
       <c r="G271" t="n">
         <v>0.959</v>
       </c>
       <c r="H271" t="n">
-        <v>2.557</v>
+        <v>2.668</v>
       </c>
       <c r="I271" t="n">
-        <v>2.557</v>
+        <v>2.668</v>
       </c>
       <c r="J271" t="n">
-        <v>1.9801</v>
+        <v>1.957</v>
       </c>
       <c r="K271" t="n">
-        <v>1.0785</v>
+        <v>1.066</v>
       </c>
       <c r="L271" t="n">
-        <v>0.5885</v>
+        <v>0.5816</v>
       </c>
       <c r="M271" t="n">
-        <v>0.313</v>
+        <v>0.3094</v>
       </c>
       <c r="N271" t="n">
         <v>0.9543</v>
@@ -23605,25 +23605,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q271" t="n">
-        <v>3.0384</v>
+        <v>3.0031</v>
       </c>
       <c r="R271" t="n">
-        <v>1.7596</v>
+        <v>1.739</v>
       </c>
       <c r="S271" t="n">
-        <v>0.9751</v>
+        <v>0.9639</v>
       </c>
       <c r="T271" t="n">
-        <v>5.7731</v>
+        <v>5.706</v>
       </c>
       <c r="U271" t="n">
-        <v>8.33</v>
+        <v>8.374000000000001</v>
       </c>
       <c r="V271" t="n">
-        <v>2.883</v>
+        <v>2.899</v>
       </c>
       <c r="W271" t="n">
-        <v>15.101</v>
+        <v>15.159</v>
       </c>
     </row>
     <row r="272">
@@ -23649,28 +23649,28 @@
         <v>-1</v>
       </c>
       <c r="F272" t="n">
-        <v>2.791</v>
+        <v>2.894</v>
       </c>
       <c r="G272" t="n">
         <v>0.959</v>
       </c>
       <c r="H272" t="n">
-        <v>2.678</v>
+        <v>2.777</v>
       </c>
       <c r="I272" t="n">
-        <v>2.678</v>
+        <v>2.777</v>
       </c>
       <c r="J272" t="n">
-        <v>1.9531</v>
+        <v>1.9405</v>
       </c>
       <c r="K272" t="n">
-        <v>1.0638</v>
+        <v>1.057</v>
       </c>
       <c r="L272" t="n">
-        <v>0.5804</v>
+        <v>0.5767</v>
       </c>
       <c r="M272" t="n">
-        <v>0.3088</v>
+        <v>0.3068</v>
       </c>
       <c r="N272" t="n">
         <v>0.9543</v>
@@ -23682,25 +23682,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q272" t="n">
-        <v>2.9969</v>
+        <v>2.9778</v>
       </c>
       <c r="R272" t="n">
-        <v>1.7354</v>
+        <v>1.7243</v>
       </c>
       <c r="S272" t="n">
-        <v>0.962</v>
+        <v>0.9558</v>
       </c>
       <c r="T272" t="n">
-        <v>5.6944</v>
+        <v>5.6579</v>
       </c>
       <c r="U272" t="n">
-        <v>8.372</v>
+        <v>8.435</v>
       </c>
       <c r="V272" t="n">
-        <v>2.898</v>
+        <v>2.92</v>
       </c>
       <c r="W272" t="n">
-        <v>15.157</v>
+        <v>15.24</v>
       </c>
     </row>
     <row r="273">
@@ -26267,28 +26267,28 @@
         <v>-1</v>
       </c>
       <c r="F306" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="G306" t="n">
         <v>0.969</v>
       </c>
       <c r="H306" t="n">
-        <v>1.831</v>
+        <v>1.851</v>
       </c>
       <c r="I306" t="n">
-        <v>1.831</v>
+        <v>1.851</v>
       </c>
       <c r="J306" t="n">
-        <v>1.8474</v>
+        <v>1.9217</v>
       </c>
       <c r="K306" t="n">
-        <v>1.0063</v>
+        <v>1.0467</v>
       </c>
       <c r="L306" t="n">
-        <v>0.5491</v>
+        <v>0.5711000000000001</v>
       </c>
       <c r="M306" t="n">
-        <v>0.2921</v>
+        <v>0.3038</v>
       </c>
       <c r="N306" t="n">
         <v>0.9412</v>
@@ -26300,25 +26300,25 @@
         <v>0.6923</v>
       </c>
       <c r="Q306" t="n">
-        <v>2.7822</v>
+        <v>2.8939</v>
       </c>
       <c r="R306" t="n">
-        <v>1.5669</v>
+        <v>1.6296</v>
       </c>
       <c r="S306" t="n">
-        <v>0.9212</v>
+        <v>0.9581</v>
       </c>
       <c r="T306" t="n">
-        <v>5.2703</v>
+        <v>5.4817</v>
       </c>
       <c r="U306" t="n">
-        <v>7.101</v>
+        <v>7.333</v>
       </c>
       <c r="V306" t="n">
-        <v>2.458</v>
+        <v>2.538</v>
       </c>
       <c r="W306" t="n">
-        <v>13.316</v>
+        <v>13.647</v>
       </c>
     </row>
     <row r="307">
@@ -26806,28 +26806,28 @@
         <v>1</v>
       </c>
       <c r="F313" t="n">
-        <v>2.156</v>
+        <v>2.129</v>
       </c>
       <c r="G313" t="n">
         <v>0.969</v>
       </c>
       <c r="H313" t="n">
-        <v>2.089</v>
+        <v>2.064</v>
       </c>
       <c r="I313" t="n">
-        <v>2.089</v>
+        <v>2.064</v>
       </c>
       <c r="J313" t="n">
-        <v>1.8381</v>
+        <v>1.8875</v>
       </c>
       <c r="K313" t="n">
-        <v>1.0012</v>
+        <v>1.0281</v>
       </c>
       <c r="L313" t="n">
-        <v>0.5463</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="M313" t="n">
-        <v>0.2906</v>
+        <v>0.2984</v>
       </c>
       <c r="N313" t="n">
         <v>0.9412</v>
@@ -26839,25 +26839,25 @@
         <v>0.6923</v>
       </c>
       <c r="Q313" t="n">
-        <v>2.7681</v>
+        <v>2.8425</v>
       </c>
       <c r="R313" t="n">
-        <v>1.5589</v>
+        <v>1.6008</v>
       </c>
       <c r="S313" t="n">
-        <v>0.9165</v>
+        <v>0.9411</v>
       </c>
       <c r="T313" t="n">
-        <v>5.2435</v>
+        <v>5.3844</v>
       </c>
       <c r="U313" t="n">
-        <v>7.332</v>
+        <v>7.448</v>
       </c>
       <c r="V313" t="n">
-        <v>2.538</v>
+        <v>2.578</v>
       </c>
       <c r="W313" t="n">
-        <v>13.648</v>
+        <v>13.815</v>
       </c>
     </row>
     <row r="314">
@@ -27345,28 +27345,28 @@
         <v>-1</v>
       </c>
       <c r="F320" t="n">
-        <v>1.914</v>
+        <v>1.91</v>
       </c>
       <c r="G320" t="n">
         <v>0.969</v>
       </c>
       <c r="H320" t="n">
-        <v>1.855</v>
+        <v>1.851</v>
       </c>
       <c r="I320" t="n">
-        <v>1.855</v>
+        <v>1.851</v>
       </c>
       <c r="J320" t="n">
-        <v>1.8314</v>
+        <v>1.9217</v>
       </c>
       <c r="K320" t="n">
-        <v>0.9976</v>
+        <v>1.0467</v>
       </c>
       <c r="L320" t="n">
-        <v>0.5443</v>
+        <v>0.5711000000000001</v>
       </c>
       <c r="M320" t="n">
-        <v>0.2895</v>
+        <v>0.3038</v>
       </c>
       <c r="N320" t="n">
         <v>0.9412</v>
@@ -27378,25 +27378,25 @@
         <v>0.6923</v>
       </c>
       <c r="Q320" t="n">
-        <v>2.7582</v>
+        <v>2.8939</v>
       </c>
       <c r="R320" t="n">
-        <v>1.5532</v>
+        <v>1.6296</v>
       </c>
       <c r="S320" t="n">
-        <v>0.913</v>
+        <v>0.9581</v>
       </c>
       <c r="T320" t="n">
-        <v>5.2243</v>
+        <v>5.4817</v>
       </c>
       <c r="U320" t="n">
-        <v>7.079</v>
+        <v>7.333</v>
       </c>
       <c r="V320" t="n">
-        <v>2.45</v>
+        <v>2.538</v>
       </c>
       <c r="W320" t="n">
-        <v>13.285</v>
+        <v>13.647</v>
       </c>
     </row>
     <row r="321">
@@ -28269,28 +28269,28 @@
         <v>-1</v>
       </c>
       <c r="F332" t="n">
-        <v>1.929</v>
+        <v>1.986</v>
       </c>
       <c r="G332" t="n">
         <v>0.904</v>
       </c>
       <c r="H332" t="n">
-        <v>1.744</v>
+        <v>1.796</v>
       </c>
       <c r="I332" t="n">
-        <v>1.744</v>
+        <v>1.796</v>
       </c>
       <c r="J332" t="n">
-        <v>1.8738</v>
+        <v>1.9304</v>
       </c>
       <c r="K332" t="n">
-        <v>1.0207</v>
+        <v>1.0515</v>
       </c>
       <c r="L332" t="n">
-        <v>0.5569</v>
+        <v>0.5737</v>
       </c>
       <c r="M332" t="n">
-        <v>0.2962</v>
+        <v>0.3052</v>
       </c>
       <c r="N332" t="n">
         <v>0.9394</v>
@@ -28302,25 +28302,25 @@
         <v>0.6364</v>
       </c>
       <c r="Q332" t="n">
-        <v>2.8147</v>
+        <v>2.8996</v>
       </c>
       <c r="R332" t="n">
-        <v>1.5886</v>
+        <v>1.6365</v>
       </c>
       <c r="S332" t="n">
-        <v>0.8348</v>
+        <v>0.8602</v>
       </c>
       <c r="T332" t="n">
-        <v>5.238</v>
+        <v>5.3963</v>
       </c>
       <c r="U332" t="n">
-        <v>6.982</v>
+        <v>7.192</v>
       </c>
       <c r="V332" t="n">
-        <v>2.417</v>
+        <v>2.489</v>
       </c>
       <c r="W332" t="n">
-        <v>13.043</v>
+        <v>13.344</v>
       </c>
     </row>
     <row r="333">
@@ -30194,28 +30194,28 @@
         <v>1</v>
       </c>
       <c r="F357" t="n">
-        <v>1.995</v>
+        <v>1.963</v>
       </c>
       <c r="G357" t="n">
         <v>0.957</v>
       </c>
       <c r="H357" t="n">
-        <v>1.909</v>
+        <v>1.879</v>
       </c>
       <c r="I357" t="n">
-        <v>1.909</v>
+        <v>1.879</v>
       </c>
       <c r="J357" t="n">
-        <v>1.8476</v>
+        <v>1.8985</v>
       </c>
       <c r="K357" t="n">
-        <v>1.0064</v>
+        <v>1.0341</v>
       </c>
       <c r="L357" t="n">
-        <v>0.5491</v>
+        <v>0.5642</v>
       </c>
       <c r="M357" t="n">
-        <v>0.2921</v>
+        <v>0.3001</v>
       </c>
       <c r="N357" t="n">
         <v>0.971</v>
@@ -30227,25 +30227,25 @@
         <v>0.7255</v>
       </c>
       <c r="Q357" t="n">
-        <v>2.9025</v>
+        <v>2.9823</v>
       </c>
       <c r="R357" t="n">
-        <v>1.5688</v>
+        <v>1.6119</v>
       </c>
       <c r="S357" t="n">
-        <v>0.9794</v>
+        <v>1.0062</v>
       </c>
       <c r="T357" t="n">
-        <v>5.4506</v>
+        <v>5.6005</v>
       </c>
       <c r="U357" t="n">
-        <v>7.36</v>
+        <v>7.48</v>
       </c>
       <c r="V357" t="n">
-        <v>2.548</v>
+        <v>2.589</v>
       </c>
       <c r="W357" t="n">
-        <v>13.756</v>
+        <v>13.927</v>
       </c>
     </row>
     <row r="358">
@@ -31888,28 +31888,28 @@
         <v>1</v>
       </c>
       <c r="F379" t="n">
-        <v>2.373</v>
+        <v>2.422</v>
       </c>
       <c r="G379" t="n">
         <v>0.953</v>
       </c>
       <c r="H379" t="n">
-        <v>2.262</v>
+        <v>2.309</v>
       </c>
       <c r="I379" t="n">
-        <v>2.262</v>
+        <v>2.309</v>
       </c>
       <c r="J379" t="n">
-        <v>1.903</v>
+        <v>1.9712</v>
       </c>
       <c r="K379" t="n">
-        <v>1.0366</v>
+        <v>1.0737</v>
       </c>
       <c r="L379" t="n">
-        <v>0.5656</v>
+        <v>0.5858</v>
       </c>
       <c r="M379" t="n">
-        <v>0.3009</v>
+        <v>0.3116</v>
       </c>
       <c r="N379" t="n">
         <v>0.9333</v>
@@ -31921,25 +31921,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q379" t="n">
-        <v>2.8332</v>
+        <v>2.9346</v>
       </c>
       <c r="R379" t="n">
-        <v>1.5817</v>
+        <v>1.6382</v>
       </c>
       <c r="S379" t="n">
-        <v>0.9374</v>
+        <v>0.9708</v>
       </c>
       <c r="T379" t="n">
-        <v>5.3524</v>
+        <v>5.5436</v>
       </c>
       <c r="U379" t="n">
-        <v>7.614</v>
+        <v>7.853</v>
       </c>
       <c r="V379" t="n">
-        <v>2.635</v>
+        <v>2.718</v>
       </c>
       <c r="W379" t="n">
-        <v>14.002</v>
+        <v>14.341</v>
       </c>
     </row>
     <row r="380">
@@ -32812,28 +32812,28 @@
         <v>1</v>
       </c>
       <c r="F391" t="n">
-        <v>2.432</v>
+        <v>2.358</v>
       </c>
       <c r="G391" t="n">
         <v>0.966</v>
       </c>
       <c r="H391" t="n">
-        <v>2.35</v>
+        <v>2.279</v>
       </c>
       <c r="I391" t="n">
-        <v>2.35</v>
+        <v>2.279</v>
       </c>
       <c r="J391" t="n">
-        <v>1.8368</v>
+        <v>1.9359</v>
       </c>
       <c r="K391" t="n">
-        <v>1.0005</v>
+        <v>1.0545</v>
       </c>
       <c r="L391" t="n">
-        <v>0.5459000000000001</v>
+        <v>0.5754</v>
       </c>
       <c r="M391" t="n">
-        <v>0.2904</v>
+        <v>0.3061</v>
       </c>
       <c r="N391" t="n">
         <v>0.9492</v>
@@ -32845,25 +32845,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q391" t="n">
-        <v>2.7982</v>
+        <v>2.9492</v>
       </c>
       <c r="R391" t="n">
-        <v>1.8315</v>
+        <v>1.9305</v>
       </c>
       <c r="S391" t="n">
-        <v>0.9046999999999999</v>
+        <v>0.9536</v>
       </c>
       <c r="T391" t="n">
-        <v>5.5344</v>
+        <v>5.8333</v>
       </c>
       <c r="U391" t="n">
-        <v>7.884</v>
+        <v>8.112</v>
       </c>
       <c r="V391" t="n">
-        <v>2.729</v>
+        <v>2.808</v>
       </c>
       <c r="W391" t="n">
-        <v>14.56</v>
+        <v>14.888</v>
       </c>
     </row>
     <row r="392">
@@ -32966,28 +32966,28 @@
         <v>-1</v>
       </c>
       <c r="F393" t="n">
-        <v>2.087</v>
+        <v>2.058</v>
       </c>
       <c r="G393" t="n">
         <v>0.966</v>
       </c>
       <c r="H393" t="n">
-        <v>2.016</v>
+        <v>1.988</v>
       </c>
       <c r="I393" t="n">
-        <v>2.016</v>
+        <v>1.988</v>
       </c>
       <c r="J393" t="n">
-        <v>1.8039</v>
+        <v>1.9465</v>
       </c>
       <c r="K393" t="n">
-        <v>0.9826</v>
+        <v>1.0603</v>
       </c>
       <c r="L393" t="n">
-        <v>0.5361</v>
+        <v>0.5785</v>
       </c>
       <c r="M393" t="n">
-        <v>0.2852</v>
+        <v>0.3077</v>
       </c>
       <c r="N393" t="n">
         <v>0.9492</v>
@@ -32999,25 +32999,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q393" t="n">
-        <v>2.7481</v>
+        <v>2.9654</v>
       </c>
       <c r="R393" t="n">
-        <v>1.7986</v>
+        <v>1.9409</v>
       </c>
       <c r="S393" t="n">
-        <v>0.8885</v>
+        <v>0.9586</v>
       </c>
       <c r="T393" t="n">
-        <v>5.4353</v>
+        <v>5.8649</v>
       </c>
       <c r="U393" t="n">
-        <v>7.451</v>
+        <v>7.853</v>
       </c>
       <c r="V393" t="n">
-        <v>2.579</v>
+        <v>2.718</v>
       </c>
       <c r="W393" t="n">
-        <v>13.945</v>
+        <v>14.518</v>
       </c>
     </row>
     <row r="394">
@@ -33428,28 +33428,28 @@
         <v>1</v>
       </c>
       <c r="F399" t="n">
-        <v>2.281</v>
+        <v>2.358</v>
       </c>
       <c r="G399" t="n">
         <v>0.966</v>
       </c>
       <c r="H399" t="n">
-        <v>2.204</v>
+        <v>2.279</v>
       </c>
       <c r="I399" t="n">
-        <v>2.204</v>
+        <v>2.279</v>
       </c>
       <c r="J399" t="n">
-        <v>1.8171</v>
+        <v>1.9359</v>
       </c>
       <c r="K399" t="n">
-        <v>0.9898</v>
+        <v>1.0545</v>
       </c>
       <c r="L399" t="n">
-        <v>0.54</v>
+        <v>0.5754</v>
       </c>
       <c r="M399" t="n">
-        <v>0.2873</v>
+        <v>0.3061</v>
       </c>
       <c r="N399" t="n">
         <v>0.9492</v>
@@ -33461,25 +33461,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q399" t="n">
-        <v>2.7683</v>
+        <v>2.9492</v>
       </c>
       <c r="R399" t="n">
-        <v>1.8117</v>
+        <v>1.9305</v>
       </c>
       <c r="S399" t="n">
-        <v>0.8951</v>
+        <v>0.9536</v>
       </c>
       <c r="T399" t="n">
-        <v>5.475</v>
+        <v>5.8333</v>
       </c>
       <c r="U399" t="n">
-        <v>7.679</v>
+        <v>8.112</v>
       </c>
       <c r="V399" t="n">
-        <v>2.658</v>
+        <v>2.808</v>
       </c>
       <c r="W399" t="n">
-        <v>14.27</v>
+        <v>14.888</v>
       </c>
     </row>
     <row r="400">
@@ -33736,28 +33736,28 @@
         <v>1</v>
       </c>
       <c r="F403" t="n">
-        <v>2.279</v>
+        <v>2.573</v>
       </c>
       <c r="G403" t="n">
         <v>0.9</v>
       </c>
       <c r="H403" t="n">
-        <v>2.051</v>
+        <v>2.316</v>
       </c>
       <c r="I403" t="n">
-        <v>2.051</v>
+        <v>2.316</v>
       </c>
       <c r="J403" t="n">
-        <v>1.8566</v>
+        <v>1.9214</v>
       </c>
       <c r="K403" t="n">
-        <v>1.0113</v>
+        <v>1.0466</v>
       </c>
       <c r="L403" t="n">
-        <v>0.5518</v>
+        <v>0.5711000000000001</v>
       </c>
       <c r="M403" t="n">
-        <v>0.2935</v>
+        <v>0.3038</v>
       </c>
       <c r="N403" t="n">
         <v>0.9543</v>
@@ -33769,25 +33769,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q403" t="n">
-        <v>2.849</v>
+        <v>2.9485</v>
       </c>
       <c r="R403" t="n">
-        <v>1.6499</v>
+        <v>1.7076</v>
       </c>
       <c r="S403" t="n">
-        <v>0.9144</v>
+        <v>0.9465</v>
       </c>
       <c r="T403" t="n">
-        <v>5.4133</v>
+        <v>5.6025</v>
       </c>
       <c r="U403" t="n">
-        <v>7.464</v>
+        <v>7.918</v>
       </c>
       <c r="V403" t="n">
-        <v>2.584</v>
+        <v>2.741</v>
       </c>
       <c r="W403" t="n">
-        <v>13.825</v>
+        <v>14.466</v>
       </c>
     </row>
     <row r="404">
@@ -36431,28 +36431,28 @@
         <v>-1</v>
       </c>
       <c r="F438" t="n">
-        <v>2.35</v>
+        <v>2.573</v>
       </c>
       <c r="G438" t="n">
         <v>0.974</v>
       </c>
       <c r="H438" t="n">
-        <v>2.289</v>
+        <v>2.506</v>
       </c>
       <c r="I438" t="n">
-        <v>2.289</v>
+        <v>2.506</v>
       </c>
       <c r="J438" t="n">
-        <v>1.9962</v>
+        <v>2.0686</v>
       </c>
       <c r="K438" t="n">
-        <v>1.0873</v>
+        <v>1.1267</v>
       </c>
       <c r="L438" t="n">
-        <v>0.5933</v>
+        <v>0.6148</v>
       </c>
       <c r="M438" t="n">
-        <v>0.3156</v>
+        <v>0.327</v>
       </c>
       <c r="N438" t="n">
         <v>0.9492</v>
@@ -36464,25 +36464,25 @@
         <v>0.5667</v>
       </c>
       <c r="Q438" t="n">
-        <v>3.041</v>
+        <v>3.1512</v>
       </c>
       <c r="R438" t="n">
-        <v>1.8425</v>
+        <v>1.9093</v>
       </c>
       <c r="S438" t="n">
-        <v>0.7575</v>
+        <v>0.7849</v>
       </c>
       <c r="T438" t="n">
-        <v>5.641</v>
+        <v>5.8453</v>
       </c>
       <c r="U438" t="n">
-        <v>7.93</v>
+        <v>8.351000000000001</v>
       </c>
       <c r="V438" t="n">
-        <v>2.745</v>
+        <v>2.891</v>
       </c>
       <c r="W438" t="n">
-        <v>14.481</v>
+        <v>15.072</v>
       </c>
     </row>
     <row r="439">
@@ -36893,28 +36893,28 @@
         <v>1</v>
       </c>
       <c r="F444" t="n">
-        <v>2.325</v>
+        <v>2.56</v>
       </c>
       <c r="G444" t="n">
         <v>0.974</v>
       </c>
       <c r="H444" t="n">
-        <v>2.265</v>
+        <v>2.493</v>
       </c>
       <c r="I444" t="n">
-        <v>2.265</v>
+        <v>2.493</v>
       </c>
       <c r="J444" t="n">
-        <v>2.0046</v>
+        <v>2.092</v>
       </c>
       <c r="K444" t="n">
-        <v>1.0919</v>
+        <v>1.1395</v>
       </c>
       <c r="L444" t="n">
-        <v>0.5958</v>
+        <v>0.6217</v>
       </c>
       <c r="M444" t="n">
-        <v>0.3169</v>
+        <v>0.3307</v>
       </c>
       <c r="N444" t="n">
         <v>0.9492</v>
@@ -36926,25 +36926,25 @@
         <v>0.5667</v>
       </c>
       <c r="Q444" t="n">
-        <v>3.0538</v>
+        <v>3.187</v>
       </c>
       <c r="R444" t="n">
-        <v>1.8503</v>
+        <v>1.9307</v>
       </c>
       <c r="S444" t="n">
-        <v>0.7606000000000001</v>
+        <v>0.7937</v>
       </c>
       <c r="T444" t="n">
-        <v>5.6647</v>
+        <v>5.9114</v>
       </c>
       <c r="U444" t="n">
-        <v>7.93</v>
+        <v>8.404</v>
       </c>
       <c r="V444" t="n">
-        <v>2.745</v>
+        <v>2.909</v>
       </c>
       <c r="W444" t="n">
-        <v>14.481</v>
+        <v>15.147</v>
       </c>
     </row>
     <row r="445">
@@ -37201,28 +37201,28 @@
         <v>1</v>
       </c>
       <c r="F448" t="n">
-        <v>2.37</v>
+        <v>2.56</v>
       </c>
       <c r="G448" t="n">
         <v>0.974</v>
       </c>
       <c r="H448" t="n">
-        <v>2.309</v>
+        <v>2.493</v>
       </c>
       <c r="I448" t="n">
-        <v>2.309</v>
+        <v>2.493</v>
       </c>
       <c r="J448" t="n">
-        <v>2.0357</v>
+        <v>2.092</v>
       </c>
       <c r="K448" t="n">
-        <v>1.1088</v>
+        <v>1.1395</v>
       </c>
       <c r="L448" t="n">
-        <v>0.605</v>
+        <v>0.6217</v>
       </c>
       <c r="M448" t="n">
-        <v>0.3218</v>
+        <v>0.3307</v>
       </c>
       <c r="N448" t="n">
         <v>0.9492</v>
@@ -37234,25 +37234,25 @@
         <v>0.5667</v>
       </c>
       <c r="Q448" t="n">
-        <v>3.1011</v>
+        <v>3.187</v>
       </c>
       <c r="R448" t="n">
-        <v>1.8788</v>
+        <v>1.9307</v>
       </c>
       <c r="S448" t="n">
-        <v>0.7724</v>
+        <v>0.7937</v>
       </c>
       <c r="T448" t="n">
-        <v>5.7523</v>
+        <v>5.9114</v>
       </c>
       <c r="U448" t="n">
-        <v>8.061</v>
+        <v>8.404</v>
       </c>
       <c r="V448" t="n">
-        <v>2.79</v>
+        <v>2.909</v>
       </c>
       <c r="W448" t="n">
-        <v>14.667</v>
+        <v>15.147</v>
       </c>
     </row>
     <row r="449">
@@ -37278,28 +37278,28 @@
         <v>1</v>
       </c>
       <c r="F449" t="n">
-        <v>2.865</v>
+        <v>2.863</v>
       </c>
       <c r="G449" t="n">
         <v>0.971</v>
       </c>
       <c r="H449" t="n">
-        <v>2.781</v>
+        <v>2.779</v>
       </c>
       <c r="I449" t="n">
-        <v>2.781</v>
+        <v>2.779</v>
       </c>
       <c r="J449" t="n">
-        <v>1.8624</v>
+        <v>1.8737</v>
       </c>
       <c r="K449" t="n">
-        <v>1.0145</v>
+        <v>1.0206</v>
       </c>
       <c r="L449" t="n">
-        <v>0.5535</v>
+        <v>0.5569</v>
       </c>
       <c r="M449" t="n">
-        <v>0.2944</v>
+        <v>0.2962</v>
       </c>
       <c r="N449" t="n">
         <v>0.9414</v>
@@ -37311,25 +37311,25 @@
         <v>0.7455000000000001</v>
       </c>
       <c r="Q449" t="n">
-        <v>2.8057</v>
+        <v>2.8226</v>
       </c>
       <c r="R449" t="n">
-        <v>1.4485</v>
+        <v>1.4574</v>
       </c>
       <c r="S449" t="n">
-        <v>1.0225</v>
+        <v>1.0287</v>
       </c>
       <c r="T449" t="n">
-        <v>5.2767</v>
+        <v>5.3087</v>
       </c>
       <c r="U449" t="n">
-        <v>8.058</v>
+        <v>8.087999999999999</v>
       </c>
       <c r="V449" t="n">
-        <v>2.789</v>
+        <v>2.8</v>
       </c>
       <c r="W449" t="n">
-        <v>14.646</v>
+        <v>14.689</v>
       </c>
     </row>
     <row r="450">
@@ -37355,28 +37355,28 @@
         <v>1</v>
       </c>
       <c r="F450" t="n">
-        <v>2.941</v>
+        <v>2.959</v>
       </c>
       <c r="G450" t="n">
         <v>0.971</v>
       </c>
       <c r="H450" t="n">
-        <v>2.856</v>
+        <v>2.872</v>
       </c>
       <c r="I450" t="n">
-        <v>2.856</v>
+        <v>2.872</v>
       </c>
       <c r="J450" t="n">
-        <v>1.8653</v>
+        <v>1.8766</v>
       </c>
       <c r="K450" t="n">
-        <v>1.016</v>
+        <v>1.0222</v>
       </c>
       <c r="L450" t="n">
-        <v>0.5544</v>
+        <v>0.5577</v>
       </c>
       <c r="M450" t="n">
-        <v>0.2949</v>
+        <v>0.2967</v>
       </c>
       <c r="N450" t="n">
         <v>0.9414</v>
@@ -37388,25 +37388,25 @@
         <v>0.7455000000000001</v>
       </c>
       <c r="Q450" t="n">
-        <v>2.8098</v>
+        <v>2.827</v>
       </c>
       <c r="R450" t="n">
-        <v>1.4509</v>
+        <v>1.4595</v>
       </c>
       <c r="S450" t="n">
-        <v>1.0242</v>
+        <v>1.0304</v>
       </c>
       <c r="T450" t="n">
-        <v>5.2849</v>
+        <v>5.3169</v>
       </c>
       <c r="U450" t="n">
-        <v>8.141</v>
+        <v>8.189</v>
       </c>
       <c r="V450" t="n">
-        <v>2.818</v>
+        <v>2.835</v>
       </c>
       <c r="W450" t="n">
-        <v>14.761</v>
+        <v>14.827</v>
       </c>
     </row>
     <row r="451">
@@ -37432,28 +37432,28 @@
         <v>-1</v>
       </c>
       <c r="F451" t="n">
-        <v>3.058</v>
+        <v>3.204</v>
       </c>
       <c r="G451" t="n">
         <v>0.971</v>
       </c>
       <c r="H451" t="n">
-        <v>2.969</v>
+        <v>3.111</v>
       </c>
       <c r="I451" t="n">
-        <v>2.969</v>
+        <v>3.111</v>
       </c>
       <c r="J451" t="n">
-        <v>1.835</v>
+        <v>1.8498</v>
       </c>
       <c r="K451" t="n">
-        <v>0.9995000000000001</v>
+        <v>1.0076</v>
       </c>
       <c r="L451" t="n">
-        <v>0.5453</v>
+        <v>0.5498</v>
       </c>
       <c r="M451" t="n">
-        <v>0.2901</v>
+        <v>0.2925</v>
       </c>
       <c r="N451" t="n">
         <v>0.9414</v>
@@ -37465,25 +37465,25 @@
         <v>0.7455000000000001</v>
       </c>
       <c r="Q451" t="n">
-        <v>2.7642</v>
+        <v>2.7866</v>
       </c>
       <c r="R451" t="n">
-        <v>1.4271</v>
+        <v>1.4388</v>
       </c>
       <c r="S451" t="n">
-        <v>1.0075</v>
+        <v>1.0159</v>
       </c>
       <c r="T451" t="n">
-        <v>5.1988</v>
+        <v>5.2413</v>
       </c>
       <c r="U451" t="n">
-        <v>8.167999999999999</v>
+        <v>8.352</v>
       </c>
       <c r="V451" t="n">
-        <v>2.827</v>
+        <v>2.891</v>
       </c>
       <c r="W451" t="n">
-        <v>14.79</v>
+        <v>15.044</v>
       </c>
     </row>
     <row r="452">
@@ -37509,28 +37509,28 @@
         <v>-1</v>
       </c>
       <c r="F452" t="n">
-        <v>3.114</v>
+        <v>3.199</v>
       </c>
       <c r="G452" t="n">
         <v>0.971</v>
       </c>
       <c r="H452" t="n">
-        <v>3.024</v>
+        <v>3.106</v>
       </c>
       <c r="I452" t="n">
-        <v>3.024</v>
+        <v>3.106</v>
       </c>
       <c r="J452" t="n">
-        <v>1.8531</v>
+        <v>1.8737</v>
       </c>
       <c r="K452" t="n">
-        <v>1.0094</v>
+        <v>1.0206</v>
       </c>
       <c r="L452" t="n">
-        <v>0.5507</v>
+        <v>0.5569</v>
       </c>
       <c r="M452" t="n">
-        <v>0.293</v>
+        <v>0.2962</v>
       </c>
       <c r="N452" t="n">
         <v>0.9414</v>
@@ -37542,25 +37542,25 @@
         <v>0.7455000000000001</v>
       </c>
       <c r="Q452" t="n">
-        <v>2.7916</v>
+        <v>2.8226</v>
       </c>
       <c r="R452" t="n">
-        <v>1.4412</v>
+        <v>1.4574</v>
       </c>
       <c r="S452" t="n">
-        <v>1.0176</v>
+        <v>1.0287</v>
       </c>
       <c r="T452" t="n">
-        <v>5.2504</v>
+        <v>5.3087</v>
       </c>
       <c r="U452" t="n">
-        <v>8.273999999999999</v>
+        <v>8.414999999999999</v>
       </c>
       <c r="V452" t="n">
-        <v>2.864</v>
+        <v>2.913</v>
       </c>
       <c r="W452" t="n">
-        <v>14.939</v>
+        <v>15.133</v>
       </c>
     </row>
     <row r="453">
@@ -37586,28 +37586,28 @@
         <v>1</v>
       </c>
       <c r="F453" t="n">
-        <v>2.995</v>
+        <v>3.014</v>
       </c>
       <c r="G453" t="n">
         <v>0.971</v>
       </c>
       <c r="H453" t="n">
-        <v>2.907</v>
+        <v>2.926</v>
       </c>
       <c r="I453" t="n">
-        <v>2.907</v>
+        <v>2.926</v>
       </c>
       <c r="J453" t="n">
-        <v>1.8551</v>
+        <v>1.8663</v>
       </c>
       <c r="K453" t="n">
-        <v>1.0105</v>
+        <v>1.0166</v>
       </c>
       <c r="L453" t="n">
-        <v>0.5513</v>
+        <v>0.5547</v>
       </c>
       <c r="M453" t="n">
-        <v>0.2933</v>
+        <v>0.2951</v>
       </c>
       <c r="N453" t="n">
         <v>0.9414</v>
@@ -37619,25 +37619,25 @@
         <v>0.7455000000000001</v>
       </c>
       <c r="Q453" t="n">
-        <v>2.7946</v>
+        <v>2.8115</v>
       </c>
       <c r="R453" t="n">
-        <v>1.4428</v>
+        <v>1.4516</v>
       </c>
       <c r="S453" t="n">
-        <v>1.0186</v>
+        <v>1.0249</v>
       </c>
       <c r="T453" t="n">
-        <v>5.256</v>
+        <v>5.288</v>
       </c>
       <c r="U453" t="n">
-        <v>8.163</v>
+        <v>8.214</v>
       </c>
       <c r="V453" t="n">
-        <v>2.826</v>
+        <v>2.843</v>
       </c>
       <c r="W453" t="n">
-        <v>14.787</v>
+        <v>14.86</v>
       </c>
     </row>
     <row r="454">
@@ -37663,28 +37663,28 @@
         <v>-1</v>
       </c>
       <c r="F454" t="n">
-        <v>2.673</v>
+        <v>2.749</v>
       </c>
       <c r="G454" t="n">
         <v>0.971</v>
       </c>
       <c r="H454" t="n">
-        <v>2.595</v>
+        <v>2.669</v>
       </c>
       <c r="I454" t="n">
-        <v>2.595</v>
+        <v>2.669</v>
       </c>
       <c r="J454" t="n">
-        <v>1.847</v>
+        <v>1.8736</v>
       </c>
       <c r="K454" t="n">
-        <v>1.006</v>
+        <v>1.0205</v>
       </c>
       <c r="L454" t="n">
-        <v>0.5489000000000001</v>
+        <v>0.5568</v>
       </c>
       <c r="M454" t="n">
-        <v>0.292</v>
+        <v>0.2962</v>
       </c>
       <c r="N454" t="n">
         <v>0.9414</v>
@@ -37696,25 +37696,25 @@
         <v>0.7455000000000001</v>
       </c>
       <c r="Q454" t="n">
-        <v>2.7822</v>
+        <v>2.8223</v>
       </c>
       <c r="R454" t="n">
-        <v>1.4365</v>
+        <v>1.4571</v>
       </c>
       <c r="S454" t="n">
-        <v>1.0141</v>
+        <v>1.0287</v>
       </c>
       <c r="T454" t="n">
-        <v>5.2328</v>
+        <v>5.3081</v>
       </c>
       <c r="U454" t="n">
-        <v>7.828</v>
+        <v>7.977</v>
       </c>
       <c r="V454" t="n">
-        <v>2.71</v>
+        <v>2.761</v>
       </c>
       <c r="W454" t="n">
-        <v>14.327</v>
+        <v>14.538</v>
       </c>
     </row>
     <row r="455">
@@ -37740,28 +37740,28 @@
         <v>-1</v>
       </c>
       <c r="F455" t="n">
-        <v>3.538</v>
+        <v>3.396</v>
       </c>
       <c r="G455" t="n">
         <v>0.971</v>
       </c>
       <c r="H455" t="n">
-        <v>3.435</v>
+        <v>3.297</v>
       </c>
       <c r="I455" t="n">
-        <v>3.435</v>
+        <v>3.297</v>
       </c>
       <c r="J455" t="n">
-        <v>1.8272</v>
+        <v>1.8319</v>
       </c>
       <c r="K455" t="n">
-        <v>0.9953</v>
+        <v>0.9979</v>
       </c>
       <c r="L455" t="n">
-        <v>0.543</v>
+        <v>0.5445</v>
       </c>
       <c r="M455" t="n">
-        <v>0.2889</v>
+        <v>0.2896</v>
       </c>
       <c r="N455" t="n">
         <v>0.9414</v>
@@ -37773,25 +37773,25 @@
         <v>0.7455000000000001</v>
       </c>
       <c r="Q455" t="n">
-        <v>2.7526</v>
+        <v>2.7598</v>
       </c>
       <c r="R455" t="n">
-        <v>1.421</v>
+        <v>1.425</v>
       </c>
       <c r="S455" t="n">
-        <v>1.0033</v>
+        <v>1.0058</v>
       </c>
       <c r="T455" t="n">
-        <v>5.177</v>
+        <v>5.1905</v>
       </c>
       <c r="U455" t="n">
-        <v>8.612</v>
+        <v>8.488</v>
       </c>
       <c r="V455" t="n">
-        <v>2.981</v>
+        <v>2.938</v>
       </c>
       <c r="W455" t="n">
-        <v>15.384</v>
+        <v>15.22</v>
       </c>
     </row>
     <row r="456">
@@ -37817,28 +37817,28 @@
         <v>1</v>
       </c>
       <c r="F456" t="n">
-        <v>3.216</v>
+        <v>3.056</v>
       </c>
       <c r="G456" t="n">
         <v>0.971</v>
       </c>
       <c r="H456" t="n">
-        <v>3.123</v>
+        <v>2.967</v>
       </c>
       <c r="I456" t="n">
-        <v>3.123</v>
+        <v>2.967</v>
       </c>
       <c r="J456" t="n">
-        <v>1.8365</v>
+        <v>1.8401</v>
       </c>
       <c r="K456" t="n">
-        <v>1.0003</v>
+        <v>1.0023</v>
       </c>
       <c r="L456" t="n">
-        <v>0.5458</v>
+        <v>0.5469000000000001</v>
       </c>
       <c r="M456" t="n">
-        <v>0.2903</v>
+        <v>0.2909</v>
       </c>
       <c r="N456" t="n">
         <v>0.9414</v>
@@ -37850,25 +37850,25 @@
         <v>0.7455000000000001</v>
       </c>
       <c r="Q456" t="n">
-        <v>2.7664</v>
+        <v>2.772</v>
       </c>
       <c r="R456" t="n">
-        <v>1.4284</v>
+        <v>1.4312</v>
       </c>
       <c r="S456" t="n">
-        <v>1.0082</v>
+        <v>1.0103</v>
       </c>
       <c r="T456" t="n">
-        <v>5.203</v>
+        <v>5.2135</v>
       </c>
       <c r="U456" t="n">
-        <v>8.326000000000001</v>
+        <v>8.18</v>
       </c>
       <c r="V456" t="n">
-        <v>2.882</v>
+        <v>2.831</v>
       </c>
       <c r="W456" t="n">
-        <v>15.005</v>
+        <v>14.809</v>
       </c>
     </row>
     <row r="457">
@@ -37894,28 +37894,28 @@
         <v>1</v>
       </c>
       <c r="F457" t="n">
-        <v>3.019</v>
+        <v>3.001</v>
       </c>
       <c r="G457" t="n">
         <v>0.971</v>
       </c>
       <c r="H457" t="n">
-        <v>2.931</v>
+        <v>2.913</v>
       </c>
       <c r="I457" t="n">
-        <v>2.931</v>
+        <v>2.913</v>
       </c>
       <c r="J457" t="n">
-        <v>1.8626</v>
+        <v>1.8688</v>
       </c>
       <c r="K457" t="n">
-        <v>1.0146</v>
+        <v>1.0179</v>
       </c>
       <c r="L457" t="n">
-        <v>0.5536</v>
+        <v>0.5554</v>
       </c>
       <c r="M457" t="n">
-        <v>0.2945</v>
+        <v>0.2955</v>
       </c>
       <c r="N457" t="n">
         <v>0.9414</v>
@@ -37927,16 +37927,16 @@
         <v>0.7455000000000001</v>
       </c>
       <c r="Q457" t="n">
-        <v>2.806</v>
+        <v>2.8151</v>
       </c>
       <c r="R457" t="n">
-        <v>1.4488</v>
+        <v>1.4535</v>
       </c>
       <c r="S457" t="n">
-        <v>1.0228</v>
+        <v>1.0263</v>
       </c>
       <c r="T457" t="n">
-        <v>5.2775</v>
+        <v>5.2949</v>
       </c>
       <c r="U457" t="n">
         <v>8.208</v>
@@ -37971,28 +37971,28 @@
         <v>-1</v>
       </c>
       <c r="F458" t="n">
-        <v>2.679</v>
+        <v>3.091</v>
       </c>
       <c r="G458" t="n">
         <v>0.971</v>
       </c>
       <c r="H458" t="n">
-        <v>2.601</v>
+        <v>3.001</v>
       </c>
       <c r="I458" t="n">
-        <v>2.601</v>
+        <v>3.001</v>
       </c>
       <c r="J458" t="n">
-        <v>1.8501</v>
+        <v>1.8756</v>
       </c>
       <c r="K458" t="n">
-        <v>1.0078</v>
+        <v>1.0216</v>
       </c>
       <c r="L458" t="n">
-        <v>0.5499000000000001</v>
+        <v>0.5574</v>
       </c>
       <c r="M458" t="n">
-        <v>0.2925</v>
+        <v>0.2965</v>
       </c>
       <c r="N458" t="n">
         <v>0.9414</v>
@@ -38004,25 +38004,25 @@
         <v>0.7455000000000001</v>
       </c>
       <c r="Q458" t="n">
-        <v>2.7872</v>
+        <v>2.8253</v>
       </c>
       <c r="R458" t="n">
-        <v>1.4391</v>
+        <v>1.4587</v>
       </c>
       <c r="S458" t="n">
-        <v>1.0159</v>
+        <v>1.0297</v>
       </c>
       <c r="T458" t="n">
-        <v>5.2421</v>
+        <v>5.3138</v>
       </c>
       <c r="U458" t="n">
-        <v>7.843</v>
+        <v>8.315</v>
       </c>
       <c r="V458" t="n">
-        <v>2.715</v>
+        <v>2.878</v>
       </c>
       <c r="W458" t="n">
-        <v>14.35</v>
+        <v>14.999</v>
       </c>
     </row>
     <row r="459">
@@ -38048,28 +38048,28 @@
         <v>-1</v>
       </c>
       <c r="F459" t="n">
-        <v>3.011</v>
+        <v>3.141</v>
       </c>
       <c r="G459" t="n">
         <v>0.971</v>
       </c>
       <c r="H459" t="n">
-        <v>2.923</v>
+        <v>3.05</v>
       </c>
       <c r="I459" t="n">
-        <v>2.923</v>
+        <v>3.05</v>
       </c>
       <c r="J459" t="n">
-        <v>1.8387</v>
+        <v>1.8507</v>
       </c>
       <c r="K459" t="n">
-        <v>1.0016</v>
+        <v>1.0081</v>
       </c>
       <c r="L459" t="n">
-        <v>0.5465</v>
+        <v>0.55</v>
       </c>
       <c r="M459" t="n">
-        <v>0.2907</v>
+        <v>0.2926</v>
       </c>
       <c r="N459" t="n">
         <v>0.9414</v>
@@ -38081,25 +38081,25 @@
         <v>0.7455000000000001</v>
       </c>
       <c r="Q459" t="n">
-        <v>2.77</v>
+        <v>2.788</v>
       </c>
       <c r="R459" t="n">
-        <v>1.4302</v>
+        <v>1.4394</v>
       </c>
       <c r="S459" t="n">
-        <v>1.0096</v>
+        <v>1.0162</v>
       </c>
       <c r="T459" t="n">
-        <v>5.2098</v>
+        <v>5.2436</v>
       </c>
       <c r="U459" t="n">
-        <v>8.132999999999999</v>
+        <v>8.294</v>
       </c>
       <c r="V459" t="n">
-        <v>2.815</v>
+        <v>2.871</v>
       </c>
       <c r="W459" t="n">
-        <v>14.744</v>
+        <v>14.965</v>
       </c>
     </row>
     <row r="460">
@@ -38125,28 +38125,28 @@
         <v>1</v>
       </c>
       <c r="F460" t="n">
-        <v>3.035</v>
+        <v>3.102</v>
       </c>
       <c r="G460" t="n">
         <v>0.971</v>
       </c>
       <c r="H460" t="n">
-        <v>2.947</v>
+        <v>3.012</v>
       </c>
       <c r="I460" t="n">
-        <v>2.947</v>
+        <v>3.012</v>
       </c>
       <c r="J460" t="n">
-        <v>1.8468</v>
+        <v>1.8406</v>
       </c>
       <c r="K460" t="n">
-        <v>1.006</v>
+        <v>1.0026</v>
       </c>
       <c r="L460" t="n">
-        <v>0.5489000000000001</v>
+        <v>0.547</v>
       </c>
       <c r="M460" t="n">
-        <v>0.292</v>
+        <v>0.291</v>
       </c>
       <c r="N460" t="n">
         <v>0.9414</v>
@@ -38158,25 +38158,25 @@
         <v>0.7455000000000001</v>
       </c>
       <c r="Q460" t="n">
-        <v>2.7822</v>
+        <v>2.7728</v>
       </c>
       <c r="R460" t="n">
-        <v>1.4365</v>
+        <v>1.4315</v>
       </c>
       <c r="S460" t="n">
-        <v>1.0141</v>
+        <v>1.0106</v>
       </c>
       <c r="T460" t="n">
-        <v>5.2328</v>
+        <v>5.2149</v>
       </c>
       <c r="U460" t="n">
-        <v>8.18</v>
+        <v>8.227</v>
       </c>
       <c r="V460" t="n">
-        <v>2.831</v>
+        <v>2.848</v>
       </c>
       <c r="W460" t="n">
-        <v>14.81</v>
+        <v>14.872</v>
       </c>
     </row>
     <row r="461">
@@ -38202,28 +38202,28 @@
         <v>-1</v>
       </c>
       <c r="F461" t="n">
-        <v>2.659</v>
+        <v>3.057</v>
       </c>
       <c r="G461" t="n">
         <v>0.971</v>
       </c>
       <c r="H461" t="n">
-        <v>2.582</v>
+        <v>2.968</v>
       </c>
       <c r="I461" t="n">
-        <v>2.582</v>
+        <v>2.968</v>
       </c>
       <c r="J461" t="n">
-        <v>1.8314</v>
+        <v>1.8567</v>
       </c>
       <c r="K461" t="n">
-        <v>0.9976</v>
+        <v>1.0113</v>
       </c>
       <c r="L461" t="n">
-        <v>0.5443</v>
+        <v>0.5518</v>
       </c>
       <c r="M461" t="n">
-        <v>0.2896</v>
+        <v>0.2935</v>
       </c>
       <c r="N461" t="n">
         <v>0.9414</v>
@@ -38235,25 +38235,25 @@
         <v>0.7455000000000001</v>
       </c>
       <c r="Q461" t="n">
-        <v>2.759</v>
+        <v>2.7969</v>
       </c>
       <c r="R461" t="n">
-        <v>1.4244</v>
+        <v>1.4441</v>
       </c>
       <c r="S461" t="n">
-        <v>1.0058</v>
+        <v>1.0193</v>
       </c>
       <c r="T461" t="n">
-        <v>5.1892</v>
+        <v>5.2602</v>
       </c>
       <c r="U461" t="n">
-        <v>7.771</v>
+        <v>8.228</v>
       </c>
       <c r="V461" t="n">
-        <v>2.69</v>
+        <v>2.848</v>
       </c>
       <c r="W461" t="n">
-        <v>14.248</v>
+        <v>14.877</v>
       </c>
     </row>
     <row r="462">
@@ -38279,28 +38279,28 @@
         <v>-1</v>
       </c>
       <c r="F462" t="n">
-        <v>3.229</v>
+        <v>3.151</v>
       </c>
       <c r="G462" t="n">
         <v>0.971</v>
       </c>
       <c r="H462" t="n">
-        <v>3.135</v>
+        <v>3.059</v>
       </c>
       <c r="I462" t="n">
-        <v>3.135</v>
+        <v>3.059</v>
       </c>
       <c r="J462" t="n">
-        <v>1.8356</v>
+        <v>1.8404</v>
       </c>
       <c r="K462" t="n">
-        <v>0.9999</v>
+        <v>1.0025</v>
       </c>
       <c r="L462" t="n">
-        <v>0.5455</v>
+        <v>0.547</v>
       </c>
       <c r="M462" t="n">
-        <v>0.2902</v>
+        <v>0.291</v>
       </c>
       <c r="N462" t="n">
         <v>0.9414</v>
@@ -38312,25 +38312,25 @@
         <v>0.7455000000000001</v>
       </c>
       <c r="Q462" t="n">
-        <v>2.7653</v>
+        <v>2.7725</v>
       </c>
       <c r="R462" t="n">
-        <v>1.4276</v>
+        <v>1.4315</v>
       </c>
       <c r="S462" t="n">
-        <v>1.0079</v>
+        <v>1.0106</v>
       </c>
       <c r="T462" t="n">
-        <v>5.2008</v>
+        <v>5.2147</v>
       </c>
       <c r="U462" t="n">
-        <v>8.336</v>
+        <v>8.273999999999999</v>
       </c>
       <c r="V462" t="n">
-        <v>2.885</v>
+        <v>2.864</v>
       </c>
       <c r="W462" t="n">
-        <v>15.018</v>
+        <v>14.935</v>
       </c>
     </row>
     <row r="463">
@@ -38356,28 +38356,28 @@
         <v>1</v>
       </c>
       <c r="F463" t="n">
-        <v>3.63</v>
+        <v>3.348</v>
       </c>
       <c r="G463" t="n">
         <v>0.971</v>
       </c>
       <c r="H463" t="n">
-        <v>3.524</v>
+        <v>3.251</v>
       </c>
       <c r="I463" t="n">
-        <v>3.524</v>
+        <v>3.251</v>
       </c>
       <c r="J463" t="n">
-        <v>1.835</v>
+        <v>1.8386</v>
       </c>
       <c r="K463" t="n">
-        <v>0.9995000000000001</v>
+        <v>1.0015</v>
       </c>
       <c r="L463" t="n">
-        <v>0.5454</v>
+        <v>0.5464</v>
       </c>
       <c r="M463" t="n">
-        <v>0.2901</v>
+        <v>0.2907</v>
       </c>
       <c r="N463" t="n">
         <v>0.9414</v>
@@ -38389,25 +38389,25 @@
         <v>0.7455000000000001</v>
       </c>
       <c r="Q463" t="n">
-        <v>2.7642</v>
+        <v>2.7697</v>
       </c>
       <c r="R463" t="n">
-        <v>1.4273</v>
+        <v>1.4299</v>
       </c>
       <c r="S463" t="n">
-        <v>1.0075</v>
+        <v>1.0096</v>
       </c>
       <c r="T463" t="n">
-        <v>5.199</v>
+        <v>5.2093</v>
       </c>
       <c r="U463" t="n">
-        <v>8.723000000000001</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="V463" t="n">
-        <v>3.03</v>
+        <v>2.928</v>
       </c>
       <c r="W463" t="n">
-        <v>15.534</v>
+        <v>15.186</v>
       </c>
     </row>
     <row r="464">
@@ -38895,28 +38895,28 @@
         <v>-1</v>
       </c>
       <c r="F470" t="n">
-        <v>2.883</v>
+        <v>3.187</v>
       </c>
       <c r="G470" t="n">
         <v>0.956</v>
       </c>
       <c r="H470" t="n">
-        <v>2.758</v>
+        <v>3.048</v>
       </c>
       <c r="I470" t="n">
-        <v>2.758</v>
+        <v>3.048</v>
       </c>
       <c r="J470" t="n">
-        <v>1.8693</v>
+        <v>1.9214</v>
       </c>
       <c r="K470" t="n">
-        <v>1.0182</v>
+        <v>1.0466</v>
       </c>
       <c r="L470" t="n">
-        <v>0.5556</v>
+        <v>0.571</v>
       </c>
       <c r="M470" t="n">
-        <v>0.2955</v>
+        <v>0.3038</v>
       </c>
       <c r="N470" t="n">
         <v>0.9543</v>
@@ -38928,25 +38928,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q470" t="n">
-        <v>2.8685</v>
+        <v>2.9485</v>
       </c>
       <c r="R470" t="n">
-        <v>1.6612</v>
+        <v>1.7073</v>
       </c>
       <c r="S470" t="n">
-        <v>0.9206</v>
+        <v>0.9465</v>
       </c>
       <c r="T470" t="n">
-        <v>5.4503</v>
+        <v>5.6022</v>
       </c>
       <c r="U470" t="n">
-        <v>8.208</v>
+        <v>8.65</v>
       </c>
       <c r="V470" t="n">
-        <v>2.841</v>
+        <v>2.994</v>
       </c>
       <c r="W470" t="n">
-        <v>14.915</v>
+        <v>15.524</v>
       </c>
     </row>
     <row r="471">
@@ -40666,28 +40666,28 @@
         <v>1</v>
       </c>
       <c r="F493" t="n">
-        <v>2.347</v>
+        <v>2.644</v>
       </c>
       <c r="G493" t="n">
         <v>0.978</v>
       </c>
       <c r="H493" t="n">
-        <v>2.295</v>
+        <v>2.586</v>
       </c>
       <c r="I493" t="n">
-        <v>2.295</v>
+        <v>2.586</v>
       </c>
       <c r="J493" t="n">
-        <v>1.9466</v>
+        <v>2.0391</v>
       </c>
       <c r="K493" t="n">
-        <v>1.0603</v>
+        <v>1.1107</v>
       </c>
       <c r="L493" t="n">
-        <v>0.5785</v>
+        <v>0.606</v>
       </c>
       <c r="M493" t="n">
-        <v>0.3078</v>
+        <v>0.3224</v>
       </c>
       <c r="N493" t="n">
         <v>0.9497</v>
@@ -40699,25 +40699,25 @@
         <v>0.617</v>
       </c>
       <c r="Q493" t="n">
-        <v>2.9676</v>
+        <v>3.1086</v>
       </c>
       <c r="R493" t="n">
-        <v>1.8266</v>
+        <v>1.9134</v>
       </c>
       <c r="S493" t="n">
-        <v>0.8317</v>
+        <v>0.8711</v>
       </c>
       <c r="T493" t="n">
-        <v>5.6259</v>
+        <v>5.8932</v>
       </c>
       <c r="U493" t="n">
-        <v>7.921</v>
+        <v>8.478999999999999</v>
       </c>
       <c r="V493" t="n">
-        <v>2.742</v>
+        <v>2.935</v>
       </c>
       <c r="W493" t="n">
-        <v>14.524</v>
+        <v>15.309</v>
       </c>
     </row>
     <row r="494">
@@ -41282,28 +41282,28 @@
         <v>-1</v>
       </c>
       <c r="F501" t="n">
-        <v>1.96</v>
+        <v>2.255</v>
       </c>
       <c r="G501" t="n">
         <v>1</v>
       </c>
       <c r="H501" t="n">
-        <v>1.96</v>
+        <v>2.255</v>
       </c>
       <c r="I501" t="n">
-        <v>1.96</v>
+        <v>2.255</v>
       </c>
       <c r="J501" t="n">
-        <v>1.9636</v>
+        <v>1.9832</v>
       </c>
       <c r="K501" t="n">
-        <v>1.0696</v>
+        <v>1.0802</v>
       </c>
       <c r="L501" t="n">
-        <v>0.5836</v>
+        <v>0.5894</v>
       </c>
       <c r="M501" t="n">
-        <v>0.3104</v>
+        <v>0.3135</v>
       </c>
       <c r="N501" t="n">
         <v>0.9543</v>
@@ -41315,25 +41315,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q501" t="n">
-        <v>3.0133</v>
+        <v>3.0431</v>
       </c>
       <c r="R501" t="n">
-        <v>1.745</v>
+        <v>1.7623</v>
       </c>
       <c r="S501" t="n">
-        <v>0.967</v>
+        <v>0.9767</v>
       </c>
       <c r="T501" t="n">
-        <v>5.7253</v>
+        <v>5.7821</v>
       </c>
       <c r="U501" t="n">
-        <v>7.685</v>
+        <v>8.037000000000001</v>
       </c>
       <c r="V501" t="n">
-        <v>2.66</v>
+        <v>2.782</v>
       </c>
       <c r="W501" t="n">
-        <v>14.23</v>
+        <v>14.731</v>
       </c>
     </row>
     <row r="502">
@@ -41359,28 +41359,28 @@
         <v>1</v>
       </c>
       <c r="F502" t="n">
-        <v>2.264</v>
+        <v>2.372</v>
       </c>
       <c r="G502" t="n">
         <v>1</v>
       </c>
       <c r="H502" t="n">
-        <v>2.264</v>
+        <v>2.372</v>
       </c>
       <c r="I502" t="n">
-        <v>2.264</v>
+        <v>2.372</v>
       </c>
       <c r="J502" t="n">
-        <v>1.9329</v>
+        <v>1.9833</v>
       </c>
       <c r="K502" t="n">
-        <v>1.0529</v>
+        <v>1.0803</v>
       </c>
       <c r="L502" t="n">
-        <v>0.5745</v>
+        <v>0.5894</v>
       </c>
       <c r="M502" t="n">
-        <v>0.3056</v>
+        <v>0.3136</v>
       </c>
       <c r="N502" t="n">
         <v>0.9543</v>
@@ -41392,25 +41392,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q502" t="n">
-        <v>2.9662</v>
+        <v>3.0434</v>
       </c>
       <c r="R502" t="n">
-        <v>1.7178</v>
+        <v>1.7623</v>
       </c>
       <c r="S502" t="n">
-        <v>0.9520999999999999</v>
+        <v>0.977</v>
       </c>
       <c r="T502" t="n">
-        <v>5.6361</v>
+        <v>5.7827</v>
       </c>
       <c r="U502" t="n">
-        <v>7.9</v>
+        <v>8.154999999999999</v>
       </c>
       <c r="V502" t="n">
-        <v>2.734</v>
+        <v>2.823</v>
       </c>
       <c r="W502" t="n">
-        <v>14.537</v>
+        <v>14.898</v>
       </c>
     </row>
     <row r="503">
@@ -41821,28 +41821,28 @@
         <v>1</v>
       </c>
       <c r="F508" t="n">
-        <v>2.287</v>
+        <v>2.372</v>
       </c>
       <c r="G508" t="n">
         <v>1</v>
       </c>
       <c r="H508" t="n">
-        <v>2.287</v>
+        <v>2.372</v>
       </c>
       <c r="I508" t="n">
-        <v>2.287</v>
+        <v>2.372</v>
       </c>
       <c r="J508" t="n">
-        <v>1.9595</v>
+        <v>1.9833</v>
       </c>
       <c r="K508" t="n">
-        <v>1.0673</v>
+        <v>1.0803</v>
       </c>
       <c r="L508" t="n">
-        <v>0.5824</v>
+        <v>0.5894</v>
       </c>
       <c r="M508" t="n">
-        <v>0.3098</v>
+        <v>0.3136</v>
       </c>
       <c r="N508" t="n">
         <v>0.9543</v>
@@ -41854,25 +41854,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q508" t="n">
-        <v>3.0068</v>
+        <v>3.0434</v>
       </c>
       <c r="R508" t="n">
-        <v>1.7414</v>
+        <v>1.7623</v>
       </c>
       <c r="S508" t="n">
-        <v>0.9651999999999999</v>
+        <v>0.977</v>
       </c>
       <c r="T508" t="n">
-        <v>5.7133</v>
+        <v>5.7827</v>
       </c>
       <c r="U508" t="n">
-        <v>8</v>
+        <v>8.154999999999999</v>
       </c>
       <c r="V508" t="n">
-        <v>2.769</v>
+        <v>2.823</v>
       </c>
       <c r="W508" t="n">
-        <v>14.679</v>
+        <v>14.898</v>
       </c>
     </row>
     <row r="509">

--- a/projections/kicker_2026_combined.xlsx
+++ b/projections/kicker_2026_combined.xlsx
@@ -583,10 +583,10 @@
         <v>0.7955</v>
       </c>
       <c r="Q2" t="n">
-        <v>79.73</v>
+        <v>79.79000000000001</v>
       </c>
       <c r="R2" t="n">
-        <v>148.76</v>
+        <v>148.81</v>
       </c>
       <c r="S2" t="n">
         <v>139.18</v>
@@ -600,46 +600,46 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Jake Bates</t>
+          <t>Harrison Mevis</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>39.55</v>
+        <v>37.28</v>
       </c>
       <c r="E3" t="n">
-        <v>37.94</v>
+        <v>37.28</v>
       </c>
       <c r="F3" t="n">
-        <v>37.94</v>
+        <v>37.28</v>
       </c>
       <c r="G3" t="n">
-        <v>24.96</v>
+        <v>25.11</v>
       </c>
       <c r="H3" t="n">
-        <v>13.59</v>
+        <v>13.68</v>
       </c>
       <c r="I3" t="n">
-        <v>7.42</v>
+        <v>7.46</v>
       </c>
       <c r="J3" t="n">
-        <v>3.95</v>
+        <v>3.97</v>
       </c>
       <c r="K3" t="n">
-        <v>72.76000000000001</v>
+        <v>73.22</v>
       </c>
       <c r="L3" t="n">
-        <v>110.7</v>
+        <v>110.5</v>
       </c>
       <c r="M3" t="n">
-        <v>0.959</v>
+        <v>1</v>
       </c>
       <c r="N3" t="n">
         <v>0.9543</v>
@@ -651,16 +651,16 @@
         <v>0.6859</v>
       </c>
       <c r="Q3" t="n">
-        <v>77.76000000000001</v>
+        <v>77.28</v>
       </c>
       <c r="R3" t="n">
-        <v>143.62</v>
+        <v>143.73</v>
       </c>
       <c r="S3" t="n">
-        <v>110.88</v>
+        <v>113.94</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.18</v>
+        <v>-3.44</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
@@ -668,67 +668,67 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Harrison Mevis</t>
+          <t>Evan McPherson</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>37.28</v>
+        <v>35.83</v>
       </c>
       <c r="E4" t="n">
-        <v>37.28</v>
+        <v>34.16</v>
       </c>
       <c r="F4" t="n">
-        <v>37.28</v>
+        <v>34.16</v>
       </c>
       <c r="G4" t="n">
-        <v>25.11</v>
+        <v>25.49</v>
       </c>
       <c r="H4" t="n">
-        <v>13.68</v>
+        <v>13.89</v>
       </c>
       <c r="I4" t="n">
-        <v>7.46</v>
+        <v>7.58</v>
       </c>
       <c r="J4" t="n">
-        <v>3.97</v>
+        <v>4.03</v>
       </c>
       <c r="K4" t="n">
-        <v>73.22</v>
+        <v>75.66</v>
       </c>
       <c r="L4" t="n">
-        <v>110.5</v>
+        <v>109.81</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>0.953</v>
       </c>
       <c r="N4" t="n">
-        <v>0.9543</v>
+        <v>0.9818</v>
       </c>
       <c r="O4" t="n">
-        <v>0.798</v>
+        <v>0.8</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6859</v>
+        <v>0.6744</v>
       </c>
       <c r="Q4" t="n">
-        <v>77.28</v>
+        <v>76.7</v>
       </c>
       <c r="R4" t="n">
-        <v>143.73</v>
+        <v>142.91</v>
       </c>
       <c r="S4" t="n">
-        <v>113.94</v>
+        <v>113.18</v>
       </c>
       <c r="T4" t="n">
-        <v>-3.44</v>
+        <v>-3.37</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
@@ -736,67 +736,67 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Evan McPherson</t>
+          <t>Jake Bates</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>13</v>
       </c>
       <c r="D5" t="n">
-        <v>35.93</v>
+        <v>38.12</v>
       </c>
       <c r="E5" t="n">
-        <v>34.26</v>
+        <v>36.57</v>
       </c>
       <c r="F5" t="n">
-        <v>34.26</v>
+        <v>36.57</v>
       </c>
       <c r="G5" t="n">
-        <v>25.54</v>
+        <v>24.9</v>
       </c>
       <c r="H5" t="n">
-        <v>13.91</v>
+        <v>13.56</v>
       </c>
       <c r="I5" t="n">
-        <v>7.59</v>
+        <v>7.4</v>
       </c>
       <c r="J5" t="n">
-        <v>4.04</v>
+        <v>3.94</v>
       </c>
       <c r="K5" t="n">
-        <v>75.8</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>110.05</v>
+        <v>109.17</v>
       </c>
       <c r="M5" t="n">
-        <v>0.953</v>
+        <v>0.959</v>
       </c>
       <c r="N5" t="n">
-        <v>0.9818</v>
+        <v>0.9543</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8</v>
+        <v>0.798</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6744</v>
+        <v>0.6859</v>
       </c>
       <c r="Q5" t="n">
-        <v>76.90000000000001</v>
+        <v>76.48999999999999</v>
       </c>
       <c r="R5" t="n">
-        <v>143.25</v>
+        <v>141.81</v>
       </c>
       <c r="S5" t="n">
-        <v>113.18</v>
+        <v>110.88</v>
       </c>
       <c r="T5" t="n">
-        <v>-3.13</v>
+        <v>-1.71</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
@@ -816,31 +816,31 @@
         <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>25.2</v>
+        <v>25.07</v>
       </c>
       <c r="E6" t="n">
-        <v>24.42</v>
+        <v>24.3</v>
       </c>
       <c r="F6" t="n">
-        <v>24.42</v>
+        <v>24.3</v>
       </c>
       <c r="G6" t="n">
-        <v>26.13</v>
+        <v>26.06</v>
       </c>
       <c r="H6" t="n">
-        <v>14.23</v>
+        <v>14.19</v>
       </c>
       <c r="I6" t="n">
-        <v>7.76</v>
+        <v>7.74</v>
       </c>
       <c r="J6" t="n">
-        <v>4.13</v>
+        <v>4.12</v>
       </c>
       <c r="K6" t="n">
-        <v>83.91</v>
+        <v>83.69</v>
       </c>
       <c r="L6" t="n">
-        <v>108.33</v>
+        <v>107.99</v>
       </c>
       <c r="M6" t="n">
         <v>0.969</v>
@@ -855,16 +855,16 @@
         <v>0.6859</v>
       </c>
       <c r="Q6" t="n">
-        <v>74.39</v>
+        <v>74.12</v>
       </c>
       <c r="R6" t="n">
-        <v>142.27</v>
+        <v>141.89</v>
       </c>
       <c r="S6" t="n">
         <v>130</v>
       </c>
       <c r="T6" t="n">
-        <v>-21.67</v>
+        <v>-22.01</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
@@ -884,31 +884,31 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>36.68</v>
+        <v>36.74</v>
       </c>
       <c r="E7" t="n">
-        <v>36.21</v>
+        <v>36.27</v>
       </c>
       <c r="F7" t="n">
-        <v>36.21</v>
+        <v>36.27</v>
       </c>
       <c r="G7" t="n">
-        <v>24.5</v>
+        <v>24.53</v>
       </c>
       <c r="H7" t="n">
-        <v>13.34</v>
+        <v>13.36</v>
       </c>
       <c r="I7" t="n">
-        <v>7.28</v>
+        <v>7.29</v>
       </c>
       <c r="J7" t="n">
-        <v>3.87</v>
+        <v>3.88</v>
       </c>
       <c r="K7" t="n">
-        <v>71.43000000000001</v>
+        <v>71.52</v>
       </c>
       <c r="L7" t="n">
-        <v>107.64</v>
+        <v>107.78</v>
       </c>
       <c r="M7" t="n">
         <v>0.987</v>
@@ -923,16 +923,16 @@
         <v>0.6859</v>
       </c>
       <c r="Q7" t="n">
-        <v>74.98</v>
+        <v>75.14</v>
       </c>
       <c r="R7" t="n">
-        <v>140.33</v>
+        <v>140.45</v>
       </c>
       <c r="S7" t="n">
         <v>113.18</v>
       </c>
       <c r="T7" t="n">
-        <v>-5.54</v>
+        <v>-5.4</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
@@ -940,67 +940,67 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ka'imi Fairbairn</t>
+          <t>Tyler Bass</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>13</v>
       </c>
       <c r="D8" t="n">
-        <v>31.44</v>
+        <v>40.71</v>
       </c>
       <c r="E8" t="n">
-        <v>29.36</v>
+        <v>39.53</v>
       </c>
       <c r="F8" t="n">
-        <v>29.36</v>
+        <v>39.53</v>
       </c>
       <c r="G8" t="n">
-        <v>25.78</v>
+        <v>24.05</v>
       </c>
       <c r="H8" t="n">
-        <v>14.04</v>
+        <v>13.1</v>
       </c>
       <c r="I8" t="n">
-        <v>7.66</v>
+        <v>7.15</v>
       </c>
       <c r="J8" t="n">
-        <v>4.08</v>
+        <v>3.8</v>
       </c>
       <c r="K8" t="n">
-        <v>78.2</v>
+        <v>68.14</v>
       </c>
       <c r="L8" t="n">
-        <v>107.56</v>
+        <v>107.67</v>
       </c>
       <c r="M8" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.971</v>
       </c>
       <c r="N8" t="n">
-        <v>0.9597</v>
+        <v>0.9414</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8356</v>
+        <v>0.7234</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7391</v>
+        <v>0.7455000000000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>74.72</v>
+        <v>75.56999999999999</v>
       </c>
       <c r="R8" t="n">
-        <v>140.36</v>
+        <v>139.75</v>
       </c>
       <c r="S8" t="n">
-        <v>120.06</v>
+        <v>107.82</v>
       </c>
       <c r="T8" t="n">
-        <v>-12.5</v>
+        <v>-0.15</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
@@ -1008,67 +1008,67 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tyler Bass</t>
+          <t>Ka'imi Fairbairn</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>13</v>
       </c>
       <c r="D9" t="n">
-        <v>40.74</v>
+        <v>30.95</v>
       </c>
       <c r="E9" t="n">
-        <v>39.56</v>
+        <v>28.9</v>
       </c>
       <c r="F9" t="n">
-        <v>39.56</v>
+        <v>28.9</v>
       </c>
       <c r="G9" t="n">
-        <v>23.97</v>
+        <v>25.72</v>
       </c>
       <c r="H9" t="n">
-        <v>13.06</v>
+        <v>14.01</v>
       </c>
       <c r="I9" t="n">
-        <v>7.12</v>
+        <v>7.64</v>
       </c>
       <c r="J9" t="n">
-        <v>3.79</v>
+        <v>4.07</v>
       </c>
       <c r="K9" t="n">
-        <v>67.91</v>
+        <v>78.02</v>
       </c>
       <c r="L9" t="n">
-        <v>107.47</v>
+        <v>106.93</v>
       </c>
       <c r="M9" t="n">
-        <v>0.971</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>0.9414</v>
+        <v>0.9597</v>
       </c>
       <c r="O9" t="n">
-        <v>0.7234</v>
+        <v>0.8356</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7455000000000001</v>
+        <v>0.7391</v>
       </c>
       <c r="Q9" t="n">
-        <v>75.39</v>
+        <v>74.20999999999999</v>
       </c>
       <c r="R9" t="n">
-        <v>139.49</v>
+        <v>139.63</v>
       </c>
       <c r="S9" t="n">
-        <v>107.82</v>
+        <v>120.06</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.35</v>
+        <v>-13.13</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
@@ -1076,67 +1076,67 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Chris Boswell</t>
+          <t>Tyler Loop</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>13</v>
       </c>
       <c r="D10" t="n">
-        <v>30.12</v>
+        <v>36.86</v>
       </c>
       <c r="E10" t="n">
-        <v>28.81</v>
+        <v>35.25</v>
       </c>
       <c r="F10" t="n">
-        <v>28.81</v>
+        <v>35.25</v>
       </c>
       <c r="G10" t="n">
-        <v>25.87</v>
+        <v>24.49</v>
       </c>
       <c r="H10" t="n">
-        <v>14.09</v>
+        <v>13.34</v>
       </c>
       <c r="I10" t="n">
-        <v>7.69</v>
+        <v>7.28</v>
       </c>
       <c r="J10" t="n">
-        <v>4.09</v>
+        <v>3.87</v>
       </c>
       <c r="K10" t="n">
-        <v>78.58</v>
+        <v>71.42</v>
       </c>
       <c r="L10" t="n">
-        <v>107.4</v>
+        <v>106.67</v>
       </c>
       <c r="M10" t="n">
-        <v>0.957</v>
+        <v>0.956</v>
       </c>
       <c r="N10" t="n">
-        <v>0.9458</v>
+        <v>0.9543</v>
       </c>
       <c r="O10" t="n">
-        <v>0.8036</v>
+        <v>0.798</v>
       </c>
       <c r="P10" t="n">
-        <v>0.8254</v>
+        <v>0.6859</v>
       </c>
       <c r="Q10" t="n">
-        <v>74.34999999999999</v>
+        <v>74.43000000000001</v>
       </c>
       <c r="R10" t="n">
-        <v>140.43</v>
+        <v>138.92</v>
       </c>
       <c r="S10" t="n">
-        <v>107.06</v>
+        <v>111.65</v>
       </c>
       <c r="T10" t="n">
-        <v>0.34</v>
+        <v>-4.98</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
@@ -1144,64 +1144,64 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Andy Borregales</t>
+          <t>Harrison Butker</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>13</v>
       </c>
       <c r="D11" t="n">
-        <v>34.79</v>
+        <v>31.07</v>
       </c>
       <c r="E11" t="n">
-        <v>33.52</v>
+        <v>29.17</v>
       </c>
       <c r="F11" t="n">
-        <v>33.52</v>
+        <v>29.17</v>
       </c>
       <c r="G11" t="n">
-        <v>25.33</v>
+        <v>25.67</v>
       </c>
       <c r="H11" t="n">
-        <v>13.8</v>
+        <v>13.98</v>
       </c>
       <c r="I11" t="n">
-        <v>7.53</v>
+        <v>7.63</v>
       </c>
       <c r="J11" t="n">
-        <v>4.01</v>
+        <v>4.06</v>
       </c>
       <c r="K11" t="n">
-        <v>73.86</v>
+        <v>77.45999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>107.39</v>
+        <v>106.62</v>
       </c>
       <c r="M11" t="n">
-        <v>0.964</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>0.9543</v>
+        <v>0.963</v>
       </c>
       <c r="O11" t="n">
-        <v>0.798</v>
+        <v>0.8696</v>
       </c>
       <c r="P11" t="n">
-        <v>0.6859</v>
+        <v>0.6604</v>
       </c>
       <c r="Q11" t="n">
-        <v>74.67</v>
+        <v>73.97</v>
       </c>
       <c r="R11" t="n">
-        <v>140.07</v>
+        <v>139.32</v>
       </c>
       <c r="S11" t="n">
-        <v>111.65</v>
+        <v>110.88</v>
       </c>
       <c r="T11" t="n">
         <v>-4.26</v>
@@ -1212,31 +1212,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Daniel Carlson</t>
+          <t>Chris Boswell</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>13</v>
       </c>
       <c r="D12" t="n">
-        <v>33.63</v>
+        <v>29.39</v>
       </c>
       <c r="E12" t="n">
-        <v>31.99</v>
+        <v>28.12</v>
       </c>
       <c r="F12" t="n">
-        <v>31.99</v>
+        <v>28.12</v>
       </c>
       <c r="G12" t="n">
-        <v>25.81</v>
+        <v>25.82</v>
       </c>
       <c r="H12" t="n">
-        <v>14.06</v>
+        <v>14.07</v>
       </c>
       <c r="I12" t="n">
         <v>7.67</v>
@@ -1245,34 +1245,34 @@
         <v>4.08</v>
       </c>
       <c r="K12" t="n">
-        <v>75.26000000000001</v>
+        <v>78.45</v>
       </c>
       <c r="L12" t="n">
-        <v>107.24</v>
+        <v>106.57</v>
       </c>
       <c r="M12" t="n">
-        <v>0.951</v>
+        <v>0.957</v>
       </c>
       <c r="N12" t="n">
-        <v>0.9543</v>
+        <v>0.9458</v>
       </c>
       <c r="O12" t="n">
-        <v>0.798</v>
+        <v>0.8036</v>
       </c>
       <c r="P12" t="n">
-        <v>0.6859</v>
+        <v>0.8254</v>
       </c>
       <c r="Q12" t="n">
-        <v>74.81</v>
+        <v>73.69</v>
       </c>
       <c r="R12" t="n">
-        <v>139.68</v>
+        <v>139.48</v>
       </c>
       <c r="S12" t="n">
         <v>107.06</v>
       </c>
       <c r="T12" t="n">
-        <v>0.18</v>
+        <v>-0.49</v>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
@@ -1280,67 +1280,67 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cairo Santos</t>
+          <t>Andy Borregales</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>13</v>
       </c>
       <c r="D13" t="n">
-        <v>35.7</v>
+        <v>34.04</v>
       </c>
       <c r="E13" t="n">
-        <v>34.12</v>
+        <v>32.8</v>
       </c>
       <c r="F13" t="n">
-        <v>34.12</v>
+        <v>32.8</v>
       </c>
       <c r="G13" t="n">
-        <v>25.41</v>
+        <v>25.25</v>
       </c>
       <c r="H13" t="n">
-        <v>13.84</v>
+        <v>13.75</v>
       </c>
       <c r="I13" t="n">
-        <v>7.55</v>
+        <v>7.5</v>
       </c>
       <c r="J13" t="n">
-        <v>4.02</v>
+        <v>3.99</v>
       </c>
       <c r="K13" t="n">
-        <v>72.77</v>
+        <v>73.62</v>
       </c>
       <c r="L13" t="n">
-        <v>106.89</v>
+        <v>106.42</v>
       </c>
       <c r="M13" t="n">
-        <v>0.956</v>
+        <v>0.964</v>
       </c>
       <c r="N13" t="n">
-        <v>0.9515</v>
+        <v>0.9543</v>
       </c>
       <c r="O13" t="n">
-        <v>0.7835</v>
+        <v>0.798</v>
       </c>
       <c r="P13" t="n">
-        <v>0.66</v>
+        <v>0.6859</v>
       </c>
       <c r="Q13" t="n">
-        <v>74.75</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="R13" t="n">
-        <v>139.04</v>
+        <v>138.92</v>
       </c>
       <c r="S13" t="n">
-        <v>114.71</v>
+        <v>111.65</v>
       </c>
       <c r="T13" t="n">
-        <v>-7.82</v>
+        <v>-5.23</v>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
@@ -1348,67 +1348,67 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tyler Loop</t>
+          <t>Cairo Santos</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>13</v>
       </c>
       <c r="D14" t="n">
-        <v>36.9</v>
+        <v>35.34</v>
       </c>
       <c r="E14" t="n">
-        <v>35.3</v>
+        <v>33.78</v>
       </c>
       <c r="F14" t="n">
-        <v>35.3</v>
+        <v>33.78</v>
       </c>
       <c r="G14" t="n">
-        <v>24.5</v>
+        <v>25.31</v>
       </c>
       <c r="H14" t="n">
-        <v>13.34</v>
+        <v>13.79</v>
       </c>
       <c r="I14" t="n">
-        <v>7.28</v>
+        <v>7.52</v>
       </c>
       <c r="J14" t="n">
-        <v>3.87</v>
+        <v>4</v>
       </c>
       <c r="K14" t="n">
-        <v>71.42</v>
+        <v>72.47</v>
       </c>
       <c r="L14" t="n">
-        <v>106.72</v>
+        <v>106.26</v>
       </c>
       <c r="M14" t="n">
         <v>0.956</v>
       </c>
       <c r="N14" t="n">
-        <v>0.9543</v>
+        <v>0.9515</v>
       </c>
       <c r="O14" t="n">
-        <v>0.798</v>
+        <v>0.7835</v>
       </c>
       <c r="P14" t="n">
-        <v>0.6859</v>
+        <v>0.66</v>
       </c>
       <c r="Q14" t="n">
-        <v>74.42</v>
+        <v>74.19</v>
       </c>
       <c r="R14" t="n">
-        <v>138.97</v>
+        <v>138.33</v>
       </c>
       <c r="S14" t="n">
-        <v>111.65</v>
+        <v>114.71</v>
       </c>
       <c r="T14" t="n">
-        <v>-4.93</v>
+        <v>-8.449999999999999</v>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
@@ -1416,67 +1416,67 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Harrison Butker</t>
+          <t>Chase McLaughlin</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>13</v>
       </c>
       <c r="D15" t="n">
-        <v>31.1</v>
+        <v>30.58</v>
       </c>
       <c r="E15" t="n">
-        <v>29.2</v>
+        <v>29.86</v>
       </c>
       <c r="F15" t="n">
-        <v>29.2</v>
+        <v>29.86</v>
       </c>
       <c r="G15" t="n">
-        <v>25.67</v>
+        <v>26.6</v>
       </c>
       <c r="H15" t="n">
-        <v>13.98</v>
+        <v>14.49</v>
       </c>
       <c r="I15" t="n">
-        <v>7.63</v>
+        <v>7.91</v>
       </c>
       <c r="J15" t="n">
-        <v>4.06</v>
+        <v>4.21</v>
       </c>
       <c r="K15" t="n">
-        <v>77.45</v>
+        <v>76.15000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>106.65</v>
+        <v>106.01</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.976</v>
       </c>
       <c r="N15" t="n">
-        <v>0.963</v>
+        <v>0.9655</v>
       </c>
       <c r="O15" t="n">
-        <v>0.8696</v>
+        <v>0.6458</v>
       </c>
       <c r="P15" t="n">
-        <v>0.6604</v>
+        <v>0.8431</v>
       </c>
       <c r="Q15" t="n">
-        <v>73.97</v>
+        <v>73.7</v>
       </c>
       <c r="R15" t="n">
-        <v>139.32</v>
+        <v>138.31</v>
       </c>
       <c r="S15" t="n">
-        <v>110.88</v>
+        <v>107.82</v>
       </c>
       <c r="T15" t="n">
-        <v>-4.23</v>
+        <v>-1.81</v>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
@@ -1496,31 +1496,31 @@
         <v>13</v>
       </c>
       <c r="D16" t="n">
-        <v>36.21</v>
+        <v>36.03</v>
       </c>
       <c r="E16" t="n">
-        <v>33.11</v>
+        <v>32.95</v>
       </c>
       <c r="F16" t="n">
-        <v>33.11</v>
+        <v>32.95</v>
       </c>
       <c r="G16" t="n">
-        <v>24.48</v>
+        <v>24.52</v>
       </c>
       <c r="H16" t="n">
-        <v>13.33</v>
+        <v>13.36</v>
       </c>
       <c r="I16" t="n">
-        <v>7.27</v>
+        <v>7.29</v>
       </c>
       <c r="J16" t="n">
-        <v>3.87</v>
+        <v>3.88</v>
       </c>
       <c r="K16" t="n">
-        <v>72.81</v>
+        <v>72.94</v>
       </c>
       <c r="L16" t="n">
-        <v>105.92</v>
+        <v>105.89</v>
       </c>
       <c r="M16" t="n">
         <v>0.915</v>
@@ -1535,16 +1535,16 @@
         <v>0.6859</v>
       </c>
       <c r="Q16" t="n">
-        <v>73.64</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="R16" t="n">
-        <v>138.17</v>
+        <v>138.12</v>
       </c>
       <c r="S16" t="n">
         <v>114.71</v>
       </c>
       <c r="T16" t="n">
-        <v>-8.789999999999999</v>
+        <v>-8.82</v>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
@@ -1552,67 +1552,67 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Chase McLaughlin</t>
+          <t>Wil Lutz</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>13</v>
       </c>
       <c r="D17" t="n">
-        <v>30.55</v>
+        <v>31.56</v>
       </c>
       <c r="E17" t="n">
-        <v>29.83</v>
+        <v>30.87</v>
       </c>
       <c r="F17" t="n">
-        <v>29.83</v>
+        <v>30.87</v>
       </c>
       <c r="G17" t="n">
-        <v>26.57</v>
+        <v>25.75</v>
       </c>
       <c r="H17" t="n">
-        <v>14.47</v>
+        <v>14.03</v>
       </c>
       <c r="I17" t="n">
-        <v>7.9</v>
+        <v>7.65</v>
       </c>
       <c r="J17" t="n">
-        <v>4.2</v>
+        <v>4.07</v>
       </c>
       <c r="K17" t="n">
-        <v>76.08</v>
+        <v>74.43000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>105.91</v>
+        <v>105.3</v>
       </c>
       <c r="M17" t="n">
-        <v>0.976</v>
+        <v>0.978</v>
       </c>
       <c r="N17" t="n">
-        <v>0.9655</v>
+        <v>0.9497</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6458</v>
+        <v>0.8315</v>
       </c>
       <c r="P17" t="n">
-        <v>0.8431</v>
+        <v>0.617</v>
       </c>
       <c r="Q17" t="n">
-        <v>73.79000000000001</v>
+        <v>73.08</v>
       </c>
       <c r="R17" t="n">
-        <v>138.03</v>
+        <v>137.5</v>
       </c>
       <c r="S17" t="n">
-        <v>107.82</v>
+        <v>113.18</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.91</v>
+        <v>-7.88</v>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
@@ -1620,67 +1620,67 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Wil Lutz</t>
+          <t>Nick Folk</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>13</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56</v>
+        <v>33.8</v>
       </c>
       <c r="E18" t="n">
-        <v>30.87</v>
+        <v>32.22</v>
       </c>
       <c r="F18" t="n">
-        <v>30.87</v>
+        <v>32.22</v>
       </c>
       <c r="G18" t="n">
-        <v>25.75</v>
+        <v>25.72</v>
       </c>
       <c r="H18" t="n">
-        <v>14.03</v>
+        <v>14.01</v>
       </c>
       <c r="I18" t="n">
-        <v>7.65</v>
+        <v>7.64</v>
       </c>
       <c r="J18" t="n">
         <v>4.07</v>
       </c>
       <c r="K18" t="n">
-        <v>74.43000000000001</v>
+        <v>72.34999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>105.3</v>
+        <v>104.56</v>
       </c>
       <c r="M18" t="n">
-        <v>0.978</v>
+        <v>0.953</v>
       </c>
       <c r="N18" t="n">
-        <v>0.9497</v>
+        <v>0.9333</v>
       </c>
       <c r="O18" t="n">
-        <v>0.8315</v>
+        <v>0.7593</v>
       </c>
       <c r="P18" t="n">
-        <v>0.617</v>
+        <v>0.6859</v>
       </c>
       <c r="Q18" t="n">
-        <v>73.08</v>
+        <v>72.92</v>
       </c>
       <c r="R18" t="n">
-        <v>137.5</v>
+        <v>136.2</v>
       </c>
       <c r="S18" t="n">
-        <v>113.18</v>
+        <v>103.24</v>
       </c>
       <c r="T18" t="n">
-        <v>-7.88</v>
+        <v>1.32</v>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
@@ -1756,49 +1756,49 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Spencer Shrader</t>
+          <t>Daniel Carlson</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>13</v>
       </c>
       <c r="D20" t="n">
-        <v>31.69</v>
+        <v>30.47</v>
       </c>
       <c r="E20" t="n">
-        <v>31.04</v>
+        <v>28.98</v>
       </c>
       <c r="F20" t="n">
-        <v>31.04</v>
+        <v>28.98</v>
       </c>
       <c r="G20" t="n">
-        <v>26.04</v>
+        <v>25.78</v>
       </c>
       <c r="H20" t="n">
-        <v>14.19</v>
+        <v>14.04</v>
       </c>
       <c r="I20" t="n">
-        <v>7.74</v>
+        <v>7.66</v>
       </c>
       <c r="J20" t="n">
-        <v>4.12</v>
+        <v>4.08</v>
       </c>
       <c r="K20" t="n">
-        <v>73.27</v>
+        <v>75.18000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>104.31</v>
+        <v>104.16</v>
       </c>
       <c r="M20" t="n">
-        <v>0.98</v>
+        <v>0.951</v>
       </c>
       <c r="N20" t="n">
-        <v>0.9074</v>
+        <v>0.9543</v>
       </c>
       <c r="O20" t="n">
         <v>0.798</v>
@@ -1807,16 +1807,16 @@
         <v>0.6859</v>
       </c>
       <c r="Q20" t="n">
-        <v>72.72</v>
+        <v>72.11</v>
       </c>
       <c r="R20" t="n">
-        <v>135.9</v>
+        <v>136.22</v>
       </c>
       <c r="S20" t="n">
-        <v>100.18</v>
+        <v>107.06</v>
       </c>
       <c r="T20" t="n">
-        <v>4.13</v>
+        <v>-2.9</v>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr"/>
@@ -1836,7 +1836,7 @@
         <v>13</v>
       </c>
       <c r="D21" t="n">
-        <v>30.74</v>
+        <v>30.73</v>
       </c>
       <c r="E21" t="n">
         <v>29.23</v>
@@ -1845,22 +1845,22 @@
         <v>29.23</v>
       </c>
       <c r="G21" t="n">
-        <v>25.64</v>
+        <v>25.68</v>
       </c>
       <c r="H21" t="n">
-        <v>13.96</v>
+        <v>13.99</v>
       </c>
       <c r="I21" t="n">
-        <v>7.62</v>
+        <v>7.63</v>
       </c>
       <c r="J21" t="n">
-        <v>4.05</v>
+        <v>4.06</v>
       </c>
       <c r="K21" t="n">
-        <v>74.75</v>
+        <v>74.88</v>
       </c>
       <c r="L21" t="n">
-        <v>103.98</v>
+        <v>104.11</v>
       </c>
       <c r="M21" t="n">
         <v>0.951</v>
@@ -1875,16 +1875,16 @@
         <v>0.6859</v>
       </c>
       <c r="Q21" t="n">
-        <v>72.03</v>
+        <v>72.16</v>
       </c>
       <c r="R21" t="n">
-        <v>135.89</v>
+        <v>136.03</v>
       </c>
       <c r="S21" t="n">
         <v>104</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.02</v>
+        <v>0.11</v>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr"/>
@@ -1892,67 +1892,67 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Trey Smack</t>
+          <t>Spencer Shrader</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>13</v>
       </c>
       <c r="D22" t="n">
-        <v>31.56</v>
+        <v>31.1</v>
       </c>
       <c r="E22" t="n">
-        <v>30.74</v>
+        <v>30.46</v>
       </c>
       <c r="F22" t="n">
-        <v>30.74</v>
+        <v>30.46</v>
       </c>
       <c r="G22" t="n">
-        <v>25.56</v>
+        <v>25.85</v>
       </c>
       <c r="H22" t="n">
-        <v>13.92</v>
+        <v>14.08</v>
       </c>
       <c r="I22" t="n">
-        <v>7.6</v>
+        <v>7.68</v>
       </c>
       <c r="J22" t="n">
-        <v>4.04</v>
+        <v>4.09</v>
       </c>
       <c r="K22" t="n">
-        <v>72.23</v>
+        <v>72.73999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>102.97</v>
+        <v>103.2</v>
       </c>
       <c r="M22" t="n">
-        <v>0.974</v>
+        <v>0.98</v>
       </c>
       <c r="N22" t="n">
-        <v>0.9492</v>
+        <v>0.9074</v>
       </c>
       <c r="O22" t="n">
-        <v>0.8211000000000001</v>
+        <v>0.798</v>
       </c>
       <c r="P22" t="n">
-        <v>0.5667</v>
+        <v>0.6859</v>
       </c>
       <c r="Q22" t="n">
-        <v>71.37</v>
+        <v>71.70999999999999</v>
       </c>
       <c r="R22" t="n">
-        <v>134.51</v>
+        <v>134.67</v>
       </c>
       <c r="S22" t="n">
-        <v>111.65</v>
+        <v>100.18</v>
       </c>
       <c r="T22" t="n">
-        <v>-8.68</v>
+        <v>3.02</v>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr"/>
@@ -1960,67 +1960,67 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Will Reichard</t>
+          <t>Trey Smack</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>13</v>
       </c>
       <c r="D23" t="n">
-        <v>28.56</v>
+        <v>31.06</v>
       </c>
       <c r="E23" t="n">
-        <v>28.56</v>
+        <v>30.25</v>
       </c>
       <c r="F23" t="n">
-        <v>28.56</v>
+        <v>30.25</v>
       </c>
       <c r="G23" t="n">
-        <v>25.03</v>
+        <v>25.5</v>
       </c>
       <c r="H23" t="n">
-        <v>13.64</v>
+        <v>13.89</v>
       </c>
       <c r="I23" t="n">
-        <v>7.44</v>
+        <v>7.58</v>
       </c>
       <c r="J23" t="n">
-        <v>3.96</v>
+        <v>4.03</v>
       </c>
       <c r="K23" t="n">
-        <v>72.98999999999999</v>
+        <v>72.06</v>
       </c>
       <c r="L23" t="n">
-        <v>101.55</v>
+        <v>102.31</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>0.974</v>
       </c>
       <c r="N23" t="n">
-        <v>0.9543</v>
+        <v>0.9492</v>
       </c>
       <c r="O23" t="n">
-        <v>0.798</v>
+        <v>0.8211000000000001</v>
       </c>
       <c r="P23" t="n">
-        <v>0.6859</v>
+        <v>0.5667</v>
       </c>
       <c r="Q23" t="n">
-        <v>69.73999999999999</v>
+        <v>70.76000000000001</v>
       </c>
       <c r="R23" t="n">
-        <v>133.41</v>
+        <v>133.87</v>
       </c>
       <c r="S23" t="n">
-        <v>110.88</v>
+        <v>111.65</v>
       </c>
       <c r="T23" t="n">
-        <v>-9.33</v>
+        <v>-9.34</v>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr"/>
@@ -2028,46 +2028,46 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ryan Fitzgerald</t>
+          <t>Will Reichard</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>13</v>
       </c>
       <c r="D24" t="n">
-        <v>33.23</v>
+        <v>28.66</v>
       </c>
       <c r="E24" t="n">
-        <v>29.91</v>
+        <v>28.66</v>
       </c>
       <c r="F24" t="n">
-        <v>29.91</v>
+        <v>28.66</v>
       </c>
       <c r="G24" t="n">
-        <v>24.27</v>
+        <v>25.04</v>
       </c>
       <c r="H24" t="n">
-        <v>13.22</v>
+        <v>13.64</v>
       </c>
       <c r="I24" t="n">
-        <v>7.21</v>
+        <v>7.44</v>
       </c>
       <c r="J24" t="n">
-        <v>3.84</v>
+        <v>3.96</v>
       </c>
       <c r="K24" t="n">
-        <v>70.77</v>
+        <v>73.02</v>
       </c>
       <c r="L24" t="n">
-        <v>100.68</v>
+        <v>101.69</v>
       </c>
       <c r="M24" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="N24" t="n">
         <v>0.9543</v>
@@ -2079,16 +2079,16 @@
         <v>0.6859</v>
       </c>
       <c r="Q24" t="n">
-        <v>69.47</v>
+        <v>69.86</v>
       </c>
       <c r="R24" t="n">
-        <v>131.86</v>
+        <v>133.55</v>
       </c>
       <c r="S24" t="n">
-        <v>105.53</v>
+        <v>110.88</v>
       </c>
       <c r="T24" t="n">
-        <v>-4.85</v>
+        <v>-9.19</v>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr"/>
@@ -2096,67 +2096,67 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Matt Gay</t>
+          <t>Ryan Fitzgerald</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>13</v>
       </c>
       <c r="D25" t="n">
-        <v>26.54</v>
+        <v>32.38</v>
       </c>
       <c r="E25" t="n">
-        <v>25.39</v>
+        <v>29.14</v>
       </c>
       <c r="F25" t="n">
-        <v>25.39</v>
+        <v>29.14</v>
       </c>
       <c r="G25" t="n">
-        <v>25.02</v>
+        <v>24.25</v>
       </c>
       <c r="H25" t="n">
-        <v>13.63</v>
+        <v>13.21</v>
       </c>
       <c r="I25" t="n">
-        <v>7.44</v>
+        <v>7.21</v>
       </c>
       <c r="J25" t="n">
-        <v>3.96</v>
+        <v>3.83</v>
       </c>
       <c r="K25" t="n">
-        <v>73.81999999999999</v>
+        <v>70.72</v>
       </c>
       <c r="L25" t="n">
-        <v>99.20999999999999</v>
+        <v>99.86</v>
       </c>
       <c r="M25" t="n">
-        <v>0.957</v>
+        <v>0.9</v>
       </c>
       <c r="N25" t="n">
-        <v>0.971</v>
+        <v>0.9543</v>
       </c>
       <c r="O25" t="n">
-        <v>0.7714</v>
+        <v>0.798</v>
       </c>
       <c r="P25" t="n">
-        <v>0.7255</v>
+        <v>0.6859</v>
       </c>
       <c r="Q25" t="n">
-        <v>67.86</v>
+        <v>68.84999999999999</v>
       </c>
       <c r="R25" t="n">
-        <v>130.59</v>
+        <v>130.88</v>
       </c>
       <c r="S25" t="n">
-        <v>101.71</v>
+        <v>105.53</v>
       </c>
       <c r="T25" t="n">
-        <v>-2.5</v>
+        <v>-5.67</v>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr"/>
@@ -2164,67 +2164,67 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Drew Stevens</t>
+          <t>Matt Gay</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>13</v>
       </c>
       <c r="D26" t="n">
-        <v>30.17</v>
+        <v>26.54</v>
       </c>
       <c r="E26" t="n">
-        <v>29.35</v>
+        <v>25.39</v>
       </c>
       <c r="F26" t="n">
-        <v>29.35</v>
+        <v>25.39</v>
       </c>
       <c r="G26" t="n">
-        <v>24.71</v>
+        <v>25.02</v>
       </c>
       <c r="H26" t="n">
-        <v>13.46</v>
+        <v>13.63</v>
       </c>
       <c r="I26" t="n">
-        <v>7.34</v>
+        <v>7.44</v>
       </c>
       <c r="J26" t="n">
-        <v>3.91</v>
+        <v>3.96</v>
       </c>
       <c r="K26" t="n">
-        <v>69.70999999999999</v>
+        <v>73.81999999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>99.06</v>
+        <v>99.20999999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>0.973</v>
+        <v>0.957</v>
       </c>
       <c r="N26" t="n">
-        <v>0.9111</v>
+        <v>0.971</v>
       </c>
       <c r="O26" t="n">
-        <v>0.798</v>
+        <v>0.7714</v>
       </c>
       <c r="P26" t="n">
-        <v>0.6859</v>
+        <v>0.7255</v>
       </c>
       <c r="Q26" t="n">
-        <v>68.08</v>
+        <v>67.89</v>
       </c>
       <c r="R26" t="n">
-        <v>129.99</v>
+        <v>130.57</v>
       </c>
       <c r="S26" t="n">
-        <v>102.47</v>
+        <v>101.71</v>
       </c>
       <c r="T26" t="n">
-        <v>-3.41</v>
+        <v>-2.5</v>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr"/>
@@ -2300,67 +2300,67 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Jason Sanders</t>
+          <t>Riley Patterson</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>13</v>
       </c>
       <c r="D28" t="n">
-        <v>28.67</v>
+        <v>24.25</v>
       </c>
       <c r="E28" t="n">
-        <v>27.78</v>
+        <v>23.43</v>
       </c>
       <c r="F28" t="n">
-        <v>27.78</v>
+        <v>23.43</v>
       </c>
       <c r="G28" t="n">
-        <v>24.67</v>
+        <v>24.75</v>
       </c>
       <c r="H28" t="n">
-        <v>13.44</v>
+        <v>13.48</v>
       </c>
       <c r="I28" t="n">
-        <v>7.33</v>
+        <v>7.36</v>
       </c>
       <c r="J28" t="n">
-        <v>3.9</v>
+        <v>3.91</v>
       </c>
       <c r="K28" t="n">
-        <v>70.39</v>
+        <v>74.58</v>
       </c>
       <c r="L28" t="n">
-        <v>98.17</v>
+        <v>98.01000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>0.969</v>
+        <v>0.966</v>
       </c>
       <c r="N28" t="n">
-        <v>0.9412</v>
+        <v>0.9492</v>
       </c>
       <c r="O28" t="n">
-        <v>0.7707000000000001</v>
+        <v>0.871</v>
       </c>
       <c r="P28" t="n">
-        <v>0.6923</v>
+        <v>0.6859</v>
       </c>
       <c r="Q28" t="n">
-        <v>67.23</v>
+        <v>66.45</v>
       </c>
       <c r="R28" t="n">
-        <v>129.11</v>
+        <v>129.57</v>
       </c>
       <c r="S28" t="n">
-        <v>1.53</v>
+        <v>89.47</v>
       </c>
       <c r="T28" t="n">
-        <v>96.64</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr"/>
@@ -2368,67 +2368,67 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Riley Patterson</t>
+          <t>Drew Stevens</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>13</v>
       </c>
       <c r="D29" t="n">
-        <v>24.25</v>
+        <v>29.1</v>
       </c>
       <c r="E29" t="n">
-        <v>23.43</v>
+        <v>28.31</v>
       </c>
       <c r="F29" t="n">
-        <v>23.43</v>
+        <v>28.31</v>
       </c>
       <c r="G29" t="n">
-        <v>24.75</v>
+        <v>24.6</v>
       </c>
       <c r="H29" t="n">
-        <v>13.48</v>
+        <v>13.4</v>
       </c>
       <c r="I29" t="n">
-        <v>7.36</v>
+        <v>7.31</v>
       </c>
       <c r="J29" t="n">
-        <v>3.91</v>
+        <v>3.89</v>
       </c>
       <c r="K29" t="n">
-        <v>74.58</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="L29" t="n">
-        <v>98.01000000000001</v>
+        <v>97.70999999999999</v>
       </c>
       <c r="M29" t="n">
-        <v>0.966</v>
+        <v>0.973</v>
       </c>
       <c r="N29" t="n">
-        <v>0.9492</v>
+        <v>0.9111</v>
       </c>
       <c r="O29" t="n">
-        <v>0.871</v>
+        <v>0.798</v>
       </c>
       <c r="P29" t="n">
         <v>0.6859</v>
       </c>
       <c r="Q29" t="n">
-        <v>66.51000000000001</v>
+        <v>67</v>
       </c>
       <c r="R29" t="n">
-        <v>129.53</v>
+        <v>128.4</v>
       </c>
       <c r="S29" t="n">
-        <v>89.47</v>
+        <v>102.47</v>
       </c>
       <c r="T29" t="n">
-        <v>8.539999999999999</v>
+        <v>-4.76</v>
       </c>
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr"/>
@@ -2436,67 +2436,67 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nick Folk</t>
+          <t>Jason Sanders</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>13</v>
       </c>
       <c r="D30" t="n">
-        <v>27.05</v>
+        <v>28.05</v>
       </c>
       <c r="E30" t="n">
-        <v>25.78</v>
+        <v>27.19</v>
       </c>
       <c r="F30" t="n">
-        <v>25.78</v>
+        <v>27.19</v>
       </c>
       <c r="G30" t="n">
-        <v>25.64</v>
+        <v>24.62</v>
       </c>
       <c r="H30" t="n">
-        <v>13.96</v>
+        <v>13.41</v>
       </c>
       <c r="I30" t="n">
-        <v>7.62</v>
+        <v>7.32</v>
       </c>
       <c r="J30" t="n">
-        <v>4.05</v>
+        <v>3.89</v>
       </c>
       <c r="K30" t="n">
-        <v>72.09999999999999</v>
+        <v>70.23</v>
       </c>
       <c r="L30" t="n">
-        <v>97.89</v>
+        <v>97.42</v>
       </c>
       <c r="M30" t="n">
-        <v>0.953</v>
+        <v>0.969</v>
       </c>
       <c r="N30" t="n">
-        <v>0.9333</v>
+        <v>0.9412</v>
       </c>
       <c r="O30" t="n">
-        <v>0.7593</v>
+        <v>0.7707000000000001</v>
       </c>
       <c r="P30" t="n">
-        <v>0.6859</v>
+        <v>0.6923</v>
       </c>
       <c r="Q30" t="n">
-        <v>67.23999999999999</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="R30" t="n">
-        <v>128.53</v>
+        <v>128.15</v>
       </c>
       <c r="S30" t="n">
-        <v>103.24</v>
+        <v>1.53</v>
       </c>
       <c r="T30" t="n">
-        <v>-5.35</v>
+        <v>95.89</v>
       </c>
       <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr"/>
@@ -2516,19 +2516,19 @@
         <v>13</v>
       </c>
       <c r="D31" t="n">
-        <v>27.89</v>
+        <v>27.86</v>
       </c>
       <c r="E31" t="n">
-        <v>26.52</v>
+        <v>26.49</v>
       </c>
       <c r="F31" t="n">
-        <v>26.52</v>
+        <v>26.49</v>
       </c>
       <c r="G31" t="n">
-        <v>24.29</v>
+        <v>24.28</v>
       </c>
       <c r="H31" t="n">
-        <v>13.23</v>
+        <v>13.22</v>
       </c>
       <c r="I31" t="n">
         <v>7.22</v>
@@ -2537,10 +2537,10 @@
         <v>3.84</v>
       </c>
       <c r="K31" t="n">
-        <v>70.81</v>
+        <v>70.79000000000001</v>
       </c>
       <c r="L31" t="n">
-        <v>97.33</v>
+        <v>97.28</v>
       </c>
       <c r="M31" t="n">
         <v>0.951</v>
@@ -2555,16 +2555,16 @@
         <v>0.6859</v>
       </c>
       <c r="Q31" t="n">
-        <v>66.29000000000001</v>
+        <v>66.26000000000001</v>
       </c>
       <c r="R31" t="n">
-        <v>128.33</v>
+        <v>128.3</v>
       </c>
       <c r="S31" t="n">
         <v>100.18</v>
       </c>
       <c r="T31" t="n">
-        <v>-2.85</v>
+        <v>-2.9</v>
       </c>
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr"/>
@@ -2584,31 +2584,31 @@
         <v>13</v>
       </c>
       <c r="D32" t="n">
-        <v>28.79</v>
+        <v>28.97</v>
       </c>
       <c r="E32" t="n">
-        <v>28.14</v>
+        <v>28.32</v>
       </c>
       <c r="F32" t="n">
-        <v>28.14</v>
+        <v>28.32</v>
       </c>
       <c r="G32" t="n">
-        <v>25.51</v>
+        <v>25.56</v>
       </c>
       <c r="H32" t="n">
-        <v>13.9</v>
+        <v>13.92</v>
       </c>
       <c r="I32" t="n">
-        <v>7.58</v>
+        <v>7.6</v>
       </c>
       <c r="J32" t="n">
-        <v>4.03</v>
+        <v>4.04</v>
       </c>
       <c r="K32" t="n">
-        <v>65.83</v>
+        <v>65.97</v>
       </c>
       <c r="L32" t="n">
-        <v>93.97</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="M32" t="n">
         <v>0.977</v>
@@ -2623,16 +2623,16 @@
         <v>0.6859</v>
       </c>
       <c r="Q32" t="n">
-        <v>64.69</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="R32" t="n">
-        <v>123.22</v>
+        <v>123.65</v>
       </c>
       <c r="S32" t="n">
         <v>102.47</v>
       </c>
       <c r="T32" t="n">
-        <v>-8.5</v>
+        <v>-8.18</v>
       </c>
       <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr"/>
@@ -2691,10 +2691,10 @@
         <v>0.6364</v>
       </c>
       <c r="Q33" t="n">
-        <v>61.18</v>
+        <v>61.09</v>
       </c>
       <c r="R33" t="n">
-        <v>119.27</v>
+        <v>119.3</v>
       </c>
       <c r="S33" t="n">
         <v>102.47</v>
@@ -2936,28 +2936,28 @@
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>2.33</v>
+        <v>2.266</v>
       </c>
       <c r="G3" t="n">
         <v>0.951</v>
       </c>
       <c r="H3" t="n">
-        <v>2.216</v>
+        <v>2.155</v>
       </c>
       <c r="I3" t="n">
-        <v>2.216</v>
+        <v>2.155</v>
       </c>
       <c r="J3" t="n">
-        <v>1.8651</v>
+        <v>1.862</v>
       </c>
       <c r="K3" t="n">
-        <v>1.0159</v>
+        <v>1.0142</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5543</v>
+        <v>0.5534</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2949</v>
+        <v>0.2944</v>
       </c>
       <c r="N3" t="n">
         <v>0.9543</v>
@@ -2969,25 +2969,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.862</v>
+        <v>2.8572</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6574</v>
+        <v>1.6547</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9187</v>
+        <v>0.9172</v>
       </c>
       <c r="T3" t="n">
-        <v>5.4381</v>
+        <v>5.429</v>
       </c>
       <c r="U3" t="n">
-        <v>7.654</v>
+        <v>7.584</v>
       </c>
       <c r="V3" t="n">
-        <v>2.649</v>
+        <v>2.625</v>
       </c>
       <c r="W3" t="n">
-        <v>14.142</v>
+        <v>14.042</v>
       </c>
     </row>
     <row r="4">
@@ -3167,28 +3167,28 @@
         <v>-1</v>
       </c>
       <c r="F6" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
         <v>0.951</v>
       </c>
       <c r="H6" t="n">
-        <v>1.959</v>
+        <v>1.902</v>
       </c>
       <c r="I6" t="n">
-        <v>1.959</v>
+        <v>1.902</v>
       </c>
       <c r="J6" t="n">
-        <v>1.8193</v>
+        <v>1.8551</v>
       </c>
       <c r="K6" t="n">
-        <v>0.991</v>
+        <v>1.0105</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5407</v>
+        <v>0.5513</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2876</v>
+        <v>0.2933</v>
       </c>
       <c r="N6" t="n">
         <v>0.9543</v>
@@ -3200,25 +3200,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.7918</v>
+        <v>2.8468</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6167</v>
+        <v>1.6484</v>
       </c>
       <c r="S6" t="n">
-        <v>0.896</v>
+        <v>0.9137</v>
       </c>
       <c r="T6" t="n">
-        <v>5.3045</v>
+        <v>5.4089</v>
       </c>
       <c r="U6" t="n">
-        <v>7.264</v>
+        <v>7.311</v>
       </c>
       <c r="V6" t="n">
-        <v>2.514</v>
+        <v>2.531</v>
       </c>
       <c r="W6" t="n">
-        <v>13.584</v>
+        <v>13.653</v>
       </c>
     </row>
     <row r="7">
@@ -3475,28 +3475,28 @@
         <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>2.266</v>
+        <v>2.369</v>
       </c>
       <c r="G10" t="n">
         <v>0.951</v>
       </c>
       <c r="H10" t="n">
-        <v>2.155</v>
+        <v>2.253</v>
       </c>
       <c r="I10" t="n">
-        <v>2.155</v>
+        <v>2.253</v>
       </c>
       <c r="J10" t="n">
-        <v>1.8592</v>
+        <v>1.8487</v>
       </c>
       <c r="K10" t="n">
-        <v>1.0127</v>
+        <v>1.007</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5526</v>
+        <v>0.5494</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2939</v>
+        <v>0.2923</v>
       </c>
       <c r="N10" t="n">
         <v>0.9543</v>
@@ -3508,25 +3508,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.853</v>
+        <v>2.8369</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6523</v>
+        <v>1.6427</v>
       </c>
       <c r="S10" t="n">
-        <v>0.9156</v>
+        <v>0.9106</v>
       </c>
       <c r="T10" t="n">
-        <v>5.4209</v>
+        <v>5.3903</v>
       </c>
       <c r="U10" t="n">
-        <v>7.576</v>
+        <v>7.643</v>
       </c>
       <c r="V10" t="n">
-        <v>2.622</v>
+        <v>2.646</v>
       </c>
       <c r="W10" t="n">
-        <v>14.031</v>
+        <v>14.125</v>
       </c>
     </row>
     <row r="11">
@@ -3629,28 +3629,28 @@
         <v>-1</v>
       </c>
       <c r="F12" t="n">
-        <v>2.069</v>
+        <v>2.058</v>
       </c>
       <c r="G12" t="n">
         <v>0.951</v>
       </c>
       <c r="H12" t="n">
-        <v>1.968</v>
+        <v>1.957</v>
       </c>
       <c r="I12" t="n">
-        <v>1.968</v>
+        <v>1.957</v>
       </c>
       <c r="J12" t="n">
-        <v>1.8874</v>
+        <v>1.8581</v>
       </c>
       <c r="K12" t="n">
-        <v>1.0281</v>
+        <v>1.0121</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5609</v>
+        <v>0.5522</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2984</v>
+        <v>0.2938</v>
       </c>
       <c r="N12" t="n">
         <v>0.9543</v>
@@ -3662,25 +3662,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.8964</v>
+        <v>2.8513</v>
       </c>
       <c r="R12" t="n">
-        <v>1.6771</v>
+        <v>1.6511</v>
       </c>
       <c r="S12" t="n">
-        <v>0.9296</v>
+        <v>0.9153</v>
       </c>
       <c r="T12" t="n">
-        <v>5.5031</v>
+        <v>5.4177</v>
       </c>
       <c r="U12" t="n">
-        <v>7.471</v>
+        <v>7.375</v>
       </c>
       <c r="V12" t="n">
-        <v>2.586</v>
+        <v>2.553</v>
       </c>
       <c r="W12" t="n">
-        <v>13.883</v>
+        <v>13.744</v>
       </c>
     </row>
     <row r="13">
@@ -4476,28 +4476,28 @@
         <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>2.971</v>
+        <v>2.224</v>
       </c>
       <c r="G23" t="n">
         <v>0.964</v>
       </c>
       <c r="H23" t="n">
-        <v>2.863</v>
+        <v>2.143</v>
       </c>
       <c r="I23" t="n">
-        <v>2.863</v>
+        <v>2.143</v>
       </c>
       <c r="J23" t="n">
-        <v>1.9905</v>
+        <v>1.9064</v>
       </c>
       <c r="K23" t="n">
-        <v>1.0842</v>
+        <v>1.0384</v>
       </c>
       <c r="L23" t="n">
-        <v>0.5916</v>
+        <v>0.5666</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3147</v>
+        <v>0.3014</v>
       </c>
       <c r="N23" t="n">
         <v>0.9543</v>
@@ -4509,25 +4509,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.0544</v>
+        <v>2.9254</v>
       </c>
       <c r="R23" t="n">
-        <v>1.7689</v>
+        <v>1.6941</v>
       </c>
       <c r="S23" t="n">
-        <v>0.9804</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>5.8037</v>
+        <v>5.5585</v>
       </c>
       <c r="U23" t="n">
-        <v>8.667</v>
+        <v>7.702</v>
       </c>
       <c r="V23" t="n">
-        <v>3</v>
+        <v>2.666</v>
       </c>
       <c r="W23" t="n">
-        <v>15.569</v>
+        <v>14.222</v>
       </c>
     </row>
     <row r="24">
@@ -5939,28 +5939,28 @@
         <v>-1</v>
       </c>
       <c r="F42" t="n">
-        <v>2.708</v>
+        <v>2.631</v>
       </c>
       <c r="G42" t="n">
         <v>0.956</v>
       </c>
       <c r="H42" t="n">
-        <v>2.588</v>
+        <v>2.514</v>
       </c>
       <c r="I42" t="n">
-        <v>2.588</v>
+        <v>2.514</v>
       </c>
       <c r="J42" t="n">
-        <v>1.9707</v>
+        <v>1.9523</v>
       </c>
       <c r="K42" t="n">
-        <v>1.0734</v>
+        <v>1.0634</v>
       </c>
       <c r="L42" t="n">
-        <v>0.5857</v>
+        <v>0.5802</v>
       </c>
       <c r="M42" t="n">
-        <v>0.3116</v>
+        <v>0.3087</v>
       </c>
       <c r="N42" t="n">
         <v>0.9515</v>
@@ -5972,25 +5972,25 @@
         <v>0.66</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.012</v>
+        <v>2.9839</v>
       </c>
       <c r="R42" t="n">
-        <v>1.7088</v>
+        <v>1.6927</v>
       </c>
       <c r="S42" t="n">
-        <v>0.9223</v>
+        <v>0.9137999999999999</v>
       </c>
       <c r="T42" t="n">
-        <v>5.6431</v>
+        <v>5.5904</v>
       </c>
       <c r="U42" t="n">
-        <v>8.231</v>
+        <v>8.103999999999999</v>
       </c>
       <c r="V42" t="n">
-        <v>2.849</v>
+        <v>2.805</v>
       </c>
       <c r="W42" t="n">
-        <v>14.912</v>
+        <v>14.735</v>
       </c>
     </row>
     <row r="43">
@@ -6247,28 +6247,28 @@
         <v>1</v>
       </c>
       <c r="F46" t="n">
-        <v>2.81</v>
+        <v>2.941</v>
       </c>
       <c r="G46" t="n">
         <v>0.956</v>
       </c>
       <c r="H46" t="n">
-        <v>2.686</v>
+        <v>2.811</v>
       </c>
       <c r="I46" t="n">
-        <v>2.686</v>
+        <v>2.811</v>
       </c>
       <c r="J46" t="n">
-        <v>1.9434</v>
+        <v>1.9752</v>
       </c>
       <c r="K46" t="n">
-        <v>1.0586</v>
+        <v>1.0759</v>
       </c>
       <c r="L46" t="n">
-        <v>0.5776</v>
+        <v>0.587</v>
       </c>
       <c r="M46" t="n">
-        <v>0.3073</v>
+        <v>0.3123</v>
       </c>
       <c r="N46" t="n">
         <v>0.9515</v>
@@ -6280,25 +6280,25 @@
         <v>0.66</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.9704</v>
+        <v>3.019</v>
       </c>
       <c r="R46" t="n">
-        <v>1.6851</v>
+        <v>1.7126</v>
       </c>
       <c r="S46" t="n">
-        <v>0.9096</v>
+        <v>0.9244</v>
       </c>
       <c r="T46" t="n">
-        <v>5.5652</v>
+        <v>5.656</v>
       </c>
       <c r="U46" t="n">
-        <v>8.250999999999999</v>
+        <v>8.467000000000001</v>
       </c>
       <c r="V46" t="n">
-        <v>2.856</v>
+        <v>2.931</v>
       </c>
       <c r="W46" t="n">
-        <v>14.937</v>
+        <v>15.237</v>
       </c>
     </row>
     <row r="47">
@@ -6786,28 +6786,28 @@
         <v>-1</v>
       </c>
       <c r="F53" t="n">
-        <v>2.745</v>
+        <v>2.333</v>
       </c>
       <c r="G53" t="n">
         <v>0.956</v>
       </c>
       <c r="H53" t="n">
-        <v>2.624</v>
+        <v>2.23</v>
       </c>
       <c r="I53" t="n">
-        <v>2.624</v>
+        <v>2.23</v>
       </c>
       <c r="J53" t="n">
-        <v>2.0102</v>
+        <v>1.8938</v>
       </c>
       <c r="K53" t="n">
-        <v>1.095</v>
+        <v>1.0316</v>
       </c>
       <c r="L53" t="n">
-        <v>0.5974</v>
+        <v>0.5629</v>
       </c>
       <c r="M53" t="n">
-        <v>0.3178</v>
+        <v>0.2994</v>
       </c>
       <c r="N53" t="n">
         <v>0.9515</v>
@@ -6819,25 +6819,25 @@
         <v>0.66</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.0726</v>
+        <v>2.8947</v>
       </c>
       <c r="R53" t="n">
-        <v>1.7429</v>
+        <v>1.6423</v>
       </c>
       <c r="S53" t="n">
-        <v>0.9407</v>
+        <v>0.8862</v>
       </c>
       <c r="T53" t="n">
-        <v>5.7562</v>
+        <v>5.4232</v>
       </c>
       <c r="U53" t="n">
-        <v>8.380000000000001</v>
+        <v>7.653</v>
       </c>
       <c r="V53" t="n">
-        <v>2.901</v>
+        <v>2.649</v>
       </c>
       <c r="W53" t="n">
-        <v>15.123</v>
+        <v>14.102</v>
       </c>
     </row>
     <row r="54">
@@ -7094,28 +7094,28 @@
         <v>-1</v>
       </c>
       <c r="F57" t="n">
-        <v>2.618</v>
+        <v>2.676</v>
       </c>
       <c r="G57" t="n">
         <v>0.987</v>
       </c>
       <c r="H57" t="n">
-        <v>2.585</v>
+        <v>2.642</v>
       </c>
       <c r="I57" t="n">
-        <v>2.585</v>
+        <v>2.642</v>
       </c>
       <c r="J57" t="n">
-        <v>1.886</v>
+        <v>1.9145</v>
       </c>
       <c r="K57" t="n">
-        <v>1.0273</v>
+        <v>1.0428</v>
       </c>
       <c r="L57" t="n">
-        <v>0.5605</v>
+        <v>0.569</v>
       </c>
       <c r="M57" t="n">
-        <v>0.2982</v>
+        <v>0.3027</v>
       </c>
       <c r="N57" t="n">
         <v>0.9543</v>
@@ -7127,25 +7127,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q57" t="n">
-        <v>2.8941</v>
+        <v>2.9378</v>
       </c>
       <c r="R57" t="n">
-        <v>1.6759</v>
+        <v>1.7013</v>
       </c>
       <c r="S57" t="n">
-        <v>0.929</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="T57" t="n">
-        <v>5.499</v>
+        <v>5.5821</v>
       </c>
       <c r="U57" t="n">
-        <v>8.084</v>
+        <v>8.224</v>
       </c>
       <c r="V57" t="n">
-        <v>2.798</v>
+        <v>2.847</v>
       </c>
       <c r="W57" t="n">
-        <v>14.779</v>
+        <v>14.975</v>
       </c>
     </row>
     <row r="58">
@@ -8172,28 +8172,28 @@
         <v>-1</v>
       </c>
       <c r="F71" t="n">
-        <v>1.985</v>
+        <v>1.864</v>
       </c>
       <c r="G71" t="n">
         <v>0.969</v>
       </c>
       <c r="H71" t="n">
-        <v>1.924</v>
+        <v>1.806</v>
       </c>
       <c r="I71" t="n">
-        <v>1.924</v>
+        <v>1.806</v>
       </c>
       <c r="J71" t="n">
-        <v>2.0684</v>
+        <v>1.9986</v>
       </c>
       <c r="K71" t="n">
-        <v>1.1266</v>
+        <v>1.0887</v>
       </c>
       <c r="L71" t="n">
-        <v>0.6147</v>
+        <v>0.594</v>
       </c>
       <c r="M71" t="n">
-        <v>0.327</v>
+        <v>0.316</v>
       </c>
       <c r="N71" t="n">
         <v>0.9857</v>
@@ -8205,25 +8205,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.3154</v>
+        <v>3.2038</v>
       </c>
       <c r="R71" t="n">
-        <v>2.3088</v>
+        <v>2.2311</v>
       </c>
       <c r="S71" t="n">
-        <v>1.0187</v>
+        <v>0.9845</v>
       </c>
       <c r="T71" t="n">
-        <v>6.6429</v>
+        <v>6.4194</v>
       </c>
       <c r="U71" t="n">
-        <v>8.567</v>
+        <v>8.225</v>
       </c>
       <c r="V71" t="n">
-        <v>2.965</v>
+        <v>2.847</v>
       </c>
       <c r="W71" t="n">
-        <v>15.697</v>
+        <v>15.21</v>
       </c>
     </row>
     <row r="72">
@@ -9635,28 +9635,28 @@
         <v>-1</v>
       </c>
       <c r="F90" t="n">
-        <v>2.084</v>
+        <v>2.269</v>
       </c>
       <c r="G90" t="n">
         <v>0.977</v>
       </c>
       <c r="H90" t="n">
-        <v>2.037</v>
+        <v>2.218</v>
       </c>
       <c r="I90" t="n">
-        <v>2.037</v>
+        <v>2.218</v>
       </c>
       <c r="J90" t="n">
-        <v>1.9215</v>
+        <v>1.9757</v>
       </c>
       <c r="K90" t="n">
-        <v>1.0466</v>
+        <v>1.0762</v>
       </c>
       <c r="L90" t="n">
-        <v>0.5711000000000001</v>
+        <v>0.5872000000000001</v>
       </c>
       <c r="M90" t="n">
-        <v>0.3038</v>
+        <v>0.3124</v>
       </c>
       <c r="N90" t="n">
         <v>0.9268</v>
@@ -9668,25 +9668,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q90" t="n">
-        <v>2.8334</v>
+        <v>2.9135</v>
       </c>
       <c r="R90" t="n">
-        <v>1.179</v>
+        <v>1.2123</v>
       </c>
       <c r="S90" t="n">
-        <v>0.9465</v>
+        <v>0.9733000000000001</v>
       </c>
       <c r="T90" t="n">
-        <v>4.9588</v>
+        <v>5.099</v>
       </c>
       <c r="U90" t="n">
-        <v>6.996</v>
+        <v>7.317</v>
       </c>
       <c r="V90" t="n">
-        <v>2.422</v>
+        <v>2.533</v>
       </c>
       <c r="W90" t="n">
-        <v>12.956</v>
+        <v>13.413</v>
       </c>
     </row>
     <row r="91">
@@ -10097,28 +10097,28 @@
         <v>1</v>
       </c>
       <c r="F96" t="n">
-        <v>2.214</v>
+        <v>2.269</v>
       </c>
       <c r="G96" t="n">
         <v>0.976</v>
       </c>
       <c r="H96" t="n">
-        <v>2.162</v>
+        <v>2.215</v>
       </c>
       <c r="I96" t="n">
-        <v>2.162</v>
+        <v>2.215</v>
       </c>
       <c r="J96" t="n">
-        <v>2.0437</v>
+        <v>2.0459</v>
       </c>
       <c r="K96" t="n">
-        <v>1.1132</v>
+        <v>1.1144</v>
       </c>
       <c r="L96" t="n">
-        <v>0.6074000000000001</v>
+        <v>0.608</v>
       </c>
       <c r="M96" t="n">
-        <v>0.3231</v>
+        <v>0.3235</v>
       </c>
       <c r="N96" t="n">
         <v>0.9655</v>
@@ -10130,25 +10130,25 @@
         <v>0.8431</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.186</v>
+        <v>3.1894</v>
       </c>
       <c r="R96" t="n">
-        <v>1.3539</v>
+        <v>1.3552</v>
       </c>
       <c r="S96" t="n">
-        <v>1.3113</v>
+        <v>1.313</v>
       </c>
       <c r="T96" t="n">
-        <v>5.8512</v>
+        <v>5.8576</v>
       </c>
       <c r="U96" t="n">
-        <v>8.013</v>
+        <v>8.073</v>
       </c>
       <c r="V96" t="n">
-        <v>2.774</v>
+        <v>2.794</v>
       </c>
       <c r="W96" t="n">
-        <v>14.632</v>
+        <v>14.716</v>
       </c>
     </row>
     <row r="97">
@@ -10482,28 +10482,28 @@
         <v>-1</v>
       </c>
       <c r="F101" t="n">
-        <v>2.711</v>
+        <v>2.178</v>
       </c>
       <c r="G101" t="n">
         <v>0.976</v>
       </c>
       <c r="H101" t="n">
-        <v>2.647</v>
+        <v>2.126</v>
       </c>
       <c r="I101" t="n">
-        <v>2.647</v>
+        <v>2.126</v>
       </c>
       <c r="J101" t="n">
-        <v>2.0956</v>
+        <v>2.0163</v>
       </c>
       <c r="K101" t="n">
-        <v>1.1415</v>
+        <v>1.0983</v>
       </c>
       <c r="L101" t="n">
-        <v>0.6228</v>
+        <v>0.5993000000000001</v>
       </c>
       <c r="M101" t="n">
-        <v>0.3313</v>
+        <v>0.3188</v>
       </c>
       <c r="N101" t="n">
         <v>0.9655</v>
@@ -10515,25 +10515,25 @@
         <v>0.8431</v>
       </c>
       <c r="Q101" t="n">
-        <v>3.267</v>
+        <v>3.1433</v>
       </c>
       <c r="R101" t="n">
-        <v>1.3882</v>
+        <v>1.3358</v>
       </c>
       <c r="S101" t="n">
-        <v>1.3446</v>
+        <v>1.2939</v>
       </c>
       <c r="T101" t="n">
-        <v>5.9998</v>
+        <v>5.7731</v>
       </c>
       <c r="U101" t="n">
-        <v>8.647</v>
+        <v>7.899</v>
       </c>
       <c r="V101" t="n">
-        <v>2.993</v>
+        <v>2.734</v>
       </c>
       <c r="W101" t="n">
-        <v>15.518</v>
+        <v>14.47</v>
       </c>
     </row>
     <row r="102">
@@ -10559,28 +10559,28 @@
         <v>1</v>
       </c>
       <c r="F102" t="n">
-        <v>2.211</v>
+        <v>2.447</v>
       </c>
       <c r="G102" t="n">
         <v>0.976</v>
       </c>
       <c r="H102" t="n">
-        <v>2.159</v>
+        <v>2.39</v>
       </c>
       <c r="I102" t="n">
-        <v>2.159</v>
+        <v>2.39</v>
       </c>
       <c r="J102" t="n">
-        <v>2.0209</v>
+        <v>2.0527</v>
       </c>
       <c r="K102" t="n">
-        <v>1.1008</v>
+        <v>1.1181</v>
       </c>
       <c r="L102" t="n">
-        <v>0.6006</v>
+        <v>0.6101</v>
       </c>
       <c r="M102" t="n">
-        <v>0.3195</v>
+        <v>0.3245</v>
       </c>
       <c r="N102" t="n">
         <v>0.9655</v>
@@ -10592,25 +10592,25 @@
         <v>0.8431</v>
       </c>
       <c r="Q102" t="n">
-        <v>3.1505</v>
+        <v>3.2</v>
       </c>
       <c r="R102" t="n">
-        <v>1.3387</v>
+        <v>1.3599</v>
       </c>
       <c r="S102" t="n">
-        <v>1.2967</v>
+        <v>1.317</v>
       </c>
       <c r="T102" t="n">
-        <v>5.7859</v>
+        <v>5.8769</v>
       </c>
       <c r="U102" t="n">
-        <v>7.945</v>
+        <v>8.266999999999999</v>
       </c>
       <c r="V102" t="n">
-        <v>2.75</v>
+        <v>2.861</v>
       </c>
       <c r="W102" t="n">
-        <v>14.536</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="103">
@@ -10636,28 +10636,28 @@
         <v>-1</v>
       </c>
       <c r="F103" t="n">
-        <v>2.15</v>
+        <v>2.197</v>
       </c>
       <c r="G103" t="n">
         <v>0.976</v>
       </c>
       <c r="H103" t="n">
-        <v>2.1</v>
+        <v>2.145</v>
       </c>
       <c r="I103" t="n">
-        <v>2.1</v>
+        <v>2.145</v>
       </c>
       <c r="J103" t="n">
-        <v>2.0227</v>
+        <v>2.0231</v>
       </c>
       <c r="K103" t="n">
-        <v>1.1017</v>
+        <v>1.102</v>
       </c>
       <c r="L103" t="n">
-        <v>0.6011</v>
+        <v>0.6012999999999999</v>
       </c>
       <c r="M103" t="n">
-        <v>0.3198</v>
+        <v>0.3199</v>
       </c>
       <c r="N103" t="n">
         <v>0.9655</v>
@@ -10669,25 +10669,25 @@
         <v>0.8431</v>
       </c>
       <c r="Q103" t="n">
-        <v>3.1531</v>
+        <v>3.1539</v>
       </c>
       <c r="R103" t="n">
-        <v>1.3399</v>
+        <v>1.3403</v>
       </c>
       <c r="S103" t="n">
-        <v>1.2979</v>
+        <v>1.2983</v>
       </c>
       <c r="T103" t="n">
-        <v>5.7909</v>
+        <v>5.7926</v>
       </c>
       <c r="U103" t="n">
-        <v>7.891</v>
+        <v>7.938</v>
       </c>
       <c r="V103" t="n">
-        <v>2.731</v>
+        <v>2.748</v>
       </c>
       <c r="W103" t="n">
-        <v>14.46</v>
+        <v>14.526</v>
       </c>
     </row>
     <row r="104">
@@ -10790,28 +10790,28 @@
         <v>-1</v>
       </c>
       <c r="F105" t="n">
-        <v>2.147</v>
+        <v>2.368</v>
       </c>
       <c r="G105" t="n">
         <v>0.976</v>
       </c>
       <c r="H105" t="n">
-        <v>2.097</v>
+        <v>2.313</v>
       </c>
       <c r="I105" t="n">
-        <v>2.097</v>
+        <v>2.313</v>
       </c>
       <c r="J105" t="n">
-        <v>1.971</v>
+        <v>2.0422</v>
       </c>
       <c r="K105" t="n">
-        <v>1.0736</v>
+        <v>1.1124</v>
       </c>
       <c r="L105" t="n">
-        <v>0.5858</v>
+        <v>0.6069</v>
       </c>
       <c r="M105" t="n">
-        <v>0.3116</v>
+        <v>0.3229</v>
       </c>
       <c r="N105" t="n">
         <v>0.9655</v>
@@ -10823,25 +10823,25 @@
         <v>0.8431</v>
       </c>
       <c r="Q105" t="n">
-        <v>3.0726</v>
+        <v>3.1837</v>
       </c>
       <c r="R105" t="n">
-        <v>1.3057</v>
+        <v>1.3528</v>
       </c>
       <c r="S105" t="n">
-        <v>1.2647</v>
+        <v>1.3105</v>
       </c>
       <c r="T105" t="n">
-        <v>5.6431</v>
+        <v>5.847</v>
       </c>
       <c r="U105" t="n">
-        <v>7.74</v>
+        <v>8.16</v>
       </c>
       <c r="V105" t="n">
-        <v>2.679</v>
+        <v>2.824</v>
       </c>
       <c r="W105" t="n">
-        <v>14.246</v>
+        <v>14.841</v>
       </c>
     </row>
     <row r="106">
@@ -11021,28 +11021,28 @@
         <v>-1</v>
       </c>
       <c r="F108" t="n">
-        <v>2.244</v>
+        <v>2.328</v>
       </c>
       <c r="G108" t="n">
         <v>0.957</v>
       </c>
       <c r="H108" t="n">
-        <v>2.146</v>
+        <v>2.227</v>
       </c>
       <c r="I108" t="n">
-        <v>2.146</v>
+        <v>2.227</v>
       </c>
       <c r="J108" t="n">
-        <v>1.9353</v>
+        <v>2.012</v>
       </c>
       <c r="K108" t="n">
-        <v>1.0542</v>
+        <v>1.0959</v>
       </c>
       <c r="L108" t="n">
-        <v>0.5752</v>
+        <v>0.598</v>
       </c>
       <c r="M108" t="n">
-        <v>0.306</v>
+        <v>0.3181</v>
       </c>
       <c r="N108" t="n">
         <v>0.9458</v>
@@ -11054,25 +11054,25 @@
         <v>0.8254</v>
       </c>
       <c r="Q108" t="n">
-        <v>2.934</v>
+        <v>3.0501</v>
       </c>
       <c r="R108" t="n">
-        <v>1.736</v>
+        <v>1.8048</v>
       </c>
       <c r="S108" t="n">
-        <v>1.2094</v>
+        <v>1.2573</v>
       </c>
       <c r="T108" t="n">
-        <v>5.8794</v>
+        <v>6.1121</v>
       </c>
       <c r="U108" t="n">
-        <v>8.025</v>
+        <v>8.339</v>
       </c>
       <c r="V108" t="n">
-        <v>2.778</v>
+        <v>2.886</v>
       </c>
       <c r="W108" t="n">
-        <v>14.776</v>
+        <v>15.22</v>
       </c>
     </row>
     <row r="109">
@@ -11560,28 +11560,28 @@
         <v>1</v>
       </c>
       <c r="F115" t="n">
-        <v>2.628</v>
+        <v>2.302</v>
       </c>
       <c r="G115" t="n">
         <v>0.957</v>
       </c>
       <c r="H115" t="n">
-        <v>2.514</v>
+        <v>2.203</v>
       </c>
       <c r="I115" t="n">
-        <v>2.514</v>
+        <v>2.203</v>
       </c>
       <c r="J115" t="n">
-        <v>2.0612</v>
+        <v>2.0034</v>
       </c>
       <c r="K115" t="n">
-        <v>1.1227</v>
+        <v>1.0913</v>
       </c>
       <c r="L115" t="n">
-        <v>0.6126</v>
+        <v>0.5954</v>
       </c>
       <c r="M115" t="n">
-        <v>0.3259</v>
+        <v>0.3167</v>
       </c>
       <c r="N115" t="n">
         <v>0.9458</v>
@@ -11593,25 +11593,25 @@
         <v>0.8254</v>
       </c>
       <c r="Q115" t="n">
-        <v>3.1247</v>
+        <v>3.0373</v>
       </c>
       <c r="R115" t="n">
-        <v>1.8488</v>
+        <v>1.7969</v>
       </c>
       <c r="S115" t="n">
-        <v>1.2881</v>
+        <v>1.2517</v>
       </c>
       <c r="T115" t="n">
-        <v>6.2616</v>
+        <v>6.0859</v>
       </c>
       <c r="U115" t="n">
-        <v>8.776</v>
+        <v>8.289</v>
       </c>
       <c r="V115" t="n">
-        <v>3.038</v>
+        <v>2.869</v>
       </c>
       <c r="W115" t="n">
-        <v>15.833</v>
+        <v>15.151</v>
       </c>
     </row>
     <row r="116">
@@ -11791,28 +11791,28 @@
         <v>-1</v>
       </c>
       <c r="F118" t="n">
-        <v>2.713</v>
+        <v>2.231</v>
       </c>
       <c r="G118" t="n">
         <v>0.957</v>
       </c>
       <c r="H118" t="n">
-        <v>2.595</v>
+        <v>2.134</v>
       </c>
       <c r="I118" t="n">
-        <v>2.595</v>
+        <v>2.134</v>
       </c>
       <c r="J118" t="n">
-        <v>2.0472</v>
+        <v>1.9829</v>
       </c>
       <c r="K118" t="n">
-        <v>1.1151</v>
+        <v>1.0801</v>
       </c>
       <c r="L118" t="n">
-        <v>0.6084000000000001</v>
+        <v>0.5893</v>
       </c>
       <c r="M118" t="n">
-        <v>0.3237</v>
+        <v>0.3135</v>
       </c>
       <c r="N118" t="n">
         <v>0.9458</v>
@@ -11824,25 +11824,25 @@
         <v>0.8254</v>
       </c>
       <c r="Q118" t="n">
-        <v>3.1035</v>
+        <v>3.0061</v>
       </c>
       <c r="R118" t="n">
-        <v>1.8362</v>
+        <v>1.7785</v>
       </c>
       <c r="S118" t="n">
-        <v>1.2794</v>
+        <v>1.2391</v>
       </c>
       <c r="T118" t="n">
-        <v>6.2191</v>
+        <v>6.0237</v>
       </c>
       <c r="U118" t="n">
-        <v>8.814</v>
+        <v>8.157999999999999</v>
       </c>
       <c r="V118" t="n">
-        <v>3.051</v>
+        <v>2.824</v>
       </c>
       <c r="W118" t="n">
-        <v>15.884</v>
+        <v>14.964</v>
       </c>
     </row>
     <row r="119">
@@ -11868,28 +11868,28 @@
         <v>1</v>
       </c>
       <c r="F119" t="n">
-        <v>3.138</v>
+        <v>2.364</v>
       </c>
       <c r="G119" t="n">
         <v>0.951</v>
       </c>
       <c r="H119" t="n">
-        <v>2.984</v>
+        <v>2.248</v>
       </c>
       <c r="I119" t="n">
-        <v>2.984</v>
+        <v>2.248</v>
       </c>
       <c r="J119" t="n">
-        <v>2.0133</v>
+        <v>1.9101</v>
       </c>
       <c r="K119" t="n">
-        <v>1.0966</v>
+        <v>1.0405</v>
       </c>
       <c r="L119" t="n">
-        <v>0.5983000000000001</v>
+        <v>0.5677</v>
       </c>
       <c r="M119" t="n">
-        <v>0.3183</v>
+        <v>0.302</v>
       </c>
       <c r="N119" t="n">
         <v>0.9543</v>
@@ -11901,25 +11901,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q119" t="n">
-        <v>3.0893</v>
+        <v>2.9313</v>
       </c>
       <c r="R119" t="n">
-        <v>1.7889</v>
+        <v>1.6974</v>
       </c>
       <c r="S119" t="n">
-        <v>0.9916</v>
+        <v>0.9409</v>
       </c>
       <c r="T119" t="n">
-        <v>5.8699</v>
+        <v>5.5696</v>
       </c>
       <c r="U119" t="n">
-        <v>8.853999999999999</v>
+        <v>7.818</v>
       </c>
       <c r="V119" t="n">
-        <v>3.065</v>
+        <v>2.706</v>
       </c>
       <c r="W119" t="n">
-        <v>15.812</v>
+        <v>14.374</v>
       </c>
     </row>
     <row r="120">
@@ -11945,28 +11945,28 @@
         <v>-1</v>
       </c>
       <c r="F120" t="n">
-        <v>2.412</v>
+        <v>2.258</v>
       </c>
       <c r="G120" t="n">
         <v>0.951</v>
       </c>
       <c r="H120" t="n">
-        <v>2.294</v>
+        <v>2.148</v>
       </c>
       <c r="I120" t="n">
-        <v>2.294</v>
+        <v>2.148</v>
       </c>
       <c r="J120" t="n">
-        <v>1.9884</v>
+        <v>1.993</v>
       </c>
       <c r="K120" t="n">
-        <v>1.0831</v>
+        <v>1.0856</v>
       </c>
       <c r="L120" t="n">
-        <v>0.591</v>
+        <v>0.5923</v>
       </c>
       <c r="M120" t="n">
-        <v>0.3144</v>
+        <v>0.3151</v>
       </c>
       <c r="N120" t="n">
         <v>0.9543</v>
@@ -11978,25 +11978,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q120" t="n">
-        <v>3.0513</v>
+        <v>3.0584</v>
       </c>
       <c r="R120" t="n">
-        <v>1.7671</v>
+        <v>1.771</v>
       </c>
       <c r="S120" t="n">
-        <v>0.9795</v>
+        <v>0.9817</v>
       </c>
       <c r="T120" t="n">
-        <v>5.7979</v>
+        <v>5.811</v>
       </c>
       <c r="U120" t="n">
-        <v>8.092000000000001</v>
+        <v>7.959</v>
       </c>
       <c r="V120" t="n">
-        <v>2.801</v>
+        <v>2.755</v>
       </c>
       <c r="W120" t="n">
-        <v>14.763</v>
+        <v>14.577</v>
       </c>
     </row>
     <row r="121">
@@ -12022,28 +12022,28 @@
         <v>1</v>
       </c>
       <c r="F121" t="n">
-        <v>2.471</v>
+        <v>2.343</v>
       </c>
       <c r="G121" t="n">
         <v>0.951</v>
       </c>
       <c r="H121" t="n">
-        <v>2.35</v>
+        <v>2.228</v>
       </c>
       <c r="I121" t="n">
-        <v>2.35</v>
+        <v>2.228</v>
       </c>
       <c r="J121" t="n">
-        <v>1.9885</v>
+        <v>1.9988</v>
       </c>
       <c r="K121" t="n">
-        <v>1.0831</v>
+        <v>1.0887</v>
       </c>
       <c r="L121" t="n">
-        <v>0.591</v>
+        <v>0.594</v>
       </c>
       <c r="M121" t="n">
-        <v>0.3144</v>
+        <v>0.316</v>
       </c>
       <c r="N121" t="n">
         <v>0.9543</v>
@@ -12055,25 +12055,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q121" t="n">
-        <v>3.0513</v>
+        <v>3.0671</v>
       </c>
       <c r="R121" t="n">
-        <v>1.7671</v>
+        <v>1.7761</v>
       </c>
       <c r="S121" t="n">
-        <v>0.9795</v>
+        <v>0.9845</v>
       </c>
       <c r="T121" t="n">
-        <v>5.7979</v>
+        <v>5.8276</v>
       </c>
       <c r="U121" t="n">
-        <v>8.148</v>
+        <v>8.055999999999999</v>
       </c>
       <c r="V121" t="n">
-        <v>2.82</v>
+        <v>2.788</v>
       </c>
       <c r="W121" t="n">
-        <v>14.84</v>
+        <v>14.712</v>
       </c>
     </row>
     <row r="122">
@@ -12099,28 +12099,28 @@
         <v>1</v>
       </c>
       <c r="F122" t="n">
-        <v>2.406</v>
+        <v>2.305</v>
       </c>
       <c r="G122" t="n">
         <v>0.951</v>
       </c>
       <c r="H122" t="n">
-        <v>2.288</v>
+        <v>2.192</v>
       </c>
       <c r="I122" t="n">
-        <v>2.288</v>
+        <v>2.192</v>
       </c>
       <c r="J122" t="n">
-        <v>1.9335</v>
+        <v>1.9436</v>
       </c>
       <c r="K122" t="n">
-        <v>1.0532</v>
+        <v>1.0587</v>
       </c>
       <c r="L122" t="n">
-        <v>0.5746</v>
+        <v>0.5776</v>
       </c>
       <c r="M122" t="n">
-        <v>0.3057</v>
+        <v>0.3073</v>
       </c>
       <c r="N122" t="n">
         <v>0.9543</v>
@@ -12132,25 +12132,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q122" t="n">
-        <v>2.9671</v>
+        <v>2.9826</v>
       </c>
       <c r="R122" t="n">
-        <v>1.7181</v>
+        <v>1.727</v>
       </c>
       <c r="S122" t="n">
-        <v>0.9524</v>
+        <v>0.9574</v>
       </c>
       <c r="T122" t="n">
-        <v>5.6375</v>
+        <v>5.667</v>
       </c>
       <c r="U122" t="n">
-        <v>7.926</v>
+        <v>7.859</v>
       </c>
       <c r="V122" t="n">
-        <v>2.743</v>
+        <v>2.72</v>
       </c>
       <c r="W122" t="n">
-        <v>14.527</v>
+        <v>14.434</v>
       </c>
     </row>
     <row r="123">
@@ -12176,28 +12176,28 @@
         <v>1</v>
       </c>
       <c r="F123" t="n">
-        <v>3.138</v>
+        <v>2.58</v>
       </c>
       <c r="G123" t="n">
         <v>0.951</v>
       </c>
       <c r="H123" t="n">
-        <v>2.984</v>
+        <v>2.454</v>
       </c>
       <c r="I123" t="n">
-        <v>2.984</v>
+        <v>2.454</v>
       </c>
       <c r="J123" t="n">
-        <v>2.0133</v>
+        <v>2.0237</v>
       </c>
       <c r="K123" t="n">
-        <v>1.0966</v>
+        <v>1.1023</v>
       </c>
       <c r="L123" t="n">
-        <v>0.5983000000000001</v>
+        <v>0.6015</v>
       </c>
       <c r="M123" t="n">
-        <v>0.3183</v>
+        <v>0.32</v>
       </c>
       <c r="N123" t="n">
         <v>0.9543</v>
@@ -12209,25 +12209,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q123" t="n">
-        <v>3.0893</v>
+        <v>3.1054</v>
       </c>
       <c r="R123" t="n">
-        <v>1.7889</v>
+        <v>1.7985</v>
       </c>
       <c r="S123" t="n">
-        <v>0.9916</v>
+        <v>0.9969</v>
       </c>
       <c r="T123" t="n">
-        <v>5.8699</v>
+        <v>5.9008</v>
       </c>
       <c r="U123" t="n">
-        <v>8.853999999999999</v>
+        <v>8.355</v>
       </c>
       <c r="V123" t="n">
-        <v>3.065</v>
+        <v>2.892</v>
       </c>
       <c r="W123" t="n">
-        <v>15.812</v>
+        <v>15.132</v>
       </c>
     </row>
     <row r="124">
@@ -12253,28 +12253,28 @@
         <v>-1</v>
       </c>
       <c r="F124" t="n">
-        <v>2.238</v>
+        <v>2.188</v>
       </c>
       <c r="G124" t="n">
         <v>0.951</v>
       </c>
       <c r="H124" t="n">
-        <v>2.129</v>
+        <v>2.081</v>
       </c>
       <c r="I124" t="n">
-        <v>2.129</v>
+        <v>2.081</v>
       </c>
       <c r="J124" t="n">
-        <v>1.9623</v>
+        <v>1.9704</v>
       </c>
       <c r="K124" t="n">
-        <v>1.0689</v>
+        <v>1.0733</v>
       </c>
       <c r="L124" t="n">
-        <v>0.5832000000000001</v>
+        <v>0.5856</v>
       </c>
       <c r="M124" t="n">
-        <v>0.3102</v>
+        <v>0.3115</v>
       </c>
       <c r="N124" t="n">
         <v>0.9543</v>
@@ -12286,25 +12286,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q124" t="n">
-        <v>3.0113</v>
+        <v>3.0237</v>
       </c>
       <c r="R124" t="n">
-        <v>1.7438</v>
+        <v>1.7509</v>
       </c>
       <c r="S124" t="n">
-        <v>0.9664</v>
+        <v>0.9704</v>
       </c>
       <c r="T124" t="n">
-        <v>5.7215</v>
+        <v>5.7451</v>
       </c>
       <c r="U124" t="n">
-        <v>7.85</v>
+        <v>7.826</v>
       </c>
       <c r="V124" t="n">
-        <v>2.717</v>
+        <v>2.709</v>
       </c>
       <c r="W124" t="n">
-        <v>14.423</v>
+        <v>14.388</v>
       </c>
     </row>
     <row r="125">
@@ -12330,28 +12330,28 @@
         <v>-1</v>
       </c>
       <c r="F125" t="n">
-        <v>2.314</v>
+        <v>2.242</v>
       </c>
       <c r="G125" t="n">
         <v>0.951</v>
       </c>
       <c r="H125" t="n">
-        <v>2.201</v>
+        <v>2.132</v>
       </c>
       <c r="I125" t="n">
-        <v>2.201</v>
+        <v>2.132</v>
       </c>
       <c r="J125" t="n">
-        <v>2.0009</v>
+        <v>2.0048</v>
       </c>
       <c r="K125" t="n">
-        <v>1.0899</v>
+        <v>1.092</v>
       </c>
       <c r="L125" t="n">
-        <v>0.5947</v>
+        <v>0.5958</v>
       </c>
       <c r="M125" t="n">
-        <v>0.3163</v>
+        <v>0.317</v>
       </c>
       <c r="N125" t="n">
         <v>0.9543</v>
@@ -12363,25 +12363,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q125" t="n">
-        <v>3.0705</v>
+        <v>3.0764</v>
       </c>
       <c r="R125" t="n">
-        <v>1.7782</v>
+        <v>1.7814</v>
       </c>
       <c r="S125" t="n">
-        <v>0.9854000000000001</v>
+        <v>0.9876</v>
       </c>
       <c r="T125" t="n">
-        <v>5.834</v>
+        <v>5.8454</v>
       </c>
       <c r="U125" t="n">
-        <v>8.035</v>
+        <v>7.977</v>
       </c>
       <c r="V125" t="n">
-        <v>2.781</v>
+        <v>2.761</v>
       </c>
       <c r="W125" t="n">
-        <v>14.683</v>
+        <v>14.601</v>
       </c>
     </row>
     <row r="126">
@@ -12407,28 +12407,28 @@
         <v>1</v>
       </c>
       <c r="F126" t="n">
-        <v>2.587</v>
+        <v>2.496</v>
       </c>
       <c r="G126" t="n">
         <v>0.951</v>
       </c>
       <c r="H126" t="n">
-        <v>2.46</v>
+        <v>2.374</v>
       </c>
       <c r="I126" t="n">
-        <v>2.46</v>
+        <v>2.374</v>
       </c>
       <c r="J126" t="n">
-        <v>1.9868</v>
+        <v>1.9955</v>
       </c>
       <c r="K126" t="n">
-        <v>1.0822</v>
+        <v>1.087</v>
       </c>
       <c r="L126" t="n">
-        <v>0.5905</v>
+        <v>0.5931</v>
       </c>
       <c r="M126" t="n">
-        <v>0.3141</v>
+        <v>0.3155</v>
       </c>
       <c r="N126" t="n">
         <v>0.9543</v>
@@ -12440,25 +12440,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q126" t="n">
-        <v>3.0488</v>
+        <v>3.0623</v>
       </c>
       <c r="R126" t="n">
-        <v>1.7656</v>
+        <v>1.7734</v>
       </c>
       <c r="S126" t="n">
-        <v>0.9785</v>
+        <v>0.9829</v>
       </c>
       <c r="T126" t="n">
-        <v>5.7929</v>
+        <v>5.8186</v>
       </c>
       <c r="U126" t="n">
-        <v>8.253</v>
+        <v>8.193</v>
       </c>
       <c r="V126" t="n">
-        <v>2.857</v>
+        <v>2.836</v>
       </c>
       <c r="W126" t="n">
-        <v>14.987</v>
+        <v>14.904</v>
       </c>
     </row>
     <row r="127">
@@ -12484,28 +12484,28 @@
         <v>-1</v>
       </c>
       <c r="F127" t="n">
-        <v>3.208</v>
+        <v>2.628</v>
       </c>
       <c r="G127" t="n">
         <v>0.951</v>
       </c>
       <c r="H127" t="n">
-        <v>3.051</v>
+        <v>2.5</v>
       </c>
       <c r="I127" t="n">
-        <v>3.051</v>
+        <v>2.5</v>
       </c>
       <c r="J127" t="n">
-        <v>2.0108</v>
+        <v>2.0191</v>
       </c>
       <c r="K127" t="n">
-        <v>1.0953</v>
+        <v>1.0998</v>
       </c>
       <c r="L127" t="n">
-        <v>0.5976</v>
+        <v>0.6001</v>
       </c>
       <c r="M127" t="n">
-        <v>0.3179</v>
+        <v>0.3192</v>
       </c>
       <c r="N127" t="n">
         <v>0.9543</v>
@@ -12517,25 +12517,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q127" t="n">
-        <v>3.0857</v>
+        <v>3.0984</v>
       </c>
       <c r="R127" t="n">
-        <v>1.7868</v>
+        <v>1.7943</v>
       </c>
       <c r="S127" t="n">
-        <v>0.9903999999999999</v>
+        <v>0.9944</v>
       </c>
       <c r="T127" t="n">
-        <v>5.8629</v>
+        <v>5.8871</v>
       </c>
       <c r="U127" t="n">
-        <v>8.914</v>
+        <v>8.387</v>
       </c>
       <c r="V127" t="n">
-        <v>3.085</v>
+        <v>2.903</v>
       </c>
       <c r="W127" t="n">
-        <v>15.893</v>
+        <v>15.176</v>
       </c>
     </row>
     <row r="128">
@@ -12561,28 +12561,28 @@
         <v>-1</v>
       </c>
       <c r="F128" t="n">
-        <v>2.236</v>
+        <v>2.156</v>
       </c>
       <c r="G128" t="n">
         <v>0.951</v>
       </c>
       <c r="H128" t="n">
-        <v>2.127</v>
+        <v>2.051</v>
       </c>
       <c r="I128" t="n">
-        <v>2.127</v>
+        <v>2.051</v>
       </c>
       <c r="J128" t="n">
-        <v>1.9646</v>
+        <v>1.9673</v>
       </c>
       <c r="K128" t="n">
-        <v>1.0701</v>
+        <v>1.0716</v>
       </c>
       <c r="L128" t="n">
-        <v>0.5839</v>
+        <v>0.5847</v>
       </c>
       <c r="M128" t="n">
-        <v>0.3106</v>
+        <v>0.311</v>
       </c>
       <c r="N128" t="n">
         <v>0.9543</v>
@@ -12594,25 +12594,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q128" t="n">
-        <v>3.0147</v>
+        <v>3.0189</v>
       </c>
       <c r="R128" t="n">
-        <v>1.7459</v>
+        <v>1.7483</v>
       </c>
       <c r="S128" t="n">
-        <v>0.9676</v>
+        <v>0.9689</v>
       </c>
       <c r="T128" t="n">
-        <v>5.7282</v>
+        <v>5.7361</v>
       </c>
       <c r="U128" t="n">
-        <v>7.855</v>
+        <v>7.787</v>
       </c>
       <c r="V128" t="n">
-        <v>2.719</v>
+        <v>2.695</v>
       </c>
       <c r="W128" t="n">
-        <v>14.429</v>
+        <v>14.333</v>
       </c>
     </row>
     <row r="129">
@@ -12638,28 +12638,28 @@
         <v>1</v>
       </c>
       <c r="F129" t="n">
-        <v>2.909</v>
+        <v>2.465</v>
       </c>
       <c r="G129" t="n">
         <v>0.951</v>
       </c>
       <c r="H129" t="n">
-        <v>2.767</v>
+        <v>2.345</v>
       </c>
       <c r="I129" t="n">
-        <v>2.767</v>
+        <v>2.345</v>
       </c>
       <c r="J129" t="n">
-        <v>2.0091</v>
+        <v>2.0202</v>
       </c>
       <c r="K129" t="n">
-        <v>1.0944</v>
+        <v>1.1004</v>
       </c>
       <c r="L129" t="n">
-        <v>0.5971</v>
+        <v>0.6004</v>
       </c>
       <c r="M129" t="n">
-        <v>0.3176</v>
+        <v>0.3194</v>
       </c>
       <c r="N129" t="n">
         <v>0.9543</v>
@@ -12671,25 +12671,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q129" t="n">
-        <v>3.0831</v>
+        <v>3.1</v>
       </c>
       <c r="R129" t="n">
-        <v>1.7853</v>
+        <v>1.7952</v>
       </c>
       <c r="S129" t="n">
-        <v>0.9895</v>
+        <v>0.9951</v>
       </c>
       <c r="T129" t="n">
-        <v>5.8579</v>
+        <v>5.8903</v>
       </c>
       <c r="U129" t="n">
-        <v>8.625</v>
+        <v>8.234999999999999</v>
       </c>
       <c r="V129" t="n">
-        <v>2.985</v>
+        <v>2.85</v>
       </c>
       <c r="W129" t="n">
-        <v>15.5</v>
+        <v>14.966</v>
       </c>
     </row>
     <row r="130">
@@ -12715,28 +12715,28 @@
         <v>-1</v>
       </c>
       <c r="F130" t="n">
-        <v>2.222</v>
+        <v>2.164</v>
       </c>
       <c r="G130" t="n">
         <v>0.951</v>
       </c>
       <c r="H130" t="n">
-        <v>2.113</v>
+        <v>2.058</v>
       </c>
       <c r="I130" t="n">
-        <v>2.113</v>
+        <v>2.058</v>
       </c>
       <c r="J130" t="n">
-        <v>1.9658</v>
+        <v>1.9584</v>
       </c>
       <c r="K130" t="n">
-        <v>1.0707</v>
+        <v>1.0667</v>
       </c>
       <c r="L130" t="n">
-        <v>0.5842000000000001</v>
+        <v>0.582</v>
       </c>
       <c r="M130" t="n">
-        <v>0.3108</v>
+        <v>0.3096</v>
       </c>
       <c r="N130" t="n">
         <v>0.9543</v>
@@ -12748,25 +12748,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q130" t="n">
-        <v>3.0164</v>
+        <v>3.0051</v>
       </c>
       <c r="R130" t="n">
-        <v>1.7468</v>
+        <v>1.7402</v>
       </c>
       <c r="S130" t="n">
-        <v>0.9683</v>
+        <v>0.9645</v>
       </c>
       <c r="T130" t="n">
-        <v>5.7314</v>
+        <v>5.7098</v>
       </c>
       <c r="U130" t="n">
-        <v>7.844</v>
+        <v>7.768</v>
       </c>
       <c r="V130" t="n">
-        <v>2.715</v>
+        <v>2.689</v>
       </c>
       <c r="W130" t="n">
-        <v>14.413</v>
+        <v>14.305</v>
       </c>
     </row>
     <row r="131">
@@ -12792,28 +12792,28 @@
         <v>1</v>
       </c>
       <c r="F131" t="n">
-        <v>2.354</v>
+        <v>2.277</v>
       </c>
       <c r="G131" t="n">
         <v>0.951</v>
       </c>
       <c r="H131" t="n">
-        <v>2.238</v>
+        <v>2.166</v>
       </c>
       <c r="I131" t="n">
-        <v>2.238</v>
+        <v>2.166</v>
       </c>
       <c r="J131" t="n">
-        <v>1.9743</v>
+        <v>1.9791</v>
       </c>
       <c r="K131" t="n">
-        <v>1.0754</v>
+        <v>1.078</v>
       </c>
       <c r="L131" t="n">
-        <v>0.5868</v>
+        <v>0.5881999999999999</v>
       </c>
       <c r="M131" t="n">
-        <v>0.3121</v>
+        <v>0.3129</v>
       </c>
       <c r="N131" t="n">
         <v>0.9543</v>
@@ -12825,25 +12825,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q131" t="n">
-        <v>3.0296</v>
+        <v>3.0369</v>
       </c>
       <c r="R131" t="n">
-        <v>1.7545</v>
+        <v>1.7587</v>
       </c>
       <c r="S131" t="n">
-        <v>0.9723000000000001</v>
+        <v>0.9748</v>
       </c>
       <c r="T131" t="n">
-        <v>5.7565</v>
+        <v>5.7705</v>
       </c>
       <c r="U131" t="n">
-        <v>7.994</v>
+        <v>7.937</v>
       </c>
       <c r="V131" t="n">
-        <v>2.767</v>
+        <v>2.747</v>
       </c>
       <c r="W131" t="n">
-        <v>14.625</v>
+        <v>14.545</v>
       </c>
     </row>
     <row r="132">
@@ -12946,28 +12946,28 @@
         <v>1</v>
       </c>
       <c r="F133" t="n">
-        <v>2.379</v>
+        <v>2.371</v>
       </c>
       <c r="G133" t="n">
         <v>0.951</v>
       </c>
       <c r="H133" t="n">
-        <v>2.263</v>
+        <v>2.255</v>
       </c>
       <c r="I133" t="n">
-        <v>2.263</v>
+        <v>2.255</v>
       </c>
       <c r="J133" t="n">
-        <v>1.9807</v>
+        <v>2.0265</v>
       </c>
       <c r="K133" t="n">
-        <v>1.0789</v>
+        <v>1.1038</v>
       </c>
       <c r="L133" t="n">
-        <v>0.5887</v>
+        <v>0.6022999999999999</v>
       </c>
       <c r="M133" t="n">
-        <v>0.3131</v>
+        <v>0.3204</v>
       </c>
       <c r="N133" t="n">
         <v>0.9543</v>
@@ -12979,25 +12979,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q133" t="n">
-        <v>3.0395</v>
+        <v>3.1096</v>
       </c>
       <c r="R133" t="n">
-        <v>1.7602</v>
+        <v>1.8009</v>
       </c>
       <c r="S133" t="n">
-        <v>0.9754</v>
+        <v>0.9982</v>
       </c>
       <c r="T133" t="n">
-        <v>5.7751</v>
+        <v>5.9087</v>
       </c>
       <c r="U133" t="n">
-        <v>8.038</v>
+        <v>8.164</v>
       </c>
       <c r="V133" t="n">
-        <v>2.782</v>
+        <v>2.826</v>
       </c>
       <c r="W133" t="n">
-        <v>14.688</v>
+        <v>14.865</v>
       </c>
     </row>
     <row r="134">
@@ -14563,28 +14563,28 @@
         <v>1</v>
       </c>
       <c r="F154" t="n">
-        <v>2.243</v>
+        <v>2.276</v>
       </c>
       <c r="G154" t="n">
         <v>0.973</v>
       </c>
       <c r="H154" t="n">
-        <v>2.181</v>
+        <v>2.214</v>
       </c>
       <c r="I154" t="n">
-        <v>2.181</v>
+        <v>2.214</v>
       </c>
       <c r="J154" t="n">
-        <v>1.9103</v>
+        <v>1.8988</v>
       </c>
       <c r="K154" t="n">
-        <v>1.0406</v>
+        <v>1.0343</v>
       </c>
       <c r="L154" t="n">
-        <v>0.5678</v>
+        <v>0.5643</v>
       </c>
       <c r="M154" t="n">
-        <v>0.302</v>
+        <v>0.3002</v>
       </c>
       <c r="N154" t="n">
         <v>0.9111</v>
@@ -14596,19 +14596,19 @@
         <v>0.6859</v>
       </c>
       <c r="Q154" t="n">
-        <v>2.7518</v>
+        <v>2.7351</v>
       </c>
       <c r="R154" t="n">
-        <v>1.6977</v>
+        <v>1.6873</v>
       </c>
       <c r="S154" t="n">
-        <v>0.9409</v>
+        <v>0.9352</v>
       </c>
       <c r="T154" t="n">
-        <v>5.3903</v>
+        <v>5.3576</v>
       </c>
       <c r="U154" t="n">
-        <v>7.571</v>
+        <v>7.572</v>
       </c>
       <c r="V154" t="n">
         <v>2.621</v>
@@ -14640,28 +14640,28 @@
         <v>-1</v>
       </c>
       <c r="F155" t="n">
-        <v>2.779</v>
+        <v>1.674</v>
       </c>
       <c r="G155" t="n">
         <v>0.973</v>
       </c>
       <c r="H155" t="n">
-        <v>2.703</v>
+        <v>1.629</v>
       </c>
       <c r="I155" t="n">
-        <v>2.703</v>
+        <v>1.629</v>
       </c>
       <c r="J155" t="n">
-        <v>1.9228</v>
+        <v>1.8237</v>
       </c>
       <c r="K155" t="n">
-        <v>1.0474</v>
+        <v>0.9933999999999999</v>
       </c>
       <c r="L155" t="n">
-        <v>0.5715</v>
+        <v>0.542</v>
       </c>
       <c r="M155" t="n">
-        <v>0.304</v>
+        <v>0.2883</v>
       </c>
       <c r="N155" t="n">
         <v>0.9111</v>
@@ -14673,25 +14673,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q155" t="n">
-        <v>2.7697</v>
+        <v>2.6269</v>
       </c>
       <c r="R155" t="n">
-        <v>1.7088</v>
+        <v>1.6206</v>
       </c>
       <c r="S155" t="n">
-        <v>0.9471000000000001</v>
+        <v>0.8982</v>
       </c>
       <c r="T155" t="n">
-        <v>5.4256</v>
+        <v>5.1457</v>
       </c>
       <c r="U155" t="n">
-        <v>8.129</v>
+        <v>6.775</v>
       </c>
       <c r="V155" t="n">
-        <v>2.814</v>
+        <v>2.345</v>
       </c>
       <c r="W155" t="n">
-        <v>14.745</v>
+        <v>12.821</v>
       </c>
     </row>
     <row r="156">
@@ -15025,28 +15025,28 @@
         <v>-1</v>
       </c>
       <c r="F160" t="n">
-        <v>2.895</v>
+        <v>2.867</v>
       </c>
       <c r="G160" t="n">
         <v>0.915</v>
       </c>
       <c r="H160" t="n">
-        <v>2.647</v>
+        <v>2.622</v>
       </c>
       <c r="I160" t="n">
-        <v>2.647</v>
+        <v>2.622</v>
       </c>
       <c r="J160" t="n">
-        <v>1.9142</v>
+        <v>1.9002</v>
       </c>
       <c r="K160" t="n">
-        <v>1.0427</v>
+        <v>1.035</v>
       </c>
       <c r="L160" t="n">
-        <v>0.5689</v>
+        <v>0.5647</v>
       </c>
       <c r="M160" t="n">
-        <v>0.3026</v>
+        <v>0.3004</v>
       </c>
       <c r="N160" t="n">
         <v>0.9639</v>
@@ -15058,25 +15058,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q160" t="n">
-        <v>2.9775</v>
+        <v>2.9555</v>
       </c>
       <c r="R160" t="n">
-        <v>1.7735</v>
+        <v>1.7605</v>
       </c>
       <c r="S160" t="n">
-        <v>0.9427</v>
+        <v>0.9359</v>
       </c>
       <c r="T160" t="n">
-        <v>5.6938</v>
+        <v>5.6519</v>
       </c>
       <c r="U160" t="n">
-        <v>8.340999999999999</v>
+        <v>8.273999999999999</v>
       </c>
       <c r="V160" t="n">
-        <v>2.887</v>
+        <v>2.864</v>
       </c>
       <c r="W160" t="n">
-        <v>15.113</v>
+        <v>15.02</v>
       </c>
     </row>
     <row r="161">
@@ -15256,28 +15256,28 @@
         <v>1</v>
       </c>
       <c r="F163" t="n">
-        <v>2.89</v>
+        <v>2.738</v>
       </c>
       <c r="G163" t="n">
         <v>0.915</v>
       </c>
       <c r="H163" t="n">
-        <v>2.643</v>
+        <v>2.504</v>
       </c>
       <c r="I163" t="n">
-        <v>2.643</v>
+        <v>2.504</v>
       </c>
       <c r="J163" t="n">
-        <v>1.8682</v>
+        <v>1.9253</v>
       </c>
       <c r="K163" t="n">
-        <v>1.0176</v>
+        <v>1.0487</v>
       </c>
       <c r="L163" t="n">
-        <v>0.5552</v>
+        <v>0.5722</v>
       </c>
       <c r="M163" t="n">
-        <v>0.2954</v>
+        <v>0.3044</v>
       </c>
       <c r="N163" t="n">
         <v>0.9639</v>
@@ -15289,25 +15289,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q163" t="n">
-        <v>2.9059</v>
+        <v>2.9947</v>
       </c>
       <c r="R163" t="n">
-        <v>1.7308</v>
+        <v>1.7838</v>
       </c>
       <c r="S163" t="n">
-        <v>0.9203</v>
+        <v>0.9483</v>
       </c>
       <c r="T163" t="n">
-        <v>5.557</v>
+        <v>5.7268</v>
       </c>
       <c r="U163" t="n">
-        <v>8.199999999999999</v>
+        <v>8.231</v>
       </c>
       <c r="V163" t="n">
-        <v>2.838</v>
+        <v>2.849</v>
       </c>
       <c r="W163" t="n">
-        <v>14.913</v>
+        <v>14.965</v>
       </c>
     </row>
     <row r="164">
@@ -15949,28 +15949,28 @@
         <v>-1</v>
       </c>
       <c r="F172" t="n">
-        <v>2.712</v>
+        <v>2.662</v>
       </c>
       <c r="G172" t="n">
         <v>0.953</v>
       </c>
       <c r="H172" t="n">
-        <v>2.585</v>
+        <v>2.537</v>
       </c>
       <c r="I172" t="n">
-        <v>2.585</v>
+        <v>2.537</v>
       </c>
       <c r="J172" t="n">
-        <v>1.9777</v>
+        <v>1.9609</v>
       </c>
       <c r="K172" t="n">
-        <v>1.0773</v>
+        <v>1.0681</v>
       </c>
       <c r="L172" t="n">
-        <v>0.5878</v>
+        <v>0.5828</v>
       </c>
       <c r="M172" t="n">
-        <v>0.3127</v>
+        <v>0.31</v>
       </c>
       <c r="N172" t="n">
         <v>0.9818</v>
@@ -15982,25 +15982,25 @@
         <v>0.6744</v>
       </c>
       <c r="Q172" t="n">
-        <v>3.1535</v>
+        <v>3.1265</v>
       </c>
       <c r="R172" t="n">
-        <v>1.7634</v>
+        <v>1.7484</v>
       </c>
       <c r="S172" t="n">
-        <v>0.9526</v>
+        <v>0.9444</v>
       </c>
       <c r="T172" t="n">
-        <v>5.8695</v>
+        <v>5.8193</v>
       </c>
       <c r="U172" t="n">
-        <v>8.454000000000001</v>
+        <v>8.356</v>
       </c>
       <c r="V172" t="n">
-        <v>2.926</v>
+        <v>2.892</v>
       </c>
       <c r="W172" t="n">
-        <v>15.314</v>
+        <v>15.176</v>
       </c>
     </row>
     <row r="173">
@@ -16103,28 +16103,28 @@
         <v>-1</v>
       </c>
       <c r="F174" t="n">
-        <v>2.68</v>
+        <v>2.655</v>
       </c>
       <c r="G174" t="n">
         <v>0.953</v>
       </c>
       <c r="H174" t="n">
-        <v>2.555</v>
+        <v>2.531</v>
       </c>
       <c r="I174" t="n">
-        <v>2.555</v>
+        <v>2.531</v>
       </c>
       <c r="J174" t="n">
-        <v>1.9735</v>
+        <v>1.952</v>
       </c>
       <c r="K174" t="n">
-        <v>1.075</v>
+        <v>1.0633</v>
       </c>
       <c r="L174" t="n">
-        <v>0.5865</v>
+        <v>0.5800999999999999</v>
       </c>
       <c r="M174" t="n">
-        <v>0.312</v>
+        <v>0.3086</v>
       </c>
       <c r="N174" t="n">
         <v>0.9818</v>
@@ -16136,25 +16136,25 @@
         <v>0.6744</v>
       </c>
       <c r="Q174" t="n">
-        <v>3.1467</v>
+        <v>3.1125</v>
       </c>
       <c r="R174" t="n">
-        <v>1.7595</v>
+        <v>1.7403</v>
       </c>
       <c r="S174" t="n">
-        <v>0.9505</v>
+        <v>0.9401</v>
       </c>
       <c r="T174" t="n">
-        <v>5.8567</v>
+        <v>5.7929</v>
       </c>
       <c r="U174" t="n">
-        <v>8.412000000000001</v>
+        <v>8.324</v>
       </c>
       <c r="V174" t="n">
-        <v>2.912</v>
+        <v>2.881</v>
       </c>
       <c r="W174" t="n">
-        <v>15.254</v>
+        <v>15.129</v>
       </c>
     </row>
     <row r="175">
@@ -16334,28 +16334,28 @@
         <v>1</v>
       </c>
       <c r="F177" t="n">
-        <v>2.796</v>
+        <v>2.866</v>
       </c>
       <c r="G177" t="n">
         <v>0.953</v>
       </c>
       <c r="H177" t="n">
-        <v>2.665</v>
+        <v>2.733</v>
       </c>
       <c r="I177" t="n">
-        <v>2.665</v>
+        <v>2.733</v>
       </c>
       <c r="J177" t="n">
-        <v>1.9592</v>
+        <v>1.9612</v>
       </c>
       <c r="K177" t="n">
-        <v>1.0672</v>
+        <v>1.0683</v>
       </c>
       <c r="L177" t="n">
-        <v>0.5823</v>
+        <v>0.5829</v>
       </c>
       <c r="M177" t="n">
-        <v>0.3098</v>
+        <v>0.3101</v>
       </c>
       <c r="N177" t="n">
         <v>0.9818</v>
@@ -16367,25 +16367,25 @@
         <v>0.6744</v>
       </c>
       <c r="Q177" t="n">
-        <v>3.1239</v>
+        <v>3.1271</v>
       </c>
       <c r="R177" t="n">
-        <v>1.7469</v>
+        <v>1.7487</v>
       </c>
       <c r="S177" t="n">
-        <v>0.9438</v>
+        <v>0.9447</v>
       </c>
       <c r="T177" t="n">
-        <v>5.8146</v>
+        <v>5.8205</v>
       </c>
       <c r="U177" t="n">
-        <v>8.48</v>
+        <v>8.554</v>
       </c>
       <c r="V177" t="n">
-        <v>2.935</v>
+        <v>2.961</v>
       </c>
       <c r="W177" t="n">
-        <v>15.346</v>
+        <v>15.448</v>
       </c>
     </row>
     <row r="178">
@@ -16719,28 +16719,28 @@
         <v>1</v>
       </c>
       <c r="F182" t="n">
-        <v>2.876</v>
+        <v>2.777</v>
       </c>
       <c r="G182" t="n">
         <v>0.953</v>
       </c>
       <c r="H182" t="n">
-        <v>2.742</v>
+        <v>2.647</v>
       </c>
       <c r="I182" t="n">
-        <v>2.742</v>
+        <v>2.647</v>
       </c>
       <c r="J182" t="n">
-        <v>1.9795</v>
+        <v>1.9673</v>
       </c>
       <c r="K182" t="n">
-        <v>1.0782</v>
+        <v>1.0716</v>
       </c>
       <c r="L182" t="n">
-        <v>0.5883</v>
+        <v>0.5847</v>
       </c>
       <c r="M182" t="n">
-        <v>0.313</v>
+        <v>0.311</v>
       </c>
       <c r="N182" t="n">
         <v>0.9818</v>
@@ -16752,25 +16752,25 @@
         <v>0.6744</v>
       </c>
       <c r="Q182" t="n">
-        <v>3.1561</v>
+        <v>3.1368</v>
       </c>
       <c r="R182" t="n">
-        <v>1.7649</v>
+        <v>1.7541</v>
       </c>
       <c r="S182" t="n">
-        <v>0.9535</v>
+        <v>0.9474</v>
       </c>
       <c r="T182" t="n">
-        <v>5.8745</v>
+        <v>5.8383</v>
       </c>
       <c r="U182" t="n">
-        <v>8.616</v>
+        <v>8.484999999999999</v>
       </c>
       <c r="V182" t="n">
-        <v>2.982</v>
+        <v>2.937</v>
       </c>
       <c r="W182" t="n">
-        <v>15.537</v>
+        <v>15.355</v>
       </c>
     </row>
     <row r="183">
@@ -17181,28 +17181,28 @@
         <v>-1</v>
       </c>
       <c r="F188" t="n">
-        <v>2.509</v>
+        <v>2.481</v>
       </c>
       <c r="G188" t="n">
         <v>0.9389999999999999</v>
       </c>
       <c r="H188" t="n">
-        <v>2.356</v>
+        <v>2.33</v>
       </c>
       <c r="I188" t="n">
-        <v>2.356</v>
+        <v>2.33</v>
       </c>
       <c r="J188" t="n">
-        <v>1.9899</v>
+        <v>1.9904</v>
       </c>
       <c r="K188" t="n">
-        <v>1.0839</v>
+        <v>1.0842</v>
       </c>
       <c r="L188" t="n">
-        <v>0.5914</v>
+        <v>0.5915</v>
       </c>
       <c r="M188" t="n">
-        <v>0.3146</v>
+        <v>0.3147</v>
       </c>
       <c r="N188" t="n">
         <v>0.963</v>
@@ -17214,25 +17214,25 @@
         <v>0.6604</v>
       </c>
       <c r="Q188" t="n">
-        <v>3.0913</v>
+        <v>3.0921</v>
       </c>
       <c r="R188" t="n">
-        <v>1.98</v>
+        <v>1.9803</v>
       </c>
       <c r="S188" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9323</v>
       </c>
       <c r="T188" t="n">
-        <v>6.0033</v>
+        <v>6.0047</v>
       </c>
       <c r="U188" t="n">
-        <v>8.359</v>
+        <v>8.335000000000001</v>
       </c>
       <c r="V188" t="n">
-        <v>2.893</v>
+        <v>2.885</v>
       </c>
       <c r="W188" t="n">
-        <v>15.213</v>
+        <v>15.179</v>
       </c>
     </row>
     <row r="189">
@@ -19029,28 +19029,28 @@
         <v>1</v>
       </c>
       <c r="F212" t="n">
-        <v>3.189</v>
+        <v>2.692</v>
       </c>
       <c r="G212" t="n">
         <v>0.959</v>
       </c>
       <c r="H212" t="n">
-        <v>3.059</v>
+        <v>2.582</v>
       </c>
       <c r="I212" t="n">
-        <v>3.059</v>
+        <v>2.582</v>
       </c>
       <c r="J212" t="n">
-        <v>1.9491</v>
+        <v>1.9401</v>
       </c>
       <c r="K212" t="n">
-        <v>1.0617</v>
+        <v>1.0568</v>
       </c>
       <c r="L212" t="n">
-        <v>0.5793</v>
+        <v>0.5766</v>
       </c>
       <c r="M212" t="n">
-        <v>0.3082</v>
+        <v>0.3067</v>
       </c>
       <c r="N212" t="n">
         <v>0.9543</v>
@@ -19062,25 +19062,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q212" t="n">
-        <v>2.991</v>
+        <v>2.9772</v>
       </c>
       <c r="R212" t="n">
-        <v>1.7321</v>
+        <v>1.724</v>
       </c>
       <c r="S212" t="n">
-        <v>0.9602000000000001</v>
+        <v>0.9555</v>
       </c>
       <c r="T212" t="n">
-        <v>5.6833</v>
+        <v>5.6567</v>
       </c>
       <c r="U212" t="n">
-        <v>8.742000000000001</v>
+        <v>8.239000000000001</v>
       </c>
       <c r="V212" t="n">
-        <v>3.026</v>
+        <v>2.852</v>
       </c>
       <c r="W212" t="n">
-        <v>15.657</v>
+        <v>14.97</v>
       </c>
     </row>
     <row r="213">
@@ -19414,28 +19414,28 @@
         <v>-1</v>
       </c>
       <c r="F217" t="n">
-        <v>3.007</v>
+        <v>2.905</v>
       </c>
       <c r="G217" t="n">
         <v>0.959</v>
       </c>
       <c r="H217" t="n">
-        <v>2.884</v>
+        <v>2.787</v>
       </c>
       <c r="I217" t="n">
-        <v>2.884</v>
+        <v>2.787</v>
       </c>
       <c r="J217" t="n">
-        <v>1.9349</v>
+        <v>1.9121</v>
       </c>
       <c r="K217" t="n">
-        <v>1.0539</v>
+        <v>1.0415</v>
       </c>
       <c r="L217" t="n">
-        <v>0.5750999999999999</v>
+        <v>0.5683</v>
       </c>
       <c r="M217" t="n">
-        <v>0.3059</v>
+        <v>0.3023</v>
       </c>
       <c r="N217" t="n">
         <v>0.9543</v>
@@ -19447,25 +19447,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q217" t="n">
-        <v>2.969</v>
+        <v>2.9341</v>
       </c>
       <c r="R217" t="n">
-        <v>1.7195</v>
+        <v>1.6992</v>
       </c>
       <c r="S217" t="n">
-        <v>0.953</v>
+        <v>0.9418</v>
       </c>
       <c r="T217" t="n">
-        <v>5.6416</v>
+        <v>5.5751</v>
       </c>
       <c r="U217" t="n">
-        <v>8.526</v>
+        <v>8.362</v>
       </c>
       <c r="V217" t="n">
-        <v>2.951</v>
+        <v>2.894</v>
       </c>
       <c r="W217" t="n">
-        <v>15.362</v>
+        <v>15.136</v>
       </c>
     </row>
     <row r="218">
@@ -19568,28 +19568,28 @@
         <v>-1</v>
       </c>
       <c r="F219" t="n">
-        <v>3.139</v>
+        <v>2.312</v>
       </c>
       <c r="G219" t="n">
         <v>0.959</v>
       </c>
       <c r="H219" t="n">
-        <v>3.011</v>
+        <v>2.218</v>
       </c>
       <c r="I219" t="n">
-        <v>3.011</v>
+        <v>2.218</v>
       </c>
       <c r="J219" t="n">
-        <v>1.9345</v>
+        <v>1.912</v>
       </c>
       <c r="K219" t="n">
-        <v>1.0537</v>
+        <v>1.0415</v>
       </c>
       <c r="L219" t="n">
-        <v>0.5749</v>
+        <v>0.5683</v>
       </c>
       <c r="M219" t="n">
-        <v>0.3059</v>
+        <v>0.3023</v>
       </c>
       <c r="N219" t="n">
         <v>0.9543</v>
@@ -19601,25 +19601,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q219" t="n">
-        <v>2.9685</v>
+        <v>2.9341</v>
       </c>
       <c r="R219" t="n">
-        <v>1.719</v>
+        <v>1.6992</v>
       </c>
       <c r="S219" t="n">
-        <v>0.953</v>
+        <v>0.9418</v>
       </c>
       <c r="T219" t="n">
-        <v>5.6404</v>
+        <v>5.5751</v>
       </c>
       <c r="U219" t="n">
-        <v>8.651</v>
+        <v>7.793</v>
       </c>
       <c r="V219" t="n">
-        <v>2.994</v>
+        <v>2.697</v>
       </c>
       <c r="W219" t="n">
-        <v>15.532</v>
+        <v>14.348</v>
       </c>
     </row>
     <row r="220">
@@ -22725,28 +22725,28 @@
         <v>1</v>
       </c>
       <c r="F260" t="n">
-        <v>2.326</v>
+        <v>1.708</v>
       </c>
       <c r="G260" t="n">
         <v>0.969</v>
       </c>
       <c r="H260" t="n">
-        <v>2.254</v>
+        <v>1.655</v>
       </c>
       <c r="I260" t="n">
-        <v>2.254</v>
+        <v>1.655</v>
       </c>
       <c r="J260" t="n">
-        <v>1.9465</v>
+        <v>1.8916</v>
       </c>
       <c r="K260" t="n">
-        <v>1.0602</v>
+        <v>1.0303</v>
       </c>
       <c r="L260" t="n">
-        <v>0.5785</v>
+        <v>0.5622</v>
       </c>
       <c r="M260" t="n">
-        <v>0.3077</v>
+        <v>0.2991</v>
       </c>
       <c r="N260" t="n">
         <v>0.9412</v>
@@ -22758,25 +22758,25 @@
         <v>0.6923</v>
       </c>
       <c r="Q260" t="n">
-        <v>2.9312</v>
+        <v>2.8486</v>
       </c>
       <c r="R260" t="n">
-        <v>1.6507</v>
+        <v>1.6042</v>
       </c>
       <c r="S260" t="n">
-        <v>0.9704</v>
+        <v>0.9433</v>
       </c>
       <c r="T260" t="n">
-        <v>5.5524</v>
+        <v>5.3961</v>
       </c>
       <c r="U260" t="n">
-        <v>7.806</v>
+        <v>7.051</v>
       </c>
       <c r="V260" t="n">
-        <v>2.702</v>
+        <v>2.441</v>
       </c>
       <c r="W260" t="n">
-        <v>14.323</v>
+        <v>13.239</v>
       </c>
     </row>
     <row r="261">
@@ -24342,28 +24342,28 @@
         <v>1</v>
       </c>
       <c r="F281" t="n">
-        <v>2.892</v>
+        <v>2.408</v>
       </c>
       <c r="G281" t="n">
         <v>0.9340000000000001</v>
       </c>
       <c r="H281" t="n">
-        <v>2.701</v>
+        <v>2.248</v>
       </c>
       <c r="I281" t="n">
-        <v>2.701</v>
+        <v>2.248</v>
       </c>
       <c r="J281" t="n">
-        <v>2.0535</v>
+        <v>1.9956</v>
       </c>
       <c r="K281" t="n">
-        <v>1.1185</v>
+        <v>1.087</v>
       </c>
       <c r="L281" t="n">
-        <v>0.6103</v>
+        <v>0.5931</v>
       </c>
       <c r="M281" t="n">
-        <v>0.3247</v>
+        <v>0.3155</v>
       </c>
       <c r="N281" t="n">
         <v>0.9597</v>
@@ -24375,25 +24375,25 @@
         <v>0.7391</v>
       </c>
       <c r="Q281" t="n">
-        <v>3.1752</v>
+        <v>3.0858</v>
       </c>
       <c r="R281" t="n">
-        <v>1.9395</v>
+        <v>1.8849</v>
       </c>
       <c r="S281" t="n">
-        <v>1.1152</v>
+        <v>1.0836</v>
       </c>
       <c r="T281" t="n">
-        <v>6.2299</v>
+        <v>6.0543</v>
       </c>
       <c r="U281" t="n">
-        <v>8.930999999999999</v>
+        <v>8.302</v>
       </c>
       <c r="V281" t="n">
-        <v>3.091</v>
+        <v>2.874</v>
       </c>
       <c r="W281" t="n">
-        <v>16.018</v>
+        <v>15.143</v>
       </c>
     </row>
     <row r="282">
@@ -25882,28 +25882,28 @@
         <v>1</v>
       </c>
       <c r="F301" t="n">
-        <v>2.22</v>
+        <v>2.577</v>
       </c>
       <c r="G301" t="n">
         <v>0.953</v>
       </c>
       <c r="H301" t="n">
-        <v>2.116</v>
+        <v>2.456</v>
       </c>
       <c r="I301" t="n">
-        <v>2.116</v>
+        <v>2.456</v>
       </c>
       <c r="J301" t="n">
-        <v>1.9961</v>
+        <v>1.9955</v>
       </c>
       <c r="K301" t="n">
-        <v>1.0873</v>
+        <v>1.0869</v>
       </c>
       <c r="L301" t="n">
-        <v>0.5931999999999999</v>
+        <v>0.5931</v>
       </c>
       <c r="M301" t="n">
-        <v>0.3156</v>
+        <v>0.3155</v>
       </c>
       <c r="N301" t="n">
         <v>0.9333</v>
@@ -25915,25 +25915,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q301" t="n">
-        <v>2.9718</v>
+        <v>2.9707</v>
       </c>
       <c r="R301" t="n">
-        <v>1.6589</v>
+        <v>1.6586</v>
       </c>
       <c r="S301" t="n">
-        <v>0.9832</v>
+        <v>0.9829</v>
       </c>
       <c r="T301" t="n">
-        <v>5.6139</v>
+        <v>5.6122</v>
       </c>
       <c r="U301" t="n">
-        <v>7.73</v>
+        <v>8.068</v>
       </c>
       <c r="V301" t="n">
-        <v>2.676</v>
+        <v>2.793</v>
       </c>
       <c r="W301" t="n">
-        <v>14.168</v>
+        <v>14.641</v>
       </c>
     </row>
     <row r="302">
@@ -25959,28 +25959,28 @@
         <v>1</v>
       </c>
       <c r="F302" t="n">
-        <v>1.943</v>
+        <v>2.611</v>
       </c>
       <c r="G302" t="n">
         <v>0.953</v>
       </c>
       <c r="H302" t="n">
-        <v>1.852</v>
+        <v>2.489</v>
       </c>
       <c r="I302" t="n">
-        <v>1.852</v>
+        <v>2.489</v>
       </c>
       <c r="J302" t="n">
-        <v>1.9738</v>
+        <v>1.9973</v>
       </c>
       <c r="K302" t="n">
-        <v>1.0751</v>
+        <v>1.0879</v>
       </c>
       <c r="L302" t="n">
-        <v>0.5866</v>
+        <v>0.5936</v>
       </c>
       <c r="M302" t="n">
-        <v>0.3121</v>
+        <v>0.3158</v>
       </c>
       <c r="N302" t="n">
         <v>0.9333</v>
@@ -25992,25 +25992,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q302" t="n">
-        <v>2.9385</v>
+        <v>2.9734</v>
       </c>
       <c r="R302" t="n">
-        <v>1.6404</v>
+        <v>1.66</v>
       </c>
       <c r="S302" t="n">
-        <v>0.9723000000000001</v>
+        <v>0.9838</v>
       </c>
       <c r="T302" t="n">
-        <v>5.5512</v>
+        <v>5.6173</v>
       </c>
       <c r="U302" t="n">
-        <v>7.403</v>
+        <v>8.106</v>
       </c>
       <c r="V302" t="n">
-        <v>2.562</v>
+        <v>2.806</v>
       </c>
       <c r="W302" t="n">
-        <v>13.702</v>
+        <v>14.694</v>
       </c>
     </row>
     <row r="303">
@@ -26036,28 +26036,28 @@
         <v>1</v>
       </c>
       <c r="F303" t="n">
-        <v>2.086</v>
+        <v>2.649</v>
       </c>
       <c r="G303" t="n">
         <v>0.953</v>
       </c>
       <c r="H303" t="n">
-        <v>1.988</v>
+        <v>2.525</v>
       </c>
       <c r="I303" t="n">
-        <v>1.988</v>
+        <v>2.525</v>
       </c>
       <c r="J303" t="n">
-        <v>1.9683</v>
+        <v>1.9961</v>
       </c>
       <c r="K303" t="n">
-        <v>1.0721</v>
+        <v>1.0873</v>
       </c>
       <c r="L303" t="n">
-        <v>0.585</v>
+        <v>0.5931999999999999</v>
       </c>
       <c r="M303" t="n">
-        <v>0.3112</v>
+        <v>0.3156</v>
       </c>
       <c r="N303" t="n">
         <v>0.9333</v>
@@ -26069,25 +26069,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q303" t="n">
-        <v>2.9303</v>
+        <v>2.9718</v>
       </c>
       <c r="R303" t="n">
-        <v>1.636</v>
+        <v>1.6589</v>
       </c>
       <c r="S303" t="n">
-        <v>0.9695</v>
+        <v>0.9832</v>
       </c>
       <c r="T303" t="n">
-        <v>5.5357</v>
+        <v>5.6139</v>
       </c>
       <c r="U303" t="n">
-        <v>7.524</v>
+        <v>8.138999999999999</v>
       </c>
       <c r="V303" t="n">
-        <v>2.604</v>
+        <v>2.817</v>
       </c>
       <c r="W303" t="n">
-        <v>13.874</v>
+        <v>14.739</v>
       </c>
     </row>
     <row r="304">
@@ -26113,28 +26113,28 @@
         <v>-1</v>
       </c>
       <c r="F304" t="n">
-        <v>1.964</v>
+        <v>2.526</v>
       </c>
       <c r="G304" t="n">
         <v>0.953</v>
       </c>
       <c r="H304" t="n">
-        <v>1.872</v>
+        <v>2.407</v>
       </c>
       <c r="I304" t="n">
-        <v>1.872</v>
+        <v>2.407</v>
       </c>
       <c r="J304" t="n">
-        <v>1.9497</v>
+        <v>1.9612</v>
       </c>
       <c r="K304" t="n">
-        <v>1.062</v>
+        <v>1.0683</v>
       </c>
       <c r="L304" t="n">
-        <v>0.5795</v>
+        <v>0.5829</v>
       </c>
       <c r="M304" t="n">
-        <v>0.3083</v>
+        <v>0.3101</v>
       </c>
       <c r="N304" t="n">
         <v>0.9333</v>
@@ -26146,25 +26146,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q304" t="n">
-        <v>2.9027</v>
+        <v>2.9199</v>
       </c>
       <c r="R304" t="n">
-        <v>1.6206</v>
+        <v>1.6301</v>
       </c>
       <c r="S304" t="n">
-        <v>0.9605</v>
+        <v>0.9661</v>
       </c>
       <c r="T304" t="n">
-        <v>5.4837</v>
+        <v>5.516</v>
       </c>
       <c r="U304" t="n">
-        <v>7.356</v>
+        <v>7.923</v>
       </c>
       <c r="V304" t="n">
-        <v>2.546</v>
+        <v>2.742</v>
       </c>
       <c r="W304" t="n">
-        <v>13.635</v>
+        <v>14.437</v>
       </c>
     </row>
     <row r="305">
@@ -26190,28 +26190,28 @@
         <v>1</v>
       </c>
       <c r="F305" t="n">
-        <v>2.182</v>
+        <v>2.561</v>
       </c>
       <c r="G305" t="n">
         <v>0.953</v>
       </c>
       <c r="H305" t="n">
-        <v>2.08</v>
+        <v>2.441</v>
       </c>
       <c r="I305" t="n">
-        <v>2.08</v>
+        <v>2.441</v>
       </c>
       <c r="J305" t="n">
-        <v>1.9793</v>
+        <v>1.997</v>
       </c>
       <c r="K305" t="n">
-        <v>1.0781</v>
+        <v>1.0878</v>
       </c>
       <c r="L305" t="n">
-        <v>0.5883</v>
+        <v>0.5935</v>
       </c>
       <c r="M305" t="n">
-        <v>0.3129</v>
+        <v>0.3157</v>
       </c>
       <c r="N305" t="n">
         <v>0.9333</v>
@@ -26223,25 +26223,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q305" t="n">
-        <v>2.9467</v>
+        <v>2.9732</v>
       </c>
       <c r="R305" t="n">
-        <v>1.6452</v>
+        <v>1.6597</v>
       </c>
       <c r="S305" t="n">
-        <v>0.9748</v>
+        <v>0.9835</v>
       </c>
       <c r="T305" t="n">
-        <v>5.5667</v>
+        <v>5.6164</v>
       </c>
       <c r="U305" t="n">
-        <v>7.647</v>
+        <v>8.057</v>
       </c>
       <c r="V305" t="n">
-        <v>2.647</v>
+        <v>2.789</v>
       </c>
       <c r="W305" t="n">
-        <v>14.05</v>
+        <v>14.627</v>
       </c>
     </row>
     <row r="306">
@@ -26267,28 +26267,28 @@
         <v>1</v>
       </c>
       <c r="F306" t="n">
-        <v>2.22</v>
+        <v>2.778</v>
       </c>
       <c r="G306" t="n">
         <v>0.953</v>
       </c>
       <c r="H306" t="n">
-        <v>2.116</v>
+        <v>2.648</v>
       </c>
       <c r="I306" t="n">
-        <v>2.116</v>
+        <v>2.648</v>
       </c>
       <c r="J306" t="n">
-        <v>1.9961</v>
+        <v>2.0229</v>
       </c>
       <c r="K306" t="n">
-        <v>1.0873</v>
+        <v>1.1018</v>
       </c>
       <c r="L306" t="n">
-        <v>0.5931999999999999</v>
+        <v>0.6012</v>
       </c>
       <c r="M306" t="n">
-        <v>0.3156</v>
+        <v>0.3198</v>
       </c>
       <c r="N306" t="n">
         <v>0.9333</v>
@@ -26300,25 +26300,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q306" t="n">
-        <v>2.9718</v>
+        <v>3.0114</v>
       </c>
       <c r="R306" t="n">
-        <v>1.6589</v>
+        <v>1.6813</v>
       </c>
       <c r="S306" t="n">
-        <v>0.9832</v>
+        <v>0.9963</v>
       </c>
       <c r="T306" t="n">
-        <v>5.6139</v>
+        <v>5.689</v>
       </c>
       <c r="U306" t="n">
-        <v>7.73</v>
+        <v>8.337</v>
       </c>
       <c r="V306" t="n">
-        <v>2.676</v>
+        <v>2.886</v>
       </c>
       <c r="W306" t="n">
-        <v>14.168</v>
+        <v>15.015</v>
       </c>
     </row>
     <row r="307">
@@ -26344,28 +26344,28 @@
         <v>-1</v>
       </c>
       <c r="F307" t="n">
-        <v>2.087</v>
+        <v>1.974</v>
       </c>
       <c r="G307" t="n">
         <v>0.953</v>
       </c>
       <c r="H307" t="n">
-        <v>1.989</v>
+        <v>1.882</v>
       </c>
       <c r="I307" t="n">
-        <v>1.989</v>
+        <v>1.882</v>
       </c>
       <c r="J307" t="n">
-        <v>2.0131</v>
+        <v>1.873</v>
       </c>
       <c r="K307" t="n">
-        <v>1.0965</v>
+        <v>1.0202</v>
       </c>
       <c r="L307" t="n">
-        <v>0.5983000000000001</v>
+        <v>0.5566</v>
       </c>
       <c r="M307" t="n">
-        <v>0.3183</v>
+        <v>0.2961</v>
       </c>
       <c r="N307" t="n">
         <v>0.9333</v>
@@ -26377,25 +26377,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q307" t="n">
-        <v>2.997</v>
+        <v>2.7884</v>
       </c>
       <c r="R307" t="n">
-        <v>1.6731</v>
+        <v>1.5565</v>
       </c>
       <c r="S307" t="n">
-        <v>0.9916</v>
+        <v>0.9225</v>
       </c>
       <c r="T307" t="n">
-        <v>5.6617</v>
+        <v>5.2674</v>
       </c>
       <c r="U307" t="n">
-        <v>7.651</v>
+        <v>7.149</v>
       </c>
       <c r="V307" t="n">
-        <v>2.648</v>
+        <v>2.475</v>
       </c>
       <c r="W307" t="n">
-        <v>14.054</v>
+        <v>13.34</v>
       </c>
     </row>
     <row r="308">
@@ -26421,28 +26421,28 @@
         <v>1</v>
       </c>
       <c r="F308" t="n">
-        <v>2.228</v>
+        <v>2.903</v>
       </c>
       <c r="G308" t="n">
         <v>0.953</v>
       </c>
       <c r="H308" t="n">
-        <v>2.124</v>
+        <v>2.767</v>
       </c>
       <c r="I308" t="n">
-        <v>2.124</v>
+        <v>2.767</v>
       </c>
       <c r="J308" t="n">
-        <v>1.9663</v>
+        <v>2.0002</v>
       </c>
       <c r="K308" t="n">
-        <v>1.0711</v>
+        <v>1.0895</v>
       </c>
       <c r="L308" t="n">
-        <v>0.5844</v>
+        <v>0.5944</v>
       </c>
       <c r="M308" t="n">
-        <v>0.3109</v>
+        <v>0.3162</v>
       </c>
       <c r="N308" t="n">
         <v>0.9333</v>
@@ -26454,25 +26454,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q308" t="n">
-        <v>2.9275</v>
+        <v>2.9778</v>
       </c>
       <c r="R308" t="n">
-        <v>1.6343</v>
+        <v>1.6622</v>
       </c>
       <c r="S308" t="n">
-        <v>0.9686</v>
+        <v>0.9851</v>
       </c>
       <c r="T308" t="n">
-        <v>5.5304</v>
+        <v>5.6252</v>
       </c>
       <c r="U308" t="n">
-        <v>7.654</v>
+        <v>8.391999999999999</v>
       </c>
       <c r="V308" t="n">
-        <v>2.649</v>
+        <v>2.905</v>
       </c>
       <c r="W308" t="n">
-        <v>14.061</v>
+        <v>15.088</v>
       </c>
     </row>
     <row r="309">
@@ -26498,28 +26498,28 @@
         <v>-1</v>
       </c>
       <c r="F309" t="n">
-        <v>2.024</v>
+        <v>2.493</v>
       </c>
       <c r="G309" t="n">
         <v>0.953</v>
       </c>
       <c r="H309" t="n">
-        <v>1.929</v>
+        <v>2.376</v>
       </c>
       <c r="I309" t="n">
-        <v>1.929</v>
+        <v>2.376</v>
       </c>
       <c r="J309" t="n">
-        <v>1.9128</v>
+        <v>1.9173</v>
       </c>
       <c r="K309" t="n">
-        <v>1.0419</v>
+        <v>1.0443</v>
       </c>
       <c r="L309" t="n">
-        <v>0.5685</v>
+        <v>0.5698</v>
       </c>
       <c r="M309" t="n">
-        <v>0.3024</v>
+        <v>0.3031</v>
       </c>
       <c r="N309" t="n">
         <v>0.9333</v>
@@ -26531,25 +26531,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q309" t="n">
-        <v>2.8477</v>
+        <v>2.8543</v>
       </c>
       <c r="R309" t="n">
-        <v>1.5898</v>
+        <v>1.5934</v>
       </c>
       <c r="S309" t="n">
-        <v>0.9421</v>
+        <v>0.9443</v>
       </c>
       <c r="T309" t="n">
-        <v>5.3796</v>
+        <v>5.392</v>
       </c>
       <c r="U309" t="n">
-        <v>7.309</v>
+        <v>7.768</v>
       </c>
       <c r="V309" t="n">
-        <v>2.53</v>
+        <v>2.689</v>
       </c>
       <c r="W309" t="n">
-        <v>13.568</v>
+        <v>14.217</v>
       </c>
     </row>
     <row r="310">
@@ -26575,28 +26575,28 @@
         <v>-1</v>
       </c>
       <c r="F310" t="n">
-        <v>2.025</v>
+        <v>2.669</v>
       </c>
       <c r="G310" t="n">
         <v>0.953</v>
       </c>
       <c r="H310" t="n">
-        <v>1.93</v>
+        <v>2.544</v>
       </c>
       <c r="I310" t="n">
-        <v>1.93</v>
+        <v>2.544</v>
       </c>
       <c r="J310" t="n">
-        <v>1.9912</v>
+        <v>2.0058</v>
       </c>
       <c r="K310" t="n">
-        <v>1.0846</v>
+        <v>1.0926</v>
       </c>
       <c r="L310" t="n">
-        <v>0.5918</v>
+        <v>0.5961</v>
       </c>
       <c r="M310" t="n">
-        <v>0.3148</v>
+        <v>0.3171</v>
       </c>
       <c r="N310" t="n">
         <v>0.9333</v>
@@ -26608,25 +26608,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q310" t="n">
-        <v>2.9644</v>
+        <v>2.9863</v>
       </c>
       <c r="R310" t="n">
-        <v>1.655</v>
+        <v>1.667</v>
       </c>
       <c r="S310" t="n">
-        <v>0.9807</v>
+        <v>0.9879</v>
       </c>
       <c r="T310" t="n">
-        <v>5.6001</v>
+        <v>5.6412</v>
       </c>
       <c r="U310" t="n">
-        <v>7.53</v>
+        <v>8.185</v>
       </c>
       <c r="V310" t="n">
-        <v>2.606</v>
+        <v>2.833</v>
       </c>
       <c r="W310" t="n">
-        <v>13.884</v>
+        <v>14.805</v>
       </c>
     </row>
     <row r="311">
@@ -26652,28 +26652,28 @@
         <v>1</v>
       </c>
       <c r="F311" t="n">
-        <v>1.98</v>
+        <v>2.607</v>
       </c>
       <c r="G311" t="n">
         <v>0.953</v>
       </c>
       <c r="H311" t="n">
-        <v>1.887</v>
+        <v>2.485</v>
       </c>
       <c r="I311" t="n">
-        <v>1.887</v>
+        <v>2.485</v>
       </c>
       <c r="J311" t="n">
-        <v>1.9404</v>
+        <v>1.9722</v>
       </c>
       <c r="K311" t="n">
-        <v>1.0569</v>
+        <v>1.0742</v>
       </c>
       <c r="L311" t="n">
-        <v>0.5767</v>
+        <v>0.5861</v>
       </c>
       <c r="M311" t="n">
-        <v>0.3068</v>
+        <v>0.3118</v>
       </c>
       <c r="N311" t="n">
         <v>0.9333</v>
@@ -26685,25 +26685,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q311" t="n">
-        <v>2.8887</v>
+        <v>2.936</v>
       </c>
       <c r="R311" t="n">
-        <v>1.6127</v>
+        <v>1.639</v>
       </c>
       <c r="S311" t="n">
-        <v>0.9558</v>
+        <v>0.9714</v>
       </c>
       <c r="T311" t="n">
-        <v>5.4573</v>
+        <v>5.5464</v>
       </c>
       <c r="U311" t="n">
-        <v>7.344</v>
+        <v>8.031000000000001</v>
       </c>
       <c r="V311" t="n">
-        <v>2.542</v>
+        <v>2.78</v>
       </c>
       <c r="W311" t="n">
-        <v>13.618</v>
+        <v>14.587</v>
       </c>
     </row>
     <row r="312">
@@ -26729,28 +26729,28 @@
         <v>1</v>
       </c>
       <c r="F312" t="n">
-        <v>2.006</v>
+        <v>2.635</v>
       </c>
       <c r="G312" t="n">
         <v>0.953</v>
       </c>
       <c r="H312" t="n">
-        <v>1.912</v>
+        <v>2.512</v>
       </c>
       <c r="I312" t="n">
-        <v>1.912</v>
+        <v>2.512</v>
       </c>
       <c r="J312" t="n">
-        <v>1.937</v>
+        <v>1.9802</v>
       </c>
       <c r="K312" t="n">
-        <v>1.0551</v>
+        <v>1.0786</v>
       </c>
       <c r="L312" t="n">
-        <v>0.5757</v>
+        <v>0.5885</v>
       </c>
       <c r="M312" t="n">
-        <v>0.3062</v>
+        <v>0.3131</v>
       </c>
       <c r="N312" t="n">
         <v>0.9333</v>
@@ -26762,25 +26762,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q312" t="n">
-        <v>2.8838</v>
+        <v>2.948</v>
       </c>
       <c r="R312" t="n">
-        <v>1.6099</v>
+        <v>1.6457</v>
       </c>
       <c r="S312" t="n">
-        <v>0.9539</v>
+        <v>0.9754</v>
       </c>
       <c r="T312" t="n">
-        <v>5.4477</v>
+        <v>5.5692</v>
       </c>
       <c r="U312" t="n">
-        <v>7.36</v>
+        <v>8.081</v>
       </c>
       <c r="V312" t="n">
-        <v>2.548</v>
+        <v>2.797</v>
       </c>
       <c r="W312" t="n">
-        <v>13.641</v>
+        <v>14.658</v>
       </c>
     </row>
     <row r="313">
@@ -26806,28 +26806,28 @@
         <v>-1</v>
       </c>
       <c r="F313" t="n">
-        <v>2.087</v>
+        <v>2.821</v>
       </c>
       <c r="G313" t="n">
         <v>0.953</v>
       </c>
       <c r="H313" t="n">
-        <v>1.989</v>
+        <v>2.689</v>
       </c>
       <c r="I313" t="n">
-        <v>1.989</v>
+        <v>2.689</v>
       </c>
       <c r="J313" t="n">
-        <v>2.0131</v>
+        <v>2.0053</v>
       </c>
       <c r="K313" t="n">
-        <v>1.0965</v>
+        <v>1.0923</v>
       </c>
       <c r="L313" t="n">
-        <v>0.5983000000000001</v>
+        <v>0.596</v>
       </c>
       <c r="M313" t="n">
-        <v>0.3183</v>
+        <v>0.317</v>
       </c>
       <c r="N313" t="n">
         <v>0.9333</v>
@@ -26839,25 +26839,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q313" t="n">
-        <v>2.997</v>
+        <v>2.9855</v>
       </c>
       <c r="R313" t="n">
-        <v>1.6731</v>
+        <v>1.6667</v>
       </c>
       <c r="S313" t="n">
-        <v>0.9916</v>
+        <v>0.9876</v>
       </c>
       <c r="T313" t="n">
-        <v>5.6617</v>
+        <v>5.6398</v>
       </c>
       <c r="U313" t="n">
-        <v>7.651</v>
+        <v>8.329000000000001</v>
       </c>
       <c r="V313" t="n">
-        <v>2.648</v>
+        <v>2.883</v>
       </c>
       <c r="W313" t="n">
-        <v>14.054</v>
+        <v>15.001</v>
       </c>
     </row>
     <row r="314">
@@ -28192,28 +28192,28 @@
         <v>-1</v>
       </c>
       <c r="F331" t="n">
-        <v>2.565</v>
+        <v>2.604</v>
       </c>
       <c r="G331" t="n">
         <v>0.9</v>
       </c>
       <c r="H331" t="n">
-        <v>2.308</v>
+        <v>2.344</v>
       </c>
       <c r="I331" t="n">
-        <v>2.308</v>
+        <v>2.344</v>
       </c>
       <c r="J331" t="n">
-        <v>1.8416</v>
+        <v>1.8574</v>
       </c>
       <c r="K331" t="n">
-        <v>1.0031</v>
+        <v>1.0117</v>
       </c>
       <c r="L331" t="n">
-        <v>0.5473</v>
+        <v>0.552</v>
       </c>
       <c r="M331" t="n">
-        <v>0.2912</v>
+        <v>0.2936</v>
       </c>
       <c r="N331" t="n">
         <v>0.9543</v>
@@ -28225,25 +28225,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q331" t="n">
-        <v>2.8259</v>
+        <v>2.8502</v>
       </c>
       <c r="R331" t="n">
-        <v>1.6364</v>
+        <v>1.6505</v>
       </c>
       <c r="S331" t="n">
-        <v>0.9072</v>
+        <v>0.9147</v>
       </c>
       <c r="T331" t="n">
-        <v>5.3696</v>
+        <v>5.4153</v>
       </c>
       <c r="U331" t="n">
-        <v>7.678</v>
+        <v>7.759</v>
       </c>
       <c r="V331" t="n">
-        <v>2.658</v>
+        <v>2.686</v>
       </c>
       <c r="W331" t="n">
-        <v>14.122</v>
+        <v>14.237</v>
       </c>
     </row>
     <row r="332">
@@ -28269,28 +28269,28 @@
         <v>1</v>
       </c>
       <c r="F332" t="n">
-        <v>2.858</v>
+        <v>2.684</v>
       </c>
       <c r="G332" t="n">
         <v>0.9</v>
       </c>
       <c r="H332" t="n">
-        <v>2.572</v>
+        <v>2.416</v>
       </c>
       <c r="I332" t="n">
-        <v>2.572</v>
+        <v>2.416</v>
       </c>
       <c r="J332" t="n">
-        <v>1.8823</v>
+        <v>1.8889</v>
       </c>
       <c r="K332" t="n">
-        <v>1.0253</v>
+        <v>1.0289</v>
       </c>
       <c r="L332" t="n">
-        <v>0.5594</v>
+        <v>0.5614</v>
       </c>
       <c r="M332" t="n">
-        <v>0.2976</v>
+        <v>0.2986</v>
       </c>
       <c r="N332" t="n">
         <v>0.9543</v>
@@ -28302,25 +28302,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q332" t="n">
-        <v>2.8885</v>
+        <v>2.8986</v>
       </c>
       <c r="R332" t="n">
-        <v>1.6726</v>
+        <v>1.6786</v>
       </c>
       <c r="S332" t="n">
-        <v>0.9271</v>
+        <v>0.9303</v>
       </c>
       <c r="T332" t="n">
-        <v>5.4882</v>
+        <v>5.5075</v>
       </c>
       <c r="U332" t="n">
-        <v>8.06</v>
+        <v>7.924</v>
       </c>
       <c r="V332" t="n">
-        <v>2.79</v>
+        <v>2.743</v>
       </c>
       <c r="W332" t="n">
-        <v>14.655</v>
+        <v>14.469</v>
       </c>
     </row>
     <row r="333">
@@ -28423,28 +28423,28 @@
         <v>-1</v>
       </c>
       <c r="F334" t="n">
-        <v>2.813</v>
+        <v>1.987</v>
       </c>
       <c r="G334" t="n">
         <v>0.9</v>
       </c>
       <c r="H334" t="n">
-        <v>2.532</v>
+        <v>1.789</v>
       </c>
       <c r="I334" t="n">
-        <v>2.532</v>
+        <v>1.789</v>
       </c>
       <c r="J334" t="n">
-        <v>1.8726</v>
+        <v>1.8336</v>
       </c>
       <c r="K334" t="n">
-        <v>1.02</v>
+        <v>0.9988</v>
       </c>
       <c r="L334" t="n">
-        <v>0.5565</v>
+        <v>0.5449000000000001</v>
       </c>
       <c r="M334" t="n">
-        <v>0.2961</v>
+        <v>0.2899</v>
       </c>
       <c r="N334" t="n">
         <v>0.9543</v>
@@ -28456,25 +28456,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q334" t="n">
-        <v>2.8735</v>
+        <v>2.8138</v>
       </c>
       <c r="R334" t="n">
-        <v>1.6639</v>
+        <v>1.6293</v>
       </c>
       <c r="S334" t="n">
-        <v>0.9225</v>
+        <v>0.9032</v>
       </c>
       <c r="T334" t="n">
-        <v>5.4599</v>
+        <v>5.3462</v>
       </c>
       <c r="U334" t="n">
-        <v>7.992</v>
+        <v>7.135</v>
       </c>
       <c r="V334" t="n">
-        <v>2.766</v>
+        <v>2.47</v>
       </c>
       <c r="W334" t="n">
-        <v>14.56</v>
+        <v>13.357</v>
       </c>
     </row>
     <row r="335">
@@ -28500,28 +28500,28 @@
         <v>1</v>
       </c>
       <c r="F335" t="n">
-        <v>2.623</v>
+        <v>2.74</v>
       </c>
       <c r="G335" t="n">
         <v>0.9</v>
       </c>
       <c r="H335" t="n">
-        <v>2.361</v>
+        <v>2.466</v>
       </c>
       <c r="I335" t="n">
-        <v>2.361</v>
+        <v>2.466</v>
       </c>
       <c r="J335" t="n">
-        <v>1.855</v>
+        <v>1.8621</v>
       </c>
       <c r="K335" t="n">
-        <v>1.0104</v>
+        <v>1.0143</v>
       </c>
       <c r="L335" t="n">
-        <v>0.5513</v>
+        <v>0.5534</v>
       </c>
       <c r="M335" t="n">
-        <v>0.2933</v>
+        <v>0.2944</v>
       </c>
       <c r="N335" t="n">
         <v>0.9543</v>
@@ -28533,25 +28533,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q335" t="n">
-        <v>2.8465</v>
+        <v>2.8575</v>
       </c>
       <c r="R335" t="n">
-        <v>1.6484</v>
+        <v>1.6547</v>
       </c>
       <c r="S335" t="n">
-        <v>0.9137</v>
+        <v>0.9172</v>
       </c>
       <c r="T335" t="n">
-        <v>5.4086</v>
+        <v>5.4293</v>
       </c>
       <c r="U335" t="n">
-        <v>7.77</v>
+        <v>7.895</v>
       </c>
       <c r="V335" t="n">
-        <v>2.689</v>
+        <v>2.733</v>
       </c>
       <c r="W335" t="n">
-        <v>14.251</v>
+        <v>14.426</v>
       </c>
     </row>
     <row r="336">
@@ -28808,28 +28808,28 @@
         <v>1</v>
       </c>
       <c r="F339" t="n">
-        <v>2.631</v>
+        <v>2.623</v>
       </c>
       <c r="G339" t="n">
         <v>0.9</v>
       </c>
       <c r="H339" t="n">
-        <v>2.368</v>
+        <v>2.361</v>
       </c>
       <c r="I339" t="n">
-        <v>2.368</v>
+        <v>2.361</v>
       </c>
       <c r="J339" t="n">
-        <v>1.8798</v>
+        <v>1.8718</v>
       </c>
       <c r="K339" t="n">
-        <v>1.0239</v>
+        <v>1.0196</v>
       </c>
       <c r="L339" t="n">
-        <v>0.5587</v>
+        <v>0.5563</v>
       </c>
       <c r="M339" t="n">
-        <v>0.2972</v>
+        <v>0.2959</v>
       </c>
       <c r="N339" t="n">
         <v>0.9543</v>
@@ -28841,25 +28841,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q339" t="n">
-        <v>2.8845</v>
+        <v>2.8724</v>
       </c>
       <c r="R339" t="n">
-        <v>1.6705</v>
+        <v>1.6633</v>
       </c>
       <c r="S339" t="n">
-        <v>0.9258999999999999</v>
+        <v>0.9218</v>
       </c>
       <c r="T339" t="n">
-        <v>5.4809</v>
+        <v>5.4576</v>
       </c>
       <c r="U339" t="n">
-        <v>7.849</v>
+        <v>7.819</v>
       </c>
       <c r="V339" t="n">
-        <v>2.717</v>
+        <v>2.706</v>
       </c>
       <c r="W339" t="n">
-        <v>14.364</v>
+        <v>14.322</v>
       </c>
     </row>
     <row r="340">
@@ -29039,28 +29039,28 @@
         <v>-1</v>
       </c>
       <c r="F342" t="n">
-        <v>2.834</v>
+        <v>2.244</v>
       </c>
       <c r="G342" t="n">
         <v>0.98</v>
       </c>
       <c r="H342" t="n">
-        <v>2.776</v>
+        <v>2.199</v>
       </c>
       <c r="I342" t="n">
-        <v>2.776</v>
+        <v>2.199</v>
       </c>
       <c r="J342" t="n">
-        <v>2.0731</v>
+        <v>1.8834</v>
       </c>
       <c r="K342" t="n">
-        <v>1.1292</v>
+        <v>1.0259</v>
       </c>
       <c r="L342" t="n">
-        <v>0.6161</v>
+        <v>0.5598</v>
       </c>
       <c r="M342" t="n">
-        <v>0.3278</v>
+        <v>0.2978</v>
       </c>
       <c r="N342" t="n">
         <v>0.9074</v>
@@ -29072,25 +29072,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q342" t="n">
-        <v>2.9693</v>
+        <v>2.6977</v>
       </c>
       <c r="R342" t="n">
-        <v>1.8421</v>
+        <v>1.6738</v>
       </c>
       <c r="S342" t="n">
-        <v>1.0212</v>
+        <v>0.9278</v>
       </c>
       <c r="T342" t="n">
-        <v>5.8327</v>
+        <v>5.2993</v>
       </c>
       <c r="U342" t="n">
-        <v>8.609</v>
+        <v>7.498</v>
       </c>
       <c r="V342" t="n">
-        <v>2.98</v>
+        <v>2.595</v>
       </c>
       <c r="W342" t="n">
-        <v>15.422</v>
+        <v>13.864</v>
       </c>
     </row>
     <row r="343">
@@ -30271,28 +30271,28 @@
         <v>1</v>
       </c>
       <c r="F358" t="n">
-        <v>2.615</v>
+        <v>2.135</v>
       </c>
       <c r="G358" t="n">
         <v>0.974</v>
       </c>
       <c r="H358" t="n">
-        <v>2.547</v>
+        <v>2.079</v>
       </c>
       <c r="I358" t="n">
-        <v>2.547</v>
+        <v>2.079</v>
       </c>
       <c r="J358" t="n">
-        <v>2.0727</v>
+        <v>1.9603</v>
       </c>
       <c r="K358" t="n">
-        <v>1.129</v>
+        <v>1.0678</v>
       </c>
       <c r="L358" t="n">
-        <v>0.616</v>
+        <v>0.5826</v>
       </c>
       <c r="M358" t="n">
-        <v>0.3277</v>
+        <v>0.3099</v>
       </c>
       <c r="N358" t="n">
         <v>0.9492</v>
@@ -30304,25 +30304,25 @@
         <v>0.5667</v>
       </c>
       <c r="Q358" t="n">
-        <v>3.1576</v>
+        <v>2.9864</v>
       </c>
       <c r="R358" t="n">
-        <v>1.913</v>
+        <v>1.8093</v>
       </c>
       <c r="S358" t="n">
-        <v>0.7865</v>
+        <v>0.7438</v>
       </c>
       <c r="T358" t="n">
-        <v>5.8571</v>
+        <v>5.5395</v>
       </c>
       <c r="U358" t="n">
-        <v>8.404</v>
+        <v>7.619</v>
       </c>
       <c r="V358" t="n">
-        <v>2.909</v>
+        <v>2.637</v>
       </c>
       <c r="W358" t="n">
-        <v>15.145</v>
+        <v>14.039</v>
       </c>
     </row>
     <row r="359">
@@ -30425,28 +30425,28 @@
         <v>-1</v>
       </c>
       <c r="F360" t="n">
-        <v>2.337</v>
+        <v>2.31</v>
       </c>
       <c r="G360" t="n">
         <v>0.974</v>
       </c>
       <c r="H360" t="n">
-        <v>2.276</v>
+        <v>2.25</v>
       </c>
       <c r="I360" t="n">
-        <v>2.276</v>
+        <v>2.25</v>
       </c>
       <c r="J360" t="n">
-        <v>1.8658</v>
+        <v>1.9168</v>
       </c>
       <c r="K360" t="n">
-        <v>1.0163</v>
+        <v>1.0441</v>
       </c>
       <c r="L360" t="n">
-        <v>0.5545</v>
+        <v>0.5697</v>
       </c>
       <c r="M360" t="n">
-        <v>0.295</v>
+        <v>0.303</v>
       </c>
       <c r="N360" t="n">
         <v>0.9492</v>
@@ -30458,25 +30458,25 @@
         <v>0.5667</v>
       </c>
       <c r="Q360" t="n">
-        <v>2.8424</v>
+        <v>2.9201</v>
       </c>
       <c r="R360" t="n">
-        <v>1.722</v>
+        <v>1.7692</v>
       </c>
       <c r="S360" t="n">
-        <v>0.7081</v>
+        <v>0.7272999999999999</v>
       </c>
       <c r="T360" t="n">
-        <v>5.2724</v>
+        <v>5.4166</v>
       </c>
       <c r="U360" t="n">
-        <v>7.548</v>
+        <v>7.667</v>
       </c>
       <c r="V360" t="n">
-        <v>2.613</v>
+        <v>2.654</v>
       </c>
       <c r="W360" t="n">
-        <v>13.937</v>
+        <v>14.107</v>
       </c>
     </row>
     <row r="361">
@@ -31041,28 +31041,28 @@
         <v>1</v>
       </c>
       <c r="F368" t="n">
-        <v>3.348</v>
+        <v>3.235</v>
       </c>
       <c r="G368" t="n">
         <v>0.971</v>
       </c>
       <c r="H368" t="n">
-        <v>3.251</v>
+        <v>3.141</v>
       </c>
       <c r="I368" t="n">
-        <v>3.251</v>
+        <v>3.141</v>
       </c>
       <c r="J368" t="n">
-        <v>1.8376</v>
+        <v>1.8759</v>
       </c>
       <c r="K368" t="n">
-        <v>1.0009</v>
+        <v>1.0218</v>
       </c>
       <c r="L368" t="n">
-        <v>0.5461</v>
+        <v>0.5575</v>
       </c>
       <c r="M368" t="n">
-        <v>0.2905</v>
+        <v>0.2966</v>
       </c>
       <c r="N368" t="n">
         <v>0.9414</v>
@@ -31074,25 +31074,25 @@
         <v>0.7455000000000001</v>
       </c>
       <c r="Q368" t="n">
-        <v>2.7681</v>
+        <v>2.8259</v>
       </c>
       <c r="R368" t="n">
-        <v>1.4291</v>
+        <v>1.459</v>
       </c>
       <c r="S368" t="n">
-        <v>1.0089</v>
+        <v>1.0301</v>
       </c>
       <c r="T368" t="n">
-        <v>5.2061</v>
+        <v>5.315</v>
       </c>
       <c r="U368" t="n">
-        <v>8.457000000000001</v>
+        <v>8.456</v>
       </c>
       <c r="V368" t="n">
         <v>2.927</v>
       </c>
       <c r="W368" t="n">
-        <v>15.181</v>
+        <v>15.19</v>
       </c>
     </row>
     <row r="369">
@@ -31118,28 +31118,28 @@
         <v>-1</v>
       </c>
       <c r="F369" t="n">
-        <v>2.857</v>
+        <v>2.94</v>
       </c>
       <c r="G369" t="n">
         <v>0.971</v>
       </c>
       <c r="H369" t="n">
-        <v>2.774</v>
+        <v>2.855</v>
       </c>
       <c r="I369" t="n">
-        <v>2.774</v>
+        <v>2.855</v>
       </c>
       <c r="J369" t="n">
-        <v>1.8196</v>
+        <v>1.8626</v>
       </c>
       <c r="K369" t="n">
-        <v>0.9911</v>
+        <v>1.0146</v>
       </c>
       <c r="L369" t="n">
-        <v>0.5407999999999999</v>
+        <v>0.5536</v>
       </c>
       <c r="M369" t="n">
-        <v>0.2877</v>
+        <v>0.2945</v>
       </c>
       <c r="N369" t="n">
         <v>0.9414</v>
@@ -31151,25 +31151,25 @@
         <v>0.7455000000000001</v>
       </c>
       <c r="Q369" t="n">
-        <v>2.741</v>
+        <v>2.806</v>
       </c>
       <c r="R369" t="n">
-        <v>1.4153</v>
+        <v>1.4488</v>
       </c>
       <c r="S369" t="n">
-        <v>0.9992</v>
+        <v>1.0228</v>
       </c>
       <c r="T369" t="n">
-        <v>5.1554</v>
+        <v>5.2775</v>
       </c>
       <c r="U369" t="n">
-        <v>7.929</v>
+        <v>8.132</v>
       </c>
       <c r="V369" t="n">
-        <v>2.745</v>
+        <v>2.815</v>
       </c>
       <c r="W369" t="n">
-        <v>14.462</v>
+        <v>14.749</v>
       </c>
     </row>
     <row r="370">
@@ -31888,28 +31888,28 @@
         <v>-1</v>
       </c>
       <c r="F379" t="n">
-        <v>2.864</v>
+        <v>2.82</v>
       </c>
       <c r="G379" t="n">
         <v>0.956</v>
       </c>
       <c r="H379" t="n">
-        <v>2.739</v>
+        <v>2.697</v>
       </c>
       <c r="I379" t="n">
-        <v>2.739</v>
+        <v>2.697</v>
       </c>
       <c r="J379" t="n">
-        <v>1.8999</v>
+        <v>1.8987</v>
       </c>
       <c r="K379" t="n">
-        <v>1.0349</v>
+        <v>1.0342</v>
       </c>
       <c r="L379" t="n">
-        <v>0.5646</v>
+        <v>0.5643</v>
       </c>
       <c r="M379" t="n">
-        <v>0.3004</v>
+        <v>0.3002</v>
       </c>
       <c r="N379" t="n">
         <v>0.9543</v>
@@ -31921,25 +31921,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q379" t="n">
-        <v>2.9155</v>
+        <v>2.9135</v>
       </c>
       <c r="R379" t="n">
-        <v>1.6882</v>
+        <v>1.6873</v>
       </c>
       <c r="S379" t="n">
-        <v>0.9359</v>
+        <v>0.9352</v>
       </c>
       <c r="T379" t="n">
-        <v>5.5395</v>
+        <v>5.536</v>
       </c>
       <c r="U379" t="n">
-        <v>8.279</v>
+        <v>8.233000000000001</v>
       </c>
       <c r="V379" t="n">
-        <v>2.866</v>
+        <v>2.85</v>
       </c>
       <c r="W379" t="n">
-        <v>15.016</v>
+        <v>14.953</v>
       </c>
     </row>
     <row r="380">
@@ -33890,28 +33890,28 @@
         <v>-1</v>
       </c>
       <c r="F405" t="n">
-        <v>2.062</v>
+        <v>2.045</v>
       </c>
       <c r="G405" t="n">
         <v>1</v>
       </c>
       <c r="H405" t="n">
-        <v>2.062</v>
+        <v>2.045</v>
       </c>
       <c r="I405" t="n">
-        <v>2.062</v>
+        <v>2.045</v>
       </c>
       <c r="J405" t="n">
-        <v>1.8951</v>
+        <v>1.9212</v>
       </c>
       <c r="K405" t="n">
-        <v>1.0323</v>
+        <v>1.0465</v>
       </c>
       <c r="L405" t="n">
-        <v>0.5632</v>
+        <v>0.571</v>
       </c>
       <c r="M405" t="n">
-        <v>0.2996</v>
+        <v>0.3037</v>
       </c>
       <c r="N405" t="n">
         <v>0.9543</v>
@@ -33923,25 +33923,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q405" t="n">
-        <v>2.9082</v>
+        <v>2.9482</v>
       </c>
       <c r="R405" t="n">
-        <v>1.684</v>
+        <v>1.7073</v>
       </c>
       <c r="S405" t="n">
-        <v>0.9334</v>
+        <v>0.9461000000000001</v>
       </c>
       <c r="T405" t="n">
-        <v>5.5255</v>
+        <v>5.6016</v>
       </c>
       <c r="U405" t="n">
-        <v>7.588</v>
+        <v>7.647</v>
       </c>
       <c r="V405" t="n">
-        <v>2.626</v>
+        <v>2.647</v>
       </c>
       <c r="W405" t="n">
-        <v>14.093</v>
+        <v>14.176</v>
       </c>
     </row>
     <row r="406">
@@ -34352,28 +34352,28 @@
         <v>1</v>
       </c>
       <c r="F411" t="n">
-        <v>2.25</v>
+        <v>2.373</v>
       </c>
       <c r="G411" t="n">
         <v>1</v>
       </c>
       <c r="H411" t="n">
-        <v>2.25</v>
+        <v>2.373</v>
       </c>
       <c r="I411" t="n">
-        <v>2.25</v>
+        <v>2.373</v>
       </c>
       <c r="J411" t="n">
-        <v>1.9184</v>
+        <v>1.9037</v>
       </c>
       <c r="K411" t="n">
-        <v>1.0449</v>
+        <v>1.0369</v>
       </c>
       <c r="L411" t="n">
-        <v>0.5701000000000001</v>
+        <v>0.5658</v>
       </c>
       <c r="M411" t="n">
-        <v>0.3033</v>
+        <v>0.301</v>
       </c>
       <c r="N411" t="n">
         <v>0.9543</v>
@@ -34385,25 +34385,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q411" t="n">
-        <v>2.9437</v>
+        <v>2.9212</v>
       </c>
       <c r="R411" t="n">
-        <v>1.7046</v>
+        <v>1.6917</v>
       </c>
       <c r="S411" t="n">
-        <v>0.9449</v>
+        <v>0.9377</v>
       </c>
       <c r="T411" t="n">
-        <v>5.5932</v>
+        <v>5.5506</v>
       </c>
       <c r="U411" t="n">
-        <v>7.843</v>
+        <v>7.924</v>
       </c>
       <c r="V411" t="n">
-        <v>2.715</v>
+        <v>2.743</v>
       </c>
       <c r="W411" t="n">
-        <v>14.456</v>
+        <v>14.569</v>
       </c>
     </row>
     <row r="412">

--- a/projections/kicker_2026_combined.xlsx
+++ b/projections/kicker_2026_combined.xlsx
@@ -544,16 +544,16 @@
         <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>39.85</v>
+        <v>39.63</v>
       </c>
       <c r="E2" t="n">
-        <v>38.22</v>
+        <v>38.01</v>
       </c>
       <c r="F2" t="n">
-        <v>38.22</v>
+        <v>38.01</v>
       </c>
       <c r="G2" t="n">
-        <v>22.66</v>
+        <v>22.65</v>
       </c>
       <c r="H2" t="n">
         <v>12.34</v>
@@ -565,10 +565,10 @@
         <v>3.58</v>
       </c>
       <c r="K2" t="n">
-        <v>66.06</v>
+        <v>66.05</v>
       </c>
       <c r="L2" t="n">
-        <v>104.28</v>
+        <v>104.06</v>
       </c>
       <c r="M2" t="n">
         <v>0.959</v>
@@ -583,16 +583,16 @@
         <v>0.6859</v>
       </c>
       <c r="Q2" t="n">
-        <v>73.66</v>
+        <v>73.47</v>
       </c>
       <c r="R2" t="n">
-        <v>134.87</v>
+        <v>134.58</v>
       </c>
       <c r="S2" t="n">
         <v>102.35</v>
       </c>
       <c r="T2" t="n">
-        <v>1.93</v>
+        <v>1.71</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
@@ -612,31 +612,31 @@
         <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>31.56</v>
+        <v>31.07</v>
       </c>
       <c r="E3" t="n">
-        <v>29.64</v>
+        <v>29.17</v>
       </c>
       <c r="F3" t="n">
-        <v>29.64</v>
+        <v>29.17</v>
       </c>
       <c r="G3" t="n">
-        <v>23.25</v>
+        <v>23.18</v>
       </c>
       <c r="H3" t="n">
-        <v>12.66</v>
+        <v>12.63</v>
       </c>
       <c r="I3" t="n">
-        <v>6.91</v>
+        <v>6.89</v>
       </c>
       <c r="J3" t="n">
-        <v>3.68</v>
+        <v>3.67</v>
       </c>
       <c r="K3" t="n">
-        <v>70.14</v>
+        <v>69.94</v>
       </c>
       <c r="L3" t="n">
-        <v>99.78</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="M3" t="n">
         <v>0.9389999999999999</v>
@@ -651,16 +651,16 @@
         <v>0.6604</v>
       </c>
       <c r="Q3" t="n">
-        <v>69.38</v>
+        <v>68.84999999999999</v>
       </c>
       <c r="R3" t="n">
-        <v>130.14</v>
+        <v>129.33</v>
       </c>
       <c r="S3" t="n">
         <v>102.35</v>
       </c>
       <c r="T3" t="n">
-        <v>-2.57</v>
+        <v>-3.25</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
@@ -680,31 +680,31 @@
         <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>32.22</v>
+        <v>32.01</v>
       </c>
       <c r="E4" t="n">
-        <v>30.72</v>
+        <v>30.52</v>
       </c>
       <c r="F4" t="n">
-        <v>30.72</v>
+        <v>30.52</v>
       </c>
       <c r="G4" t="n">
-        <v>23.06</v>
+        <v>23.02</v>
       </c>
       <c r="H4" t="n">
-        <v>12.56</v>
+        <v>12.54</v>
       </c>
       <c r="I4" t="n">
-        <v>6.85</v>
+        <v>6.84</v>
       </c>
       <c r="J4" t="n">
-        <v>3.65</v>
+        <v>3.64</v>
       </c>
       <c r="K4" t="n">
-        <v>68.43000000000001</v>
+        <v>68.3</v>
       </c>
       <c r="L4" t="n">
-        <v>99.16</v>
+        <v>98.81999999999999</v>
       </c>
       <c r="M4" t="n">
         <v>0.953</v>
@@ -719,16 +719,16 @@
         <v>0.6744</v>
       </c>
       <c r="Q4" t="n">
-        <v>68.98</v>
+        <v>68.77</v>
       </c>
       <c r="R4" t="n">
-        <v>129.27</v>
+        <v>128.9</v>
       </c>
       <c r="S4" t="n">
         <v>104.47</v>
       </c>
       <c r="T4" t="n">
-        <v>-5.31</v>
+        <v>-5.65</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
@@ -748,19 +748,19 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>29.69</v>
+        <v>29.49</v>
       </c>
       <c r="E5" t="n">
-        <v>28.78</v>
+        <v>28.58</v>
       </c>
       <c r="F5" t="n">
-        <v>28.78</v>
+        <v>28.58</v>
       </c>
       <c r="G5" t="n">
-        <v>21.99</v>
+        <v>22.01</v>
       </c>
       <c r="H5" t="n">
-        <v>11.98</v>
+        <v>11.99</v>
       </c>
       <c r="I5" t="n">
         <v>6.54</v>
@@ -769,10 +769,10 @@
         <v>3.48</v>
       </c>
       <c r="K5" t="n">
-        <v>69.40000000000001</v>
+        <v>69.47</v>
       </c>
       <c r="L5" t="n">
-        <v>98.18000000000001</v>
+        <v>98.06</v>
       </c>
       <c r="M5" t="n">
         <v>0.969</v>
@@ -787,16 +787,16 @@
         <v>0.7955</v>
       </c>
       <c r="Q5" t="n">
-        <v>68.64</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="R5" t="n">
-        <v>127.71</v>
+        <v>127.51</v>
       </c>
       <c r="S5" t="n">
         <v>117.76</v>
       </c>
       <c r="T5" t="n">
-        <v>-19.58</v>
+        <v>-19.7</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
@@ -804,46 +804,46 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Will Reichard</t>
+          <t>Ryan Fitzgerald</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>23.8</v>
+        <v>30.35</v>
       </c>
       <c r="E6" t="n">
-        <v>23.8</v>
+        <v>27.31</v>
       </c>
       <c r="F6" t="n">
-        <v>23.8</v>
+        <v>27.31</v>
       </c>
       <c r="G6" t="n">
-        <v>23.68</v>
+        <v>22.37</v>
       </c>
       <c r="H6" t="n">
-        <v>12.9</v>
+        <v>12.19</v>
       </c>
       <c r="I6" t="n">
-        <v>7.04</v>
+        <v>6.65</v>
       </c>
       <c r="J6" t="n">
-        <v>3.74</v>
+        <v>3.54</v>
       </c>
       <c r="K6" t="n">
-        <v>69.05</v>
+        <v>65.23</v>
       </c>
       <c r="L6" t="n">
-        <v>92.84</v>
+        <v>92.54000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="N6" t="n">
         <v>0.9543</v>
@@ -855,16 +855,16 @@
         <v>0.6859</v>
       </c>
       <c r="Q6" t="n">
-        <v>63.57</v>
+        <v>63.86</v>
       </c>
       <c r="R6" t="n">
-        <v>122.1</v>
+        <v>121.22</v>
       </c>
       <c r="S6" t="n">
-        <v>102.35</v>
+        <v>97.41</v>
       </c>
       <c r="T6" t="n">
-        <v>-9.51</v>
+        <v>-4.87</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
@@ -872,46 +872,46 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ryan Fitzgerald</t>
+          <t>Will Reichard</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>30.59</v>
+        <v>23.6</v>
       </c>
       <c r="E7" t="n">
-        <v>27.53</v>
+        <v>23.6</v>
       </c>
       <c r="F7" t="n">
-        <v>27.53</v>
+        <v>23.6</v>
       </c>
       <c r="G7" t="n">
-        <v>22.39</v>
+        <v>23.62</v>
       </c>
       <c r="H7" t="n">
-        <v>12.2</v>
+        <v>12.87</v>
       </c>
       <c r="I7" t="n">
-        <v>6.65</v>
+        <v>7.02</v>
       </c>
       <c r="J7" t="n">
-        <v>3.54</v>
+        <v>3.73</v>
       </c>
       <c r="K7" t="n">
-        <v>65.28</v>
+        <v>68.87</v>
       </c>
       <c r="L7" t="n">
-        <v>92.81</v>
+        <v>92.47</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="N7" t="n">
         <v>0.9543</v>
@@ -923,16 +923,16 @@
         <v>0.6859</v>
       </c>
       <c r="Q7" t="n">
-        <v>64.06</v>
+        <v>63.32</v>
       </c>
       <c r="R7" t="n">
-        <v>121.55</v>
+        <v>121.66</v>
       </c>
       <c r="S7" t="n">
-        <v>97.41</v>
+        <v>102.35</v>
       </c>
       <c r="T7" t="n">
-        <v>-4.6</v>
+        <v>-9.880000000000001</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
@@ -1020,19 +1020,19 @@
         <v>11</v>
       </c>
       <c r="D9" t="n">
-        <v>31.34</v>
+        <v>31.38</v>
       </c>
       <c r="E9" t="n">
-        <v>30.94</v>
+        <v>30.98</v>
       </c>
       <c r="F9" t="n">
-        <v>30.94</v>
+        <v>30.98</v>
       </c>
       <c r="G9" t="n">
-        <v>20.98</v>
+        <v>21.01</v>
       </c>
       <c r="H9" t="n">
-        <v>11.43</v>
+        <v>11.44</v>
       </c>
       <c r="I9" t="n">
         <v>6.24</v>
@@ -1041,10 +1041,10 @@
         <v>3.32</v>
       </c>
       <c r="K9" t="n">
-        <v>61.17</v>
+        <v>61.26</v>
       </c>
       <c r="L9" t="n">
-        <v>92.11</v>
+        <v>92.23999999999999</v>
       </c>
       <c r="M9" t="n">
         <v>0.987</v>
@@ -1059,16 +1059,16 @@
         <v>0.6859</v>
       </c>
       <c r="Q9" t="n">
-        <v>64.33</v>
+        <v>64.48999999999999</v>
       </c>
       <c r="R9" t="n">
-        <v>119.87</v>
+        <v>119.99</v>
       </c>
       <c r="S9" t="n">
         <v>95.76000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>-3.65</v>
+        <v>-3.52</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
@@ -1088,19 +1088,19 @@
         <v>11</v>
       </c>
       <c r="D10" t="n">
-        <v>27.06</v>
+        <v>27.11</v>
       </c>
       <c r="E10" t="n">
-        <v>25.27</v>
+        <v>25.32</v>
       </c>
       <c r="F10" t="n">
-        <v>25.27</v>
+        <v>25.32</v>
       </c>
       <c r="G10" t="n">
-        <v>21.94</v>
+        <v>21.95</v>
       </c>
       <c r="H10" t="n">
-        <v>11.95</v>
+        <v>11.96</v>
       </c>
       <c r="I10" t="n">
         <v>6.52</v>
@@ -1109,10 +1109,10 @@
         <v>3.47</v>
       </c>
       <c r="K10" t="n">
-        <v>66.56999999999999</v>
+        <v>66.59</v>
       </c>
       <c r="L10" t="n">
-        <v>91.84999999999999</v>
+        <v>91.91</v>
       </c>
       <c r="M10" t="n">
         <v>0.9340000000000001</v>
@@ -1127,16 +1127,16 @@
         <v>0.7391</v>
       </c>
       <c r="Q10" t="n">
-        <v>63.98</v>
+        <v>64.05</v>
       </c>
       <c r="R10" t="n">
-        <v>119.66</v>
+        <v>119.79</v>
       </c>
       <c r="S10" t="n">
         <v>101.59</v>
       </c>
       <c r="T10" t="n">
-        <v>-9.74</v>
+        <v>-9.68</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         <v>0.6859</v>
       </c>
       <c r="Q11" t="n">
-        <v>62.41</v>
+        <v>62.4</v>
       </c>
       <c r="R11" t="n">
-        <v>121.14</v>
+        <v>121.13</v>
       </c>
       <c r="S11" t="n">
         <v>82.59</v>
@@ -1331,10 +1331,10 @@
         <v>0.6859</v>
       </c>
       <c r="Q13" t="n">
-        <v>63.61</v>
+        <v>63.6</v>
       </c>
       <c r="R13" t="n">
-        <v>118.7</v>
+        <v>118.71</v>
       </c>
       <c r="S13" t="n">
         <v>94.47</v>
@@ -1399,7 +1399,7 @@
         <v>0.8254</v>
       </c>
       <c r="Q14" t="n">
-        <v>62.79</v>
+        <v>62.73</v>
       </c>
       <c r="R14" t="n">
         <v>118.65</v>
@@ -1416,67 +1416,67 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Dominic Zvada</t>
+          <t>Cameron Dicker</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>26.55</v>
+        <v>19.63</v>
       </c>
       <c r="E15" t="n">
-        <v>25.25</v>
+        <v>19.02</v>
       </c>
       <c r="F15" t="n">
-        <v>25.25</v>
+        <v>19.02</v>
       </c>
       <c r="G15" t="n">
-        <v>22.22</v>
+        <v>22.02</v>
       </c>
       <c r="H15" t="n">
-        <v>12.1</v>
+        <v>11.99</v>
       </c>
       <c r="I15" t="n">
-        <v>6.6</v>
+        <v>6.54</v>
       </c>
       <c r="J15" t="n">
-        <v>3.51</v>
+        <v>3.48</v>
       </c>
       <c r="K15" t="n">
-        <v>64.78</v>
+        <v>70.70999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>90.03</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>0.951</v>
+        <v>0.969</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9543</v>
+        <v>0.9857</v>
       </c>
       <c r="O15" t="n">
-        <v>0.798</v>
+        <v>0.9512</v>
       </c>
       <c r="P15" t="n">
         <v>0.6859</v>
       </c>
       <c r="Q15" t="n">
-        <v>62.77</v>
+        <v>61.33</v>
       </c>
       <c r="R15" t="n">
-        <v>117.33</v>
+        <v>118.09</v>
       </c>
       <c r="S15" t="n">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="T15" t="n">
-        <v>2.03</v>
+        <v>-20.26</v>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
@@ -1484,67 +1484,67 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cameron Dicker</t>
+          <t>Dominic Zvada</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>11</v>
       </c>
       <c r="D16" t="n">
-        <v>19.74</v>
+        <v>26.13</v>
       </c>
       <c r="E16" t="n">
-        <v>19.14</v>
+        <v>24.85</v>
       </c>
       <c r="F16" t="n">
-        <v>19.14</v>
+        <v>24.85</v>
       </c>
       <c r="G16" t="n">
-        <v>22.01</v>
+        <v>22.25</v>
       </c>
       <c r="H16" t="n">
-        <v>11.99</v>
+        <v>12.12</v>
       </c>
       <c r="I16" t="n">
-        <v>6.54</v>
+        <v>6.61</v>
       </c>
       <c r="J16" t="n">
-        <v>3.48</v>
+        <v>3.52</v>
       </c>
       <c r="K16" t="n">
-        <v>70.7</v>
+        <v>64.86</v>
       </c>
       <c r="L16" t="n">
-        <v>89.84</v>
+        <v>89.70999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>0.969</v>
+        <v>0.951</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9857</v>
+        <v>0.9543</v>
       </c>
       <c r="O16" t="n">
-        <v>0.9512</v>
+        <v>0.798</v>
       </c>
       <c r="P16" t="n">
         <v>0.6859</v>
       </c>
       <c r="Q16" t="n">
-        <v>61.42</v>
+        <v>62.5</v>
       </c>
       <c r="R16" t="n">
-        <v>118.26</v>
+        <v>116.92</v>
       </c>
       <c r="S16" t="n">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="T16" t="n">
-        <v>-20.16</v>
+        <v>1.71</v>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
@@ -1564,31 +1564,31 @@
         <v>11</v>
       </c>
       <c r="D17" t="n">
-        <v>30.66</v>
+        <v>31.01</v>
       </c>
       <c r="E17" t="n">
-        <v>28.04</v>
+        <v>28.36</v>
       </c>
       <c r="F17" t="n">
-        <v>28.04</v>
+        <v>28.36</v>
       </c>
       <c r="G17" t="n">
-        <v>20.57</v>
+        <v>20.47</v>
       </c>
       <c r="H17" t="n">
-        <v>11.2</v>
+        <v>11.15</v>
       </c>
       <c r="I17" t="n">
-        <v>6.11</v>
+        <v>6.08</v>
       </c>
       <c r="J17" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="K17" t="n">
-        <v>61.19</v>
+        <v>60.89</v>
       </c>
       <c r="L17" t="n">
-        <v>89.22</v>
+        <v>89.26000000000001</v>
       </c>
       <c r="M17" t="n">
         <v>0.915</v>
@@ -1603,16 +1603,16 @@
         <v>0.6859</v>
       </c>
       <c r="Q17" t="n">
-        <v>61.99</v>
+        <v>61.98</v>
       </c>
       <c r="R17" t="n">
-        <v>116.48</v>
+        <v>116.51</v>
       </c>
       <c r="S17" t="n">
         <v>97.06</v>
       </c>
       <c r="T17" t="n">
-        <v>-7.84</v>
+        <v>-7.8</v>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
@@ -1620,67 +1620,67 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Jason Myers</t>
+          <t>Cairo Santos</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>11</v>
       </c>
       <c r="D18" t="n">
-        <v>26.36</v>
+        <v>27.07</v>
       </c>
       <c r="E18" t="n">
-        <v>24.51</v>
+        <v>25.88</v>
       </c>
       <c r="F18" t="n">
-        <v>24.51</v>
+        <v>25.88</v>
       </c>
       <c r="G18" t="n">
-        <v>21.73</v>
+        <v>21.82</v>
       </c>
       <c r="H18" t="n">
-        <v>11.84</v>
+        <v>11.89</v>
       </c>
       <c r="I18" t="n">
-        <v>6.46</v>
+        <v>6.48</v>
       </c>
       <c r="J18" t="n">
-        <v>3.44</v>
+        <v>3.45</v>
       </c>
       <c r="K18" t="n">
-        <v>64.11</v>
+        <v>62.48</v>
       </c>
       <c r="L18" t="n">
-        <v>88.62</v>
+        <v>88.36</v>
       </c>
       <c r="M18" t="n">
-        <v>0.93</v>
+        <v>0.956</v>
       </c>
       <c r="N18" t="n">
-        <v>0.9408</v>
+        <v>0.9515</v>
       </c>
       <c r="O18" t="n">
-        <v>0.8447</v>
+        <v>0.7835</v>
       </c>
       <c r="P18" t="n">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="Q18" t="n">
-        <v>61.51</v>
+        <v>61.33</v>
       </c>
       <c r="R18" t="n">
-        <v>115.72</v>
+        <v>115.4</v>
       </c>
       <c r="S18" t="n">
-        <v>95.76000000000001</v>
+        <v>97.06</v>
       </c>
       <c r="T18" t="n">
-        <v>-7.14</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
@@ -1688,67 +1688,67 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cairo Santos</t>
+          <t>Jason Myers</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>11</v>
       </c>
       <c r="D19" t="n">
-        <v>27.07</v>
+        <v>26.01</v>
       </c>
       <c r="E19" t="n">
-        <v>25.88</v>
+        <v>24.19</v>
       </c>
       <c r="F19" t="n">
-        <v>25.88</v>
+        <v>24.19</v>
       </c>
       <c r="G19" t="n">
-        <v>21.82</v>
+        <v>21.73</v>
       </c>
       <c r="H19" t="n">
-        <v>11.89</v>
+        <v>11.84</v>
       </c>
       <c r="I19" t="n">
-        <v>6.48</v>
+        <v>6.46</v>
       </c>
       <c r="J19" t="n">
-        <v>3.45</v>
+        <v>3.44</v>
       </c>
       <c r="K19" t="n">
-        <v>62.48</v>
+        <v>64.11</v>
       </c>
       <c r="L19" t="n">
-        <v>88.36</v>
+        <v>88.3</v>
       </c>
       <c r="M19" t="n">
-        <v>0.956</v>
+        <v>0.93</v>
       </c>
       <c r="N19" t="n">
-        <v>0.9515</v>
+        <v>0.9408</v>
       </c>
       <c r="O19" t="n">
-        <v>0.7835</v>
+        <v>0.8447</v>
       </c>
       <c r="P19" t="n">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="Q19" t="n">
-        <v>61.41</v>
+        <v>61.29</v>
       </c>
       <c r="R19" t="n">
-        <v>115.34</v>
+        <v>115.3</v>
       </c>
       <c r="S19" t="n">
-        <v>97.06</v>
+        <v>95.76000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>-8.699999999999999</v>
+        <v>-7.46</v>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr"/>
@@ -1768,31 +1768,31 @@
         <v>11</v>
       </c>
       <c r="D20" t="n">
-        <v>22.9</v>
+        <v>22.83</v>
       </c>
       <c r="E20" t="n">
-        <v>21.92</v>
+        <v>21.85</v>
       </c>
       <c r="F20" t="n">
-        <v>21.92</v>
+        <v>21.85</v>
       </c>
       <c r="G20" t="n">
         <v>22.06</v>
       </c>
       <c r="H20" t="n">
-        <v>12.02</v>
+        <v>12.01</v>
       </c>
       <c r="I20" t="n">
-        <v>6.56</v>
+        <v>6.55</v>
       </c>
       <c r="J20" t="n">
         <v>3.49</v>
       </c>
       <c r="K20" t="n">
-        <v>65.08</v>
+        <v>65.06999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>86.98999999999999</v>
+        <v>86.91</v>
       </c>
       <c r="M20" t="n">
         <v>0.957</v>
@@ -1807,16 +1807,16 @@
         <v>0.7255</v>
       </c>
       <c r="Q20" t="n">
-        <v>59.99</v>
+        <v>59.95</v>
       </c>
       <c r="R20" t="n">
-        <v>114.01</v>
+        <v>113.91</v>
       </c>
       <c r="S20" t="n">
         <v>86.06</v>
       </c>
       <c r="T20" t="n">
-        <v>0.93</v>
+        <v>0.85</v>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr"/>
@@ -1875,10 +1875,10 @@
         <v>0.617</v>
       </c>
       <c r="Q21" t="n">
-        <v>59.77</v>
+        <v>59.73</v>
       </c>
       <c r="R21" t="n">
-        <v>113.68</v>
+        <v>113.73</v>
       </c>
       <c r="S21" t="n">
         <v>95.76000000000001</v>
@@ -1904,31 +1904,31 @@
         <v>11</v>
       </c>
       <c r="D22" t="n">
-        <v>23.46</v>
+        <v>23.2</v>
       </c>
       <c r="E22" t="n">
-        <v>22.31</v>
+        <v>22.07</v>
       </c>
       <c r="F22" t="n">
-        <v>22.31</v>
+        <v>22.07</v>
       </c>
       <c r="G22" t="n">
-        <v>22.06</v>
+        <v>22.02</v>
       </c>
       <c r="H22" t="n">
-        <v>12.02</v>
+        <v>11.99</v>
       </c>
       <c r="I22" t="n">
-        <v>6.56</v>
+        <v>6.54</v>
       </c>
       <c r="J22" t="n">
-        <v>3.49</v>
+        <v>3.48</v>
       </c>
       <c r="K22" t="n">
-        <v>64.33</v>
+        <v>64.2</v>
       </c>
       <c r="L22" t="n">
-        <v>86.64</v>
+        <v>86.26000000000001</v>
       </c>
       <c r="M22" t="n">
         <v>0.951</v>
@@ -1943,16 +1943,16 @@
         <v>0.6859</v>
       </c>
       <c r="Q22" t="n">
-        <v>59.82</v>
+        <v>59.47</v>
       </c>
       <c r="R22" t="n">
-        <v>113.46</v>
+        <v>113.04</v>
       </c>
       <c r="S22" t="n">
         <v>90.59</v>
       </c>
       <c r="T22" t="n">
-        <v>-3.95</v>
+        <v>-4.33</v>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr"/>
@@ -2011,10 +2011,10 @@
         <v>0.6859</v>
       </c>
       <c r="Q23" t="n">
-        <v>59.56</v>
+        <v>59.6</v>
       </c>
       <c r="R23" t="n">
-        <v>112.83</v>
+        <v>112.84</v>
       </c>
       <c r="S23" t="n">
         <v>84.76000000000001</v>
@@ -2079,10 +2079,10 @@
         <v>0.5667</v>
       </c>
       <c r="Q24" t="n">
-        <v>59.56</v>
+        <v>59.48</v>
       </c>
       <c r="R24" t="n">
-        <v>112.61</v>
+        <v>112.64</v>
       </c>
       <c r="S24" t="n">
         <v>94.47</v>
@@ -2108,31 +2108,31 @@
         <v>11</v>
       </c>
       <c r="D25" t="n">
-        <v>22.05</v>
+        <v>21.76</v>
       </c>
       <c r="E25" t="n">
-        <v>21.53</v>
+        <v>21.25</v>
       </c>
       <c r="F25" t="n">
-        <v>21.53</v>
+        <v>21.25</v>
       </c>
       <c r="G25" t="n">
-        <v>22.54</v>
+        <v>22.41</v>
       </c>
       <c r="H25" t="n">
-        <v>12.28</v>
+        <v>12.21</v>
       </c>
       <c r="I25" t="n">
-        <v>6.7</v>
+        <v>6.66</v>
       </c>
       <c r="J25" t="n">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="K25" t="n">
-        <v>64.53</v>
+        <v>64.16</v>
       </c>
       <c r="L25" t="n">
-        <v>86.06999999999999</v>
+        <v>85.41</v>
       </c>
       <c r="M25" t="n">
         <v>0.976</v>
@@ -2147,16 +2147,16 @@
         <v>0.8431</v>
       </c>
       <c r="Q25" t="n">
-        <v>59.29</v>
+        <v>58.74</v>
       </c>
       <c r="R25" t="n">
-        <v>112.86</v>
+        <v>112.03</v>
       </c>
       <c r="S25" t="n">
         <v>91.23999999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>-5.17</v>
+        <v>-5.83</v>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr"/>
@@ -2176,31 +2176,31 @@
         <v>11</v>
       </c>
       <c r="D26" t="n">
-        <v>28.15</v>
+        <v>27.72</v>
       </c>
       <c r="E26" t="n">
-        <v>27.38</v>
+        <v>26.96</v>
       </c>
       <c r="F26" t="n">
-        <v>27.38</v>
+        <v>26.96</v>
       </c>
       <c r="G26" t="n">
-        <v>20.72</v>
+        <v>20.52</v>
       </c>
       <c r="H26" t="n">
-        <v>11.29</v>
+        <v>11.18</v>
       </c>
       <c r="I26" t="n">
-        <v>6.16</v>
+        <v>6.1</v>
       </c>
       <c r="J26" t="n">
-        <v>3.28</v>
+        <v>3.24</v>
       </c>
       <c r="K26" t="n">
-        <v>58.48</v>
+        <v>57.9</v>
       </c>
       <c r="L26" t="n">
-        <v>85.86</v>
+        <v>84.86</v>
       </c>
       <c r="M26" t="n">
         <v>0.973</v>
@@ -2215,16 +2215,16 @@
         <v>0.6859</v>
       </c>
       <c r="Q26" t="n">
-        <v>59.33</v>
+        <v>58.52</v>
       </c>
       <c r="R26" t="n">
-        <v>112.39</v>
+        <v>111.23</v>
       </c>
       <c r="S26" t="n">
         <v>86.70999999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.85</v>
+        <v>-1.85</v>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr"/>
@@ -2244,19 +2244,19 @@
         <v>11</v>
       </c>
       <c r="D27" t="n">
-        <v>25.37</v>
+        <v>25.39</v>
       </c>
       <c r="E27" t="n">
-        <v>24.18</v>
+        <v>24.2</v>
       </c>
       <c r="F27" t="n">
-        <v>24.18</v>
+        <v>24.2</v>
       </c>
       <c r="G27" t="n">
-        <v>21.32</v>
+        <v>21.33</v>
       </c>
       <c r="H27" t="n">
-        <v>11.61</v>
+        <v>11.62</v>
       </c>
       <c r="I27" t="n">
         <v>6.34</v>
@@ -2265,10 +2265,10 @@
         <v>3.37</v>
       </c>
       <c r="K27" t="n">
-        <v>59.95</v>
+        <v>59.99</v>
       </c>
       <c r="L27" t="n">
-        <v>84.14</v>
+        <v>84.19</v>
       </c>
       <c r="M27" t="n">
         <v>0.953</v>
@@ -2283,16 +2283,16 @@
         <v>0.6859</v>
       </c>
       <c r="Q27" t="n">
-        <v>57.96</v>
+        <v>58.07</v>
       </c>
       <c r="R27" t="n">
-        <v>110.27</v>
+        <v>110.33</v>
       </c>
       <c r="S27" t="n">
         <v>87.34999999999999</v>
       </c>
       <c r="T27" t="n">
-        <v>-3.21</v>
+        <v>-3.16</v>
       </c>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr"/>
@@ -2312,31 +2312,31 @@
         <v>11</v>
       </c>
       <c r="D28" t="n">
-        <v>24.89</v>
+        <v>24.93</v>
       </c>
       <c r="E28" t="n">
-        <v>23.67</v>
+        <v>23.71</v>
       </c>
       <c r="F28" t="n">
-        <v>23.67</v>
+        <v>23.71</v>
       </c>
       <c r="G28" t="n">
-        <v>20.67</v>
+        <v>20.63</v>
       </c>
       <c r="H28" t="n">
-        <v>11.26</v>
+        <v>11.24</v>
       </c>
       <c r="I28" t="n">
-        <v>6.14</v>
+        <v>6.13</v>
       </c>
       <c r="J28" t="n">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="K28" t="n">
-        <v>60.25</v>
+        <v>60.14</v>
       </c>
       <c r="L28" t="n">
-        <v>83.92</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="M28" t="n">
         <v>0.951</v>
@@ -2351,16 +2351,16 @@
         <v>0.6859</v>
       </c>
       <c r="Q28" t="n">
-        <v>57.48</v>
+        <v>57.41</v>
       </c>
       <c r="R28" t="n">
-        <v>110.36</v>
+        <v>110.3</v>
       </c>
       <c r="S28" t="n">
         <v>84.76000000000001</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.84</v>
+        <v>-0.91</v>
       </c>
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr"/>
@@ -2380,31 +2380,31 @@
         <v>11</v>
       </c>
       <c r="D29" t="n">
-        <v>22.65</v>
+        <v>22.58</v>
       </c>
       <c r="E29" t="n">
-        <v>21.8</v>
+        <v>21.74</v>
       </c>
       <c r="F29" t="n">
-        <v>21.8</v>
+        <v>21.74</v>
       </c>
       <c r="G29" t="n">
-        <v>20.99</v>
+        <v>20.95</v>
       </c>
       <c r="H29" t="n">
-        <v>11.43</v>
+        <v>11.41</v>
       </c>
       <c r="I29" t="n">
-        <v>6.24</v>
+        <v>6.22</v>
       </c>
       <c r="J29" t="n">
-        <v>3.32</v>
+        <v>3.31</v>
       </c>
       <c r="K29" t="n">
-        <v>59.63</v>
+        <v>59.5</v>
       </c>
       <c r="L29" t="n">
-        <v>81.43000000000001</v>
+        <v>81.23999999999999</v>
       </c>
       <c r="M29" t="n">
         <v>0.962</v>
@@ -2419,16 +2419,16 @@
         <v>0.5962</v>
       </c>
       <c r="Q29" t="n">
-        <v>55.59</v>
+        <v>55.45</v>
       </c>
       <c r="R29" t="n">
-        <v>107.27</v>
+        <v>107.03</v>
       </c>
       <c r="S29" t="n">
         <v>89.94</v>
       </c>
       <c r="T29" t="n">
-        <v>-8.51</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr"/>
@@ -2516,19 +2516,19 @@
         <v>11</v>
       </c>
       <c r="D31" t="n">
-        <v>22.59</v>
+        <v>22.5</v>
       </c>
       <c r="E31" t="n">
-        <v>22.08</v>
+        <v>21.98</v>
       </c>
       <c r="F31" t="n">
-        <v>22.08</v>
+        <v>21.98</v>
       </c>
       <c r="G31" t="n">
-        <v>21.86</v>
+        <v>21.87</v>
       </c>
       <c r="H31" t="n">
-        <v>11.9</v>
+        <v>11.91</v>
       </c>
       <c r="I31" t="n">
         <v>6.5</v>
@@ -2537,10 +2537,10 @@
         <v>3.46</v>
       </c>
       <c r="K31" t="n">
-        <v>56.4</v>
+        <v>56.45</v>
       </c>
       <c r="L31" t="n">
-        <v>78.48</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="M31" t="n">
         <v>0.977</v>
@@ -2555,16 +2555,16 @@
         <v>0.6859</v>
       </c>
       <c r="Q31" t="n">
-        <v>53.98</v>
+        <v>53.88</v>
       </c>
       <c r="R31" t="n">
-        <v>102.97</v>
+        <v>102.94</v>
       </c>
       <c r="S31" t="n">
         <v>86.70999999999999</v>
       </c>
       <c r="T31" t="n">
-        <v>-8.23</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr"/>
@@ -2584,13 +2584,13 @@
         <v>11</v>
       </c>
       <c r="D32" t="n">
-        <v>21.22</v>
+        <v>21.14</v>
       </c>
       <c r="E32" t="n">
-        <v>19.19</v>
+        <v>19.12</v>
       </c>
       <c r="F32" t="n">
-        <v>19.19</v>
+        <v>19.12</v>
       </c>
       <c r="G32" t="n">
         <v>21.04</v>
@@ -2608,7 +2608,7 @@
         <v>58.83</v>
       </c>
       <c r="L32" t="n">
-        <v>78.02</v>
+        <v>77.95</v>
       </c>
       <c r="M32" t="n">
         <v>0.904</v>
@@ -2623,16 +2623,16 @@
         <v>0.6364</v>
       </c>
       <c r="Q32" t="n">
-        <v>53.06</v>
+        <v>52.99</v>
       </c>
       <c r="R32" t="n">
-        <v>102.99</v>
+        <v>102.9</v>
       </c>
       <c r="S32" t="n">
         <v>86.70999999999999</v>
       </c>
       <c r="T32" t="n">
-        <v>-8.69</v>
+        <v>-8.76</v>
       </c>
       <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr"/>
@@ -3321,28 +3321,28 @@
         <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>2.38</v>
+        <v>2.425</v>
       </c>
       <c r="G8" t="n">
         <v>0.951</v>
       </c>
       <c r="H8" t="n">
-        <v>2.263</v>
+        <v>2.306</v>
       </c>
       <c r="I8" t="n">
-        <v>2.263</v>
+        <v>2.306</v>
       </c>
       <c r="J8" t="n">
-        <v>1.8878</v>
+        <v>1.8489</v>
       </c>
       <c r="K8" t="n">
-        <v>1.0283</v>
+        <v>1.0071</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.5495</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2985</v>
+        <v>0.2923</v>
       </c>
       <c r="N8" t="n">
         <v>0.9543</v>
@@ -3354,25 +3354,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.8969</v>
+        <v>2.8372</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6774</v>
+        <v>1.643</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9298999999999999</v>
+        <v>0.9106</v>
       </c>
       <c r="T8" t="n">
-        <v>5.5043</v>
+        <v>5.3908</v>
       </c>
       <c r="U8" t="n">
-        <v>7.767</v>
+        <v>7.697</v>
       </c>
       <c r="V8" t="n">
-        <v>2.688</v>
+        <v>2.664</v>
       </c>
       <c r="W8" t="n">
-        <v>14.301</v>
+        <v>14.199</v>
       </c>
     </row>
     <row r="9">
@@ -5631,28 +5631,28 @@
         <v>1</v>
       </c>
       <c r="F38" t="n">
-        <v>2.826</v>
+        <v>2.677</v>
       </c>
       <c r="G38" t="n">
         <v>0.969</v>
       </c>
       <c r="H38" t="n">
-        <v>2.739</v>
+        <v>2.595</v>
       </c>
       <c r="I38" t="n">
-        <v>2.739</v>
+        <v>2.595</v>
       </c>
       <c r="J38" t="n">
-        <v>2.0002</v>
+        <v>1.988</v>
       </c>
       <c r="K38" t="n">
-        <v>1.0895</v>
+        <v>1.0829</v>
       </c>
       <c r="L38" t="n">
-        <v>0.5945</v>
+        <v>0.5908</v>
       </c>
       <c r="M38" t="n">
-        <v>0.3162</v>
+        <v>0.3143</v>
       </c>
       <c r="N38" t="n">
         <v>0.9245</v>
@@ -5664,25 +5664,25 @@
         <v>0.7955</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.9395</v>
+        <v>2.9217</v>
       </c>
       <c r="R38" t="n">
-        <v>2.1797</v>
+        <v>2.1662</v>
       </c>
       <c r="S38" t="n">
-        <v>1.193</v>
+        <v>1.1859</v>
       </c>
       <c r="T38" t="n">
-        <v>6.3122</v>
+        <v>6.2737</v>
       </c>
       <c r="U38" t="n">
-        <v>9.051</v>
+        <v>8.869</v>
       </c>
       <c r="V38" t="n">
-        <v>3.133</v>
+        <v>3.07</v>
       </c>
       <c r="W38" t="n">
-        <v>16.325</v>
+        <v>16.073</v>
       </c>
     </row>
     <row r="39">
@@ -6170,28 +6170,28 @@
         <v>-1</v>
       </c>
       <c r="F45" t="n">
-        <v>2.8</v>
+        <v>2.749</v>
       </c>
       <c r="G45" t="n">
         <v>0.969</v>
       </c>
       <c r="H45" t="n">
-        <v>2.714</v>
+        <v>2.664</v>
       </c>
       <c r="I45" t="n">
-        <v>2.714</v>
+        <v>2.664</v>
       </c>
       <c r="J45" t="n">
-        <v>2.006</v>
+        <v>2.0404</v>
       </c>
       <c r="K45" t="n">
-        <v>1.0927</v>
+        <v>1.1114</v>
       </c>
       <c r="L45" t="n">
-        <v>0.5962</v>
+        <v>0.6064000000000001</v>
       </c>
       <c r="M45" t="n">
-        <v>0.3172</v>
+        <v>0.3226</v>
       </c>
       <c r="N45" t="n">
         <v>0.9245</v>
@@ -6203,25 +6203,25 @@
         <v>0.7955</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.9481</v>
+        <v>2.9986</v>
       </c>
       <c r="R45" t="n">
-        <v>2.186</v>
+        <v>2.2234</v>
       </c>
       <c r="S45" t="n">
-        <v>1.1968</v>
+        <v>1.2172</v>
       </c>
       <c r="T45" t="n">
-        <v>6.3309</v>
+        <v>6.4391</v>
       </c>
       <c r="U45" t="n">
-        <v>9.045</v>
+        <v>9.103</v>
       </c>
       <c r="V45" t="n">
-        <v>3.131</v>
+        <v>3.151</v>
       </c>
       <c r="W45" t="n">
-        <v>16.317</v>
+        <v>16.401</v>
       </c>
     </row>
     <row r="46">
@@ -7787,28 +7787,28 @@
         <v>1</v>
       </c>
       <c r="F66" t="n">
-        <v>3.028</v>
+        <v>3.073</v>
       </c>
       <c r="G66" t="n">
         <v>0.987</v>
       </c>
       <c r="H66" t="n">
-        <v>2.989</v>
+        <v>3.034</v>
       </c>
       <c r="I66" t="n">
-        <v>2.989</v>
+        <v>3.034</v>
       </c>
       <c r="J66" t="n">
-        <v>1.9082</v>
+        <v>1.9398</v>
       </c>
       <c r="K66" t="n">
-        <v>1.0394</v>
+        <v>1.0566</v>
       </c>
       <c r="L66" t="n">
-        <v>0.5671</v>
+        <v>0.5765</v>
       </c>
       <c r="M66" t="n">
-        <v>0.3017</v>
+        <v>0.3067</v>
       </c>
       <c r="N66" t="n">
         <v>0.9543</v>
@@ -7820,25 +7820,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q66" t="n">
-        <v>2.9282</v>
+        <v>2.9767</v>
       </c>
       <c r="R66" t="n">
-        <v>1.6956</v>
+        <v>1.7237</v>
       </c>
       <c r="S66" t="n">
-        <v>0.9399</v>
+        <v>0.9555</v>
       </c>
       <c r="T66" t="n">
-        <v>5.5637</v>
+        <v>5.6559</v>
       </c>
       <c r="U66" t="n">
-        <v>8.553000000000001</v>
+        <v>8.69</v>
       </c>
       <c r="V66" t="n">
-        <v>2.96</v>
+        <v>3.008</v>
       </c>
       <c r="W66" t="n">
-        <v>15.423</v>
+        <v>15.616</v>
       </c>
     </row>
     <row r="67">
@@ -8480,28 +8480,28 @@
         <v>1</v>
       </c>
       <c r="F75" t="n">
-        <v>1.869</v>
+        <v>1.754</v>
       </c>
       <c r="G75" t="n">
         <v>0.969</v>
       </c>
       <c r="H75" t="n">
-        <v>1.811</v>
+        <v>1.7</v>
       </c>
       <c r="I75" t="n">
-        <v>1.811</v>
+        <v>1.7</v>
       </c>
       <c r="J75" t="n">
-        <v>2.0296</v>
+        <v>2.0333</v>
       </c>
       <c r="K75" t="n">
-        <v>1.1055</v>
+        <v>1.1075</v>
       </c>
       <c r="L75" t="n">
-        <v>0.6032</v>
+        <v>0.6042999999999999</v>
       </c>
       <c r="M75" t="n">
-        <v>0.3209</v>
+        <v>0.3215</v>
       </c>
       <c r="N75" t="n">
         <v>0.9857</v>
@@ -8513,25 +8513,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.2533</v>
+        <v>3.2592</v>
       </c>
       <c r="R75" t="n">
-        <v>2.2656</v>
+        <v>2.2698</v>
       </c>
       <c r="S75" t="n">
-        <v>0.9997</v>
+        <v>1.0016</v>
       </c>
       <c r="T75" t="n">
-        <v>6.5186</v>
+        <v>6.5305</v>
       </c>
       <c r="U75" t="n">
-        <v>8.33</v>
+        <v>8.23</v>
       </c>
       <c r="V75" t="n">
-        <v>2.883</v>
+        <v>2.849</v>
       </c>
       <c r="W75" t="n">
-        <v>15.358</v>
+        <v>15.212</v>
       </c>
     </row>
     <row r="76">
@@ -9173,28 +9173,28 @@
         <v>1</v>
       </c>
       <c r="F84" t="n">
-        <v>2.218</v>
+        <v>2.422</v>
       </c>
       <c r="G84" t="n">
         <v>0.977</v>
       </c>
       <c r="H84" t="n">
-        <v>2.168</v>
+        <v>2.367</v>
       </c>
       <c r="I84" t="n">
-        <v>2.168</v>
+        <v>2.367</v>
       </c>
       <c r="J84" t="n">
-        <v>2.0488</v>
+        <v>2.0655</v>
       </c>
       <c r="K84" t="n">
-        <v>1.116</v>
+        <v>1.1251</v>
       </c>
       <c r="L84" t="n">
-        <v>0.6089</v>
+        <v>0.6139</v>
       </c>
       <c r="M84" t="n">
-        <v>0.3239</v>
+        <v>0.3266</v>
       </c>
       <c r="N84" t="n">
         <v>0.9268</v>
@@ -9206,25 +9206,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.0212</v>
+        <v>3.0459</v>
       </c>
       <c r="R84" t="n">
-        <v>1.2571</v>
+        <v>1.2674</v>
       </c>
       <c r="S84" t="n">
-        <v>1.0091</v>
+        <v>1.0175</v>
       </c>
       <c r="T84" t="n">
-        <v>5.2874</v>
+        <v>5.3308</v>
       </c>
       <c r="U84" t="n">
-        <v>7.455</v>
+        <v>7.698</v>
       </c>
       <c r="V84" t="n">
-        <v>2.58</v>
+        <v>2.665</v>
       </c>
       <c r="W84" t="n">
-        <v>13.609</v>
+        <v>13.95</v>
       </c>
     </row>
     <row r="85">
@@ -9558,28 +9558,28 @@
         <v>1</v>
       </c>
       <c r="F89" t="n">
-        <v>2.056</v>
+        <v>1.758</v>
       </c>
       <c r="G89" t="n">
         <v>0.977</v>
       </c>
       <c r="H89" t="n">
-        <v>2.009</v>
+        <v>1.718</v>
       </c>
       <c r="I89" t="n">
-        <v>2.009</v>
+        <v>1.718</v>
       </c>
       <c r="J89" t="n">
-        <v>1.9992</v>
+        <v>1.9989</v>
       </c>
       <c r="K89" t="n">
-        <v>1.089</v>
+        <v>1.0888</v>
       </c>
       <c r="L89" t="n">
-        <v>0.5942</v>
+        <v>0.5941</v>
       </c>
       <c r="M89" t="n">
-        <v>0.3161</v>
+        <v>0.316</v>
       </c>
       <c r="N89" t="n">
         <v>0.9268</v>
@@ -9591,25 +9591,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q89" t="n">
-        <v>2.9481</v>
+        <v>2.9476</v>
       </c>
       <c r="R89" t="n">
-        <v>1.2267</v>
+        <v>1.2265</v>
       </c>
       <c r="S89" t="n">
-        <v>0.9848</v>
+        <v>0.9845</v>
       </c>
       <c r="T89" t="n">
-        <v>5.1596</v>
+        <v>5.1586</v>
       </c>
       <c r="U89" t="n">
-        <v>7.169</v>
+        <v>6.877</v>
       </c>
       <c r="V89" t="n">
-        <v>2.481</v>
+        <v>2.38</v>
       </c>
       <c r="W89" t="n">
-        <v>13.202</v>
+        <v>12.778</v>
       </c>
     </row>
     <row r="90">
@@ -9712,28 +9712,28 @@
         <v>1</v>
       </c>
       <c r="F91" t="n">
-        <v>2.196</v>
+        <v>2.081</v>
       </c>
       <c r="G91" t="n">
         <v>0.976</v>
       </c>
       <c r="H91" t="n">
-        <v>2.144</v>
+        <v>2.032</v>
       </c>
       <c r="I91" t="n">
-        <v>2.144</v>
+        <v>2.032</v>
       </c>
       <c r="J91" t="n">
-        <v>2.0894</v>
+        <v>2.0292</v>
       </c>
       <c r="K91" t="n">
-        <v>1.1381</v>
+        <v>1.1053</v>
       </c>
       <c r="L91" t="n">
-        <v>0.621</v>
+        <v>0.6031</v>
       </c>
       <c r="M91" t="n">
-        <v>0.3303</v>
+        <v>0.3208</v>
       </c>
       <c r="N91" t="n">
         <v>0.9655</v>
@@ -9745,25 +9745,25 @@
         <v>0.8431</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.2572</v>
+        <v>3.1634</v>
       </c>
       <c r="R91" t="n">
-        <v>1.3842</v>
+        <v>1.3443</v>
       </c>
       <c r="S91" t="n">
-        <v>1.3406</v>
+        <v>1.302</v>
       </c>
       <c r="T91" t="n">
-        <v>5.982</v>
+        <v>5.8097</v>
       </c>
       <c r="U91" t="n">
-        <v>8.125999999999999</v>
+        <v>7.842</v>
       </c>
       <c r="V91" t="n">
-        <v>2.813</v>
+        <v>2.714</v>
       </c>
       <c r="W91" t="n">
-        <v>14.791</v>
+        <v>14.388</v>
       </c>
     </row>
     <row r="92">
@@ -10251,28 +10251,28 @@
         <v>-1</v>
       </c>
       <c r="F98" t="n">
-        <v>2.051</v>
+        <v>1.874</v>
       </c>
       <c r="G98" t="n">
         <v>0.976</v>
       </c>
       <c r="H98" t="n">
-        <v>2.002</v>
+        <v>1.83</v>
       </c>
       <c r="I98" t="n">
-        <v>2.002</v>
+        <v>1.83</v>
       </c>
       <c r="J98" t="n">
-        <v>2.0823</v>
+        <v>2.0121</v>
       </c>
       <c r="K98" t="n">
-        <v>1.1342</v>
+        <v>1.096</v>
       </c>
       <c r="L98" t="n">
-        <v>0.6189</v>
+        <v>0.598</v>
       </c>
       <c r="M98" t="n">
-        <v>0.3292</v>
+        <v>0.3181</v>
       </c>
       <c r="N98" t="n">
         <v>0.9655</v>
@@ -10284,25 +10284,25 @@
         <v>0.8431</v>
       </c>
       <c r="Q98" t="n">
-        <v>3.2461</v>
+        <v>3.1368</v>
       </c>
       <c r="R98" t="n">
-        <v>1.3795</v>
+        <v>1.3329</v>
       </c>
       <c r="S98" t="n">
-        <v>1.3361</v>
+        <v>1.291</v>
       </c>
       <c r="T98" t="n">
-        <v>5.9617</v>
+        <v>5.7607</v>
       </c>
       <c r="U98" t="n">
-        <v>7.964</v>
+        <v>7.591</v>
       </c>
       <c r="V98" t="n">
-        <v>2.757</v>
+        <v>2.628</v>
       </c>
       <c r="W98" t="n">
-        <v>14.56</v>
+        <v>14.028</v>
       </c>
     </row>
     <row r="99">
@@ -12022,28 +12022,28 @@
         <v>-1</v>
       </c>
       <c r="F121" t="n">
-        <v>2.273</v>
+        <v>2.021</v>
       </c>
       <c r="G121" t="n">
         <v>0.951</v>
       </c>
       <c r="H121" t="n">
-        <v>2.162</v>
+        <v>1.923</v>
       </c>
       <c r="I121" t="n">
-        <v>2.162</v>
+        <v>1.923</v>
       </c>
       <c r="J121" t="n">
-        <v>2.0322</v>
+        <v>1.9866</v>
       </c>
       <c r="K121" t="n">
-        <v>1.1069</v>
+        <v>1.0821</v>
       </c>
       <c r="L121" t="n">
-        <v>0.604</v>
+        <v>0.5904</v>
       </c>
       <c r="M121" t="n">
-        <v>0.3213</v>
+        <v>0.3141</v>
       </c>
       <c r="N121" t="n">
         <v>0.9543</v>
@@ -12055,25 +12055,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q121" t="n">
-        <v>3.1184</v>
+        <v>3.0485</v>
       </c>
       <c r="R121" t="n">
-        <v>1.806</v>
+        <v>1.7653</v>
       </c>
       <c r="S121" t="n">
-        <v>1.001</v>
+        <v>0.9785</v>
       </c>
       <c r="T121" t="n">
-        <v>5.9253</v>
+        <v>5.7923</v>
       </c>
       <c r="U121" t="n">
-        <v>8.087</v>
+        <v>7.715</v>
       </c>
       <c r="V121" t="n">
-        <v>2.799</v>
+        <v>2.67</v>
       </c>
       <c r="W121" t="n">
-        <v>14.758</v>
+        <v>14.23</v>
       </c>
     </row>
     <row r="122">
@@ -12330,28 +12330,28 @@
         <v>1</v>
       </c>
       <c r="F125" t="n">
-        <v>2.624</v>
+        <v>2.638</v>
       </c>
       <c r="G125" t="n">
         <v>0.951</v>
       </c>
       <c r="H125" t="n">
-        <v>2.496</v>
+        <v>2.509</v>
       </c>
       <c r="I125" t="n">
-        <v>2.496</v>
+        <v>2.509</v>
       </c>
       <c r="J125" t="n">
-        <v>2.0903</v>
+        <v>2.1208</v>
       </c>
       <c r="K125" t="n">
-        <v>1.1386</v>
+        <v>1.1552</v>
       </c>
       <c r="L125" t="n">
-        <v>0.6212</v>
+        <v>0.6303</v>
       </c>
       <c r="M125" t="n">
-        <v>0.3305</v>
+        <v>0.3353</v>
       </c>
       <c r="N125" t="n">
         <v>0.9543</v>
@@ -12363,25 +12363,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q125" t="n">
-        <v>3.2077</v>
+        <v>3.2544</v>
       </c>
       <c r="R125" t="n">
-        <v>1.8574</v>
+        <v>1.8846</v>
       </c>
       <c r="S125" t="n">
-        <v>1.0296</v>
+        <v>1.0446</v>
       </c>
       <c r="T125" t="n">
-        <v>6.0947</v>
+        <v>6.1836</v>
       </c>
       <c r="U125" t="n">
-        <v>8.590999999999999</v>
+        <v>8.693</v>
       </c>
       <c r="V125" t="n">
-        <v>2.974</v>
+        <v>3.009</v>
       </c>
       <c r="W125" t="n">
-        <v>15.463</v>
+        <v>15.607</v>
       </c>
     </row>
     <row r="126">
@@ -12561,28 +12561,28 @@
         <v>1</v>
       </c>
       <c r="F128" t="n">
-        <v>2.307</v>
+        <v>1.872</v>
       </c>
       <c r="G128" t="n">
         <v>0.951</v>
       </c>
       <c r="H128" t="n">
-        <v>2.194</v>
+        <v>1.781</v>
       </c>
       <c r="I128" t="n">
-        <v>2.194</v>
+        <v>1.781</v>
       </c>
       <c r="J128" t="n">
-        <v>2.0428</v>
+        <v>2.0408</v>
       </c>
       <c r="K128" t="n">
-        <v>1.1127</v>
+        <v>1.1116</v>
       </c>
       <c r="L128" t="n">
-        <v>0.6071</v>
+        <v>0.6065</v>
       </c>
       <c r="M128" t="n">
-        <v>0.323</v>
+        <v>0.3227</v>
       </c>
       <c r="N128" t="n">
         <v>0.9543</v>
@@ -12594,25 +12594,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q128" t="n">
-        <v>3.1347</v>
+        <v>3.1316</v>
       </c>
       <c r="R128" t="n">
-        <v>1.8152</v>
+        <v>1.8134</v>
       </c>
       <c r="S128" t="n">
-        <v>1.0063</v>
+        <v>1.0053</v>
       </c>
       <c r="T128" t="n">
-        <v>5.9562</v>
+        <v>5.9504</v>
       </c>
       <c r="U128" t="n">
-        <v>8.15</v>
+        <v>7.731</v>
       </c>
       <c r="V128" t="n">
-        <v>2.821</v>
+        <v>2.676</v>
       </c>
       <c r="W128" t="n">
-        <v>14.846</v>
+        <v>14.248</v>
       </c>
     </row>
     <row r="129">
@@ -13023,28 +13023,28 @@
         <v>1</v>
       </c>
       <c r="F134" t="n">
-        <v>2.552</v>
+        <v>2.516</v>
       </c>
       <c r="G134" t="n">
         <v>0.973</v>
       </c>
       <c r="H134" t="n">
-        <v>2.482</v>
+        <v>2.448</v>
       </c>
       <c r="I134" t="n">
-        <v>2.482</v>
+        <v>2.448</v>
       </c>
       <c r="J134" t="n">
-        <v>1.8845</v>
+        <v>1.8702</v>
       </c>
       <c r="K134" t="n">
-        <v>1.0265</v>
+        <v>1.0187</v>
       </c>
       <c r="L134" t="n">
-        <v>0.5601</v>
+        <v>0.5558</v>
       </c>
       <c r="M134" t="n">
-        <v>0.2979</v>
+        <v>0.2957</v>
       </c>
       <c r="N134" t="n">
         <v>0.9111</v>
@@ -13056,25 +13056,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q134" t="n">
-        <v>2.7145</v>
+        <v>2.6939</v>
       </c>
       <c r="R134" t="n">
-        <v>1.6747</v>
+        <v>1.6618</v>
       </c>
       <c r="S134" t="n">
-        <v>0.9281</v>
+        <v>0.9212</v>
       </c>
       <c r="T134" t="n">
-        <v>5.3173</v>
+        <v>5.2769</v>
       </c>
       <c r="U134" t="n">
-        <v>7.799</v>
+        <v>7.725</v>
       </c>
       <c r="V134" t="n">
-        <v>2.7</v>
+        <v>2.674</v>
       </c>
       <c r="W134" t="n">
-        <v>14.285</v>
+        <v>14.181</v>
       </c>
     </row>
     <row r="135">
@@ -13100,28 +13100,28 @@
         <v>1</v>
       </c>
       <c r="F135" t="n">
-        <v>2.319</v>
+        <v>2.29</v>
       </c>
       <c r="G135" t="n">
         <v>0.973</v>
       </c>
       <c r="H135" t="n">
-        <v>2.256</v>
+        <v>2.227</v>
       </c>
       <c r="I135" t="n">
-        <v>2.256</v>
+        <v>2.227</v>
       </c>
       <c r="J135" t="n">
-        <v>1.8895</v>
+        <v>1.8617</v>
       </c>
       <c r="K135" t="n">
-        <v>1.0292</v>
+        <v>1.0141</v>
       </c>
       <c r="L135" t="n">
-        <v>0.5615</v>
+        <v>0.5533</v>
       </c>
       <c r="M135" t="n">
-        <v>0.2987</v>
+        <v>0.2943</v>
       </c>
       <c r="N135" t="n">
         <v>0.9111</v>
@@ -13133,25 +13133,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q135" t="n">
-        <v>2.7216</v>
+        <v>2.6817</v>
       </c>
       <c r="R135" t="n">
-        <v>1.6789</v>
+        <v>1.6544</v>
       </c>
       <c r="S135" t="n">
-        <v>0.9306</v>
+        <v>0.9169</v>
       </c>
       <c r="T135" t="n">
-        <v>5.3311</v>
+        <v>5.2529</v>
       </c>
       <c r="U135" t="n">
-        <v>7.587</v>
+        <v>7.48</v>
       </c>
       <c r="V135" t="n">
-        <v>2.626</v>
+        <v>2.589</v>
       </c>
       <c r="W135" t="n">
-        <v>13.989</v>
+        <v>13.836</v>
       </c>
     </row>
     <row r="136">
@@ -13177,28 +13177,28 @@
         <v>-1</v>
       </c>
       <c r="F136" t="n">
-        <v>2.502</v>
+        <v>2.477</v>
       </c>
       <c r="G136" t="n">
         <v>0.973</v>
       </c>
       <c r="H136" t="n">
-        <v>2.433</v>
+        <v>2.41</v>
       </c>
       <c r="I136" t="n">
-        <v>2.433</v>
+        <v>2.41</v>
       </c>
       <c r="J136" t="n">
-        <v>1.876</v>
+        <v>1.8569</v>
       </c>
       <c r="K136" t="n">
-        <v>1.0219</v>
+        <v>1.0115</v>
       </c>
       <c r="L136" t="n">
-        <v>0.5575</v>
+        <v>0.5518999999999999</v>
       </c>
       <c r="M136" t="n">
-        <v>0.2966</v>
+        <v>0.2936</v>
       </c>
       <c r="N136" t="n">
         <v>0.9111</v>
@@ -13210,25 +13210,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q136" t="n">
-        <v>2.7023</v>
+        <v>2.6748</v>
       </c>
       <c r="R136" t="n">
-        <v>1.6669</v>
+        <v>1.6502</v>
       </c>
       <c r="S136" t="n">
-        <v>0.924</v>
+        <v>0.9147</v>
       </c>
       <c r="T136" t="n">
-        <v>5.2933</v>
+        <v>5.2397</v>
       </c>
       <c r="U136" t="n">
-        <v>7.726</v>
+        <v>7.65</v>
       </c>
       <c r="V136" t="n">
-        <v>2.674</v>
+        <v>2.648</v>
       </c>
       <c r="W136" t="n">
-        <v>14.182</v>
+        <v>14.075</v>
       </c>
     </row>
     <row r="137">
@@ -13254,28 +13254,28 @@
         <v>1</v>
       </c>
       <c r="F137" t="n">
-        <v>2.593</v>
+        <v>2.589</v>
       </c>
       <c r="G137" t="n">
         <v>0.973</v>
       </c>
       <c r="H137" t="n">
-        <v>2.522</v>
+        <v>2.518</v>
       </c>
       <c r="I137" t="n">
-        <v>2.522</v>
+        <v>2.518</v>
       </c>
       <c r="J137" t="n">
-        <v>1.8869</v>
+        <v>1.853</v>
       </c>
       <c r="K137" t="n">
-        <v>1.0278</v>
+        <v>1.0093</v>
       </c>
       <c r="L137" t="n">
-        <v>0.5608</v>
+        <v>0.5507</v>
       </c>
       <c r="M137" t="n">
-        <v>0.2983</v>
+        <v>0.293</v>
       </c>
       <c r="N137" t="n">
         <v>0.9111</v>
@@ -13287,25 +13287,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q137" t="n">
-        <v>2.7179</v>
+        <v>2.669</v>
       </c>
       <c r="R137" t="n">
-        <v>1.6768</v>
+        <v>1.6466</v>
       </c>
       <c r="S137" t="n">
-        <v>0.9293</v>
+        <v>0.9127999999999999</v>
       </c>
       <c r="T137" t="n">
-        <v>5.324</v>
+        <v>5.2284</v>
       </c>
       <c r="U137" t="n">
-        <v>7.846</v>
+        <v>7.746</v>
       </c>
       <c r="V137" t="n">
-        <v>2.716</v>
+        <v>2.681</v>
       </c>
       <c r="W137" t="n">
-        <v>14.35</v>
+        <v>14.207</v>
       </c>
     </row>
     <row r="138">
@@ -13331,28 +13331,28 @@
         <v>-1</v>
       </c>
       <c r="F138" t="n">
-        <v>2.853</v>
+        <v>2.877</v>
       </c>
       <c r="G138" t="n">
         <v>0.973</v>
       </c>
       <c r="H138" t="n">
-        <v>2.775</v>
+        <v>2.798</v>
       </c>
       <c r="I138" t="n">
-        <v>2.775</v>
+        <v>2.798</v>
       </c>
       <c r="J138" t="n">
-        <v>1.893</v>
+        <v>1.9155</v>
       </c>
       <c r="K138" t="n">
-        <v>1.0311</v>
+        <v>1.0434</v>
       </c>
       <c r="L138" t="n">
-        <v>0.5626</v>
+        <v>0.5693</v>
       </c>
       <c r="M138" t="n">
-        <v>0.2993</v>
+        <v>0.3028</v>
       </c>
       <c r="N138" t="n">
         <v>0.9111</v>
@@ -13364,25 +13364,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q138" t="n">
-        <v>2.7266</v>
+        <v>2.7592</v>
       </c>
       <c r="R138" t="n">
-        <v>1.6822</v>
+        <v>1.7022</v>
       </c>
       <c r="S138" t="n">
-        <v>0.9324</v>
+        <v>0.9433</v>
       </c>
       <c r="T138" t="n">
-        <v>5.3413</v>
+        <v>5.4047</v>
       </c>
       <c r="U138" t="n">
-        <v>8.116</v>
+        <v>8.202999999999999</v>
       </c>
       <c r="V138" t="n">
-        <v>2.809</v>
+        <v>2.839</v>
       </c>
       <c r="W138" t="n">
-        <v>14.723</v>
+        <v>14.844</v>
       </c>
     </row>
     <row r="139">
@@ -13408,28 +13408,28 @@
         <v>-1</v>
       </c>
       <c r="F139" t="n">
-        <v>2.536</v>
+        <v>2.505</v>
       </c>
       <c r="G139" t="n">
         <v>0.973</v>
       </c>
       <c r="H139" t="n">
-        <v>2.467</v>
+        <v>2.436</v>
       </c>
       <c r="I139" t="n">
-        <v>2.467</v>
+        <v>2.436</v>
       </c>
       <c r="J139" t="n">
-        <v>1.881</v>
+        <v>1.8637</v>
       </c>
       <c r="K139" t="n">
-        <v>1.0246</v>
+        <v>1.0151</v>
       </c>
       <c r="L139" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.5538999999999999</v>
       </c>
       <c r="M139" t="n">
-        <v>0.2974</v>
+        <v>0.2946</v>
       </c>
       <c r="N139" t="n">
         <v>0.9111</v>
@@ -13441,25 +13441,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q139" t="n">
-        <v>2.7095</v>
+        <v>2.6843</v>
       </c>
       <c r="R139" t="n">
-        <v>1.6714</v>
+        <v>1.6562</v>
       </c>
       <c r="S139" t="n">
-        <v>0.9265</v>
+        <v>0.9177999999999999</v>
       </c>
       <c r="T139" t="n">
-        <v>5.3074</v>
+        <v>5.2583</v>
       </c>
       <c r="U139" t="n">
-        <v>7.774</v>
+        <v>7.694</v>
       </c>
       <c r="V139" t="n">
-        <v>2.691</v>
+        <v>2.663</v>
       </c>
       <c r="W139" t="n">
-        <v>14.25</v>
+        <v>14.136</v>
       </c>
     </row>
     <row r="140">
@@ -13485,28 +13485,28 @@
         <v>1</v>
       </c>
       <c r="F140" t="n">
-        <v>2.561</v>
+        <v>2.497</v>
       </c>
       <c r="G140" t="n">
         <v>0.973</v>
       </c>
       <c r="H140" t="n">
-        <v>2.491</v>
+        <v>2.429</v>
       </c>
       <c r="I140" t="n">
-        <v>2.491</v>
+        <v>2.429</v>
       </c>
       <c r="J140" t="n">
-        <v>1.869</v>
+        <v>1.8265</v>
       </c>
       <c r="K140" t="n">
-        <v>1.0181</v>
+        <v>0.9949</v>
       </c>
       <c r="L140" t="n">
-        <v>0.5555</v>
+        <v>0.5427999999999999</v>
       </c>
       <c r="M140" t="n">
-        <v>0.2955</v>
+        <v>0.2888</v>
       </c>
       <c r="N140" t="n">
         <v>0.9111</v>
@@ -13518,25 +13518,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q140" t="n">
-        <v>2.6923</v>
+        <v>2.6309</v>
       </c>
       <c r="R140" t="n">
-        <v>1.6609</v>
+        <v>1.623</v>
       </c>
       <c r="S140" t="n">
-        <v>0.9206</v>
+        <v>0.8997000000000001</v>
       </c>
       <c r="T140" t="n">
-        <v>5.2738</v>
+        <v>5.1536</v>
       </c>
       <c r="U140" t="n">
-        <v>7.765</v>
+        <v>7.583</v>
       </c>
       <c r="V140" t="n">
-        <v>2.688</v>
+        <v>2.625</v>
       </c>
       <c r="W140" t="n">
-        <v>14.236</v>
+        <v>13.976</v>
       </c>
     </row>
     <row r="141">
@@ -13562,28 +13562,28 @@
         <v>1</v>
       </c>
       <c r="F141" t="n">
-        <v>2.756</v>
+        <v>2.558</v>
       </c>
       <c r="G141" t="n">
         <v>0.973</v>
       </c>
       <c r="H141" t="n">
-        <v>2.681</v>
+        <v>2.488</v>
       </c>
       <c r="I141" t="n">
-        <v>2.681</v>
+        <v>2.488</v>
       </c>
       <c r="J141" t="n">
-        <v>1.9124</v>
+        <v>1.8439</v>
       </c>
       <c r="K141" t="n">
-        <v>1.0417</v>
+        <v>1.0044</v>
       </c>
       <c r="L141" t="n">
-        <v>0.5684</v>
+        <v>0.548</v>
       </c>
       <c r="M141" t="n">
-        <v>0.3024</v>
+        <v>0.2915</v>
       </c>
       <c r="N141" t="n">
         <v>0.9111</v>
@@ -13595,25 +13595,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q141" t="n">
-        <v>2.7547</v>
+        <v>2.656</v>
       </c>
       <c r="R141" t="n">
-        <v>1.6995</v>
+        <v>1.6385</v>
       </c>
       <c r="S141" t="n">
-        <v>0.9421</v>
+        <v>0.9081</v>
       </c>
       <c r="T141" t="n">
-        <v>5.3963</v>
+        <v>5.2027</v>
       </c>
       <c r="U141" t="n">
-        <v>8.077</v>
+        <v>7.691</v>
       </c>
       <c r="V141" t="n">
-        <v>2.796</v>
+        <v>2.662</v>
       </c>
       <c r="W141" t="n">
-        <v>14.673</v>
+        <v>14.13</v>
       </c>
     </row>
     <row r="142">
@@ -13639,28 +13639,28 @@
         <v>-1</v>
       </c>
       <c r="F142" t="n">
-        <v>1.93</v>
+        <v>1.882</v>
       </c>
       <c r="G142" t="n">
         <v>0.973</v>
       </c>
       <c r="H142" t="n">
-        <v>1.878</v>
+        <v>1.831</v>
       </c>
       <c r="I142" t="n">
-        <v>1.878</v>
+        <v>1.831</v>
       </c>
       <c r="J142" t="n">
-        <v>1.8203</v>
+        <v>1.8125</v>
       </c>
       <c r="K142" t="n">
-        <v>0.9915</v>
+        <v>0.9873</v>
       </c>
       <c r="L142" t="n">
-        <v>0.541</v>
+        <v>0.5387</v>
       </c>
       <c r="M142" t="n">
-        <v>0.2878</v>
+        <v>0.2866</v>
       </c>
       <c r="N142" t="n">
         <v>0.9111</v>
@@ -13672,25 +13672,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q142" t="n">
-        <v>2.6219</v>
+        <v>2.6108</v>
       </c>
       <c r="R142" t="n">
-        <v>1.6176</v>
+        <v>1.6107</v>
       </c>
       <c r="S142" t="n">
-        <v>0.8966</v>
+        <v>0.8929</v>
       </c>
       <c r="T142" t="n">
-        <v>5.1361</v>
+        <v>5.1144</v>
       </c>
       <c r="U142" t="n">
-        <v>7.014</v>
+        <v>6.945</v>
       </c>
       <c r="V142" t="n">
-        <v>2.428</v>
+        <v>2.404</v>
       </c>
       <c r="W142" t="n">
-        <v>13.171</v>
+        <v>13.072</v>
       </c>
     </row>
     <row r="143">
@@ -13716,28 +13716,28 @@
         <v>-1</v>
       </c>
       <c r="F143" t="n">
-        <v>2.729</v>
+        <v>2.718</v>
       </c>
       <c r="G143" t="n">
         <v>0.973</v>
       </c>
       <c r="H143" t="n">
-        <v>2.654</v>
+        <v>2.644</v>
       </c>
       <c r="I143" t="n">
-        <v>2.654</v>
+        <v>2.644</v>
       </c>
       <c r="J143" t="n">
-        <v>1.9082</v>
+        <v>1.8973</v>
       </c>
       <c r="K143" t="n">
-        <v>1.0394</v>
+        <v>1.0335</v>
       </c>
       <c r="L143" t="n">
-        <v>0.5671</v>
+        <v>0.5639</v>
       </c>
       <c r="M143" t="n">
-        <v>0.3017</v>
+        <v>0.3</v>
       </c>
       <c r="N143" t="n">
         <v>0.9111</v>
@@ -13749,25 +13749,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q143" t="n">
-        <v>2.7486</v>
+        <v>2.733</v>
       </c>
       <c r="R143" t="n">
-        <v>1.6956</v>
+        <v>1.6861</v>
       </c>
       <c r="S143" t="n">
-        <v>0.9399</v>
+        <v>0.9346</v>
       </c>
       <c r="T143" t="n">
-        <v>5.3841</v>
+        <v>5.3537</v>
       </c>
       <c r="U143" t="n">
-        <v>8.038</v>
+        <v>7.998</v>
       </c>
       <c r="V143" t="n">
-        <v>2.782</v>
+        <v>2.768</v>
       </c>
       <c r="W143" t="n">
-        <v>14.618</v>
+        <v>14.561</v>
       </c>
     </row>
     <row r="144">
@@ -13793,28 +13793,28 @@
         <v>1</v>
       </c>
       <c r="F144" t="n">
-        <v>2.819</v>
+        <v>2.811</v>
       </c>
       <c r="G144" t="n">
         <v>0.973</v>
       </c>
       <c r="H144" t="n">
-        <v>2.742</v>
+        <v>2.734</v>
       </c>
       <c r="I144" t="n">
-        <v>2.742</v>
+        <v>2.734</v>
       </c>
       <c r="J144" t="n">
-        <v>1.9042</v>
+        <v>1.9173</v>
       </c>
       <c r="K144" t="n">
-        <v>1.0372</v>
+        <v>1.0444</v>
       </c>
       <c r="L144" t="n">
-        <v>0.5659</v>
+        <v>0.5698</v>
       </c>
       <c r="M144" t="n">
-        <v>0.301</v>
+        <v>0.3031</v>
       </c>
       <c r="N144" t="n">
         <v>0.9111</v>
@@ -13826,25 +13826,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q144" t="n">
-        <v>2.7428</v>
+        <v>2.7618</v>
       </c>
       <c r="R144" t="n">
-        <v>1.692</v>
+        <v>1.7037</v>
       </c>
       <c r="S144" t="n">
-        <v>0.9377</v>
+        <v>0.9443</v>
       </c>
       <c r="T144" t="n">
-        <v>5.3725</v>
+        <v>5.4098</v>
       </c>
       <c r="U144" t="n">
-        <v>8.114000000000001</v>
+        <v>8.144</v>
       </c>
       <c r="V144" t="n">
-        <v>2.809</v>
+        <v>2.819</v>
       </c>
       <c r="W144" t="n">
-        <v>14.721</v>
+        <v>14.765</v>
       </c>
     </row>
     <row r="145">
@@ -13870,28 +13870,28 @@
         <v>-1</v>
       </c>
       <c r="F145" t="n">
-        <v>2.526</v>
+        <v>2.715</v>
       </c>
       <c r="G145" t="n">
         <v>0.915</v>
       </c>
       <c r="H145" t="n">
-        <v>2.31</v>
+        <v>2.483</v>
       </c>
       <c r="I145" t="n">
-        <v>2.31</v>
+        <v>2.483</v>
       </c>
       <c r="J145" t="n">
-        <v>1.8374</v>
+        <v>1.8422</v>
       </c>
       <c r="K145" t="n">
-        <v>1.0008</v>
+        <v>1.0035</v>
       </c>
       <c r="L145" t="n">
-        <v>0.5461</v>
+        <v>0.5475</v>
       </c>
       <c r="M145" t="n">
-        <v>0.2905</v>
+        <v>0.2913</v>
       </c>
       <c r="N145" t="n">
         <v>0.9639</v>
@@ -13903,25 +13903,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q145" t="n">
-        <v>2.8579</v>
+        <v>2.8656</v>
       </c>
       <c r="R145" t="n">
-        <v>1.7025</v>
+        <v>1.7068</v>
       </c>
       <c r="S145" t="n">
-        <v>0.905</v>
+        <v>0.9075</v>
       </c>
       <c r="T145" t="n">
-        <v>5.4654</v>
+        <v>5.4799</v>
       </c>
       <c r="U145" t="n">
-        <v>7.775</v>
+        <v>7.963</v>
       </c>
       <c r="V145" t="n">
-        <v>2.691</v>
+        <v>2.756</v>
       </c>
       <c r="W145" t="n">
-        <v>14.323</v>
+        <v>14.583</v>
       </c>
     </row>
     <row r="146">
@@ -13947,28 +13947,28 @@
         <v>1</v>
       </c>
       <c r="F146" t="n">
-        <v>3.03</v>
+        <v>3.039</v>
       </c>
       <c r="G146" t="n">
         <v>0.915</v>
       </c>
       <c r="H146" t="n">
-        <v>2.771</v>
+        <v>2.779</v>
       </c>
       <c r="I146" t="n">
-        <v>2.771</v>
+        <v>2.779</v>
       </c>
       <c r="J146" t="n">
-        <v>1.873</v>
+        <v>1.8596</v>
       </c>
       <c r="K146" t="n">
-        <v>1.0202</v>
+        <v>1.0129</v>
       </c>
       <c r="L146" t="n">
-        <v>0.5567</v>
+        <v>0.5527</v>
       </c>
       <c r="M146" t="n">
-        <v>0.2961</v>
+        <v>0.294</v>
       </c>
       <c r="N146" t="n">
         <v>0.9639</v>
@@ -13980,25 +13980,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q146" t="n">
-        <v>2.9133</v>
+        <v>2.8924</v>
       </c>
       <c r="R146" t="n">
-        <v>1.7355</v>
+        <v>1.723</v>
       </c>
       <c r="S146" t="n">
-        <v>0.9225</v>
+        <v>0.9159</v>
       </c>
       <c r="T146" t="n">
-        <v>5.5713</v>
+        <v>5.5314</v>
       </c>
       <c r="U146" t="n">
-        <v>8.342000000000001</v>
+        <v>8.31</v>
       </c>
       <c r="V146" t="n">
-        <v>2.887</v>
+        <v>2.876</v>
       </c>
       <c r="W146" t="n">
-        <v>15.108</v>
+        <v>15.061</v>
       </c>
     </row>
     <row r="147">
@@ -14024,28 +14024,28 @@
         <v>-1</v>
       </c>
       <c r="F147" t="n">
-        <v>2.752</v>
+        <v>2.806</v>
       </c>
       <c r="G147" t="n">
         <v>0.915</v>
       </c>
       <c r="H147" t="n">
-        <v>2.517</v>
+        <v>2.567</v>
       </c>
       <c r="I147" t="n">
-        <v>2.517</v>
+        <v>2.567</v>
       </c>
       <c r="J147" t="n">
-        <v>1.8491</v>
+        <v>1.8485</v>
       </c>
       <c r="K147" t="n">
-        <v>1.0072</v>
+        <v>1.0069</v>
       </c>
       <c r="L147" t="n">
-        <v>0.5496</v>
+        <v>0.5494</v>
       </c>
       <c r="M147" t="n">
-        <v>0.2923</v>
+        <v>0.2922</v>
       </c>
       <c r="N147" t="n">
         <v>0.9639</v>
@@ -14057,25 +14057,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q147" t="n">
-        <v>2.8762</v>
+        <v>2.8753</v>
       </c>
       <c r="R147" t="n">
-        <v>1.7134</v>
+        <v>1.7128</v>
       </c>
       <c r="S147" t="n">
-        <v>0.9106</v>
+        <v>0.9103</v>
       </c>
       <c r="T147" t="n">
-        <v>5.5002</v>
+        <v>5.4984</v>
       </c>
       <c r="U147" t="n">
-        <v>8.016999999999999</v>
+        <v>8.065</v>
       </c>
       <c r="V147" t="n">
-        <v>2.775</v>
+        <v>2.792</v>
       </c>
       <c r="W147" t="n">
-        <v>14.659</v>
+        <v>14.726</v>
       </c>
     </row>
     <row r="148">
@@ -14101,28 +14101,28 @@
         <v>1</v>
       </c>
       <c r="F148" t="n">
-        <v>2.847</v>
+        <v>2.846</v>
       </c>
       <c r="G148" t="n">
         <v>0.915</v>
       </c>
       <c r="H148" t="n">
-        <v>2.604</v>
+        <v>2.603</v>
       </c>
       <c r="I148" t="n">
-        <v>2.604</v>
+        <v>2.603</v>
       </c>
       <c r="J148" t="n">
-        <v>1.8993</v>
+        <v>1.8866</v>
       </c>
       <c r="K148" t="n">
-        <v>1.0345</v>
+        <v>1.0276</v>
       </c>
       <c r="L148" t="n">
-        <v>0.5645</v>
+        <v>0.5607</v>
       </c>
       <c r="M148" t="n">
-        <v>0.3003</v>
+        <v>0.2983</v>
       </c>
       <c r="N148" t="n">
         <v>0.9639</v>
@@ -14134,25 +14134,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q148" t="n">
-        <v>2.9541</v>
+        <v>2.9344</v>
       </c>
       <c r="R148" t="n">
-        <v>1.7598</v>
+        <v>1.748</v>
       </c>
       <c r="S148" t="n">
-        <v>0.9356</v>
+        <v>0.9293</v>
       </c>
       <c r="T148" t="n">
-        <v>5.6495</v>
+        <v>5.6117</v>
       </c>
       <c r="U148" t="n">
-        <v>8.253</v>
+        <v>8.215</v>
       </c>
       <c r="V148" t="n">
-        <v>2.857</v>
+        <v>2.844</v>
       </c>
       <c r="W148" t="n">
-        <v>14.992</v>
+        <v>14.937</v>
       </c>
     </row>
     <row r="149">
@@ -14178,28 +14178,28 @@
         <v>1</v>
       </c>
       <c r="F149" t="n">
-        <v>2.859</v>
+        <v>2.839</v>
       </c>
       <c r="G149" t="n">
         <v>0.915</v>
       </c>
       <c r="H149" t="n">
-        <v>2.615</v>
+        <v>2.597</v>
       </c>
       <c r="I149" t="n">
-        <v>2.615</v>
+        <v>2.597</v>
       </c>
       <c r="J149" t="n">
-        <v>1.8703</v>
+        <v>1.8578</v>
       </c>
       <c r="K149" t="n">
-        <v>1.0187</v>
+        <v>1.0119</v>
       </c>
       <c r="L149" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.5521</v>
       </c>
       <c r="M149" t="n">
-        <v>0.2957</v>
+        <v>0.2937</v>
       </c>
       <c r="N149" t="n">
         <v>0.9639</v>
@@ -14211,25 +14211,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q149" t="n">
-        <v>2.909</v>
+        <v>2.8896</v>
       </c>
       <c r="R149" t="n">
-        <v>1.733</v>
+        <v>1.7212</v>
       </c>
       <c r="S149" t="n">
-        <v>0.9212</v>
+        <v>0.915</v>
       </c>
       <c r="T149" t="n">
-        <v>5.5632</v>
+        <v>5.5257</v>
       </c>
       <c r="U149" t="n">
-        <v>8.178000000000001</v>
+        <v>8.122999999999999</v>
       </c>
       <c r="V149" t="n">
-        <v>2.831</v>
+        <v>2.812</v>
       </c>
       <c r="W149" t="n">
-        <v>14.883</v>
+        <v>14.805</v>
       </c>
     </row>
     <row r="150">
@@ -14255,28 +14255,28 @@
         <v>-1</v>
       </c>
       <c r="F150" t="n">
-        <v>2.669</v>
+        <v>2.713</v>
       </c>
       <c r="G150" t="n">
         <v>0.915</v>
       </c>
       <c r="H150" t="n">
-        <v>2.441</v>
+        <v>2.481</v>
       </c>
       <c r="I150" t="n">
-        <v>2.441</v>
+        <v>2.481</v>
       </c>
       <c r="J150" t="n">
-        <v>1.8607</v>
+        <v>1.8493</v>
       </c>
       <c r="K150" t="n">
-        <v>1.0135</v>
+        <v>1.0073</v>
       </c>
       <c r="L150" t="n">
-        <v>0.553</v>
+        <v>0.5496</v>
       </c>
       <c r="M150" t="n">
-        <v>0.2942</v>
+        <v>0.2924</v>
       </c>
       <c r="N150" t="n">
         <v>0.9639</v>
@@ -14288,25 +14288,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q150" t="n">
-        <v>2.8942</v>
+        <v>2.8764</v>
       </c>
       <c r="R150" t="n">
-        <v>1.724</v>
+        <v>1.7134</v>
       </c>
       <c r="S150" t="n">
-        <v>0.9166</v>
+        <v>0.9109</v>
       </c>
       <c r="T150" t="n">
-        <v>5.5347</v>
+        <v>5.5008</v>
       </c>
       <c r="U150" t="n">
-        <v>7.976</v>
+        <v>7.982</v>
       </c>
       <c r="V150" t="n">
-        <v>2.761</v>
+        <v>2.763</v>
       </c>
       <c r="W150" t="n">
-        <v>14.604</v>
+        <v>14.61</v>
       </c>
     </row>
     <row r="151">
@@ -14332,28 +14332,28 @@
         <v>1</v>
       </c>
       <c r="F151" t="n">
-        <v>2.906</v>
+        <v>2.886</v>
       </c>
       <c r="G151" t="n">
         <v>0.915</v>
       </c>
       <c r="H151" t="n">
-        <v>2.658</v>
+        <v>2.64</v>
       </c>
       <c r="I151" t="n">
-        <v>2.658</v>
+        <v>2.64</v>
       </c>
       <c r="J151" t="n">
-        <v>1.9072</v>
+        <v>1.8931</v>
       </c>
       <c r="K151" t="n">
-        <v>1.0388</v>
+        <v>1.0312</v>
       </c>
       <c r="L151" t="n">
-        <v>0.5668</v>
+        <v>0.5626</v>
       </c>
       <c r="M151" t="n">
-        <v>0.3015</v>
+        <v>0.2993</v>
       </c>
       <c r="N151" t="n">
         <v>0.9639</v>
@@ -14365,25 +14365,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q151" t="n">
-        <v>2.9664</v>
+        <v>2.9447</v>
       </c>
       <c r="R151" t="n">
-        <v>1.767</v>
+        <v>1.7539</v>
       </c>
       <c r="S151" t="n">
-        <v>0.9393</v>
+        <v>0.9324</v>
       </c>
       <c r="T151" t="n">
-        <v>5.6727</v>
+        <v>5.631</v>
       </c>
       <c r="U151" t="n">
-        <v>8.331</v>
+        <v>8.271000000000001</v>
       </c>
       <c r="V151" t="n">
-        <v>2.884</v>
+        <v>2.863</v>
       </c>
       <c r="W151" t="n">
-        <v>15.1</v>
+        <v>15.015</v>
       </c>
     </row>
     <row r="152">
@@ -14409,28 +14409,28 @@
         <v>-1</v>
       </c>
       <c r="F152" t="n">
-        <v>2.526</v>
+        <v>2.585</v>
       </c>
       <c r="G152" t="n">
         <v>0.915</v>
       </c>
       <c r="H152" t="n">
-        <v>2.31</v>
+        <v>2.364</v>
       </c>
       <c r="I152" t="n">
-        <v>2.31</v>
+        <v>2.364</v>
       </c>
       <c r="J152" t="n">
-        <v>1.8374</v>
+        <v>1.8333</v>
       </c>
       <c r="K152" t="n">
-        <v>1.0008</v>
+        <v>0.9986</v>
       </c>
       <c r="L152" t="n">
-        <v>0.5461</v>
+        <v>0.5449000000000001</v>
       </c>
       <c r="M152" t="n">
-        <v>0.2905</v>
+        <v>0.2898</v>
       </c>
       <c r="N152" t="n">
         <v>0.9639</v>
@@ -14442,25 +14442,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q152" t="n">
-        <v>2.8579</v>
+        <v>2.8516</v>
       </c>
       <c r="R152" t="n">
-        <v>1.7025</v>
+        <v>1.6987</v>
       </c>
       <c r="S152" t="n">
-        <v>0.905</v>
+        <v>0.9028</v>
       </c>
       <c r="T152" t="n">
-        <v>5.4654</v>
+        <v>5.4532</v>
       </c>
       <c r="U152" t="n">
-        <v>7.775</v>
+        <v>7.817</v>
       </c>
       <c r="V152" t="n">
-        <v>2.691</v>
+        <v>2.706</v>
       </c>
       <c r="W152" t="n">
-        <v>14.323</v>
+        <v>14.381</v>
       </c>
     </row>
     <row r="153">
@@ -14486,28 +14486,28 @@
         <v>-1</v>
       </c>
       <c r="F153" t="n">
-        <v>2.56</v>
+        <v>2.552</v>
       </c>
       <c r="G153" t="n">
         <v>0.915</v>
       </c>
       <c r="H153" t="n">
-        <v>2.341</v>
+        <v>2.334</v>
       </c>
       <c r="I153" t="n">
-        <v>2.341</v>
+        <v>2.334</v>
       </c>
       <c r="J153" t="n">
-        <v>1.897</v>
+        <v>1.8775</v>
       </c>
       <c r="K153" t="n">
-        <v>1.0333</v>
+        <v>1.0227</v>
       </c>
       <c r="L153" t="n">
-        <v>0.5638</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="M153" t="n">
-        <v>0.2999</v>
+        <v>0.2968</v>
       </c>
       <c r="N153" t="n">
         <v>0.9639</v>
@@ -14519,25 +14519,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q153" t="n">
-        <v>2.9507</v>
+        <v>2.9204</v>
       </c>
       <c r="R153" t="n">
-        <v>1.7576</v>
+        <v>1.7396</v>
       </c>
       <c r="S153" t="n">
-        <v>0.9343</v>
+        <v>0.9247</v>
       </c>
       <c r="T153" t="n">
-        <v>5.6426</v>
+        <v>5.5846</v>
       </c>
       <c r="U153" t="n">
-        <v>7.984</v>
+        <v>7.919</v>
       </c>
       <c r="V153" t="n">
-        <v>2.764</v>
+        <v>2.741</v>
       </c>
       <c r="W153" t="n">
-        <v>14.62</v>
+        <v>14.528</v>
       </c>
     </row>
     <row r="154">
@@ -14563,28 +14563,28 @@
         <v>1</v>
       </c>
       <c r="F154" t="n">
-        <v>3.035</v>
+        <v>3.038</v>
       </c>
       <c r="G154" t="n">
         <v>0.915</v>
       </c>
       <c r="H154" t="n">
-        <v>2.776</v>
+        <v>2.779</v>
       </c>
       <c r="I154" t="n">
-        <v>2.776</v>
+        <v>2.779</v>
       </c>
       <c r="J154" t="n">
-        <v>1.8811</v>
+        <v>1.8699</v>
       </c>
       <c r="K154" t="n">
-        <v>1.0246</v>
+        <v>1.0186</v>
       </c>
       <c r="L154" t="n">
-        <v>0.5591</v>
+        <v>0.5557</v>
       </c>
       <c r="M154" t="n">
-        <v>0.2974</v>
+        <v>0.2956</v>
       </c>
       <c r="N154" t="n">
         <v>0.9639</v>
@@ -14596,25 +14596,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q154" t="n">
-        <v>2.9258</v>
+        <v>2.9087</v>
       </c>
       <c r="R154" t="n">
-        <v>1.743</v>
+        <v>1.7324</v>
       </c>
       <c r="S154" t="n">
-        <v>0.9265</v>
+        <v>0.9209000000000001</v>
       </c>
       <c r="T154" t="n">
-        <v>5.5954</v>
+        <v>5.562</v>
       </c>
       <c r="U154" t="n">
-        <v>8.371</v>
+        <v>8.340999999999999</v>
       </c>
       <c r="V154" t="n">
-        <v>2.897</v>
+        <v>2.887</v>
       </c>
       <c r="W154" t="n">
-        <v>15.148</v>
+        <v>15.106</v>
       </c>
     </row>
     <row r="155">
@@ -14640,28 +14640,28 @@
         <v>-1</v>
       </c>
       <c r="F155" t="n">
-        <v>2.949</v>
+        <v>2.993</v>
       </c>
       <c r="G155" t="n">
         <v>0.915</v>
       </c>
       <c r="H155" t="n">
-        <v>2.697</v>
+        <v>2.738</v>
       </c>
       <c r="I155" t="n">
-        <v>2.697</v>
+        <v>2.738</v>
       </c>
       <c r="J155" t="n">
-        <v>1.858</v>
+        <v>1.8534</v>
       </c>
       <c r="K155" t="n">
-        <v>1.012</v>
+        <v>1.0096</v>
       </c>
       <c r="L155" t="n">
-        <v>0.5522</v>
+        <v>0.5508</v>
       </c>
       <c r="M155" t="n">
-        <v>0.2937</v>
+        <v>0.293</v>
       </c>
       <c r="N155" t="n">
         <v>0.9639</v>
@@ -14673,25 +14673,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q155" t="n">
-        <v>2.8899</v>
+        <v>2.883</v>
       </c>
       <c r="R155" t="n">
-        <v>1.7215</v>
+        <v>1.7171</v>
       </c>
       <c r="S155" t="n">
-        <v>0.915</v>
+        <v>0.9127999999999999</v>
       </c>
       <c r="T155" t="n">
-        <v>5.5263</v>
+        <v>5.5129</v>
       </c>
       <c r="U155" t="n">
-        <v>8.223000000000001</v>
+        <v>8.250999999999999</v>
       </c>
       <c r="V155" t="n">
-        <v>2.846</v>
+        <v>2.856</v>
       </c>
       <c r="W155" t="n">
-        <v>14.942</v>
+        <v>14.98</v>
       </c>
     </row>
     <row r="156">
@@ -14871,28 +14871,28 @@
         <v>-1</v>
       </c>
       <c r="F158" t="n">
-        <v>2.761</v>
+        <v>2.714</v>
       </c>
       <c r="G158" t="n">
         <v>0.953</v>
       </c>
       <c r="H158" t="n">
-        <v>2.632</v>
+        <v>2.588</v>
       </c>
       <c r="I158" t="n">
-        <v>2.632</v>
+        <v>2.588</v>
       </c>
       <c r="J158" t="n">
-        <v>1.9238</v>
+        <v>1.8852</v>
       </c>
       <c r="K158" t="n">
-        <v>1.0479</v>
+        <v>1.0268</v>
       </c>
       <c r="L158" t="n">
-        <v>0.5718</v>
+        <v>0.5603</v>
       </c>
       <c r="M158" t="n">
-        <v>0.3042</v>
+        <v>0.298</v>
       </c>
       <c r="N158" t="n">
         <v>0.9818</v>
@@ -14904,25 +14904,25 @@
         <v>0.6744</v>
       </c>
       <c r="Q158" t="n">
-        <v>3.0674</v>
+        <v>3.0056</v>
       </c>
       <c r="R158" t="n">
-        <v>1.7154</v>
+        <v>1.6809</v>
       </c>
       <c r="S158" t="n">
-        <v>0.9267</v>
+        <v>0.9078000000000001</v>
       </c>
       <c r="T158" t="n">
-        <v>5.7095</v>
+        <v>5.5944</v>
       </c>
       <c r="U158" t="n">
-        <v>8.342000000000001</v>
+        <v>8.182</v>
       </c>
       <c r="V158" t="n">
-        <v>2.887</v>
+        <v>2.832</v>
       </c>
       <c r="W158" t="n">
-        <v>15.151</v>
+        <v>14.927</v>
       </c>
     </row>
     <row r="159">
@@ -15025,28 +15025,28 @@
         <v>-1</v>
       </c>
       <c r="F160" t="n">
-        <v>2.925</v>
+        <v>2.761</v>
       </c>
       <c r="G160" t="n">
         <v>0.953</v>
       </c>
       <c r="H160" t="n">
-        <v>2.789</v>
+        <v>2.632</v>
       </c>
       <c r="I160" t="n">
-        <v>2.789</v>
+        <v>2.632</v>
       </c>
       <c r="J160" t="n">
-        <v>1.9293</v>
+        <v>1.9238</v>
       </c>
       <c r="K160" t="n">
-        <v>1.0509</v>
+        <v>1.0479</v>
       </c>
       <c r="L160" t="n">
-        <v>0.5734</v>
+        <v>0.5718</v>
       </c>
       <c r="M160" t="n">
-        <v>0.305</v>
+        <v>0.3042</v>
       </c>
       <c r="N160" t="n">
         <v>0.9818</v>
@@ -15058,25 +15058,25 @@
         <v>0.6744</v>
       </c>
       <c r="Q160" t="n">
-        <v>3.0762</v>
+        <v>3.0674</v>
       </c>
       <c r="R160" t="n">
-        <v>1.7202</v>
+        <v>1.7154</v>
       </c>
       <c r="S160" t="n">
-        <v>0.9292</v>
+        <v>0.9267</v>
       </c>
       <c r="T160" t="n">
-        <v>5.7255</v>
+        <v>5.7095</v>
       </c>
       <c r="U160" t="n">
-        <v>8.513999999999999</v>
+        <v>8.342000000000001</v>
       </c>
       <c r="V160" t="n">
-        <v>2.947</v>
+        <v>2.887</v>
       </c>
       <c r="W160" t="n">
-        <v>15.389</v>
+        <v>15.151</v>
       </c>
     </row>
     <row r="161">
@@ -15872,28 +15872,28 @@
         <v>-1</v>
       </c>
       <c r="F171" t="n">
-        <v>2.894</v>
+        <v>2.564</v>
       </c>
       <c r="G171" t="n">
         <v>0.9389999999999999</v>
       </c>
       <c r="H171" t="n">
-        <v>2.717</v>
+        <v>2.407</v>
       </c>
       <c r="I171" t="n">
-        <v>2.717</v>
+        <v>2.407</v>
       </c>
       <c r="J171" t="n">
-        <v>1.9611</v>
+        <v>1.9139</v>
       </c>
       <c r="K171" t="n">
-        <v>1.0682</v>
+        <v>1.0425</v>
       </c>
       <c r="L171" t="n">
-        <v>0.5829</v>
+        <v>0.5688</v>
       </c>
       <c r="M171" t="n">
-        <v>0.3101</v>
+        <v>0.3026</v>
       </c>
       <c r="N171" t="n">
         <v>0.963</v>
@@ -15905,25 +15905,25 @@
         <v>0.6604</v>
       </c>
       <c r="Q171" t="n">
-        <v>3.0465</v>
+        <v>2.9732</v>
       </c>
       <c r="R171" t="n">
-        <v>1.9515</v>
+        <v>1.9043</v>
       </c>
       <c r="S171" t="n">
-        <v>0.9186</v>
+        <v>0.8964</v>
       </c>
       <c r="T171" t="n">
-        <v>5.9167</v>
+        <v>5.774</v>
       </c>
       <c r="U171" t="n">
-        <v>8.634</v>
+        <v>8.180999999999999</v>
       </c>
       <c r="V171" t="n">
-        <v>2.989</v>
+        <v>2.832</v>
       </c>
       <c r="W171" t="n">
-        <v>15.587</v>
+        <v>14.958</v>
       </c>
     </row>
     <row r="172">
@@ -16334,28 +16334,28 @@
         <v>1</v>
       </c>
       <c r="F177" t="n">
-        <v>2.688</v>
+        <v>2.52</v>
       </c>
       <c r="G177" t="n">
         <v>0.9389999999999999</v>
       </c>
       <c r="H177" t="n">
-        <v>2.524</v>
+        <v>2.366</v>
       </c>
       <c r="I177" t="n">
-        <v>2.524</v>
+        <v>2.366</v>
       </c>
       <c r="J177" t="n">
-        <v>1.9557</v>
+        <v>1.9339</v>
       </c>
       <c r="K177" t="n">
-        <v>1.0653</v>
+        <v>1.0534</v>
       </c>
       <c r="L177" t="n">
-        <v>0.5812</v>
+        <v>0.5748</v>
       </c>
       <c r="M177" t="n">
-        <v>0.3092</v>
+        <v>0.3058</v>
       </c>
       <c r="N177" t="n">
         <v>0.963</v>
@@ -16367,25 +16367,25 @@
         <v>0.6604</v>
       </c>
       <c r="Q177" t="n">
-        <v>3.0382</v>
+        <v>3.0043</v>
       </c>
       <c r="R177" t="n">
-        <v>1.9459</v>
+        <v>1.9244</v>
       </c>
       <c r="S177" t="n">
-        <v>0.916</v>
+        <v>0.9059</v>
       </c>
       <c r="T177" t="n">
-        <v>5.9001</v>
+        <v>5.8346</v>
       </c>
       <c r="U177" t="n">
-        <v>8.423999999999999</v>
+        <v>8.201000000000001</v>
       </c>
       <c r="V177" t="n">
-        <v>2.916</v>
+        <v>2.839</v>
       </c>
       <c r="W177" t="n">
-        <v>15.299</v>
+        <v>14.987</v>
       </c>
     </row>
     <row r="178">
@@ -17027,28 +17027,28 @@
         <v>-1</v>
       </c>
       <c r="F186" t="n">
-        <v>3.465</v>
+        <v>3.245</v>
       </c>
       <c r="G186" t="n">
         <v>0.959</v>
       </c>
       <c r="H186" t="n">
-        <v>3.324</v>
+        <v>3.113</v>
       </c>
       <c r="I186" t="n">
-        <v>3.324</v>
+        <v>3.113</v>
       </c>
       <c r="J186" t="n">
-        <v>1.8781</v>
+        <v>1.8756</v>
       </c>
       <c r="K186" t="n">
-        <v>1.023</v>
+        <v>1.0217</v>
       </c>
       <c r="L186" t="n">
-        <v>0.5582</v>
+        <v>0.5574</v>
       </c>
       <c r="M186" t="n">
-        <v>0.2969</v>
+        <v>0.2965</v>
       </c>
       <c r="N186" t="n">
         <v>0.9543</v>
@@ -17060,25 +17060,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q186" t="n">
-        <v>2.882</v>
+        <v>2.8783</v>
       </c>
       <c r="R186" t="n">
-        <v>1.669</v>
+        <v>1.6666</v>
       </c>
       <c r="S186" t="n">
-        <v>0.925</v>
+        <v>0.9237</v>
       </c>
       <c r="T186" t="n">
-        <v>5.476</v>
+        <v>5.4687</v>
       </c>
       <c r="U186" t="n">
-        <v>8.800000000000001</v>
+        <v>8.582000000000001</v>
       </c>
       <c r="V186" t="n">
-        <v>3.046</v>
+        <v>2.971</v>
       </c>
       <c r="W186" t="n">
-        <v>15.717</v>
+        <v>15.425</v>
       </c>
     </row>
     <row r="187">
@@ -17566,28 +17566,28 @@
         <v>-1</v>
       </c>
       <c r="F193" t="n">
-        <v>1.973</v>
+        <v>2.074</v>
       </c>
       <c r="G193" t="n">
         <v>0.962</v>
       </c>
       <c r="H193" t="n">
-        <v>1.899</v>
+        <v>1.996</v>
       </c>
       <c r="I193" t="n">
-        <v>1.899</v>
+        <v>1.996</v>
       </c>
       <c r="J193" t="n">
-        <v>1.9458</v>
+        <v>1.8976</v>
       </c>
       <c r="K193" t="n">
-        <v>1.0599</v>
+        <v>1.0336</v>
       </c>
       <c r="L193" t="n">
-        <v>0.5783</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="M193" t="n">
-        <v>0.3076</v>
+        <v>0.3</v>
       </c>
       <c r="N193" t="n">
         <v>0.9318</v>
@@ -17599,25 +17599,25 @@
         <v>0.5962</v>
       </c>
       <c r="Q193" t="n">
-        <v>2.8906</v>
+        <v>2.8188</v>
       </c>
       <c r="R193" t="n">
-        <v>1.8442</v>
+        <v>1.7986</v>
       </c>
       <c r="S193" t="n">
-        <v>0.7927</v>
+        <v>0.7732</v>
       </c>
       <c r="T193" t="n">
-        <v>5.5275</v>
+        <v>5.3906</v>
       </c>
       <c r="U193" t="n">
-        <v>7.426</v>
+        <v>7.387</v>
       </c>
       <c r="V193" t="n">
-        <v>2.57</v>
+        <v>2.557</v>
       </c>
       <c r="W193" t="n">
-        <v>13.767</v>
+        <v>13.711</v>
       </c>
     </row>
     <row r="194">
@@ -18182,25 +18182,25 @@
         <v>-1</v>
       </c>
       <c r="F201" t="n">
-        <v>1.827</v>
+        <v>1.665</v>
       </c>
       <c r="G201" t="n">
         <v>0.962</v>
       </c>
       <c r="H201" t="n">
-        <v>1.759</v>
+        <v>1.602</v>
       </c>
       <c r="I201" t="n">
-        <v>1.759</v>
+        <v>1.602</v>
       </c>
       <c r="J201" t="n">
-        <v>1.867</v>
+        <v>1.8674</v>
       </c>
       <c r="K201" t="n">
-        <v>1.0169</v>
+        <v>1.0172</v>
       </c>
       <c r="L201" t="n">
-        <v>0.5548999999999999</v>
+        <v>0.555</v>
       </c>
       <c r="M201" t="n">
         <v>0.2952</v>
@@ -18215,25 +18215,25 @@
         <v>0.5962</v>
       </c>
       <c r="Q201" t="n">
-        <v>2.7733</v>
+        <v>2.7741</v>
       </c>
       <c r="R201" t="n">
-        <v>1.7696</v>
+        <v>1.7699</v>
       </c>
       <c r="S201" t="n">
         <v>0.7608</v>
       </c>
       <c r="T201" t="n">
-        <v>5.3037</v>
+        <v>5.3048</v>
       </c>
       <c r="U201" t="n">
-        <v>7.063</v>
+        <v>6.907</v>
       </c>
       <c r="V201" t="n">
-        <v>2.445</v>
+        <v>2.391</v>
       </c>
       <c r="W201" t="n">
-        <v>13.245</v>
+        <v>13.015</v>
       </c>
     </row>
     <row r="202">
@@ -18644,28 +18644,28 @@
         <v>-1</v>
       </c>
       <c r="F207" t="n">
-        <v>2.347</v>
+        <v>2.003</v>
       </c>
       <c r="G207" t="n">
         <v>0.93</v>
       </c>
       <c r="H207" t="n">
-        <v>2.183</v>
+        <v>1.863</v>
       </c>
       <c r="I207" t="n">
-        <v>2.183</v>
+        <v>1.863</v>
       </c>
       <c r="J207" t="n">
-        <v>1.9872</v>
+        <v>1.9866</v>
       </c>
       <c r="K207" t="n">
-        <v>1.0824</v>
+        <v>1.0821</v>
       </c>
       <c r="L207" t="n">
-        <v>0.5906</v>
+        <v>0.5904</v>
       </c>
       <c r="M207" t="n">
-        <v>0.3142</v>
+        <v>0.3141</v>
       </c>
       <c r="N207" t="n">
         <v>0.9408</v>
@@ -18677,25 +18677,25 @@
         <v>0.68</v>
       </c>
       <c r="Q207" t="n">
-        <v>2.9909</v>
+        <v>2.9901</v>
       </c>
       <c r="R207" t="n">
-        <v>1.9038</v>
+        <v>1.9032</v>
       </c>
       <c r="S207" t="n">
-        <v>0.9677</v>
+        <v>0.9674</v>
       </c>
       <c r="T207" t="n">
-        <v>5.8624</v>
+        <v>5.8606</v>
       </c>
       <c r="U207" t="n">
-        <v>8.045</v>
+        <v>7.724</v>
       </c>
       <c r="V207" t="n">
-        <v>2.785</v>
+        <v>2.674</v>
       </c>
       <c r="W207" t="n">
-        <v>14.708</v>
+        <v>14.25</v>
       </c>
     </row>
     <row r="208">
@@ -20415,28 +20415,28 @@
         <v>1</v>
       </c>
       <c r="F230" t="n">
-        <v>2.078</v>
+        <v>1.999</v>
       </c>
       <c r="G230" t="n">
         <v>0.904</v>
       </c>
       <c r="H230" t="n">
-        <v>1.88</v>
+        <v>1.808</v>
       </c>
       <c r="I230" t="n">
-        <v>1.88</v>
+        <v>1.808</v>
       </c>
       <c r="J230" t="n">
-        <v>1.9427</v>
+        <v>1.9431</v>
       </c>
       <c r="K230" t="n">
-        <v>1.0582</v>
+        <v>1.0584</v>
       </c>
       <c r="L230" t="n">
-        <v>0.5774</v>
+        <v>0.5775</v>
       </c>
       <c r="M230" t="n">
-        <v>0.3071</v>
+        <v>0.3072</v>
       </c>
       <c r="N230" t="n">
         <v>0.9394</v>
@@ -20448,25 +20448,25 @@
         <v>0.6364</v>
       </c>
       <c r="Q230" t="n">
-        <v>2.9181</v>
+        <v>2.9186</v>
       </c>
       <c r="R230" t="n">
-        <v>1.647</v>
+        <v>1.6473</v>
       </c>
       <c r="S230" t="n">
-        <v>0.8655</v>
+        <v>0.8658</v>
       </c>
       <c r="T230" t="n">
-        <v>5.4307</v>
+        <v>5.4318</v>
       </c>
       <c r="U230" t="n">
-        <v>7.311</v>
+        <v>7.24</v>
       </c>
       <c r="V230" t="n">
-        <v>2.531</v>
+        <v>2.506</v>
       </c>
       <c r="W230" t="n">
-        <v>13.514</v>
+        <v>13.412</v>
       </c>
     </row>
     <row r="231">
@@ -21339,28 +21339,28 @@
         <v>-1</v>
       </c>
       <c r="F242" t="n">
-        <v>2.67</v>
+        <v>2.718</v>
       </c>
       <c r="G242" t="n">
         <v>0.9340000000000001</v>
       </c>
       <c r="H242" t="n">
-        <v>2.493</v>
+        <v>2.538</v>
       </c>
       <c r="I242" t="n">
-        <v>2.493</v>
+        <v>2.538</v>
       </c>
       <c r="J242" t="n">
-        <v>2.0353</v>
+        <v>2.0401</v>
       </c>
       <c r="K242" t="n">
-        <v>1.1086</v>
+        <v>1.1113</v>
       </c>
       <c r="L242" t="n">
-        <v>0.6049</v>
+        <v>0.6063</v>
       </c>
       <c r="M242" t="n">
-        <v>0.3218</v>
+        <v>0.3225</v>
       </c>
       <c r="N242" t="n">
         <v>0.9597</v>
@@ -21372,25 +21372,25 @@
         <v>0.7391</v>
       </c>
       <c r="Q242" t="n">
-        <v>3.1471</v>
+        <v>3.1548</v>
       </c>
       <c r="R242" t="n">
-        <v>1.9224</v>
+        <v>1.9268</v>
       </c>
       <c r="S242" t="n">
-        <v>1.1053</v>
+        <v>1.1077</v>
       </c>
       <c r="T242" t="n">
-        <v>6.1747</v>
+        <v>6.1892</v>
       </c>
       <c r="U242" t="n">
-        <v>8.667999999999999</v>
+        <v>8.727</v>
       </c>
       <c r="V242" t="n">
-        <v>3</v>
+        <v>3.021</v>
       </c>
       <c r="W242" t="n">
-        <v>15.654</v>
+        <v>15.736</v>
       </c>
     </row>
     <row r="243">
@@ -21878,28 +21878,28 @@
         <v>-1</v>
       </c>
       <c r="F249" t="n">
-        <v>1.858</v>
+        <v>1.787</v>
       </c>
       <c r="G249" t="n">
         <v>0.957</v>
       </c>
       <c r="H249" t="n">
-        <v>1.778</v>
+        <v>1.71</v>
       </c>
       <c r="I249" t="n">
-        <v>1.778</v>
+        <v>1.71</v>
       </c>
       <c r="J249" t="n">
-        <v>2.0306</v>
+        <v>2.0268</v>
       </c>
       <c r="K249" t="n">
-        <v>1.1061</v>
+        <v>1.104</v>
       </c>
       <c r="L249" t="n">
-        <v>0.6035</v>
+        <v>0.6024</v>
       </c>
       <c r="M249" t="n">
-        <v>0.321</v>
+        <v>0.3204</v>
       </c>
       <c r="N249" t="n">
         <v>0.971</v>
@@ -21911,25 +21911,25 @@
         <v>0.7255</v>
       </c>
       <c r="Q249" t="n">
-        <v>3.19</v>
+        <v>3.1839</v>
       </c>
       <c r="R249" t="n">
-        <v>1.7242</v>
+        <v>1.7211</v>
       </c>
       <c r="S249" t="n">
-        <v>1.0763</v>
+        <v>1.0743</v>
       </c>
       <c r="T249" t="n">
-        <v>5.9905</v>
+        <v>5.9793</v>
       </c>
       <c r="U249" t="n">
-        <v>7.768</v>
+        <v>7.689</v>
       </c>
       <c r="V249" t="n">
-        <v>2.689</v>
+        <v>2.661</v>
       </c>
       <c r="W249" t="n">
-        <v>14.334</v>
+        <v>14.218</v>
       </c>
     </row>
     <row r="250">
@@ -22571,28 +22571,28 @@
         <v>1</v>
       </c>
       <c r="F258" t="n">
-        <v>2.403</v>
+        <v>2.017</v>
       </c>
       <c r="G258" t="n">
         <v>0.953</v>
       </c>
       <c r="H258" t="n">
-        <v>2.291</v>
+        <v>1.923</v>
       </c>
       <c r="I258" t="n">
-        <v>2.291</v>
+        <v>1.923</v>
       </c>
       <c r="J258" t="n">
-        <v>1.9598</v>
+        <v>1.96</v>
       </c>
       <c r="K258" t="n">
-        <v>1.0675</v>
+        <v>1.0676</v>
       </c>
       <c r="L258" t="n">
         <v>0.5825</v>
       </c>
       <c r="M258" t="n">
-        <v>0.3098</v>
+        <v>0.3099</v>
       </c>
       <c r="N258" t="n">
         <v>0.9333</v>
@@ -22604,25 +22604,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q258" t="n">
-        <v>2.9177</v>
+        <v>2.918</v>
       </c>
       <c r="R258" t="n">
         <v>1.629</v>
       </c>
       <c r="S258" t="n">
-        <v>0.9651999999999999</v>
+        <v>0.9655</v>
       </c>
       <c r="T258" t="n">
-        <v>5.5118</v>
+        <v>5.5124</v>
       </c>
       <c r="U258" t="n">
-        <v>7.803</v>
+        <v>7.435</v>
       </c>
       <c r="V258" t="n">
-        <v>2.701</v>
+        <v>2.574</v>
       </c>
       <c r="W258" t="n">
-        <v>14.27</v>
+        <v>13.749</v>
       </c>
     </row>
     <row r="259">
@@ -23110,28 +23110,28 @@
         <v>-1</v>
       </c>
       <c r="F265" t="n">
-        <v>2.578</v>
+        <v>2.979</v>
       </c>
       <c r="G265" t="n">
         <v>0.953</v>
       </c>
       <c r="H265" t="n">
-        <v>2.458</v>
+        <v>2.84</v>
       </c>
       <c r="I265" t="n">
-        <v>2.458</v>
+        <v>2.84</v>
       </c>
       <c r="J265" t="n">
-        <v>1.9559</v>
+        <v>1.97</v>
       </c>
       <c r="K265" t="n">
-        <v>1.0654</v>
+        <v>1.0731</v>
       </c>
       <c r="L265" t="n">
-        <v>0.5813</v>
+        <v>0.5855</v>
       </c>
       <c r="M265" t="n">
-        <v>0.3092</v>
+        <v>0.3115</v>
       </c>
       <c r="N265" t="n">
         <v>0.9333</v>
@@ -23143,25 +23143,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q265" t="n">
-        <v>2.912</v>
+        <v>2.933</v>
       </c>
       <c r="R265" t="n">
-        <v>1.6256</v>
+        <v>1.6374</v>
       </c>
       <c r="S265" t="n">
-        <v>0.9633</v>
+        <v>0.9704</v>
       </c>
       <c r="T265" t="n">
-        <v>5.5008</v>
+        <v>5.5408</v>
       </c>
       <c r="U265" t="n">
-        <v>7.959</v>
+        <v>8.381</v>
       </c>
       <c r="V265" t="n">
-        <v>2.755</v>
+        <v>2.901</v>
       </c>
       <c r="W265" t="n">
-        <v>14.487</v>
+        <v>15.067</v>
       </c>
     </row>
     <row r="266">
@@ -25189,28 +25189,28 @@
         <v>1</v>
       </c>
       <c r="F292" t="n">
-        <v>3.005</v>
+        <v>2.759</v>
       </c>
       <c r="G292" t="n">
         <v>0.9</v>
       </c>
       <c r="H292" t="n">
-        <v>2.704</v>
+        <v>2.483</v>
       </c>
       <c r="I292" t="n">
-        <v>2.704</v>
+        <v>2.483</v>
       </c>
       <c r="J292" t="n">
-        <v>1.8833</v>
+        <v>1.8658</v>
       </c>
       <c r="K292" t="n">
-        <v>1.0258</v>
+        <v>1.0163</v>
       </c>
       <c r="L292" t="n">
-        <v>0.5597</v>
+        <v>0.5545</v>
       </c>
       <c r="M292" t="n">
-        <v>0.2977</v>
+        <v>0.295</v>
       </c>
       <c r="N292" t="n">
         <v>0.9543</v>
@@ -25222,25 +25222,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q292" t="n">
-        <v>2.8899</v>
+        <v>2.8631</v>
       </c>
       <c r="R292" t="n">
-        <v>1.6735</v>
+        <v>1.658</v>
       </c>
       <c r="S292" t="n">
-        <v>0.9275</v>
+        <v>0.919</v>
       </c>
       <c r="T292" t="n">
-        <v>5.4908</v>
+        <v>5.4401</v>
       </c>
       <c r="U292" t="n">
-        <v>8.195</v>
+        <v>7.923</v>
       </c>
       <c r="V292" t="n">
-        <v>2.837</v>
+        <v>2.742</v>
       </c>
       <c r="W292" t="n">
-        <v>14.838</v>
+        <v>14.464</v>
       </c>
     </row>
     <row r="293">
@@ -29809,28 +29809,28 @@
         <v>-1</v>
       </c>
       <c r="F352" t="n">
-        <v>1.939</v>
+        <v>1.776</v>
       </c>
       <c r="G352" t="n">
         <v>1</v>
       </c>
       <c r="H352" t="n">
-        <v>1.939</v>
+        <v>1.776</v>
       </c>
       <c r="I352" t="n">
-        <v>1.939</v>
+        <v>1.776</v>
       </c>
       <c r="J352" t="n">
-        <v>1.9624</v>
+        <v>1.9577</v>
       </c>
       <c r="K352" t="n">
-        <v>1.0689</v>
+        <v>1.0664</v>
       </c>
       <c r="L352" t="n">
-        <v>0.5832000000000001</v>
+        <v>0.5818</v>
       </c>
       <c r="M352" t="n">
-        <v>0.3102</v>
+        <v>0.3095</v>
       </c>
       <c r="N352" t="n">
         <v>0.9543</v>
@@ -29842,25 +29842,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q352" t="n">
-        <v>3.0113</v>
+        <v>3.0043</v>
       </c>
       <c r="R352" t="n">
-        <v>1.7438</v>
+        <v>1.7396</v>
       </c>
       <c r="S352" t="n">
-        <v>0.9664</v>
+        <v>0.9641999999999999</v>
       </c>
       <c r="T352" t="n">
-        <v>5.7215</v>
+        <v>5.7081</v>
       </c>
       <c r="U352" t="n">
-        <v>7.66</v>
+        <v>7.484</v>
       </c>
       <c r="V352" t="n">
-        <v>2.651</v>
+        <v>2.59</v>
       </c>
       <c r="W352" t="n">
-        <v>14.194</v>
+        <v>13.938</v>
       </c>
     </row>
     <row r="353">
@@ -29886,28 +29886,28 @@
         <v>1</v>
       </c>
       <c r="F353" t="n">
-        <v>2.015</v>
+        <v>1.97</v>
       </c>
       <c r="G353" t="n">
         <v>1</v>
       </c>
       <c r="H353" t="n">
-        <v>2.015</v>
+        <v>1.97</v>
       </c>
       <c r="I353" t="n">
-        <v>2.015</v>
+        <v>1.97</v>
       </c>
       <c r="J353" t="n">
-        <v>2.0036</v>
+        <v>1.947</v>
       </c>
       <c r="K353" t="n">
-        <v>1.0914</v>
+        <v>1.0605</v>
       </c>
       <c r="L353" t="n">
-        <v>0.5955</v>
+        <v>0.5786</v>
       </c>
       <c r="M353" t="n">
-        <v>0.3168</v>
+        <v>0.3078</v>
       </c>
       <c r="N353" t="n">
         <v>0.9543</v>
@@ -29919,25 +29919,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q353" t="n">
-        <v>3.0747</v>
+        <v>2.9876</v>
       </c>
       <c r="R353" t="n">
-        <v>1.7805</v>
+        <v>1.73</v>
       </c>
       <c r="S353" t="n">
-        <v>0.987</v>
+        <v>0.9589</v>
       </c>
       <c r="T353" t="n">
-        <v>5.8422</v>
+        <v>5.6766</v>
       </c>
       <c r="U353" t="n">
-        <v>7.857</v>
+        <v>7.647</v>
       </c>
       <c r="V353" t="n">
-        <v>2.72</v>
+        <v>2.647</v>
       </c>
       <c r="W353" t="n">
-        <v>14.475</v>
+        <v>14.176</v>
       </c>
     </row>
     <row r="354">
@@ -30194,25 +30194,25 @@
         <v>1</v>
       </c>
       <c r="F357" t="n">
-        <v>2.006</v>
+        <v>2.015</v>
       </c>
       <c r="G357" t="n">
         <v>1</v>
       </c>
       <c r="H357" t="n">
-        <v>2.006</v>
+        <v>2.015</v>
       </c>
       <c r="I357" t="n">
-        <v>2.006</v>
+        <v>2.015</v>
       </c>
       <c r="J357" t="n">
-        <v>2.0035</v>
+        <v>2.0036</v>
       </c>
       <c r="K357" t="n">
-        <v>1.0913</v>
+        <v>1.0914</v>
       </c>
       <c r="L357" t="n">
-        <v>0.5954</v>
+        <v>0.5955</v>
       </c>
       <c r="M357" t="n">
         <v>0.3168</v>
@@ -30227,25 +30227,25 @@
         <v>0.6859</v>
       </c>
       <c r="Q357" t="n">
-        <v>3.0744</v>
+        <v>3.0747</v>
       </c>
       <c r="R357" t="n">
-        <v>1.7802</v>
+        <v>1.7805</v>
       </c>
       <c r="S357" t="n">
         <v>0.987</v>
       </c>
       <c r="T357" t="n">
-        <v>5.8416</v>
+        <v>5.8422</v>
       </c>
       <c r="U357" t="n">
-        <v>7.848</v>
+        <v>7.857</v>
       </c>
       <c r="V357" t="n">
-        <v>2.716</v>
+        <v>2.72</v>
       </c>
       <c r="W357" t="n">
-        <v>14.462</v>
+        <v>14.475</v>
       </c>
     </row>
     <row r="358">
